--- a/المنتجات/batch1-products-complete.xlsx
+++ b/المنتجات/batch1-products-complete.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN96"/>
+  <dimension ref="A1:AN95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7506,17 +7506,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>صبغة طاوس بني</t>
+          <t>زيت فيتامين E من دي لا كروز، 65 مل</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>العناية والجمال &gt; العناية بالشعر</t>
+          <t>العناية والجمال &gt; العناية بالبشرة &gt; زيوت وزبدات</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81eXnqEv0dL.jpg</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>صبغة طاوس بني</t>
+          <t>زيت فيتامين E من دي لا كروز، 65 مل</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -7526,12 +7531,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>&lt;p&gt;صبغة طاوس بني Taous Brown Hair Dye من طاوس، نوعها صبغة شعر، ودرجتها بني.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | صبغة طاوس بني&lt;/li&gt;&lt;li&gt;النوع | صبغة شعر&lt;/li&gt;&lt;li&gt;الدرجة | بني&lt;/li&gt;&lt;li&gt;العلامة التجارية | طاوس&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;صبغة شعر من طاوس بدرجة بني، كما يرد في اسم المنتج. تقدم خياراً لتلوين الشعر ضمن روتين العناية بالشعر، من دون أن يحدد الاسم المتاح حجماً أو تفاصيل عن النتيجة أو مدة اللون. لذلك ينبغي مراجعة بيانات العبوة لمعرفة محتوياتها وطريقة التحضير والتطبيق والمدة المحددة.&lt;/p&gt;&lt;p&gt;اختيار درجة اللون يعتمد على لون الشعر الحالي والنتيجة المرغوبة، وقد تختلف النتيجة باختلاف حالة الشعر وطريقة الاستخدام. اقرئي الإرشادات كاملة قبل البدء، ونفذي اختبار الحساسية بالطريقة والمدة اللتين تحددهما العبوة، مع عدم تجاوز التعليمات.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;صبغة شعر من علامة طاوس.&lt;/li&gt;&lt;li&gt;الدرجة المذكورة في الاسم هي البني.&lt;/li&gt;&lt;li&gt;تندرج ضمن منتجات العناية بالشعر.&lt;/li&gt;&lt;li&gt;يوضح الاسم نوع المنتج ودرجة اللون.&lt;/li&gt;&lt;li&gt;يمكن استخدامها لتلوين الشعر وفق إرشادات العبوة.&lt;/li&gt;&lt;li&gt;لا يذكر الاسم المتاح حجماً محدداً.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن صبغة شعر بدرجة بني.&lt;/li&gt;&lt;li&gt;لمن يرغب في اختيار منتج تلوين من طاوس.&lt;/li&gt;&lt;li&gt;لمن يستطيع اتباع تعليمات الصبغة والتحذيرات المرفقة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;اقرئي النشرة وتعليمات العبوة قبل الاستخدام، والتزمي بخطوات التحضير والتطبيق والمدة المحددة من الشركة. نفذي اختبار الحساسية الموصى به، واستخدمي أدوات الوقاية المذكورة على العبوة. لا تخلطي المنتج مع مواد أخرى أو تتركيه مدة أطول من المحدد.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، تجنبي ملامسة العينين، وأبقي المنتج بعيداً عن متناول الأطفال. لا تستخدميه عند وجود تحسس أو تهيج، واتّبعي تحذيرات العبوة بدقة.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;طاوس علامة تجارية يظهر اسمها على منتجات العناية بالشعر، ومن بينها صبغة الشعر بدرجة البني. تختلف تفاصيل الاستخدام بين منتجات التلوين، لذا تعد العبوة المرجع الأساسي لطريقة الاستعمال والتحذيرات.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;س: ما نوع المنتج؟&lt;/p&gt;&lt;p&gt;ج: هو صبغة مخصصة للشعر.&lt;/p&gt;&lt;p&gt;س: ما الدرجة المذكورة؟&lt;/p&gt;&lt;p&gt;ج: الدرجة المذكورة في الاسم هي البني.&lt;/p&gt;&lt;p&gt;س: هل يذكر الاسم حجم العبوة؟&lt;/p&gt;&lt;p&gt;ج: لا يتضمن الاسم المتاح حجماً محدداً.&lt;/p&gt;&lt;p&gt;س: ما أهم ما يسبق استخدامها؟&lt;/p&gt;&lt;p&gt;ج: قراءة التعليمات وإجراء اختبار الحساسية وفق ما توضحه العبوة.&lt;/p&gt;</t>
+          <t>زيت فيتامين هـ من دي لا كروز، 65 مل — De La Cruz Vitamin E Oil, 65 ml؛ زيت للعناية بالبشرة من علامة دي لا كروز، بالحجم المذكور في الاسم. تأتي صيغته الزيتية لتكون خياراً واضحاً لمن يفضّلون إدراج الزيوت ضمن خطوات عنايتهم اليومية، مع الحفاظ على بساطة الاختيار بحسب طبيعة الروتين الشخصي.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | زيت فيتامين هـ من دي لا كروز&lt;/li&gt;&lt;li&gt;النوع | زيت فيتامين هـ&lt;/li&gt;&lt;li&gt;الحجم | 65 مل&lt;/li&gt;&lt;li&gt;العلامة التجارية | دي لا كروز&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;يجمع هذا المنتج بين شكل الزيت واسم فيتامين هـ في عبوة محددة الحجم، ليمنحك خياراً عملياً عند ترتيب منتجات العناية بالبشرة. ويمكن التعامل معه كخطوة مستقلة أو إدراجه ضمن الروتين المعتاد وفق تعليمات العبوة، مع اختيار موضع الاستخدام والكمية بما يلائم تفضيلاتك.&lt;/p&gt;&lt;p&gt;لا يذكر الاسم درجة لونية أو رائحة أو مواصفات إضافية؛ لذلك يظل التركيز هنا على هويته كزيت فيتامين هـ من دي لا كروز وحجمه البالغ 65 مل. اختاريه بناءً على رغبتك في استخدام مستحضر ذي قوام زيتي، وتحققي من إرشادات العبوة قبل إدخاله في روتينك.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مستحضر زيتي يحمل اسم فيتامين هـ.&lt;/li&gt;&lt;li&gt;حجم العبوة 65 مل كما ورد في اسم المنتج.&lt;/li&gt;&lt;li&gt;من علامة دي لا كروز.&lt;/li&gt;&lt;li&gt;يمكن إدراجه ضمن خطوات العناية بالبشرة بحسب تفضيلاتك.&lt;/li&gt;&lt;li&gt;اسم المنتج واضح ويسهل تمييزه عند تنظيم المستحضرات.&lt;/li&gt;&lt;li&gt;لا يتضمن الاسم درجة لونية محددة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحثون عن زيت فيتامين هـ للعناية بالبشرة.&lt;/li&gt;&lt;li&gt;لمن يفضّلون المستحضرات ذات القوام الزيتي.&lt;/li&gt;&lt;li&gt;لمن يرغبون في عبوة بحجم 65 مل.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;راجعي تعليمات العبوة أولاً، ثم ضعي كمية مناسبة على بشرة نظيفة في الموضع المرغوب. ابدئي بكمية قليلة، ووزّعيها بلطف، ولا تستخدميه بطريقة تخالف الإرشادات المدونة على المنتج.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. يُحفظ بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;دي لا كروز هي العلامة التجارية المذكورة على هذا المنتج. يظهر اسمها هنا على زيت فيتامين هـ بحجم 65 مل، وتُعرَف هوية المنتج من الاسم والعلامة المدونين عليه.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع هذا المنتج؟&lt;/p&gt;&lt;p&gt;هو زيت فيتامين هـ من دي لا كروز.&lt;/p&gt;&lt;p&gt;ما حجم العبوة؟&lt;/p&gt;&lt;p&gt;الحجم المذكور في الاسم هو 65 مل.&lt;/p&gt;&lt;p&gt;هل يذكر الاسم درجة لونية؟&lt;/p&gt;&lt;p&gt;لا، لا تظهر درجة لونية في اسم المنتج.&lt;/p&gt;&lt;p&gt;كيف أستخدمه؟&lt;/p&gt;&lt;p&gt;اتبعي تعليمات العبوة وضعي كمية مناسبة على البشرة مع تجنب ملامسة العينين.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -7541,7 +7546,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>MNT-R89</t>
+          <t>MNT-R91</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -7552,6 +7557,11 @@
       <c r="S86" t="inlineStr">
         <is>
           <t>g</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>De La Cruz</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -7573,22 +7583,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>زيت فيتامين E من دي لا كروز، 65 مل</t>
+          <t>كريم فيتامين هـ من دي لا كروز - 12جم</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>العناية والجمال &gt; العناية بالبشرة &gt; زيوت وزبدات</t>
+          <t>العناية والجمال &gt; العناية بالبشرة &gt; مرطبات</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/81eXnqEv0dL.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0790/6462/9503/files/A2014VitminECreamTrialSize2025_1-PDP.png?v=1771025932</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>زيت فيتامين E من دي لا كروز، 65 مل</t>
+          <t>كريم فيتامين هـ من دي لا كروز - 12جم</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -7598,12 +7608,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>زيت فيتامين هـ من دي لا كروز، 65 مل — De La Cruz Vitamin E Oil, 65 ml؛ زيت للعناية بالبشرة من علامة دي لا كروز، بالحجم المذكور في الاسم. تأتي صيغته الزيتية لتكون خياراً واضحاً لمن يفضّلون إدراج الزيوت ضمن خطوات عنايتهم اليومية، مع الحفاظ على بساطة الاختيار بحسب طبيعة الروتين الشخصي.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | زيت فيتامين هـ من دي لا كروز&lt;/li&gt;&lt;li&gt;النوع | زيت فيتامين هـ&lt;/li&gt;&lt;li&gt;الحجم | 65 مل&lt;/li&gt;&lt;li&gt;العلامة التجارية | دي لا كروز&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;يجمع هذا المنتج بين شكل الزيت واسم فيتامين هـ في عبوة محددة الحجم، ليمنحك خياراً عملياً عند ترتيب منتجات العناية بالبشرة. ويمكن التعامل معه كخطوة مستقلة أو إدراجه ضمن الروتين المعتاد وفق تعليمات العبوة، مع اختيار موضع الاستخدام والكمية بما يلائم تفضيلاتك.&lt;/p&gt;&lt;p&gt;لا يذكر الاسم درجة لونية أو رائحة أو مواصفات إضافية؛ لذلك يظل التركيز هنا على هويته كزيت فيتامين هـ من دي لا كروز وحجمه البالغ 65 مل. اختاريه بناءً على رغبتك في استخدام مستحضر ذي قوام زيتي، وتحققي من إرشادات العبوة قبل إدخاله في روتينك.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مستحضر زيتي يحمل اسم فيتامين هـ.&lt;/li&gt;&lt;li&gt;حجم العبوة 65 مل كما ورد في اسم المنتج.&lt;/li&gt;&lt;li&gt;من علامة دي لا كروز.&lt;/li&gt;&lt;li&gt;يمكن إدراجه ضمن خطوات العناية بالبشرة بحسب تفضيلاتك.&lt;/li&gt;&lt;li&gt;اسم المنتج واضح ويسهل تمييزه عند تنظيم المستحضرات.&lt;/li&gt;&lt;li&gt;لا يتضمن الاسم درجة لونية محددة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحثون عن زيت فيتامين هـ للعناية بالبشرة.&lt;/li&gt;&lt;li&gt;لمن يفضّلون المستحضرات ذات القوام الزيتي.&lt;/li&gt;&lt;li&gt;لمن يرغبون في عبوة بحجم 65 مل.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;راجعي تعليمات العبوة أولاً، ثم ضعي كمية مناسبة على بشرة نظيفة في الموضع المرغوب. ابدئي بكمية قليلة، ووزّعيها بلطف، ولا تستخدميه بطريقة تخالف الإرشادات المدونة على المنتج.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. يُحفظ بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;دي لا كروز هي العلامة التجارية المذكورة على هذا المنتج. يظهر اسمها هنا على زيت فيتامين هـ بحجم 65 مل، وتُعرَف هوية المنتج من الاسم والعلامة المدونين عليه.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع هذا المنتج؟&lt;/p&gt;&lt;p&gt;هو زيت فيتامين هـ من دي لا كروز.&lt;/p&gt;&lt;p&gt;ما حجم العبوة؟&lt;/p&gt;&lt;p&gt;الحجم المذكور في الاسم هو 65 مل.&lt;/p&gt;&lt;p&gt;هل يذكر الاسم درجة لونية؟&lt;/p&gt;&lt;p&gt;لا، لا تظهر درجة لونية في اسم المنتج.&lt;/p&gt;&lt;p&gt;كيف أستخدمه؟&lt;/p&gt;&lt;p&gt;اتبعي تعليمات العبوة وضعي كمية مناسبة على البشرة مع تجنب ملامسة العينين.&lt;/p&gt;</t>
+          <t>كريم فيتامين هـ من دي لا كروز، 12 جم — De La Cruz Vitamin E Cream, 12 g؛ كريم للعناية بالبشرة من علامة دي لا كروز، بحجم 12 جم. يأتي في صورة كريم سهلة التمييز عن المستحضرات الزيتية، ويقدّم خياراً محدد الاسم والحجم لمن يرغب في تنظيم مستحضراته واختيارها وفق شكل المنتج الذي يفضّله.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | كريم فيتامين هـ من دي لا كروز&lt;/li&gt;&lt;li&gt;النوع | كريم فيتامين هـ&lt;/li&gt;&lt;li&gt;الحجم | 12 جم&lt;/li&gt;&lt;li&gt;العلامة التجارية | دي لا كروز&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;يحمل الكريم اسم فيتامين هـ، وتأتي العبوة بحجم 12 جم، ما يجعل تفاصيله الأساسية واضحة عند المقارنة أو ترتيب منتجات العناية. ينسجم شكله الكريمي مع الروتين الذي يفضّل فيه المستخدم مستحضراً بهذا القوام، ويمكن استعماله وفق الإرشادات المكتوبة على العبوة.&lt;/p&gt;&lt;p&gt;لا يتضمن الاسم درجة أو رائحة أو معلومات أخرى عن خصائص المنتج؛ لذا يقتصر التعريف به على كونه كريم فيتامين هـ من دي لا كروز وحجمه المحدد. اختاري موضع الاستعمال وطريقته بالرجوع إلى تعليمات العبوة، وادمجيه في روتينك بما يتوافق مع تفضيلاتك.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;قوام كريم وفق نوع المنتج الوارد في الاسم.&lt;/li&gt;&lt;li&gt;يحمل اسم فيتامين هـ.&lt;/li&gt;&lt;li&gt;حجم العبوة 12 جم.&lt;/li&gt;&lt;li&gt;من علامة دي لا كروز.&lt;/li&gt;&lt;li&gt;تفاصيل النوع والحجم ظاهرة بوضوح في تعريف المنتج.&lt;/li&gt;&lt;li&gt;يمكن إدراجه ضمن روتين العناية وفق تعليمات العبوة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يفضلون الكريمات ضمن مستحضرات العناية بالبشرة.&lt;/li&gt;&lt;li&gt;لمن يبحثون عن كريم يحمل اسم فيتامين هـ.&lt;/li&gt;&lt;li&gt;لمن يريدون عبوة بحجم 12 جم.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;استخدميه وفق التعليمات المدونة على العبوة. ضعي كمية مناسبة على المنطقة المرغوبة من البشرة، ووزعيها بلطف، مع الحرص على عدم تجاوز طريقة الاستخدام المحددة من الشركة.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. أبقي العبوة بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;دي لا كروز هي العلامة التجارية المدونة على هذا الكريم. ويظهر المنتج ضمن اسمها بصيغة كريم فيتامين هـ وحجم 12 جم، وهما التفصيلان الأساسيان الواردان في تعريفه.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما شكل المنتج؟&lt;/p&gt;&lt;p&gt;هو كريم للعناية بالبشرة يحمل اسم فيتامين هـ.&lt;/p&gt;&lt;p&gt;كم يبلغ حجمه؟&lt;/p&gt;&lt;p&gt;حجم العبوة المذكور هو 12 جم.&lt;/p&gt;&lt;p&gt;ما العلامة التجارية؟&lt;/p&gt;&lt;p&gt;العلامة التجارية هي دي لا كروز.&lt;/p&gt;&lt;p&gt;هل وردت درجة لونية في الاسم؟&lt;/p&gt;&lt;p&gt;لا، لا يذكر الاسم درجة لونية لهذا المنتج.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -7613,7 +7623,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>MNT-R91</t>
+          <t>MNT-R92</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -7650,22 +7660,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>كريم فيتامين هـ من دي لا كروز - 12جم</t>
+          <t>كريم أساس 1 دبليو1 دبل وير من استي لودر</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>العناية والجمال &gt; العناية بالبشرة &gt; مرطبات</t>
+          <t>العناية والجمال &gt; الوجه &gt; أساس وبرايمر</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0790/6462/9503/files/A2014VitminECreamTrialSize2025_1-PDP.png?v=1771025932</t>
+          <t>https://m.media-amazon.com/images/I/41xbYsVsvFL.jpg</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>كريم فيتامين هـ من دي لا كروز - 12جم</t>
+          <t>كريم أساس 1 دبليو1 دبل وير من استي لودر</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -7675,12 +7685,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>156</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>كريم فيتامين هـ من دي لا كروز، 12 جم — De La Cruz Vitamin E Cream, 12 g؛ كريم للعناية بالبشرة من علامة دي لا كروز، بحجم 12 جم. يأتي في صورة كريم سهلة التمييز عن المستحضرات الزيتية، ويقدّم خياراً محدد الاسم والحجم لمن يرغب في تنظيم مستحضراته واختيارها وفق شكل المنتج الذي يفضّله.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | كريم فيتامين هـ من دي لا كروز&lt;/li&gt;&lt;li&gt;النوع | كريم فيتامين هـ&lt;/li&gt;&lt;li&gt;الحجم | 12 جم&lt;/li&gt;&lt;li&gt;العلامة التجارية | دي لا كروز&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;يحمل الكريم اسم فيتامين هـ، وتأتي العبوة بحجم 12 جم، ما يجعل تفاصيله الأساسية واضحة عند المقارنة أو ترتيب منتجات العناية. ينسجم شكله الكريمي مع الروتين الذي يفضّل فيه المستخدم مستحضراً بهذا القوام، ويمكن استعماله وفق الإرشادات المكتوبة على العبوة.&lt;/p&gt;&lt;p&gt;لا يتضمن الاسم درجة أو رائحة أو معلومات أخرى عن خصائص المنتج؛ لذا يقتصر التعريف به على كونه كريم فيتامين هـ من دي لا كروز وحجمه المحدد. اختاري موضع الاستعمال وطريقته بالرجوع إلى تعليمات العبوة، وادمجيه في روتينك بما يتوافق مع تفضيلاتك.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;قوام كريم وفق نوع المنتج الوارد في الاسم.&lt;/li&gt;&lt;li&gt;يحمل اسم فيتامين هـ.&lt;/li&gt;&lt;li&gt;حجم العبوة 12 جم.&lt;/li&gt;&lt;li&gt;من علامة دي لا كروز.&lt;/li&gt;&lt;li&gt;تفاصيل النوع والحجم ظاهرة بوضوح في تعريف المنتج.&lt;/li&gt;&lt;li&gt;يمكن إدراجه ضمن روتين العناية وفق تعليمات العبوة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يفضلون الكريمات ضمن مستحضرات العناية بالبشرة.&lt;/li&gt;&lt;li&gt;لمن يبحثون عن كريم يحمل اسم فيتامين هـ.&lt;/li&gt;&lt;li&gt;لمن يريدون عبوة بحجم 12 جم.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;استخدميه وفق التعليمات المدونة على العبوة. ضعي كمية مناسبة على المنطقة المرغوبة من البشرة، ووزعيها بلطف، مع الحرص على عدم تجاوز طريقة الاستخدام المحددة من الشركة.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. أبقي العبوة بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;دي لا كروز هي العلامة التجارية المدونة على هذا الكريم. ويظهر المنتج ضمن اسمها بصيغة كريم فيتامين هـ وحجم 12 جم، وهما التفصيلان الأساسيان الواردان في تعريفه.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما شكل المنتج؟&lt;/p&gt;&lt;p&gt;هو كريم للعناية بالبشرة يحمل اسم فيتامين هـ.&lt;/p&gt;&lt;p&gt;كم يبلغ حجمه؟&lt;/p&gt;&lt;p&gt;حجم العبوة المذكور هو 12 جم.&lt;/p&gt;&lt;p&gt;ما العلامة التجارية؟&lt;/p&gt;&lt;p&gt;العلامة التجارية هي دي لا كروز.&lt;/p&gt;&lt;p&gt;هل وردت درجة لونية في الاسم؟&lt;/p&gt;&lt;p&gt;لا، لا يذكر الاسم درجة لونية لهذا المنتج.&lt;/p&gt;</t>
+          <t>كريم أساس دبل وير بدرجة 1W1 من استي لودر — Estée Lauder Double Wear Foundation 1W1؛ كريم أساس للوجه من العلامة التجارية استي لودر، والدرجة المذكورة في الاسم هي 1W1. يقدم تعريف المنتج اسمه ودرجته بوضوح لتسهيل تمييزه عند اختيار كريم الأساس ومقارنته بالدرجات الأخرى من المجموعة.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | كريم أساس دبل وير من استي لودر&lt;/li&gt;&lt;li&gt;النوع | كريم أساس&lt;/li&gt;&lt;li&gt;الدرجة | 1W1&lt;/li&gt;&lt;li&gt;العلامة التجارية | استي لودر&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;يحمل هذا المنتج اسم دبل وير ودرجة 1W1، وهما التفصيلان الظاهران في تسمية كريم الأساس. يتيح لك تحديد الدرجة وفق ما تبحثين عنه عند تنسيق مكياج الوجه، مع الرجوع إلى ما يناسبك من خيارات الدرجات المتاحة لديك؛ فالاسم وحده لا يحدد وصفاً لونياً إضافياً للدرجة.&lt;/p&gt;&lt;p&gt;يمكن توزيع كريم الأساس على الوجه بالطريقة التي تفضلينها ضمن خطوات المكياج، مع مراعاة تجهيز البشرة بما يلائم روتينك. لا يذكر الاسم حجماً أو تفاصيل عن مستوى التغطية أو اللمسة النهائية، لذلك يقتصر الوصف على العلامة التجارية ونوع المنتج واسمه ودرجة 1W1.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;كريم أساس للوجه من استي لودر.&lt;/li&gt;&lt;li&gt;يحمل اسم دبل وير كما ورد في تعريف المنتج.&lt;/li&gt;&lt;li&gt;الدرجة المحددة في الاسم هي 1W1.&lt;/li&gt;&lt;li&gt;يُعرّف بوضوح كمنتج أساس ضمن المكياج.&lt;/li&gt;&lt;li&gt;يمكن توزيعه ضمن خطوات إعداد مكياج الوجه.&lt;/li&gt;&lt;li&gt;لا يذكر الاسم حجماً محدداً للعبوة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحثن عن كريم أساس من استي لودر.&lt;/li&gt;&lt;li&gt;لمن يختَرن درجة 1W1 بحسب تفضيلاتهن.&lt;/li&gt;&lt;li&gt;لمن يرغبن في إدراج كريم أساس ضمن خطوات المكياج.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;ضعي كمية مناسبة على بشرة الوجه بعد تجهيزها بالطريقة المعتادة، ثم وزعي المنتج بأداة المكياج التي تفضلينها حتى يصبح المظهر متناسقاً. ابدئي بكمية قليلة، وأضيفي المزيد عند الحاجة، مع الالتزام بإرشادات العبوة.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. يُحفظ بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;استي لودر هي العلامة التجارية المذكورة على هذا المنتج. يظهر كريم الأساس باسم دبل وير وبدرجة 1W1، وتتيح هذه البيانات التعرف إلى المنتج عند اختيار مستحضرات الوجه.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع المنتج؟&lt;/p&gt;&lt;p&gt;هو كريم أساس للوجه من استي لودر.&lt;/p&gt;&lt;p&gt;ما الدرجة المذكورة؟&lt;/p&gt;&lt;p&gt;الدرجة الواردة في الاسم هي 1W1.&lt;/p&gt;&lt;p&gt;هل يحدد الاسم حجم العبوة؟&lt;/p&gt;&lt;p&gt;لا، لا يظهر حجم في اسم المنتج.&lt;/p&gt;&lt;p&gt;كيف يوزع على الوجه؟&lt;/p&gt;&lt;p&gt;يوزع بكمية مناسبة وبالأداة المفضلة بعد تجهيز البشرة.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -7690,7 +7700,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>MNT-R92</t>
+          <t>MNT-R93</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -7705,7 +7715,7 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>De La Cruz</t>
+          <t>Estée Lauder</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
@@ -7727,7 +7737,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>كريم أساس 1 دبليو1 دبل وير من استي لودر</t>
+          <t>كريم أساس دبل وير 1w2 من استي لودر</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -7737,12 +7747,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41xbYsVsvFL.jpg</t>
+          <t>https://m.media-amazon.com/images/I/51WxgrBQnPL.jpg</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>كريم أساس 1 دبليو1 دبل وير من استي لودر</t>
+          <t>كريم أساس دبل وير 1w2 من استي لودر</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -7752,12 +7762,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>155</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>كريم أساس دبل وير بدرجة 1W1 من استي لودر — Estée Lauder Double Wear Foundation 1W1؛ كريم أساس للوجه من العلامة التجارية استي لودر، والدرجة المذكورة في الاسم هي 1W1. يقدم تعريف المنتج اسمه ودرجته بوضوح لتسهيل تمييزه عند اختيار كريم الأساس ومقارنته بالدرجات الأخرى من المجموعة.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | كريم أساس دبل وير من استي لودر&lt;/li&gt;&lt;li&gt;النوع | كريم أساس&lt;/li&gt;&lt;li&gt;الدرجة | 1W1&lt;/li&gt;&lt;li&gt;العلامة التجارية | استي لودر&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;يحمل هذا المنتج اسم دبل وير ودرجة 1W1، وهما التفصيلان الظاهران في تسمية كريم الأساس. يتيح لك تحديد الدرجة وفق ما تبحثين عنه عند تنسيق مكياج الوجه، مع الرجوع إلى ما يناسبك من خيارات الدرجات المتاحة لديك؛ فالاسم وحده لا يحدد وصفاً لونياً إضافياً للدرجة.&lt;/p&gt;&lt;p&gt;يمكن توزيع كريم الأساس على الوجه بالطريقة التي تفضلينها ضمن خطوات المكياج، مع مراعاة تجهيز البشرة بما يلائم روتينك. لا يذكر الاسم حجماً أو تفاصيل عن مستوى التغطية أو اللمسة النهائية، لذلك يقتصر الوصف على العلامة التجارية ونوع المنتج واسمه ودرجة 1W1.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;كريم أساس للوجه من استي لودر.&lt;/li&gt;&lt;li&gt;يحمل اسم دبل وير كما ورد في تعريف المنتج.&lt;/li&gt;&lt;li&gt;الدرجة المحددة في الاسم هي 1W1.&lt;/li&gt;&lt;li&gt;يُعرّف بوضوح كمنتج أساس ضمن المكياج.&lt;/li&gt;&lt;li&gt;يمكن توزيعه ضمن خطوات إعداد مكياج الوجه.&lt;/li&gt;&lt;li&gt;لا يذكر الاسم حجماً محدداً للعبوة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحثن عن كريم أساس من استي لودر.&lt;/li&gt;&lt;li&gt;لمن يختَرن درجة 1W1 بحسب تفضيلاتهن.&lt;/li&gt;&lt;li&gt;لمن يرغبن في إدراج كريم أساس ضمن خطوات المكياج.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;ضعي كمية مناسبة على بشرة الوجه بعد تجهيزها بالطريقة المعتادة، ثم وزعي المنتج بأداة المكياج التي تفضلينها حتى يصبح المظهر متناسقاً. ابدئي بكمية قليلة، وأضيفي المزيد عند الحاجة، مع الالتزام بإرشادات العبوة.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. يُحفظ بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;استي لودر هي العلامة التجارية المذكورة على هذا المنتج. يظهر كريم الأساس باسم دبل وير وبدرجة 1W1، وتتيح هذه البيانات التعرف إلى المنتج عند اختيار مستحضرات الوجه.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع المنتج؟&lt;/p&gt;&lt;p&gt;هو كريم أساس للوجه من استي لودر.&lt;/p&gt;&lt;p&gt;ما الدرجة المذكورة؟&lt;/p&gt;&lt;p&gt;الدرجة الواردة في الاسم هي 1W1.&lt;/p&gt;&lt;p&gt;هل يحدد الاسم حجم العبوة؟&lt;/p&gt;&lt;p&gt;لا، لا يظهر حجم في اسم المنتج.&lt;/p&gt;&lt;p&gt;كيف يوزع على الوجه؟&lt;/p&gt;&lt;p&gt;يوزع بكمية مناسبة وبالأداة المفضلة بعد تجهيز البشرة.&lt;/p&gt;</t>
+          <t>كريم أساس دبل وير بدرجة 1W2 من استي لودر — Estée Lauder Double Wear Foundation 1W2؛ مستحضر أساس للوجه من علامة استي لودر، بدرجة 1W2 كما وردت في الاسم. يجمع تعريفه بين اسم دبل وير ورقم الدرجة، لتتمكني من تمييز هذا الخيار عن الدرجات الأخرى عند ترتيب مستحضرات المكياج أو اختيارها.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | كريم أساس دبل وير من استي لودر&lt;/li&gt;&lt;li&gt;النوع | كريم أساس&lt;/li&gt;&lt;li&gt;الدرجة | 1W2&lt;/li&gt;&lt;li&gt;العلامة التجارية | استي لودر&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;هذا كريم أساس يحمل اسم دبل وير، وتحدد التسمية درجته برقم 1W2. يساعد وضوح الاسم والدرجة على التعرف إلى النسخة المطلوبة عند المقارنة بين خيارات المكياج، مع اختيار الدرجة وفق تفضيلك الشخصي وما تعتمدينه عادةً لمظهر الوجه.&lt;/p&gt;&lt;p&gt;يُستخدم ضمن خطوات المكياج ويمكن توزيعه على الوجه بأداة مناسبة. لا يتضمن الاسم حجم العبوة أو وصفاً إضافياً للدرجة أو للنتيجة على البشرة؛ لذا لا تُفترض خصائص أخرى غير المعلومات الواردة. راجعي بيانات العبوة عند الحاجة إلى تفاصيل إضافية عن المنتج وطريقة استخدامه.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;كريم أساس من استي لودر.&lt;/li&gt;&lt;li&gt;يحمل تسمية دبل وير.&lt;/li&gt;&lt;li&gt;الدرجة الظاهرة في الاسم هي 1W2.&lt;/li&gt;&lt;li&gt;ينتمي إلى مستحضرات مكياج الوجه.&lt;/li&gt;&lt;li&gt;يمكن توزيعه بأداة المكياج التي تفضلينها.&lt;/li&gt;&lt;li&gt;يُعرّف بالعلامة التجارية والدرجة بوضوح.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يفضلن كريم الأساس ضمن روتين المكياج.&lt;/li&gt;&lt;li&gt;لمن يبحثن عن درجة 1W2 من استي لودر.&lt;/li&gt;&lt;li&gt;لمن يرغبن في اختيار منتج محدد الدرجة بالاسم.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;بعد تجهيز البشرة، وزعي كمية مناسبة من كريم الأساس على الوجه باستخدام الأصابع أو أداة المكياج المفضلة. ابدئي بطبقة خفيفة، ثم أكملي التوزيع بحسب رغبتك، مع اتباع الإرشادات المرفقة بالعبوة.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. أبقيه بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;استي لودر هي العلامة التجارية المدونة على المنتج. ويظهر هذا الخيار باسم دبل وير مع درجة 1W2، بما يحدد فئته ونسخته المذكورة في الاسم.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما درجة كريم الأساس؟&lt;/p&gt;&lt;p&gt;الدرجة المذكورة في اسم المنتج هي 1W2.&lt;/p&gt;&lt;p&gt;ما العلامة التجارية؟&lt;/p&gt;&lt;p&gt;العلامة التجارية هي استي لودر.&lt;/p&gt;&lt;p&gt;هل يتضمن الاسم حجم العبوة؟&lt;/p&gt;&lt;p&gt;لا، لا يورد الاسم حجماً محدداً.&lt;/p&gt;&lt;p&gt;كيف يمكن توزيعه؟&lt;/p&gt;&lt;p&gt;يوزع على الوجه بأداة المكياج المفضلة وفق طريقة الاستخدام المعتادة.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -7767,7 +7777,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>MNT-R93</t>
+          <t>MNT-R94</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -7804,7 +7814,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>كريم أساس دبل وير 1w2 من استي لودر</t>
+          <t>Estée Lauder كريم أساس مزدوج الثبات من ايستية لودر 2دابليو</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -7814,12 +7824,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/51WxgrBQnPL.jpg</t>
+          <t>https://m.media-amazon.com/images/I/612XaNC86pL.jpg</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>كريم أساس دبل وير 1w2 من استي لودر</t>
+          <t>Estée Lauder كريم أساس مزدوج الثبات من ايستية لودر 2دابليو</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -7829,12 +7839,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>156</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>كريم أساس دبل وير بدرجة 1W2 من استي لودر — Estée Lauder Double Wear Foundation 1W2؛ مستحضر أساس للوجه من علامة استي لودر، بدرجة 1W2 كما وردت في الاسم. يجمع تعريفه بين اسم دبل وير ورقم الدرجة، لتتمكني من تمييز هذا الخيار عن الدرجات الأخرى عند ترتيب مستحضرات المكياج أو اختيارها.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | كريم أساس دبل وير من استي لودر&lt;/li&gt;&lt;li&gt;النوع | كريم أساس&lt;/li&gt;&lt;li&gt;الدرجة | 1W2&lt;/li&gt;&lt;li&gt;العلامة التجارية | استي لودر&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;هذا كريم أساس يحمل اسم دبل وير، وتحدد التسمية درجته برقم 1W2. يساعد وضوح الاسم والدرجة على التعرف إلى النسخة المطلوبة عند المقارنة بين خيارات المكياج، مع اختيار الدرجة وفق تفضيلك الشخصي وما تعتمدينه عادةً لمظهر الوجه.&lt;/p&gt;&lt;p&gt;يُستخدم ضمن خطوات المكياج ويمكن توزيعه على الوجه بأداة مناسبة. لا يتضمن الاسم حجم العبوة أو وصفاً إضافياً للدرجة أو للنتيجة على البشرة؛ لذا لا تُفترض خصائص أخرى غير المعلومات الواردة. راجعي بيانات العبوة عند الحاجة إلى تفاصيل إضافية عن المنتج وطريقة استخدامه.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;كريم أساس من استي لودر.&lt;/li&gt;&lt;li&gt;يحمل تسمية دبل وير.&lt;/li&gt;&lt;li&gt;الدرجة الظاهرة في الاسم هي 1W2.&lt;/li&gt;&lt;li&gt;ينتمي إلى مستحضرات مكياج الوجه.&lt;/li&gt;&lt;li&gt;يمكن توزيعه بأداة المكياج التي تفضلينها.&lt;/li&gt;&lt;li&gt;يُعرّف بالعلامة التجارية والدرجة بوضوح.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يفضلن كريم الأساس ضمن روتين المكياج.&lt;/li&gt;&lt;li&gt;لمن يبحثن عن درجة 1W2 من استي لودر.&lt;/li&gt;&lt;li&gt;لمن يرغبن في اختيار منتج محدد الدرجة بالاسم.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;بعد تجهيز البشرة، وزعي كمية مناسبة من كريم الأساس على الوجه باستخدام الأصابع أو أداة المكياج المفضلة. ابدئي بطبقة خفيفة، ثم أكملي التوزيع بحسب رغبتك، مع اتباع الإرشادات المرفقة بالعبوة.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. أبقيه بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;استي لودر هي العلامة التجارية المدونة على المنتج. ويظهر هذا الخيار باسم دبل وير مع درجة 1W2، بما يحدد فئته ونسخته المذكورة في الاسم.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما درجة كريم الأساس؟&lt;/p&gt;&lt;p&gt;الدرجة المذكورة في اسم المنتج هي 1W2.&lt;/p&gt;&lt;p&gt;ما العلامة التجارية؟&lt;/p&gt;&lt;p&gt;العلامة التجارية هي استي لودر.&lt;/p&gt;&lt;p&gt;هل يتضمن الاسم حجم العبوة؟&lt;/p&gt;&lt;p&gt;لا، لا يورد الاسم حجماً محدداً.&lt;/p&gt;&lt;p&gt;كيف يمكن توزيعه؟&lt;/p&gt;&lt;p&gt;يوزع على الوجه بأداة المكياج المفضلة وفق طريقة الاستخدام المعتادة.&lt;/p&gt;</t>
+          <t>كريم أساس مزدوج الثبات من استي لودر بدرجة 2W — Estée Lauder Double Wear Foundation 2W؛ مستحضر أساس للوجه من العلامة التجارية استي لودر، والدرجة المذكورة في الاسم هي 2W. يوضح اسم المنتج فئته ونسخته لتسهيل التعرف إليه عند اختيار كريم الأساس أو تنظيم مستحضرات المكياج.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | كريم أساس مزدوج الثبات من استي لودر&lt;/li&gt;&lt;li&gt;النوع | كريم أساس&lt;/li&gt;&lt;li&gt;الدرجة | 2W&lt;/li&gt;&lt;li&gt;العلامة التجارية | استي لودر&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;يأتي هذا المنتج تحت اسم كريم أساس مزدوج الثبات، مع الإشارة إلى الدرجة 2W في التسمية. يتيح ذلك تحديد الخيار المقصود بالاسم والدرجة عند المقارنة مع مستحضرات أخرى، من دون الحاجة إلى افتراض وصف لوني أو خصائص غير واردة في بيانات المنتج.&lt;/p&gt;&lt;p&gt;يمكن إدراجه ضمن مكياج الوجه وتوزيعه بالطريقة التي تفضلينها بعد تهيئة البشرة. لا يذكر الاسم حجماً للعبوة، كما لا يورد تفاصيل عن مستوى التغطية أو اللمسة النهائية؛ لذا يظل التعريف مقتصراً على كونه كريم أساس من استي لودر بدرجة 2W.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مستحضر كريم أساس للوجه.&lt;/li&gt;&lt;li&gt;من علامة استي لودر.&lt;/li&gt;&lt;li&gt;يحمل وصف مزدوج الثبات في الاسم.&lt;/li&gt;&lt;li&gt;الدرجة المذكورة هي 2W.&lt;/li&gt;&lt;li&gt;يمكن استخدامه ضمن خطوات المكياج المعتادة.&lt;/li&gt;&lt;li&gt;تظهر معلومات العلامة والدرجة في تسمية المنتج.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحثن عن كريم أساس من استي لودر.&lt;/li&gt;&lt;li&gt;لمن يختَرن الدرجة 2W وفق تفضيلاتهن.&lt;/li&gt;&lt;li&gt;لمن يرغبن في مستحضر أساس لمكياج الوجه.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;ضعي كمية مناسبة على الوجه بعد تجهيز البشرة، ثم وزعيها بالتساوي باستخدام أصابعك أو أداة مكياج مناسبة. يمكن إضافة كمية أخرى عند الحاجة، مع مراعاة تعليمات الاستخدام المكتوبة على العبوة.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. احفظيه بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;استي لودر هي العلامة التجارية المحددة لهذا المنتج. ويُعرَف هذا الخيار من كريم الأساس باسمه ودرجة 2W المذكورة في التسمية.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما درجة كريم الأساس؟&lt;/p&gt;&lt;p&gt;الدرجة الواردة في اسم المنتج هي 2W.&lt;/p&gt;&lt;p&gt;ما نوع المستحضر؟&lt;/p&gt;&lt;p&gt;هو كريم أساس للوجه من استي لودر.&lt;/p&gt;&lt;p&gt;هل يذكر الاسم حجم العبوة؟&lt;/p&gt;&lt;p&gt;لا، لا يرد حجم العبوة ضمن الاسم.&lt;/p&gt;&lt;p&gt;هل يوضح الاسم وصف الدرجة؟&lt;/p&gt;&lt;p&gt;يورد الاسم رمز 2W فقط، ولا يقدم وصفاً لونياً إضافياً.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -7844,7 +7854,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>MNT-R94</t>
+          <t>MNT-R95</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -7881,22 +7891,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Estée Lauder كريم أساس مزدوج الثبات من ايستية لودر 2دابليو</t>
+          <t>ارم اند هامر اسنشيالز مزيل عرق النظافه 71 جم</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>العناية والجمال &gt; الوجه &gt; أساس وبرايمر</t>
+          <t>العناية والجمال &gt; العناية الشخصية</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/612XaNC86pL.jpg</t>
+          <t>https://m.media-amazon.com/images/I/61O6HPC++jL.jpg</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Estée Lauder كريم أساس مزدوج الثبات من ايستية لودر 2دابليو</t>
+          <t>ارم اند هامر اسنشيالز مزيل عرق النظافه 71 جم</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -7906,12 +7916,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>كريم أساس مزدوج الثبات من استي لودر بدرجة 2W — Estée Lauder Double Wear Foundation 2W؛ مستحضر أساس للوجه من العلامة التجارية استي لودر، والدرجة المذكورة في الاسم هي 2W. يوضح اسم المنتج فئته ونسخته لتسهيل التعرف إليه عند اختيار كريم الأساس أو تنظيم مستحضرات المكياج.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | كريم أساس مزدوج الثبات من استي لودر&lt;/li&gt;&lt;li&gt;النوع | كريم أساس&lt;/li&gt;&lt;li&gt;الدرجة | 2W&lt;/li&gt;&lt;li&gt;العلامة التجارية | استي لودر&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;يأتي هذا المنتج تحت اسم كريم أساس مزدوج الثبات، مع الإشارة إلى الدرجة 2W في التسمية. يتيح ذلك تحديد الخيار المقصود بالاسم والدرجة عند المقارنة مع مستحضرات أخرى، من دون الحاجة إلى افتراض وصف لوني أو خصائص غير واردة في بيانات المنتج.&lt;/p&gt;&lt;p&gt;يمكن إدراجه ضمن مكياج الوجه وتوزيعه بالطريقة التي تفضلينها بعد تهيئة البشرة. لا يذكر الاسم حجماً للعبوة، كما لا يورد تفاصيل عن مستوى التغطية أو اللمسة النهائية؛ لذا يظل التعريف مقتصراً على كونه كريم أساس من استي لودر بدرجة 2W.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مستحضر كريم أساس للوجه.&lt;/li&gt;&lt;li&gt;من علامة استي لودر.&lt;/li&gt;&lt;li&gt;يحمل وصف مزدوج الثبات في الاسم.&lt;/li&gt;&lt;li&gt;الدرجة المذكورة هي 2W.&lt;/li&gt;&lt;li&gt;يمكن استخدامه ضمن خطوات المكياج المعتادة.&lt;/li&gt;&lt;li&gt;تظهر معلومات العلامة والدرجة في تسمية المنتج.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحثن عن كريم أساس من استي لودر.&lt;/li&gt;&lt;li&gt;لمن يختَرن الدرجة 2W وفق تفضيلاتهن.&lt;/li&gt;&lt;li&gt;لمن يرغبن في مستحضر أساس لمكياج الوجه.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;ضعي كمية مناسبة على الوجه بعد تجهيز البشرة، ثم وزعيها بالتساوي باستخدام أصابعك أو أداة مكياج مناسبة. يمكن إضافة كمية أخرى عند الحاجة، مع مراعاة تعليمات الاستخدام المكتوبة على العبوة.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. احفظيه بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;استي لودر هي العلامة التجارية المحددة لهذا المنتج. ويُعرَف هذا الخيار من كريم الأساس باسمه ودرجة 2W المذكورة في التسمية.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما درجة كريم الأساس؟&lt;/p&gt;&lt;p&gt;الدرجة الواردة في اسم المنتج هي 2W.&lt;/p&gt;&lt;p&gt;ما نوع المستحضر؟&lt;/p&gt;&lt;p&gt;هو كريم أساس للوجه من استي لودر.&lt;/p&gt;&lt;p&gt;هل يذكر الاسم حجم العبوة؟&lt;/p&gt;&lt;p&gt;لا، لا يرد حجم العبوة ضمن الاسم.&lt;/p&gt;&lt;p&gt;هل يوضح الاسم وصف الدرجة؟&lt;/p&gt;&lt;p&gt;يورد الاسم رمز 2W فقط، ولا يقدم وصفاً لونياً إضافياً.&lt;/p&gt;</t>
+          <t>مزيل عرق إسنشيالز برائحة النظافة من ارم اند هامر، 71 جم — Arm &amp; Hammer Essentials Deodorant Clean, 71 g؛ مزيل عرق من علامة ارم اند هامر، بحجم 71 جم، ويشير الاسم إلى رائحة النظافة. يقدّم المنتج تعريفاً مباشراً بنوعه ورائحته وحجم العبوة، ليسهل تمييزه ضمن مستحضرات العناية الشخصية.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | مزيل عرق إسنشيالز برائحة النظافة من ارم اند هامر&lt;/li&gt;&lt;li&gt;النوع | مزيل عرق&lt;/li&gt;&lt;li&gt;الحجم | 71 جم&lt;/li&gt;&lt;li&gt;العلامة التجارية | ارم اند هامر&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;ينتمي هذا المنتج إلى فئة مزيلات العرق، ويحمل اسم إسنشيالز مع وصف رائحة النظافة كما ورد في التسمية. تأتي العبوة بحجم 71 جم، وهو تفصيل عملي عند التعرف إلى المنتج أو تمييزه عن أحجام أخرى. لا يذكر الاسم نوعاً آخر من الحماية أو خصائص إضافية، لذلك يقتصر وصفه على هويته ورائحته وحجمه.&lt;/p&gt;&lt;p&gt;يمكن إدراجه ضمن روتين العناية الشخصية اليومي وفق الطريقة الموضحة على العبوة. اختيار المنتج يعتمد على تفضيلك لرائحة النظافة وعلى شكل المستحضر المناسب لك؛ ويُرجى الرجوع إلى بيانات العبوة لمعرفة تعليمات الاستخدام الخاصة به.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مزيل عرق من علامة ارم اند هامر.&lt;/li&gt;&lt;li&gt;يحمل اسم إسنشيالز.&lt;/li&gt;&lt;li&gt;يرد وصف رائحة النظافة ضمن اسم المنتج.&lt;/li&gt;&lt;li&gt;حجم العبوة 71 جم.&lt;/li&gt;&lt;li&gt;ينتمي إلى مستحضرات العناية الشخصية.&lt;/li&gt;&lt;li&gt;تظهر تفاصيل النوع والحجم في تسمية المنتج.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحثون عن مزيل عرق للاستخدام ضمن العناية الشخصية.&lt;/li&gt;&lt;li&gt;لمن يفضلون المنتج الموصوف برائحة النظافة.&lt;/li&gt;&lt;li&gt;لمن يرغبون في عبوة بحجم 71 جم.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;استخدميه وفق التعليمات المكتوبة على العبوة وعلى بشرة نظيفة وجافة إذا كانت الإرشادات تسمح بذلك. مرريه أو ضعيه بالطريقة المحددة للمنتج، وأغلقي العبوة بعد الاستعمال.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. يُحفظ بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;ارم اند هامر هي العلامة التجارية المذكورة على هذا المنتج. ويظهر مزيل العرق هنا ضمن مجموعة إسنشيالز بالوصف والحجم الواردين في الاسم.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع هذا المنتج؟&lt;/p&gt;&lt;p&gt;هو مزيل عرق من ارم اند هامر.&lt;/p&gt;&lt;p&gt;ما حجمه؟&lt;/p&gt;&lt;p&gt;حجم العبوة المذكور هو 71 جم.&lt;/p&gt;&lt;p&gt;ما وصف الرائحة الوارد؟&lt;/p&gt;&lt;p&gt;يذكر الاسم رائحة النظافة.&lt;/p&gt;&lt;p&gt;ما المجموعة المذكورة في الاسم؟&lt;/p&gt;&lt;p&gt;المجموعة الواردة هي إسنشيالز.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -7921,7 +7931,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>MNT-R95</t>
+          <t>MNT-R96</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -7936,7 +7946,7 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>Estée Lauder</t>
+          <t>Arm &amp; Hammer</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
@@ -7958,7 +7968,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ارم اند هامر اسنشيالز مزيل عرق النظافه 71 جم</t>
+          <t>Arm &amp; Hammer مزيل العرق برائحة الروزماري واللافندر 71 جم</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -7968,12 +7978,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/61O6HPC++jL.jpg</t>
+          <t>https://m.media-amazon.com/images/I/71Ua50uoKcL.jpg</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>ارم اند هامر اسنشيالز مزيل عرق النظافه 71 جم</t>
+          <t>Arm &amp; Hammer مزيل العرق برائحة الروزماري واللافندر 71 جم</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -7983,12 +7993,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>مزيل عرق إسنشيالز برائحة النظافة من ارم اند هامر، 71 جم — Arm &amp; Hammer Essentials Deodorant Clean, 71 g؛ مزيل عرق من علامة ارم اند هامر، بحجم 71 جم، ويشير الاسم إلى رائحة النظافة. يقدّم المنتج تعريفاً مباشراً بنوعه ورائحته وحجم العبوة، ليسهل تمييزه ضمن مستحضرات العناية الشخصية.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | مزيل عرق إسنشيالز برائحة النظافة من ارم اند هامر&lt;/li&gt;&lt;li&gt;النوع | مزيل عرق&lt;/li&gt;&lt;li&gt;الحجم | 71 جم&lt;/li&gt;&lt;li&gt;العلامة التجارية | ارم اند هامر&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;ينتمي هذا المنتج إلى فئة مزيلات العرق، ويحمل اسم إسنشيالز مع وصف رائحة النظافة كما ورد في التسمية. تأتي العبوة بحجم 71 جم، وهو تفصيل عملي عند التعرف إلى المنتج أو تمييزه عن أحجام أخرى. لا يذكر الاسم نوعاً آخر من الحماية أو خصائص إضافية، لذلك يقتصر وصفه على هويته ورائحته وحجمه.&lt;/p&gt;&lt;p&gt;يمكن إدراجه ضمن روتين العناية الشخصية اليومي وفق الطريقة الموضحة على العبوة. اختيار المنتج يعتمد على تفضيلك لرائحة النظافة وعلى شكل المستحضر المناسب لك؛ ويُرجى الرجوع إلى بيانات العبوة لمعرفة تعليمات الاستخدام الخاصة به.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مزيل عرق من علامة ارم اند هامر.&lt;/li&gt;&lt;li&gt;يحمل اسم إسنشيالز.&lt;/li&gt;&lt;li&gt;يرد وصف رائحة النظافة ضمن اسم المنتج.&lt;/li&gt;&lt;li&gt;حجم العبوة 71 جم.&lt;/li&gt;&lt;li&gt;ينتمي إلى مستحضرات العناية الشخصية.&lt;/li&gt;&lt;li&gt;تظهر تفاصيل النوع والحجم في تسمية المنتج.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحثون عن مزيل عرق للاستخدام ضمن العناية الشخصية.&lt;/li&gt;&lt;li&gt;لمن يفضلون المنتج الموصوف برائحة النظافة.&lt;/li&gt;&lt;li&gt;لمن يرغبون في عبوة بحجم 71 جم.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;استخدميه وفق التعليمات المكتوبة على العبوة وعلى بشرة نظيفة وجافة إذا كانت الإرشادات تسمح بذلك. مرريه أو ضعيه بالطريقة المحددة للمنتج، وأغلقي العبوة بعد الاستعمال.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. يُحفظ بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;ارم اند هامر هي العلامة التجارية المذكورة على هذا المنتج. ويظهر مزيل العرق هنا ضمن مجموعة إسنشيالز بالوصف والحجم الواردين في الاسم.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع هذا المنتج؟&lt;/p&gt;&lt;p&gt;هو مزيل عرق من ارم اند هامر.&lt;/p&gt;&lt;p&gt;ما حجمه؟&lt;/p&gt;&lt;p&gt;حجم العبوة المذكور هو 71 جم.&lt;/p&gt;&lt;p&gt;ما وصف الرائحة الوارد؟&lt;/p&gt;&lt;p&gt;يذكر الاسم رائحة النظافة.&lt;/p&gt;&lt;p&gt;ما المجموعة المذكورة في الاسم؟&lt;/p&gt;&lt;p&gt;المجموعة الواردة هي إسنشيالز.&lt;/p&gt;</t>
+          <t>مزيل العرق من ارم اند هامر برائحة الروزماري واللافندر، 71 جم — Arm &amp; Hammer Rosemary Lavender Deodorant, 71 g؛ مزيل عرق للعناية الشخصية من علامة ارم اند هامر، بحجم 71 جم، ويذكر الاسم رائحتي الروزماري واللافندر. يجمع تعريفه بين العلامة التجارية ونوع المستحضر والرائحة والحجم في صياغة واضحة.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | مزيل العرق برائحة الروزماري واللافندر من ارم اند هامر&lt;/li&gt;&lt;li&gt;النوع | مزيل عرق&lt;/li&gt;&lt;li&gt;الحجم | 71 جم&lt;/li&gt;&lt;li&gt;العلامة التجارية | ارم اند هامر&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;يُعرَف هذا المنتج بوصفه مزيل عرق يحمل رائحة الروزماري واللافندر، وفق ما ورد في اسمه، وتبلغ كمية العبوة 71 جم. تمنحك هذه التفاصيل طريقة مباشرة للتمييز بينه وبين المنتجات ذات الروائح أو الأحجام الأخرى، من غير إضافة وصف لمكونات أو خصائص لم ترد في التسمية.&lt;/p&gt;&lt;p&gt;يناسب إدراجه ضمن خطوات العناية الشخصية بالطريقة الموضحة على العبوة. اختاريه إذا كان وصف الرائحة المذكور قريباً من تفضيلك، وراجعي بيانات المنتج لمعرفة إرشادات الاستخدام الدقيقة. لا يذكر الاسم أنه مانع للتعرق، لذا يُعرّف هنا بمزيل عرق فقط.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مزيل عرق من ارم اند هامر.&lt;/li&gt;&lt;li&gt;يذكر الاسم رائحة الروزماري واللافندر.&lt;/li&gt;&lt;li&gt;حجم العبوة 71 جم.&lt;/li&gt;&lt;li&gt;مخصص للاستخدام ضمن العناية الشخصية.&lt;/li&gt;&lt;li&gt;يوفر تعريفاً واضحاً بالرائحة والحجم.&lt;/li&gt;&lt;li&gt;لا يرد في الاسم وصف بأنه مانع للتعرق.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحثون عن مزيل عرق ضمن العناية الشخصية.&lt;/li&gt;&lt;li&gt;لمن يختارون المنتجات بحسب وصف رائحتها.&lt;/li&gt;&lt;li&gt;لمن يفضلون عبوة بحجم 71 جم.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;اتبعي طريقة الاستخدام المدونة على العبوة. ضعي المنتج بالطريقة المحددة على المنطقة المطلوبة، مع مراعاة أن تكون البشرة مناسبة للاستخدام وفق إرشادات المنتج، ثم أعيدي إغلاق العبوة.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. أبقيه بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;ارم اند هامر هي العلامة التجارية الظاهرة على مزيل العرق. ويرتبط هذا الخيار بوصف الروزماري واللافندر وبحجم 71 جم كما وردا في اسم المنتج.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما الرائحة المذكورة في الاسم؟&lt;/p&gt;&lt;p&gt;الروزماري واللافندر.&lt;/p&gt;&lt;p&gt;كم يبلغ حجم العبوة؟&lt;/p&gt;&lt;p&gt;حجمها المذكور هو 71 جم.&lt;/p&gt;&lt;p&gt;هل المنتج مانع للتعرق؟&lt;/p&gt;&lt;p&gt;لا يذكر الاسم ذلك؛ فهو مصنف كمزيل عرق.&lt;/p&gt;&lt;p&gt;ما العلامة التجارية؟&lt;/p&gt;&lt;p&gt;العلامة التجارية هي ارم اند هامر.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -7998,7 +8008,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>MNT-R96</t>
+          <t>MNT-R97</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -8035,7 +8045,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Arm &amp; Hammer مزيل العرق برائحة الروزماري واللافندر 71 جم</t>
+          <t>Arm &amp; Hammer مزيل مانع للتعرق الترا ماكس من ارم اندهامر28غ</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -8045,12 +8055,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71Ua50uoKcL.jpg</t>
+          <t>https://m.media-amazon.com/images/I/61Tx3mgRaWL.jpg</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Arm &amp; Hammer مزيل العرق برائحة الروزماري واللافندر 71 جم</t>
+          <t>Arm &amp; Hammer مزيل مانع للتعرق الترا ماكس من ارم اندهامر28غ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -8060,12 +8070,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>مزيل العرق من ارم اند هامر برائحة الروزماري واللافندر، 71 جم — Arm &amp; Hammer Rosemary Lavender Deodorant, 71 g؛ مزيل عرق للعناية الشخصية من علامة ارم اند هامر، بحجم 71 جم، ويذكر الاسم رائحتي الروزماري واللافندر. يجمع تعريفه بين العلامة التجارية ونوع المستحضر والرائحة والحجم في صياغة واضحة.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | مزيل العرق برائحة الروزماري واللافندر من ارم اند هامر&lt;/li&gt;&lt;li&gt;النوع | مزيل عرق&lt;/li&gt;&lt;li&gt;الحجم | 71 جم&lt;/li&gt;&lt;li&gt;العلامة التجارية | ارم اند هامر&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;يُعرَف هذا المنتج بوصفه مزيل عرق يحمل رائحة الروزماري واللافندر، وفق ما ورد في اسمه، وتبلغ كمية العبوة 71 جم. تمنحك هذه التفاصيل طريقة مباشرة للتمييز بينه وبين المنتجات ذات الروائح أو الأحجام الأخرى، من غير إضافة وصف لمكونات أو خصائص لم ترد في التسمية.&lt;/p&gt;&lt;p&gt;يناسب إدراجه ضمن خطوات العناية الشخصية بالطريقة الموضحة على العبوة. اختاريه إذا كان وصف الرائحة المذكور قريباً من تفضيلك، وراجعي بيانات المنتج لمعرفة إرشادات الاستخدام الدقيقة. لا يذكر الاسم أنه مانع للتعرق، لذا يُعرّف هنا بمزيل عرق فقط.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مزيل عرق من ارم اند هامر.&lt;/li&gt;&lt;li&gt;يذكر الاسم رائحة الروزماري واللافندر.&lt;/li&gt;&lt;li&gt;حجم العبوة 71 جم.&lt;/li&gt;&lt;li&gt;مخصص للاستخدام ضمن العناية الشخصية.&lt;/li&gt;&lt;li&gt;يوفر تعريفاً واضحاً بالرائحة والحجم.&lt;/li&gt;&lt;li&gt;لا يرد في الاسم وصف بأنه مانع للتعرق.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحثون عن مزيل عرق ضمن العناية الشخصية.&lt;/li&gt;&lt;li&gt;لمن يختارون المنتجات بحسب وصف رائحتها.&lt;/li&gt;&lt;li&gt;لمن يفضلون عبوة بحجم 71 جم.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;اتبعي طريقة الاستخدام المدونة على العبوة. ضعي المنتج بالطريقة المحددة على المنطقة المطلوبة، مع مراعاة أن تكون البشرة مناسبة للاستخدام وفق إرشادات المنتج، ثم أعيدي إغلاق العبوة.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. أبقيه بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;ارم اند هامر هي العلامة التجارية الظاهرة على مزيل العرق. ويرتبط هذا الخيار بوصف الروزماري واللافندر وبحجم 71 جم كما وردا في اسم المنتج.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما الرائحة المذكورة في الاسم؟&lt;/p&gt;&lt;p&gt;الروزماري واللافندر.&lt;/p&gt;&lt;p&gt;كم يبلغ حجم العبوة؟&lt;/p&gt;&lt;p&gt;حجمها المذكور هو 71 جم.&lt;/p&gt;&lt;p&gt;هل المنتج مانع للتعرق؟&lt;/p&gt;&lt;p&gt;لا يذكر الاسم ذلك؛ فهو مصنف كمزيل عرق.&lt;/p&gt;&lt;p&gt;ما العلامة التجارية؟&lt;/p&gt;&lt;p&gt;العلامة التجارية هي ارم اند هامر.&lt;/p&gt;</t>
+          <t>مزيل مانع للتعرق ألترا ماكس من ارم اند هامر، 28 جم — Arm &amp; Hammer Ultra Max Antiperspirant, 28 g؛ مستحضر للعناية الشخصية من علامة ارم اند هامر، بحجم 28 جم، ويحمل اسم ألترا ماكس. يعرّف الاسم المنتج بصفته مانعاً للتعرق، ويميزه عن مزيلات العرق التي لا يرد فيها هذا الوصف.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | مزيل مانع للتعرق ألترا ماكس من ارم اند هامر&lt;/li&gt;&lt;li&gt;النوع | مانع تعرّق&lt;/li&gt;&lt;li&gt;الحجم | 28 جم&lt;/li&gt;&lt;li&gt;العلامة التجارية | ارم اند هامر&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;يجمع المنتج بين وصف مانع التعرق واسم ألترا ماكس، ويأتي في عبوة محددة بحجم 28 جم. تبرز هذه المعلومات الأساسية لمن يرغب في تحديد نوع المستحضر وحجمه قبل إدراجه ضمن مستلزمات العناية الشخصية. لا يورد الاسم رائحة أو صيغة تطبيق محددة، لذلك لا تُضاف تفاصيل غير واردة في التسمية.&lt;/p&gt;&lt;p&gt;يمكن استخدامه وفق الإرشادات المدونة على العبوة، مع الانتباه إلى طريقة التطبيق المناسبة للمنتج. يظل اختيار هذا المستحضر مرتبطاً بتفضيلك لفئة موانع التعرق واسم ألترا ماكس، بينما يوضح الحجم مقدار العبوة المذكور للمنتج.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مانع تعرّق من علامة ارم اند هامر.&lt;/li&gt;&lt;li&gt;يحمل اسم ألترا ماكس.&lt;/li&gt;&lt;li&gt;حجم العبوة المذكور 28 جم.&lt;/li&gt;&lt;li&gt;يندرج ضمن مستحضرات العناية الشخصية.&lt;/li&gt;&lt;li&gt;يحدد الاسم فئة المنتج بوضوح.&lt;/li&gt;&lt;li&gt;لا يذكر الاسم رائحة أو صيغة تطبيق محددة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحثون عن مستحضر موصوف بأنه مانع للتعرق.&lt;/li&gt;&lt;li&gt;لمن يفضلون منتجات ألترا ماكس من ارم اند هامر.&lt;/li&gt;&lt;li&gt;لمن يرغبون في عبوة بحجم 28 جم.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;راجعي تعليمات العبوة قبل الاستخدام، ثم طبقي المنتج على المنطقة المحددة بالطريقة والوقت الواردين فيها. لا تستخدميه على نحو يخالف الإرشادات، وأعيدي إغلاق العبوة بعد الانتهاء.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. يُحفظ بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;ارم اند هامر هي العلامة التجارية المذكورة على المنتج. ويظهر هذا المستحضر ضمن اسم ألترا ماكس بوصفه مانعاً للتعرق وبحجم 28 جم.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع المنتج؟&lt;/p&gt;&lt;p&gt;هو مانع تعرّق من ارم اند هامر.&lt;/p&gt;&lt;p&gt;ما اسم المجموعة؟&lt;/p&gt;&lt;p&gt;الاسم الوارد للمنتج هو ألترا ماكس.&lt;/p&gt;&lt;p&gt;ما حجم العبوة؟&lt;/p&gt;&lt;p&gt;حجمها المذكور 28 جم.&lt;/p&gt;&lt;p&gt;هل يذكر الاسم رائحة؟&lt;/p&gt;&lt;p&gt;لا، لا يحدد الاسم رائحة معينة.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -8075,7 +8085,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>MNT-R97</t>
+          <t>MNT-R98</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -8112,7 +8122,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Arm &amp; Hammer مزيل مانع للتعرق الترا ماكس من ارم اندهامر28غ</t>
+          <t>Arm &amp; Hammer مزيل مانع للتعرق الترا ماكس للنساء 28غ</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -8122,12 +8132,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/61Tx3mgRaWL.jpg</t>
+          <t>https://m.media-amazon.com/images/I/71MkO0H7iSL.jpg</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Arm &amp; Hammer مزيل مانع للتعرق الترا ماكس من ارم اندهامر28غ</t>
+          <t>Arm &amp; Hammer مزيل مانع للتعرق الترا ماكس للنساء 28غ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -8142,7 +8152,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>مزيل مانع للتعرق ألترا ماكس من ارم اند هامر، 28 جم — Arm &amp; Hammer Ultra Max Antiperspirant, 28 g؛ مستحضر للعناية الشخصية من علامة ارم اند هامر، بحجم 28 جم، ويحمل اسم ألترا ماكس. يعرّف الاسم المنتج بصفته مانعاً للتعرق، ويميزه عن مزيلات العرق التي لا يرد فيها هذا الوصف.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | مزيل مانع للتعرق ألترا ماكس من ارم اند هامر&lt;/li&gt;&lt;li&gt;النوع | مانع تعرّق&lt;/li&gt;&lt;li&gt;الحجم | 28 جم&lt;/li&gt;&lt;li&gt;العلامة التجارية | ارم اند هامر&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;يجمع المنتج بين وصف مانع التعرق واسم ألترا ماكس، ويأتي في عبوة محددة بحجم 28 جم. تبرز هذه المعلومات الأساسية لمن يرغب في تحديد نوع المستحضر وحجمه قبل إدراجه ضمن مستلزمات العناية الشخصية. لا يورد الاسم رائحة أو صيغة تطبيق محددة، لذلك لا تُضاف تفاصيل غير واردة في التسمية.&lt;/p&gt;&lt;p&gt;يمكن استخدامه وفق الإرشادات المدونة على العبوة، مع الانتباه إلى طريقة التطبيق المناسبة للمنتج. يظل اختيار هذا المستحضر مرتبطاً بتفضيلك لفئة موانع التعرق واسم ألترا ماكس، بينما يوضح الحجم مقدار العبوة المذكور للمنتج.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مانع تعرّق من علامة ارم اند هامر.&lt;/li&gt;&lt;li&gt;يحمل اسم ألترا ماكس.&lt;/li&gt;&lt;li&gt;حجم العبوة المذكور 28 جم.&lt;/li&gt;&lt;li&gt;يندرج ضمن مستحضرات العناية الشخصية.&lt;/li&gt;&lt;li&gt;يحدد الاسم فئة المنتج بوضوح.&lt;/li&gt;&lt;li&gt;لا يذكر الاسم رائحة أو صيغة تطبيق محددة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحثون عن مستحضر موصوف بأنه مانع للتعرق.&lt;/li&gt;&lt;li&gt;لمن يفضلون منتجات ألترا ماكس من ارم اند هامر.&lt;/li&gt;&lt;li&gt;لمن يرغبون في عبوة بحجم 28 جم.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;راجعي تعليمات العبوة قبل الاستخدام، ثم طبقي المنتج على المنطقة المحددة بالطريقة والوقت الواردين فيها. لا تستخدميه على نحو يخالف الإرشادات، وأعيدي إغلاق العبوة بعد الانتهاء.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. يُحفظ بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;ارم اند هامر هي العلامة التجارية المذكورة على المنتج. ويظهر هذا المستحضر ضمن اسم ألترا ماكس بوصفه مانعاً للتعرق وبحجم 28 جم.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع المنتج؟&lt;/p&gt;&lt;p&gt;هو مانع تعرّق من ارم اند هامر.&lt;/p&gt;&lt;p&gt;ما اسم المجموعة؟&lt;/p&gt;&lt;p&gt;الاسم الوارد للمنتج هو ألترا ماكس.&lt;/p&gt;&lt;p&gt;ما حجم العبوة؟&lt;/p&gt;&lt;p&gt;حجمها المذكور 28 جم.&lt;/p&gt;&lt;p&gt;هل يذكر الاسم رائحة؟&lt;/p&gt;&lt;p&gt;لا، لا يحدد الاسم رائحة معينة.&lt;/p&gt;</t>
+          <t>مزيل مانع للتعرق ألترا ماكس للنساء من ارم اند هامر، 28 جم — Arm &amp; Hammer Ultra Max Antiperspirant for Women, 28 g؛ مستحضر عناية شخصية موصوف للنساء، من علامة ارم اند هامر، بحجم 28 جم. يجمع الاسم بين فئة المنتج واسم ألترا ماكس والفئة المذكورة والحجم، لتكون معلوماته الأساسية واضحة عند الاختيار.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | مزيل مانع للتعرق ألترا ماكس للنساء من ارم اند هامر&lt;/li&gt;&lt;li&gt;النوع | مانع تعرّق&lt;/li&gt;&lt;li&gt;الحجم | 28 جم&lt;/li&gt;&lt;li&gt;العلامة التجارية | ارم اند هامر&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;هذا المنتج من فئة موانع التعرق، ويحمل اسم ألترا ماكس ويُذكر في تسميته أنه مخصص للنساء. حجم العبوة هو 28 جم، ما يتيح تمييزه من حيث الكمية إلى جانب اسم العلامة التجارية والفئة. ولا يذكر الاسم رائحة أو تفاصيل تركيب أو صيغة استخدام بعينها.&lt;/p&gt;&lt;p&gt;يمكن إدراجه ضمن روتين العناية الشخصية بحسب التعليمات المدونة على العبوة. عند اختيار المنتج، راجعي طريقة استعماله والبيانات المرفقة به، واستخدميه وفق ما توضحه الشركة. يقتصر هذا التعريف على تفاصيل الاسم والنوع والحجم دون إضافة ادعاءات أو مواصفات غير متاحة.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مانع تعرّق من ارم اند هامر.&lt;/li&gt;&lt;li&gt;يحمل اسم ألترا ماكس.&lt;/li&gt;&lt;li&gt;موصوف في الاسم بأنه للنساء.&lt;/li&gt;&lt;li&gt;حجم العبوة 28 جم.&lt;/li&gt;&lt;li&gt;مصنف ضمن مستحضرات العناية الشخصية.&lt;/li&gt;&lt;li&gt;لا يحدد الاسم رائحة معينة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;للنساء الباحثات عن مستحضر من فئة موانع التعرق.&lt;/li&gt;&lt;li&gt;لمن يفضلن اسم ألترا ماكس من ارم اند هامر.&lt;/li&gt;&lt;li&gt;لمن يرغبن في عبوة بحجم 28 جم.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;اتبعي الإرشادات الموضحة على العبوة، وطبقي المنتج بالطريقة المحددة فيها. تحققي من ملاءمة موضع الاستخدام المذكور، ولا تستخدميه على نحو مختلف عن التعليمات المرفقة.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. أبقي المنتج بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;ارم اند هامر هي العلامة التجارية المدونة على هذا المنتج. ويظهر خيار ألترا ماكس للنساء باسم مانع للتعرق وبحجم 28 جم، وفق المعلومات الواردة في التسمية.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;لمن وُصف هذا المنتج؟&lt;/p&gt;&lt;p&gt;يذكر الاسم أنه مخصص للنساء.&lt;/p&gt;&lt;p&gt;ما فئة المستحضر؟&lt;/p&gt;&lt;p&gt;هو مانع تعرّق من ارم اند هامر.&lt;/p&gt;&lt;p&gt;ما الحجم المذكور؟&lt;/p&gt;&lt;p&gt;حجم العبوة هو 28 جم.&lt;/p&gt;&lt;p&gt;هل يذكر الاسم رائحة محددة؟&lt;/p&gt;&lt;p&gt;لا، لا تظهر رائحة معينة ضمن الاسم.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -8152,7 +8162,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>MNT-R98</t>
+          <t>MNT-R99</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -8189,7 +8199,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Arm &amp; Hammer مزيل مانع للتعرق الترا ماكس للنساء 28غ</t>
+          <t>ارم اند هامر الترا ماكس مزيل عرق ستيك غير معط</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -8199,12 +8209,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71MkO0H7iSL.jpg</t>
+          <t>https://m.media-amazon.com/images/I/71EE7M3-uvL.jpg</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Arm &amp; Hammer مزيل مانع للتعرق الترا ماكس للنساء 28غ</t>
+          <t>ارم اند هامر الترا ماكس مزيل عرق ستيك غير معط</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -8214,12 +8224,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>مزيل مانع للتعرق ألترا ماكس للنساء من ارم اند هامر، 28 جم — Arm &amp; Hammer Ultra Max Antiperspirant for Women, 28 g؛ مستحضر عناية شخصية موصوف للنساء، من علامة ارم اند هامر، بحجم 28 جم. يجمع الاسم بين فئة المنتج واسم ألترا ماكس والفئة المذكورة والحجم، لتكون معلوماته الأساسية واضحة عند الاختيار.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | مزيل مانع للتعرق ألترا ماكس للنساء من ارم اند هامر&lt;/li&gt;&lt;li&gt;النوع | مانع تعرّق&lt;/li&gt;&lt;li&gt;الحجم | 28 جم&lt;/li&gt;&lt;li&gt;العلامة التجارية | ارم اند هامر&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;هذا المنتج من فئة موانع التعرق، ويحمل اسم ألترا ماكس ويُذكر في تسميته أنه مخصص للنساء. حجم العبوة هو 28 جم، ما يتيح تمييزه من حيث الكمية إلى جانب اسم العلامة التجارية والفئة. ولا يذكر الاسم رائحة أو تفاصيل تركيب أو صيغة استخدام بعينها.&lt;/p&gt;&lt;p&gt;يمكن إدراجه ضمن روتين العناية الشخصية بحسب التعليمات المدونة على العبوة. عند اختيار المنتج، راجعي طريقة استعماله والبيانات المرفقة به، واستخدميه وفق ما توضحه الشركة. يقتصر هذا التعريف على تفاصيل الاسم والنوع والحجم دون إضافة ادعاءات أو مواصفات غير متاحة.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مانع تعرّق من ارم اند هامر.&lt;/li&gt;&lt;li&gt;يحمل اسم ألترا ماكس.&lt;/li&gt;&lt;li&gt;موصوف في الاسم بأنه للنساء.&lt;/li&gt;&lt;li&gt;حجم العبوة 28 جم.&lt;/li&gt;&lt;li&gt;مصنف ضمن مستحضرات العناية الشخصية.&lt;/li&gt;&lt;li&gt;لا يحدد الاسم رائحة معينة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;للنساء الباحثات عن مستحضر من فئة موانع التعرق.&lt;/li&gt;&lt;li&gt;لمن يفضلن اسم ألترا ماكس من ارم اند هامر.&lt;/li&gt;&lt;li&gt;لمن يرغبن في عبوة بحجم 28 جم.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;اتبعي الإرشادات الموضحة على العبوة، وطبقي المنتج بالطريقة المحددة فيها. تحققي من ملاءمة موضع الاستخدام المذكور، ولا تستخدميه على نحو مختلف عن التعليمات المرفقة.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. أبقي المنتج بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;ارم اند هامر هي العلامة التجارية المدونة على هذا المنتج. ويظهر خيار ألترا ماكس للنساء باسم مانع للتعرق وبحجم 28 جم، وفق المعلومات الواردة في التسمية.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;لمن وُصف هذا المنتج؟&lt;/p&gt;&lt;p&gt;يذكر الاسم أنه مخصص للنساء.&lt;/p&gt;&lt;p&gt;ما فئة المستحضر؟&lt;/p&gt;&lt;p&gt;هو مانع تعرّق من ارم اند هامر.&lt;/p&gt;&lt;p&gt;ما الحجم المذكور؟&lt;/p&gt;&lt;p&gt;حجم العبوة هو 28 جم.&lt;/p&gt;&lt;p&gt;هل يذكر الاسم رائحة محددة؟&lt;/p&gt;&lt;p&gt;لا، لا تظهر رائحة معينة ضمن الاسم.&lt;/p&gt;</t>
+          <t>مزيل عرق ستيك ألترا ماكس غير معطر من ارم اند هامر — Arm &amp; Hammer Ultra Max Unscented Deodorant Stick؛ مستحضر للعناية الشخصية بصيغة ستيك، وتوضح التسمية أنه غير معطر. يحمل المنتج اسم ألترا ماكس من علامة ارم اند هامر، ولا يرد حجم للعبوة في الاسم المتاح.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | مزيل عرق ستيك ألترا ماكس غير معطر من ارم اند هامر&lt;/li&gt;&lt;li&gt;النوع | مزيل عرق ستيك&lt;/li&gt;&lt;li&gt;العلامة التجارية | ارم اند هامر&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;يأتي هذا الخيار بصيغة ستيك، ويُعرَف بأنه مزيل عرق غير معطر وفق الوصف الوارد في الاسم. وتظهر علامة ارم اند هامر واسم ألترا ماكس ضمن هويته، ما يساعد على تحديد المنتج عند مقارنته بمزيلات العرق الأخرى. لا يتضمن الاسم حجم العبوة، لذلك لا تُضاف كمية غير مذكورة.&lt;/p&gt;&lt;p&gt;يمكن إدراجه ضمن روتين العناية الشخصية بالطريقة الموضحة على العبوة. ويمنح وصف غير معطر معلومة مباشرة عن الرائحة كما وردت في التسمية، من دون افتراض وجود رائحة أخرى. تحققي من الإرشادات المرفقة لتحديد كيفية التطبيق والموضع المناسب للاستخدام.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مزيل عرق بصيغة ستيك.&lt;/li&gt;&lt;li&gt;يحمل اسم ألترا ماكس من ارم اند هامر.&lt;/li&gt;&lt;li&gt;موصوف بأنه غير معطر.&lt;/li&gt;&lt;li&gt;ينتمي إلى مستحضرات العناية الشخصية.&lt;/li&gt;&lt;li&gt;لا يذكر الاسم حجماً محدداً للعبوة.&lt;/li&gt;&lt;li&gt;تظهر صيغة المنتج ووصف الرائحة في التسمية.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يفضلون مزيل العرق بصيغة ستيك.&lt;/li&gt;&lt;li&gt;لمن يبحثون عن منتج موصوف بأنه غير معطر.&lt;/li&gt;&lt;li&gt;لمن يختارون مستحضرات ألترا ماكس من ارم اند هامر.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;راجعي تعليمات العبوة قبل التطبيق، ثم مرري ستيك مزيل العرق على المنطقة المحددة بالطريقة الواردة فيها. استخدميه وفق الإرشادات وأغلقي الغطاء بعد الانتهاء. لا يرد حجم العبوة في الاسم المتاح.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. يُحفظ بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;ارم اند هامر هي العلامة التجارية المذكورة على هذا المنتج. ويظهر مزيل العرق ضمن اسم ألترا ماكس بصيغة ستيك وبوصف غير معطر، وفق التسمية المتاحة.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما صيغة المنتج؟&lt;/p&gt;&lt;p&gt;هو مزيل عرق بصيغة ستيك.&lt;/p&gt;&lt;p&gt;هل يذكر الاسم رائحة؟&lt;/p&gt;&lt;p&gt;نعم، يصفه بأنه غير معطر.&lt;/p&gt;&lt;p&gt;ما العلامة التجارية؟&lt;/p&gt;&lt;p&gt;العلامة التجارية هي ارم اند هامر.&lt;/p&gt;&lt;p&gt;هل يتوفر حجم محدد في الاسم؟&lt;/p&gt;&lt;p&gt;لا، لا يرد حجم للعبوة في الاسم المتاح.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -8229,7 +8239,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>MNT-R99</t>
+          <t>MNT-R100</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -8253,83 +8263,6 @@
         </is>
       </c>
       <c r="AA95" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>منتج</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>ارم اند هامر الترا ماكس مزيل عرق ستيك غير معط</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>العناية والجمال &gt; العناية الشخصية</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71EE7M3-uvL.jpg</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>ارم اند هامر الترا ماكس مزيل عرق ستيك غير معط</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>منتج جاهز</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>مزيل عرق ستيك ألترا ماكس غير معطر من ارم اند هامر — Arm &amp; Hammer Ultra Max Unscented Deodorant Stick؛ مستحضر للعناية الشخصية بصيغة ستيك، وتوضح التسمية أنه غير معطر. يحمل المنتج اسم ألترا ماكس من علامة ارم اند هامر، ولا يرد حجم للعبوة في الاسم المتاح.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | مزيل عرق ستيك ألترا ماكس غير معطر من ارم اند هامر&lt;/li&gt;&lt;li&gt;النوع | مزيل عرق ستيك&lt;/li&gt;&lt;li&gt;العلامة التجارية | ارم اند هامر&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;يأتي هذا الخيار بصيغة ستيك، ويُعرَف بأنه مزيل عرق غير معطر وفق الوصف الوارد في الاسم. وتظهر علامة ارم اند هامر واسم ألترا ماكس ضمن هويته، ما يساعد على تحديد المنتج عند مقارنته بمزيلات العرق الأخرى. لا يتضمن الاسم حجم العبوة، لذلك لا تُضاف كمية غير مذكورة.&lt;/p&gt;&lt;p&gt;يمكن إدراجه ضمن روتين العناية الشخصية بالطريقة الموضحة على العبوة. ويمنح وصف غير معطر معلومة مباشرة عن الرائحة كما وردت في التسمية، من دون افتراض وجود رائحة أخرى. تحققي من الإرشادات المرفقة لتحديد كيفية التطبيق والموضع المناسب للاستخدام.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مزيل عرق بصيغة ستيك.&lt;/li&gt;&lt;li&gt;يحمل اسم ألترا ماكس من ارم اند هامر.&lt;/li&gt;&lt;li&gt;موصوف بأنه غير معطر.&lt;/li&gt;&lt;li&gt;ينتمي إلى مستحضرات العناية الشخصية.&lt;/li&gt;&lt;li&gt;لا يذكر الاسم حجماً محدداً للعبوة.&lt;/li&gt;&lt;li&gt;تظهر صيغة المنتج ووصف الرائحة في التسمية.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يفضلون مزيل العرق بصيغة ستيك.&lt;/li&gt;&lt;li&gt;لمن يبحثون عن منتج موصوف بأنه غير معطر.&lt;/li&gt;&lt;li&gt;لمن يختارون مستحضرات ألترا ماكس من ارم اند هامر.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;راجعي تعليمات العبوة قبل التطبيق، ثم مرري ستيك مزيل العرق على المنطقة المحددة بالطريقة الواردة فيها. استخدميه وفق الإرشادات وأغلقي الغطاء بعد الانتهاء. لا يرد حجم العبوة في الاسم المتاح.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. يُحفظ بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;ارم اند هامر هي العلامة التجارية المذكورة على هذا المنتج. ويظهر مزيل العرق ضمن اسم ألترا ماكس بصيغة ستيك وبوصف غير معطر، وفق التسمية المتاحة.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما صيغة المنتج؟&lt;/p&gt;&lt;p&gt;هو مزيل عرق بصيغة ستيك.&lt;/p&gt;&lt;p&gt;هل يذكر الاسم رائحة؟&lt;/p&gt;&lt;p&gt;نعم، يصفه بأنه غير معطر.&lt;/p&gt;&lt;p&gt;ما العلامة التجارية؟&lt;/p&gt;&lt;p&gt;العلامة التجارية هي ارم اند هامر.&lt;/p&gt;&lt;p&gt;هل يتوفر حجم محدد في الاسم؟&lt;/p&gt;&lt;p&gt;لا، لا يرد حجم للعبوة في الاسم المتاح.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>MNT-R100</t>
-        </is>
-      </c>
-      <c r="R96" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>Arm &amp; Hammer</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="AA96" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>

--- a/المنتجات/batch1-products-complete.xlsx
+++ b/المنتجات/batch1-products-complete.xlsx
@@ -1274,7 +1274,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/51J9cSiQedL.jpg</t>
+          <t>https://cdn.lifepharmacy.com/products/maybelline-fit-me-concealer-20-sand/118881-1.png</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/61qCrnC0lPL.jpg</t>
+          <t>https://cdn.lifepharmacy.com/products/maybelline-fit-me-concealer-30-cafe/125651-1.png</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/61q4Jm5+xrL.jpg</t>
+          <t>https://www.loreal-paris-me.com/-/media/project/loreal/brand-sites/oap/emea/mena/products/makeup/face-makeup/infaillible/more-than-concealer/products/322-ivory/packshot/oap-makeup-face-infaillible-more-than-concealer-322-ivory-packshot.png</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/612mEWVLkCL.jpg</t>
+          <t>https://www.faces.eg/dw/image/v2/BJSM_PRD/on/demandware.static/-/Sites-faces-master-catalog/default/dw388e7a25/product/30173590_1/30173590_1.jpg?sw=800&amp;sh=800</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/413w-wxhdML.jpg</t>
+          <t>https://www.faces.eg/dw/image/v2/BJSM_PRD/on/demandware.static/-/Sites-faces-master-catalog/default/dw99255bd9/product/30173651_1/30173651_1.jpg?sw=800&amp;sh=800</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -7055,6 +7055,11 @@
       <c r="C80" t="inlineStr">
         <is>
           <t>العناية والجمال &gt; العناية الشخصية</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://ecombe.nahdionline.com/media/catalog/product/1/0/100589334_63bbffcd646319bc6_19139.jpg?width=1050&amp;height=1050&amp;canvas=1050,1050&amp;optimize=high&amp;bg-color=255,255,255&amp;fit=bounds</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">

--- a/المنتجات/batch1-products-complete.xlsx
+++ b/المنتجات/batch1-products-complete.xlsx
@@ -2057,7 +2057,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.maybelline-me.com/-/media/project/loreal/brand-sites/mny/apac/mena/products/eye-makeup/mascara/maybelline-lash-sensational-sky-high-wtp-802-very-black-o.jpg?rev=807776a9a9b2476f8d5f7a8f71051f4a&amp;cx=0.45&amp;cy=0.47&amp;cw=0&amp;ch=0&amp;hash=5F493901247AF12801FDA38D3D712874</t>
+          <t>https://cdn.lifepharmacy.com/products/mayb-lash-sensational-sky-high-mascara/133769-1.jpg?width=1050&amp;height=1050&amp;canvas=1050,1050&amp;optimize=high&amp;bg-color=255,255,255&amp;fit=bounds</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41PyHjlNU2L.jpg</t>
+          <t>https://www.mccabespharmacy.com/cdn/shop/files/30158672_T1.jpg?v=1706614262&amp;width=2000</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.maybelline-me.com/-/media/project/loreal/brand-sites/mny/apac/mena/products/eye-makeup/mascara/maybelline-lash-sensational-sky-high-wtp-802-very-black-o.jpg?rev=807776a9a9b2476f8d5f7a8f71051f4a&amp;cx=0.45&amp;cy=0.47&amp;cw=0&amp;ch=0&amp;hash=5F493901247AF12801FDA38D3D712874</t>
+          <t>https://www.renzoebox.com/cdn/shop/products/2574523_a25b8a51-e7ae-4e70-b285-7f6490682f6c_1200x1200.png?v=1678232842</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71mAl87nvkL.jpg</t>
+          <t>https://public.cosmetify.com/images/products/5132330.webp</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.cerave.com/-/media/project/loreal/brand-sites/cerave/americas/us/product_dec2020/sa-cream/700x700c/sacream700x700.jpg?rev=7eda2163e2ab4f139aa06f7fb14d239b</t>
+          <t>https://cosmetis.com/media/catalog/product/cache/8357f3cfca25f65dc286e017d4e3bdcd/6/3/6323071-cerave_sa_smoothing_cream_340g.jpg</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5365,7 +5365,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/61OSmmAPf9L.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0749/1387/4134/files/3645.jpg?v=1748506255</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/81JnW+0q47L.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0749/1387/4134/files/3227.jpg?v=1748505207</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0749/1387/4134/files/406.jpg?v=1748505763&amp;width=1000&amp;height=1000&amp;crop=center</t>
+          <t>https://sa.palmers.com/cdn/shop/files/hair_food.jpg?v=1780119467&amp;width=1780</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71RKg0cK7ES.jpg</t>
+          <t>https://cdn.beautybay.com/images/eoaaqxyywn6o/CLIQ0500F_1.jpg_s3.lmb_4pija/5eb7dc3dd4906118282d33236053753d/CLIQ0500F_1.jpg?w=1200&amp;fm=jpg&amp;q=90</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/81eXnqEv0dL.jpg</t>
+          <t>https://ecombe.nahdionline.com/media/catalog/product/1/0/102925696_65f774f377ff032f9_32226.png?width=1050&amp;height=1050&amp;canvas=1050,1050&amp;optimize=high&amp;bg-color=255,255,255&amp;fit=bounds</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">

--- a/المنتجات/batch1-products-complete.xlsx
+++ b/المنتجات/batch1-products-complete.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN95"/>
+  <dimension ref="A1:AN92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4990,22 +4990,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>كريم تنعيم البشرة الخشنة باليوريا، 454 جرام</t>
+          <t>St. Ives مرطب الكولاجين والايلاستين المجدد من سانت اي</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>العناية والجمال &gt; العناية بالجسم</t>
+          <t>العناية والجمال &gt; العناية بالبشرة &gt; مرطبات</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://cosmetis.com/media/catalog/product/cache/8357f3cfca25f65dc286e017d4e3bdcd/6/3/6323071-cerave_sa_smoothing_cream_340g.jpg</t>
+          <t>https://m.media-amazon.com/images/I/712llFBWEVL.jpg</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>كريم تنعيم البشرة الخشنة باليوريا، 454 جرام</t>
+          <t>St. Ives مرطب الكولاجين والايلاستين المجدد من سانت اي</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -5015,12 +5015,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>28</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>&lt;p&gt;كريم تنعيم البشرة الخشنة باليوريا | Urea Rough Skin Smoothing Cream | كريم لتنعيم البشرة الخشنة | 454 جرام. يعرّف الاسم المنتج بوصفه كريماً موجهاً للبشرة الخشنة، ويذكر اليوريا ضمن التسمية.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | كريم تنعيم البشرة الخشنة باليوريا&lt;/li&gt;&lt;li&gt;النوع | كريم تنعيم&lt;/li&gt;&lt;li&gt;الحجم | 454 جرام&lt;/li&gt;&lt;li&gt;العلامة التجارية | غير مذكورة&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;صُمم هذا الكريم للعناية بالبشرة الخشنة، ويأتي اسمه واضحاً في تحديد غرضه: تنعيم البشرة. وتبرز اليوريا في التسمية بوصفها العنصر المعرّف للمنتج، من دون أن تتضمن البيانات المتاحة تفاصيل أخرى عن التركيبة أو طريقة عملها.&lt;/p&gt;&lt;p&gt;يأتي المنتج بوزن 454 جراماً، وتناسب هذه العبوة من يبحث عن كريم ضمن فئة العناية بالجسم. وللحصول على المعلومات الدقيقة بشأن طريقة التطبيق أو تكراره، يُرجى اتباع التعليمات المطبوعة على العبوة.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;كريم مخصص للعناية بالبشرة الخشنة وفقاً للاسم.&lt;/li&gt;&lt;li&gt;يذكر اليوريا ضمن تعريف المنتج.&lt;/li&gt;&lt;li&gt;يوضح اسم المنتج الغرض المقصود، وهو تنعيم البشرة.&lt;/li&gt;&lt;li&gt;يأتي بوزن 454 جراماً.&lt;/li&gt;&lt;li&gt;يندرج ضمن منتجات العناية بالجسم.&lt;/li&gt;&lt;li&gt;تسمية مباشرة تساعد على تمييز نوع المنتج ووظيفته.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن كريم للبشرة الخشنة.&lt;/li&gt;&lt;li&gt;لمن يفضل اختيار منتج يذكر اليوريا في اسمه.&lt;/li&gt;&lt;li&gt;لمن يرغب في كريم تنعيم ضمن روتين العناية بالجسم.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;يُستخدم على المنطقة المستهدفة وفق طريقة الاستعمال الموضحة على العبوة. تُتبع إرشادات المنتج بشأن الكمية وتكرار الاستخدام، إذ لا تحدد بيانات الاسم المتاحة هذه التفاصيل.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط. تجنب ملامسة العينين، وأبعد المنتج عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;لا تذكر بيانات المنتج المتاحة علامة تجارية محددة. لذلك يقتصر التعريف هنا على وصفه كما ورد: كريم تنعيم للبشرة الخشنة باليوريا. لا تُنسب إليه علامة أو معلومات إضافية غير ظاهرة في الاسم.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما الغرض الموضح لهذا الكريم؟&lt;/p&gt;&lt;p&gt;يذكر الاسم أنه كريم لتنعيم البشرة الخشنة.&lt;/p&gt;&lt;p&gt;ما العنصر المذكور في اسم المنتج؟&lt;/p&gt;&lt;p&gt;اليوريا، وفق التسمية المتاحة للمنتج.&lt;/p&gt;&lt;p&gt;ما وزن العبوة؟&lt;/p&gt;&lt;p&gt;وزنها 454 جراماً.&lt;/p&gt;&lt;p&gt;كيف يُستخدم؟&lt;/p&gt;&lt;p&gt;تُتبع طريقة الاستخدام المدونة على العبوة؛ فالاسم المتاح لا يحدد الكمية أو وتيرة التطبيق.&lt;/p&gt;</t>
+          <t>&lt;p&gt;مرطب الكولاجين والإيلاستين المجدد | Renewing Collagen Elastin Moisturizer | St. Ives | مرطب. يجمع اسم المنتج بين وصف المرطب وعبارة التجديد، ويذكر الكولاجين والإيلاستين ضمن التسمية.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | مرطب الكولاجين والإيلاستين المجدد&lt;/li&gt;&lt;li&gt;النوع | مرطب&lt;/li&gt;&lt;li&gt;العلامة التجارية | St. Ives&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;مرطب من St. Ives يحمل اسماً يعرّفه بالكولاجين والإيلاستين، مع وصف المجدد الوارد في التسمية. ويقدّم الاسم صورة مباشرة عن فئة المنتج، من دون تحديد حجم العبوة أو درجة لونية أو موضع استخدام بعينه في البيانات المتاحة.&lt;/p&gt;&lt;p&gt;يمكن إدراجه ضمن روتين العناية بالبشرة بوصفه مرطباً، مع الرجوع إلى العبوة لمعرفة تفاصيل الاستعمال والملاءمة. وتبقى المعلومات المؤكدة هنا هي اسم العلامة، ونوع المنتج، والعناصر المذكورة في اسمه، لا تفاصيل إضافية عن تركيبته أو خصائصه.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مرطب يحمل اسم St. Ives.&lt;/li&gt;&lt;li&gt;يذكر الكولاجين والإيلاستين في تسمية المنتج.&lt;/li&gt;&lt;li&gt;تتضمن التسمية وصف المجدد.&lt;/li&gt;&lt;li&gt;يندرج ضمن فئة مرطبات العناية بالبشرة.&lt;/li&gt;&lt;li&gt;اسم واضح يسهل تمييزه عند ترتيب منتجات العناية.&lt;/li&gt;&lt;li&gt;لا يحدد الاسم حجماً أو درجة لونية.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن مرطب للعناية بالبشرة.&lt;/li&gt;&lt;li&gt;لمن يفضل منتجاً يذكر الكولاجين والإيلاستين في اسمه.&lt;/li&gt;&lt;li&gt;لمن يرغب في إضافة مرطب إلى روتين العناية، وفق إرشادات العبوة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;يُستخدم وفق التعليمات الموضحة على العبوة. لا تتضمن التسمية المتاحة كمية محددة أو عدد مرات التطبيق أو موضعاً دقيقاً للاستخدام، لذا يُرجع إلى بيانات المنتج المطبوعة.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط. يُرجى تجنب ملامسة العينين، وحفظ المنتج بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;يحمل المنتج اسم St. Ives كما ورد في بياناته. وتُعرّف هذه الصفحة العلامة من خلال المنتج المسمى بمرطب الكولاجين والإيلاستين المجدد، دون إضافة معلومات غير مذكورة عن العلامة أو المنتج.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع المنتج؟&lt;/p&gt;&lt;p&gt;هو مرطب، بحسب الاسم الوارد في بيانات المنتج.&lt;/p&gt;&lt;p&gt;ما العنصران المذكوران في التسمية؟&lt;/p&gt;&lt;p&gt;الكولاجين والإيلاستين.&lt;/p&gt;&lt;p&gt;هل يتضمن الاسم حجماً للعبوة؟&lt;/p&gt;&lt;p&gt;لا يظهر حجم محدد في الاسم المتاح.&lt;/p&gt;&lt;p&gt;أين أجد طريقة الاستخدام؟&lt;/p&gt;&lt;p&gt;تُراجع العبوة للتعرف إلى تعليمات الاستخدام والكمية المناسبة.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>MNT-R51</t>
+          <t>MNT-R52</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -5062,22 +5062,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>St. Ives مرطب الكولاجين والايلاستين المجدد من سانت اي</t>
+          <t>فورميولا ليب بالم يرطب الشفاه الجافة 15</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>العناية والجمال &gt; العناية بالبشرة &gt; مرطبات</t>
+          <t>العناية والجمال &gt; الشفاه &gt; مرطب الشفاه</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/712llFBWEVL.jpg</t>
+          <t>https://m.media-amazon.com/images/I/71HBiZqEApL.jpg</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>St. Ives مرطب الكولاجين والايلاستين المجدد من سانت اي</t>
+          <t>فورميولا ليب بالم يرطب الشفاه الجافة 15</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>&lt;p&gt;مرطب الكولاجين والإيلاستين المجدد | Renewing Collagen Elastin Moisturizer | St. Ives | مرطب. يجمع اسم المنتج بين وصف المرطب وعبارة التجديد، ويذكر الكولاجين والإيلاستين ضمن التسمية.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | مرطب الكولاجين والإيلاستين المجدد&lt;/li&gt;&lt;li&gt;النوع | مرطب&lt;/li&gt;&lt;li&gt;العلامة التجارية | St. Ives&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;مرطب من St. Ives يحمل اسماً يعرّفه بالكولاجين والإيلاستين، مع وصف المجدد الوارد في التسمية. ويقدّم الاسم صورة مباشرة عن فئة المنتج، من دون تحديد حجم العبوة أو درجة لونية أو موضع استخدام بعينه في البيانات المتاحة.&lt;/p&gt;&lt;p&gt;يمكن إدراجه ضمن روتين العناية بالبشرة بوصفه مرطباً، مع الرجوع إلى العبوة لمعرفة تفاصيل الاستعمال والملاءمة. وتبقى المعلومات المؤكدة هنا هي اسم العلامة، ونوع المنتج، والعناصر المذكورة في اسمه، لا تفاصيل إضافية عن تركيبته أو خصائصه.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مرطب يحمل اسم St. Ives.&lt;/li&gt;&lt;li&gt;يذكر الكولاجين والإيلاستين في تسمية المنتج.&lt;/li&gt;&lt;li&gt;تتضمن التسمية وصف المجدد.&lt;/li&gt;&lt;li&gt;يندرج ضمن فئة مرطبات العناية بالبشرة.&lt;/li&gt;&lt;li&gt;اسم واضح يسهل تمييزه عند ترتيب منتجات العناية.&lt;/li&gt;&lt;li&gt;لا يحدد الاسم حجماً أو درجة لونية.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن مرطب للعناية بالبشرة.&lt;/li&gt;&lt;li&gt;لمن يفضل منتجاً يذكر الكولاجين والإيلاستين في اسمه.&lt;/li&gt;&lt;li&gt;لمن يرغب في إضافة مرطب إلى روتين العناية، وفق إرشادات العبوة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;يُستخدم وفق التعليمات الموضحة على العبوة. لا تتضمن التسمية المتاحة كمية محددة أو عدد مرات التطبيق أو موضعاً دقيقاً للاستخدام، لذا يُرجع إلى بيانات المنتج المطبوعة.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط. يُرجى تجنب ملامسة العينين، وحفظ المنتج بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;يحمل المنتج اسم St. Ives كما ورد في بياناته. وتُعرّف هذه الصفحة العلامة من خلال المنتج المسمى بمرطب الكولاجين والإيلاستين المجدد، دون إضافة معلومات غير مذكورة عن العلامة أو المنتج.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع المنتج؟&lt;/p&gt;&lt;p&gt;هو مرطب، بحسب الاسم الوارد في بيانات المنتج.&lt;/p&gt;&lt;p&gt;ما العنصران المذكوران في التسمية؟&lt;/p&gt;&lt;p&gt;الكولاجين والإيلاستين.&lt;/p&gt;&lt;p&gt;هل يتضمن الاسم حجماً للعبوة؟&lt;/p&gt;&lt;p&gt;لا يظهر حجم محدد في الاسم المتاح.&lt;/p&gt;&lt;p&gt;أين أجد طريقة الاستخدام؟&lt;/p&gt;&lt;p&gt;تُراجع العبوة للتعرف إلى تعليمات الاستخدام والكمية المناسبة.&lt;/p&gt;</t>
+          <t>&lt;p&gt;ليب بالم فورميولا لترطيب الشفاه الجافة | Formula Lip Balm for Dry Lips 15 | Formula | مرطب شفاه. يعرّف الاسم المنتج بأنه بلسم للشفاه الجافة، ويتضمن الرقم 15 من دون وحدة قياس ظاهرة.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | ليب بالم فورميولا لترطيب الشفاه الجافة 15&lt;/li&gt;&lt;li&gt;النوع | مرطب شفاه&lt;/li&gt;&lt;li&gt;العلامة التجارية | Formula&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;بلسم شفاه من Formula، يوضح اسمه أنه موجه لترطيب الشفاه الجافة. وتناسب تسميته من يبحث عن منتج مخصص للعناية بالشفاه، مع الانتباه إلى أن البيانات المتاحة لا تعرض تفاصيل إضافية عن مكوناته أو قوامه.&lt;/p&gt;&lt;p&gt;يرد الرقم 15 في الاسم، لكن من دون وحدة قياس؛ لذلك لا يمكن اعتباره حجماً محدداً. أما طريقة الاستعمال والكمية أو عدد مرات التطبيق، فتُعرف من التعليمات المطبوعة على العبوة، لا من الاسم وحده.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;بلسم شفاه من علامة Formula.&lt;/li&gt;&lt;li&gt;يوضح الاسم أنه مخصص للشفاه الجافة.&lt;/li&gt;&lt;li&gt;يُصنف ضمن منتجات العناية الشخصية.&lt;/li&gt;&lt;li&gt;اسم مباشر يحدد نوع المنتج ومنطقة استخدامه.&lt;/li&gt;&lt;li&gt;يتضمن الاسم الرقم 15 دون بيان وحدة قياس.&lt;/li&gt;&lt;li&gt;لا تُنسب إليه تفاصيل تركيبة غير مذكورة في بيانات المنتج.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن بلسم مخصص للشفاه الجافة.&lt;/li&gt;&lt;li&gt;لمن يفضل منتجاً للعناية بالشفاه ضمن الاستخدام اليومي.&lt;/li&gt;&lt;li&gt;لمن يريد تمييز المنتج بحسب اسمه وعلامته التجارية.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;يُطبق على الشفاه وفق الإرشادات الواردة على العبوة. لا تحدد البيانات المتاحة عدد مرات الاستخدام أو الكمية، كما لا توضح وحدة قياس الرقم 15 الوارد في الاسم.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط. تجنب ملامسة العينين، واحفظ المنتج بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;تظهر علامة Formula في اسم هذا البلسم، وتُذكر هنا كما وردت في بيانات المنتج. ويقتصر التعريف على ارتباط العلامة ببلسم الشفاه المخصص للشفاه الجافة، دون إضافة معلومات أخرى غير متاحة.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع هذا المنتج؟&lt;/p&gt;&lt;p&gt;هو بلسم شفاه، وفقاً للاسم الوارد.&lt;/p&gt;&lt;p&gt;لأي غرض يقدمه الاسم؟&lt;/p&gt;&lt;p&gt;يذكر الاسم أنه مخصص لترطيب الشفاه الجافة.&lt;/p&gt;&lt;p&gt;هل الرقم 15 هو حجم العبوة؟&lt;/p&gt;&lt;p&gt;لا تتضمن البيانات وحدة قياس بجانب الرقم، لذلك لا يمكن تحديده كحجم.&lt;/p&gt;&lt;p&gt;كيف تُعرف طريقة الاستعمال؟&lt;/p&gt;&lt;p&gt;تُراجع تعليمات الاستخدام المطبوعة على العبوة.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>MNT-R52</t>
+          <t>MNT-R53</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5134,22 +5134,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>فورميولا ليب بالم يرطب الشفاه الجافة 15</t>
+          <t>كريم تصفيف الشعر بزيت الزيتون من بالمرز 150 ج</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>العناية والجمال &gt; الشفاه &gt; مرطب الشفاه</t>
+          <t>العناية والجمال &gt; العناية بالشعر</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71HBiZqEApL.jpg</t>
+          <t>https://m.media-amazon.com/images/I/715HCv1yuNL.jpg</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>فورميولا ليب بالم يرطب الشفاه الجافة 15</t>
+          <t>كريم تصفيف الشعر بزيت الزيتون من بالمرز 150 ج</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -5159,12 +5159,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>25</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>&lt;p&gt;ليب بالم فورميولا لترطيب الشفاه الجافة | Formula Lip Balm for Dry Lips 15 | Formula | مرطب شفاه. يعرّف الاسم المنتج بأنه بلسم للشفاه الجافة، ويتضمن الرقم 15 من دون وحدة قياس ظاهرة.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | ليب بالم فورميولا لترطيب الشفاه الجافة 15&lt;/li&gt;&lt;li&gt;النوع | مرطب شفاه&lt;/li&gt;&lt;li&gt;العلامة التجارية | Formula&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;بلسم شفاه من Formula، يوضح اسمه أنه موجه لترطيب الشفاه الجافة. وتناسب تسميته من يبحث عن منتج مخصص للعناية بالشفاه، مع الانتباه إلى أن البيانات المتاحة لا تعرض تفاصيل إضافية عن مكوناته أو قوامه.&lt;/p&gt;&lt;p&gt;يرد الرقم 15 في الاسم، لكن من دون وحدة قياس؛ لذلك لا يمكن اعتباره حجماً محدداً. أما طريقة الاستعمال والكمية أو عدد مرات التطبيق، فتُعرف من التعليمات المطبوعة على العبوة، لا من الاسم وحده.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;بلسم شفاه من علامة Formula.&lt;/li&gt;&lt;li&gt;يوضح الاسم أنه مخصص للشفاه الجافة.&lt;/li&gt;&lt;li&gt;يُصنف ضمن منتجات العناية الشخصية.&lt;/li&gt;&lt;li&gt;اسم مباشر يحدد نوع المنتج ومنطقة استخدامه.&lt;/li&gt;&lt;li&gt;يتضمن الاسم الرقم 15 دون بيان وحدة قياس.&lt;/li&gt;&lt;li&gt;لا تُنسب إليه تفاصيل تركيبة غير مذكورة في بيانات المنتج.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن بلسم مخصص للشفاه الجافة.&lt;/li&gt;&lt;li&gt;لمن يفضل منتجاً للعناية بالشفاه ضمن الاستخدام اليومي.&lt;/li&gt;&lt;li&gt;لمن يريد تمييز المنتج بحسب اسمه وعلامته التجارية.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;يُطبق على الشفاه وفق الإرشادات الواردة على العبوة. لا تحدد البيانات المتاحة عدد مرات الاستخدام أو الكمية، كما لا توضح وحدة قياس الرقم 15 الوارد في الاسم.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط. تجنب ملامسة العينين، واحفظ المنتج بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;تظهر علامة Formula في اسم هذا البلسم، وتُذكر هنا كما وردت في بيانات المنتج. ويقتصر التعريف على ارتباط العلامة ببلسم الشفاه المخصص للشفاه الجافة، دون إضافة معلومات أخرى غير متاحة.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع هذا المنتج؟&lt;/p&gt;&lt;p&gt;هو بلسم شفاه، وفقاً للاسم الوارد.&lt;/p&gt;&lt;p&gt;لأي غرض يقدمه الاسم؟&lt;/p&gt;&lt;p&gt;يذكر الاسم أنه مخصص لترطيب الشفاه الجافة.&lt;/p&gt;&lt;p&gt;هل الرقم 15 هو حجم العبوة؟&lt;/p&gt;&lt;p&gt;لا تتضمن البيانات وحدة قياس بجانب الرقم، لذلك لا يمكن تحديده كحجم.&lt;/p&gt;&lt;p&gt;كيف تُعرف طريقة الاستعمال؟&lt;/p&gt;&lt;p&gt;تُراجع تعليمات الاستخدام المطبوعة على العبوة.&lt;/p&gt;</t>
+          <t>&lt;p&gt;كريم تصفيف الشعر بزيت الزيتون من بالمرز | Palmer's Olive Oil Hair Styling Cream | Palmer's | كريم تصفيف الشعر | 150 جرام. يحدد اسم المنتج نوعه بوصفه كريم تصفيف، ويذكر زيت الزيتون وحجم العبوة.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | كريم تصفيف الشعر بزيت الزيتون من بالمرز&lt;/li&gt;&lt;li&gt;النوع | كريم تصفيف الشعر&lt;/li&gt;&lt;li&gt;الحجم | 150 جرام&lt;/li&gt;&lt;li&gt;العلامة التجارية | Palmer's&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;كريم تصفيف للشعر من Palmer's، يذكر زيت الزيتون في اسمه ويأتي بوزن 150 جراماً. يوضح الاسم وظيفة المنتج بوصفه مخصصاً للتصفيف، ما يجعله خياراً ضمن منتجات العناية بالشعر لمن يبحث عن كريم يحمل هذه التسمية.&lt;/p&gt;&lt;p&gt;لا تتضمن البيانات المتاحة تفاصيل عن درجة التثبيت أو نوع الشعر أو ملمس المنتج، لذلك لا تُنسب إليه خصائص إضافية. وللتعرف إلى أسلوب التطبيق والكمية المناسبة، تُراجع التعليمات الموجودة على العبوة.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;كريم مخصص لتصفيف الشعر وفق الاسم.&lt;/li&gt;&lt;li&gt;يحمل علامة Palmer's.&lt;/li&gt;&lt;li&gt;يذكر زيت الزيتون ضمن التسمية.&lt;/li&gt;&lt;li&gt;يأتي بوزن 150 جراماً.&lt;/li&gt;&lt;li&gt;يندرج ضمن منتجات العناية بالشعر.&lt;/li&gt;&lt;li&gt;لا يحدد الاسم نوع الشعر أو درجة التثبيت.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن كريم لتصفيف الشعر.&lt;/li&gt;&lt;li&gt;لمن يفضل منتجاً يذكر زيت الزيتون في اسمه.&lt;/li&gt;&lt;li&gt;لمن يرغب في إضافة كريم تصفيف من Palmer's إلى روتين العناية بالشعر.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;يُستخدم لتصفيف الشعر بحسب الإرشادات المدونة على العبوة. لا تحدد البيانات المتاحة كمية المنتج أو طريقة توزيعه، لذا تُتبع التعليمات المرفقة لتفاصيل التطبيق.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط. تجنب ملامسة العينين، واحفظ المنتج بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;يرتبط هذا المنتج بعلامة Palmer's كما يظهر في اسمه. وتقتصر المعلومات الواردة هنا على تعريف العلامة المذكورة مع كريم تصفيف الشعر بزيت الزيتون، دون إضافة تفاصيل غير معروضة عن العلامة أو المنتج.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما وظيفة الكريم بحسب اسمه؟&lt;/p&gt;&lt;p&gt;هو كريم لتصفيف الشعر.&lt;/p&gt;&lt;p&gt;ما العنصر المذكور في التسمية؟&lt;/p&gt;&lt;p&gt;زيت الزيتون.&lt;/p&gt;&lt;p&gt;ما وزن العبوة؟&lt;/p&gt;&lt;p&gt;وزنها 150 جراماً.&lt;/p&gt;&lt;p&gt;هل يوضح الاسم نوع الشعر المناسب أو درجة التثبيت؟&lt;/p&gt;&lt;p&gt;لا يذكر الاسم هذه التفاصيل؛ تُراجع بيانات العبوة لأي معلومات إضافية.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>MNT-R53</t>
+          <t>MNT-R58</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5185,6 +5185,11 @@
       <c r="S55" t="inlineStr">
         <is>
           <t>g</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Palmer's</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5206,17 +5211,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Palmer's كريم باللمرز بجوز الهند 150 مل</t>
+          <t>بالمرز مرطب الشفاه بخلاصة جوز الهند 4 جرام</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>العناية والجمال &gt; العناية بالجسم</t>
+          <t>العناية والجمال &gt; الشفاه &gt; مرطب الشفاه</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0749/1387/4134/files/3645.jpg?v=1748506255</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Palmer's كريم باللمرز بجوز الهند 150 مل</t>
+          <t>بالمرز مرطب الشفاه بخلاصة جوز الهند 4 جرام</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5226,12 +5236,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>&lt;p&gt;كريم بالمرز بجوز الهند | Palmer's Coconut Cream | Palmer's | كريم | 150 مل. يجمع اسم المنتج بين علامة Palmer's، ووصف الكريم، وذكر جوز الهند، كما يحدد حجم العبوة.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | كريم بالمرز بجوز الهند&lt;/li&gt;&lt;li&gt;النوع | كريم&lt;/li&gt;&lt;li&gt;الحجم | 150 مل&lt;/li&gt;&lt;li&gt;العلامة التجارية | Palmer's&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;كريم من Palmer's يرد جوز الهند في اسمه، ويأتي بحجم 150 مل. يتيح الاسم التعرف إلى العلامة التجارية ونوع المنتج والعنصر المسمى، من دون تحديد خصائص إضافية أو تفاصيل عن الرائحة أو القوام أو التركيبة.&lt;/p&gt;&lt;p&gt;يمكن إدراجه ضمن منتجات العناية بالجسم، مع الرجوع إلى العبوة لمعرفة موضع الاستخدام المحدد وطريقته. وتظل البيانات الواردة في الاسم هي المرجع المتاح لوصف هذا الكريم، فلا تُضاف إليه استخدامات أو مزايا أخرى غير مذكورة.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;كريم يحمل علامة Palmer's.&lt;/li&gt;&lt;li&gt;يذكر جوز الهند في اسم المنتج.&lt;/li&gt;&lt;li&gt;يأتي بحجم 150 مل.&lt;/li&gt;&lt;li&gt;يندرج ضمن فئة العناية بالجسم.&lt;/li&gt;&lt;li&gt;تسمية واضحة تجمع العلامة ونوع المنتج.&lt;/li&gt;&lt;li&gt;لا يتضمن الاسم درجة لونية أو معلومات عن الرائحة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن كريم من Palmer's يذكر جوز الهند في اسمه.&lt;/li&gt;&lt;li&gt;لمن يفضل منتجات العناية بالجسم بصيغة الكريم.&lt;/li&gt;&lt;li&gt;لمن يرغب في عبوة محددة الحجم قدرها 150 مل.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;يُستخدم وفق الإرشادات الموضحة على العبوة، مع الرجوع إليها لتحديد موضع التطبيق والكمية وتكرار الاستخدام. لا تقدم التسمية المتاحة تفاصيل محددة عن هذه الخطوات.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط. يُرجى تجنب ملامسة العينين وإبقاء المنتج بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;يحمل الكريم اسم Palmer's، وهي العلامة الواردة في بيانات المنتج. ويعرّف الاسم المنتج بأنه كريم بجوز الهند، من دون أن يقدم معلومات أخرى عن خطه أو تفاصيل تصنيعه.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع المنتج؟&lt;/p&gt;&lt;p&gt;هو كريم من Palmer's.&lt;/p&gt;&lt;p&gt;ما العنصر المذكور في اسمه؟&lt;/p&gt;&lt;p&gt;جوز الهند، وفق الاسم المتاح.&lt;/p&gt;&lt;p&gt;ما حجم العبوة؟&lt;/p&gt;&lt;p&gt;حجمها 150 مل.&lt;/p&gt;&lt;p&gt;هل يوضح الاسم طريقة الاستخدام؟&lt;/p&gt;&lt;p&gt;لا، لذلك يُرجع إلى التعليمات المطبوعة على العبوة لمعرفة تفاصيل التطبيق.&lt;/p&gt;</t>
+          <t>&lt;p&gt;مرطب الشفاه بالمرز بخلاصة جوز الهند | Palmer's Coconut Extract Lip Balm | Palmer's | مرطب شفاه | 4 جرام. يحدد الاسم نوع المنتج، ويذكر خلاصة جوز الهند ووزن العبوة.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | مرطب الشفاه بالمرز بخلاصة جوز الهند&lt;/li&gt;&lt;li&gt;النوع | مرطب شفاه&lt;/li&gt;&lt;li&gt;الحجم | 4 جرام&lt;/li&gt;&lt;li&gt;العلامة التجارية | Palmer's&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;مرطب شفاه من Palmer's يذكر خلاصة جوز الهند في اسمه، ويأتي بوزن 4 جرام. وتوضح التسمية بجلاء أن المنتج مخصص للعناية بالشفاه، ضمن عبوة محددة الحجم يسهل التعرف إلى بياناتها الأساسية.&lt;/p&gt;&lt;p&gt;لا تتضمن المعلومات المتاحة وصفاً إضافياً للتركيبة أو الرائحة أو القوام، كما لا تحدد عدد مرات الاستخدام. لذلك يُكتفى بالبيانات المعلنة في الاسم، وتُراجع العبوة لمعرفة تفاصيل التطبيق وأي تعليمات مصاحبة.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مرطب شفاه يحمل علامة Palmer's.&lt;/li&gt;&lt;li&gt;يذكر خلاصة جوز الهند ضمن اسمه.&lt;/li&gt;&lt;li&gt;يأتي بوزن 4 جرام.&lt;/li&gt;&lt;li&gt;مخصص للعناية بالشفاه بحسب تسمية المنتج.&lt;/li&gt;&lt;li&gt;يندرج ضمن فئة العناية الشخصية.&lt;/li&gt;&lt;li&gt;اسم المنتج يوضح نوعه والعنصر المذكور فيه.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن مرطب شفاه من Palmer's.&lt;/li&gt;&lt;li&gt;لمن يفضل منتجاً يذكر خلاصة جوز الهند في اسمه.&lt;/li&gt;&lt;li&gt;لمن يرغب في عبوة مرطب شفاه بوزن 4 جرام.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;يُطبق على الشفاه وفق الإرشادات الواردة على العبوة. لا تحدد بيانات الاسم عدد مرات الاستخدام أو كمية التطبيق، لذا يُرجع إلى التعليمات المرفقة بالمنتج.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط. يُرجى تجنب ملامسة العينين وإبقاء المنتج بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;يحمل مرطب الشفاه اسم Palmer's، كما ورد في معلومات المنتج. ويجمع الاسم بين العلامة التجارية ونوع المنتج وخلاصة جوز الهند المذكورة، دون تقديم تفاصيل أخرى عن العلامة أو تركيبة البلسم.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع هذا المنتج؟&lt;/p&gt;&lt;p&gt;هو مرطب شفاه من Palmer's.&lt;/p&gt;&lt;p&gt;ما الذي يذكره الاسم عن المنتج؟&lt;/p&gt;&lt;p&gt;يذكر خلاصة جوز الهند.&lt;/p&gt;&lt;p&gt;ما وزن العبوة؟&lt;/p&gt;&lt;p&gt;وزنها 4 جرام.&lt;/p&gt;&lt;p&gt;هل يوضح الاسم عدد مرات الاستخدام؟&lt;/p&gt;&lt;p&gt;لا، وتُراجع العبوة لمعرفة تعليمات التطبيق.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5241,7 +5251,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>MNT-R55</t>
+          <t>MNT-R59</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5278,22 +5288,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>كريم تصفيف الشعر بزيت الزيتون من بالمرز 150 ج</t>
+          <t>بالمرز كريم زبدة الكاكاو 100 جم</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>العناية والجمال &gt; العناية بالشعر</t>
+          <t>العناية والجمال &gt; العناية بالجسم</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/715HCv1yuNL.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0749/1387/4134/files/4350_Front.png?v=1754427362</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>كريم تصفيف الشعر بزيت الزيتون من بالمرز 150 ج</t>
+          <t>بالمرز كريم زبدة الكاكاو 100 جم</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -5303,12 +5313,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>&lt;p&gt;كريم تصفيف الشعر بزيت الزيتون من بالمرز | Palmer's Olive Oil Hair Styling Cream | Palmer's | كريم تصفيف الشعر | 150 جرام. يحدد اسم المنتج نوعه بوصفه كريم تصفيف، ويذكر زيت الزيتون وحجم العبوة.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | كريم تصفيف الشعر بزيت الزيتون من بالمرز&lt;/li&gt;&lt;li&gt;النوع | كريم تصفيف الشعر&lt;/li&gt;&lt;li&gt;الحجم | 150 جرام&lt;/li&gt;&lt;li&gt;العلامة التجارية | Palmer's&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;كريم تصفيف للشعر من Palmer's، يذكر زيت الزيتون في اسمه ويأتي بوزن 150 جراماً. يوضح الاسم وظيفة المنتج بوصفه مخصصاً للتصفيف، ما يجعله خياراً ضمن منتجات العناية بالشعر لمن يبحث عن كريم يحمل هذه التسمية.&lt;/p&gt;&lt;p&gt;لا تتضمن البيانات المتاحة تفاصيل عن درجة التثبيت أو نوع الشعر أو ملمس المنتج، لذلك لا تُنسب إليه خصائص إضافية. وللتعرف إلى أسلوب التطبيق والكمية المناسبة، تُراجع التعليمات الموجودة على العبوة.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;كريم مخصص لتصفيف الشعر وفق الاسم.&lt;/li&gt;&lt;li&gt;يحمل علامة Palmer's.&lt;/li&gt;&lt;li&gt;يذكر زيت الزيتون ضمن التسمية.&lt;/li&gt;&lt;li&gt;يأتي بوزن 150 جراماً.&lt;/li&gt;&lt;li&gt;يندرج ضمن منتجات العناية بالشعر.&lt;/li&gt;&lt;li&gt;لا يحدد الاسم نوع الشعر أو درجة التثبيت.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن كريم لتصفيف الشعر.&lt;/li&gt;&lt;li&gt;لمن يفضل منتجاً يذكر زيت الزيتون في اسمه.&lt;/li&gt;&lt;li&gt;لمن يرغب في إضافة كريم تصفيف من Palmer's إلى روتين العناية بالشعر.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;يُستخدم لتصفيف الشعر بحسب الإرشادات المدونة على العبوة. لا تحدد البيانات المتاحة كمية المنتج أو طريقة توزيعه، لذا تُتبع التعليمات المرفقة لتفاصيل التطبيق.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط. تجنب ملامسة العينين، واحفظ المنتج بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;يرتبط هذا المنتج بعلامة Palmer's كما يظهر في اسمه. وتقتصر المعلومات الواردة هنا على تعريف العلامة المذكورة مع كريم تصفيف الشعر بزيت الزيتون، دون إضافة تفاصيل غير معروضة عن العلامة أو المنتج.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما وظيفة الكريم بحسب اسمه؟&lt;/p&gt;&lt;p&gt;هو كريم لتصفيف الشعر.&lt;/p&gt;&lt;p&gt;ما العنصر المذكور في التسمية؟&lt;/p&gt;&lt;p&gt;زيت الزيتون.&lt;/p&gt;&lt;p&gt;ما وزن العبوة؟&lt;/p&gt;&lt;p&gt;وزنها 150 جراماً.&lt;/p&gt;&lt;p&gt;هل يوضح الاسم نوع الشعر المناسب أو درجة التثبيت؟&lt;/p&gt;&lt;p&gt;لا يذكر الاسم هذه التفاصيل؛ تُراجع بيانات العبوة لأي معلومات إضافية.&lt;/p&gt;</t>
+          <t>&lt;p&gt;كريم بالمرز بزبدة الكاكاو | Palmer's Cocoa Butter Cream | Palmer's | كريم | 100 جرام. يذكر اسم المنتج زبدة الكاكاو، ويحدد نوعه وحجم العبوة.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | كريم بالمرز بزبدة الكاكاو&lt;/li&gt;&lt;li&gt;النوع | كريم&lt;/li&gt;&lt;li&gt;الحجم | 100 جرام&lt;/li&gt;&lt;li&gt;العلامة التجارية | Palmer's&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;كريم من Palmer's يحمل زبدة الكاكاو في اسمه، ويأتي بوزن 100 جرام. ويتيح الاسم التعرف إلى العلامة التجارية ونوع المنتج والعنصر المذكور، كما يندرج المنتج ضمن فئة العناية بالجسم.&lt;/p&gt;&lt;p&gt;لا تعرض البيانات المتاحة تفاصيل إضافية عن تركيبة الكريم أو قوامه أو طريقة استخدامه. لذلك يُقدَّم المنتج وفق المعلومات الواردة في اسمه، مع الرجوع إلى العبوة للتعرف إلى موضع التطبيق والتعليمات وأي تفاصيل أخرى.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;كريم يحمل علامة Palmer's.&lt;/li&gt;&lt;li&gt;يذكر زبدة الكاكاو في اسم المنتج.&lt;/li&gt;&lt;li&gt;يأتي بوزن 100 جرام.&lt;/li&gt;&lt;li&gt;يندرج ضمن منتجات العناية بالجسم.&lt;/li&gt;&lt;li&gt;يسهل التعرف إلى نوعه من التسمية المباشرة.&lt;/li&gt;&lt;li&gt;لا يحدد الاسم درجة لونية أو رائحة للمنتج.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن كريم من Palmer's يذكر زبدة الكاكاو.&lt;/li&gt;&lt;li&gt;لمن يفضل منتجات العناية بالجسم بصيغة الكريم.&lt;/li&gt;&lt;li&gt;لمن يرغب في عبوة بوزن 100 جرام.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;يُستخدم وفق التعليمات الموجودة على العبوة. لا تحدد المعلومات المتاحة موضع الاستخدام أو الكمية أو وتيرة التطبيق، لذا تُعتمد الإرشادات المطبوعة على المنتج.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط. تجنب ملامسة العينين، واحفظ العبوة بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;تظهر علامة Palmer's على اسم الكريم ضمن البيانات المتاحة. ويُعرّف المنتج هنا بوصفه كريم زبدة الكاكاو من هذه العلامة، دون إضافة معلومات غير مذكورة عن تاريخها أو خطوط منتجاتها.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع المنتج؟&lt;/p&gt;&lt;p&gt;هو كريم من Palmer's.&lt;/p&gt;&lt;p&gt;ما العنصر المذكور في الاسم؟&lt;/p&gt;&lt;p&gt;زبدة الكاكاو.&lt;/p&gt;&lt;p&gt;ما وزن العبوة؟&lt;/p&gt;&lt;p&gt;وزنها 100 جرام.&lt;/p&gt;&lt;p&gt;هل يوضح الاسم طريقة الاستخدام؟&lt;/p&gt;&lt;p&gt;لا، لذا يُرجع إلى التعليمات المدونة على العبوة لمعرفة تفاصيل التطبيق.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5318,7 +5328,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>MNT-R58</t>
+          <t>MNT-R60</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5355,22 +5365,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>بالمرز مرطب الشفاه بخلاصة جوز الهند 4 جرام</t>
+          <t>بالمرز كريم زبدة كاكاو 200 جرام</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>العناية والجمال &gt; الشفاه &gt; مرطب الشفاه</t>
+          <t>العناية والجمال &gt; العناية بالجسم</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0749/1387/4134/files/3645.jpg?v=1748506255</t>
+          <t>https://cdn.shopify.com/s/files/1/0749/1387/4134/files/4008_Front.webp?v=1762800446&amp;width=1000&amp;height=1000&amp;crop=center</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>بالمرز مرطب الشفاه بخلاصة جوز الهند 4 جرام</t>
+          <t>بالمرز كريم زبدة كاكاو 200 جرام</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5380,12 +5390,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>44</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>&lt;p&gt;مرطب الشفاه بالمرز بخلاصة جوز الهند | Palmer's Coconut Extract Lip Balm | Palmer's | مرطب شفاه | 4 جرام. يحدد الاسم نوع المنتج، ويذكر خلاصة جوز الهند ووزن العبوة.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | مرطب الشفاه بالمرز بخلاصة جوز الهند&lt;/li&gt;&lt;li&gt;النوع | مرطب شفاه&lt;/li&gt;&lt;li&gt;الحجم | 4 جرام&lt;/li&gt;&lt;li&gt;العلامة التجارية | Palmer's&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;مرطب شفاه من Palmer's يذكر خلاصة جوز الهند في اسمه، ويأتي بوزن 4 جرام. وتوضح التسمية بجلاء أن المنتج مخصص للعناية بالشفاه، ضمن عبوة محددة الحجم يسهل التعرف إلى بياناتها الأساسية.&lt;/p&gt;&lt;p&gt;لا تتضمن المعلومات المتاحة وصفاً إضافياً للتركيبة أو الرائحة أو القوام، كما لا تحدد عدد مرات الاستخدام. لذلك يُكتفى بالبيانات المعلنة في الاسم، وتُراجع العبوة لمعرفة تفاصيل التطبيق وأي تعليمات مصاحبة.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مرطب شفاه يحمل علامة Palmer's.&lt;/li&gt;&lt;li&gt;يذكر خلاصة جوز الهند ضمن اسمه.&lt;/li&gt;&lt;li&gt;يأتي بوزن 4 جرام.&lt;/li&gt;&lt;li&gt;مخصص للعناية بالشفاه بحسب تسمية المنتج.&lt;/li&gt;&lt;li&gt;يندرج ضمن فئة العناية الشخصية.&lt;/li&gt;&lt;li&gt;اسم المنتج يوضح نوعه والعنصر المذكور فيه.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن مرطب شفاه من Palmer's.&lt;/li&gt;&lt;li&gt;لمن يفضل منتجاً يذكر خلاصة جوز الهند في اسمه.&lt;/li&gt;&lt;li&gt;لمن يرغب في عبوة مرطب شفاه بوزن 4 جرام.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;يُطبق على الشفاه وفق الإرشادات الواردة على العبوة. لا تحدد بيانات الاسم عدد مرات الاستخدام أو كمية التطبيق، لذا يُرجع إلى التعليمات المرفقة بالمنتج.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط. يُرجى تجنب ملامسة العينين وإبقاء المنتج بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;يحمل مرطب الشفاه اسم Palmer's، كما ورد في معلومات المنتج. ويجمع الاسم بين العلامة التجارية ونوع المنتج وخلاصة جوز الهند المذكورة، دون تقديم تفاصيل أخرى عن العلامة أو تركيبة البلسم.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع هذا المنتج؟&lt;/p&gt;&lt;p&gt;هو مرطب شفاه من Palmer's.&lt;/p&gt;&lt;p&gt;ما الذي يذكره الاسم عن المنتج؟&lt;/p&gt;&lt;p&gt;يذكر خلاصة جوز الهند.&lt;/p&gt;&lt;p&gt;ما وزن العبوة؟&lt;/p&gt;&lt;p&gt;وزنها 4 جرام.&lt;/p&gt;&lt;p&gt;هل يوضح الاسم عدد مرات الاستخدام؟&lt;/p&gt;&lt;p&gt;لا، وتُراجع العبوة لمعرفة تعليمات التطبيق.&lt;/p&gt;</t>
+          <t>&lt;p&gt;كريم بالمرز بزبدة الكاكاو 200 جرام، Palmer's Cocoa Butter Cream، من علامة بالمرز، كريم للعناية بالجسم بحجم 200 جرام.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | كريم بالمرز بزبدة الكاكاو&lt;/li&gt;&lt;li&gt;النوع | كريم جسم&lt;/li&gt;&lt;li&gt;الحجم | 200 جرام&lt;/li&gt;&lt;li&gt;العلامة التجارية | بالمرز&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;كريم للجسم يحمل زبدة الكاكاو في اسمه، ويأتي من بالمرز في عبوة 200 جرام. صيغته الكريمية مخصصة للعناية ببشرة الجسم، ويمكن إدراجه ضمن خطوات العناية اليومية وفق الحاجة وطريقة الاستخدام الموضحة على العبوة.&lt;/p&gt;&lt;p&gt;يمنحك حجمه مساحة مناسبة للاستخدام ضمن روتينك المعتاد، سواء خصصتِ له وقتاً بعد الاستحمام أو جعلتِه جزءاً من عنايتك بالبشرة في أي وقت آخر. يظل وصف المنتج محصوراً في اسمه ونوعه وحجمه، لذا يُرجى الرجوع إلى بيانات العبوة للتفاصيل الإضافية.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;كريم مخصص للعناية ببشرة الجسم.&lt;/li&gt;&lt;li&gt;يحمل اسم زبدة الكاكاو ضمن تعريف المنتج.&lt;/li&gt;&lt;li&gt;عبوة بحجم 200 جرام.&lt;/li&gt;&lt;li&gt;يمكن إدراجه في روتين العناية اليومي.&lt;/li&gt;&lt;li&gt;قوام كريمي سهل التوزيع على البشرة.&lt;/li&gt;&lt;li&gt;من علامة بالمرز.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يفضلن مستحضرات العناية بالجسم بصيغة الكريم.&lt;/li&gt;&lt;li&gt;للمهتمين باختيار منتج يحمل زبدة الكاكاو في اسمه.&lt;/li&gt;&lt;li&gt;لمن يرغبون بإضافة كريم جسم إلى روتين العناية المعتاد.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;يُوزع مقدار مناسب على بشرة الجسم النظيفة، ثم يُدلك بلطف حتى يتوزع. يُستخدم وفق تعليمات العبوة، ويمكن تكرار الاستخدام بحسب ما توضحه الجهة المصنّعة. تجنبي وضعه على بشرة متهيجة أو غير سليمة، وتحققي من ملاءمته لبشرتك قبل إدخاله في روتينك.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، مع تجنب ملامسة العينين. يُحفظ بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;بالمرز هي العلامة التجارية الظاهرة على عبوة هذا الكريم، ويُعرف المنتج باسم كريم زبدة الكاكاو. يأتي هذا الإصدار بوزن 200 جرام، وتُستكمل تفاصيله من المعلومات المطبوعة على العبوة.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع هذا المنتج؟&lt;/p&gt;&lt;p&gt;هو كريم مخصص للعناية ببشرة الجسم، ويُعرف في الاسم بزبدة الكاكاو.&lt;/p&gt;&lt;p&gt;ما حجم العبوة؟&lt;/p&gt;&lt;p&gt;تحتوي العبوة على 200 جرام من المنتج.&lt;/p&gt;&lt;p&gt;كيف يُستخدم؟&lt;/p&gt;&lt;p&gt;يوزع على بشرة الجسم النظيفة مع اتباع الإرشادات المكتوبة على العبوة.&lt;/p&gt;&lt;p&gt;هل يحتوي الاسم على درجة لونية؟&lt;/p&gt;&lt;p&gt;لا، لا ترد درجة لونية ضمن اسم المنتج؛ فهو كريم للجسم وليس منتج مكياج بدرجة محددة.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5395,7 +5405,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>MNT-R59</t>
+          <t>MNT-R61</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5432,7 +5442,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>بالمرز كريم زبدة الكاكاو 100 جم</t>
+          <t>كريم بالمرز لعلامات تمدد الجلد 125جم</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5442,12 +5452,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0749/1387/4134/files/4350_Front.png?v=1754427362</t>
+          <t>https://m.media-amazon.com/images/I/71S2urregML.jpg</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>بالمرز كريم زبدة الكاكاو 100 جم</t>
+          <t>كريم بالمرز لعلامات تمدد الجلد 125جم</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5457,12 +5467,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>&lt;p&gt;كريم بالمرز بزبدة الكاكاو | Palmer's Cocoa Butter Cream | Palmer's | كريم | 100 جرام. يذكر اسم المنتج زبدة الكاكاو، ويحدد نوعه وحجم العبوة.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | كريم بالمرز بزبدة الكاكاو&lt;/li&gt;&lt;li&gt;النوع | كريم&lt;/li&gt;&lt;li&gt;الحجم | 100 جرام&lt;/li&gt;&lt;li&gt;العلامة التجارية | Palmer's&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;كريم من Palmer's يحمل زبدة الكاكاو في اسمه، ويأتي بوزن 100 جرام. ويتيح الاسم التعرف إلى العلامة التجارية ونوع المنتج والعنصر المذكور، كما يندرج المنتج ضمن فئة العناية بالجسم.&lt;/p&gt;&lt;p&gt;لا تعرض البيانات المتاحة تفاصيل إضافية عن تركيبة الكريم أو قوامه أو طريقة استخدامه. لذلك يُقدَّم المنتج وفق المعلومات الواردة في اسمه، مع الرجوع إلى العبوة للتعرف إلى موضع التطبيق والتعليمات وأي تفاصيل أخرى.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;كريم يحمل علامة Palmer's.&lt;/li&gt;&lt;li&gt;يذكر زبدة الكاكاو في اسم المنتج.&lt;/li&gt;&lt;li&gt;يأتي بوزن 100 جرام.&lt;/li&gt;&lt;li&gt;يندرج ضمن منتجات العناية بالجسم.&lt;/li&gt;&lt;li&gt;يسهل التعرف إلى نوعه من التسمية المباشرة.&lt;/li&gt;&lt;li&gt;لا يحدد الاسم درجة لونية أو رائحة للمنتج.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن كريم من Palmer's يذكر زبدة الكاكاو.&lt;/li&gt;&lt;li&gt;لمن يفضل منتجات العناية بالجسم بصيغة الكريم.&lt;/li&gt;&lt;li&gt;لمن يرغب في عبوة بوزن 100 جرام.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;يُستخدم وفق التعليمات الموجودة على العبوة. لا تحدد المعلومات المتاحة موضع الاستخدام أو الكمية أو وتيرة التطبيق، لذا تُعتمد الإرشادات المطبوعة على المنتج.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط. تجنب ملامسة العينين، واحفظ العبوة بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;تظهر علامة Palmer's على اسم الكريم ضمن البيانات المتاحة. ويُعرّف المنتج هنا بوصفه كريم زبدة الكاكاو من هذه العلامة، دون إضافة معلومات غير مذكورة عن تاريخها أو خطوط منتجاتها.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع المنتج؟&lt;/p&gt;&lt;p&gt;هو كريم من Palmer's.&lt;/p&gt;&lt;p&gt;ما العنصر المذكور في الاسم؟&lt;/p&gt;&lt;p&gt;زبدة الكاكاو.&lt;/p&gt;&lt;p&gt;ما وزن العبوة؟&lt;/p&gt;&lt;p&gt;وزنها 100 جرام.&lt;/p&gt;&lt;p&gt;هل يوضح الاسم طريقة الاستخدام؟&lt;/p&gt;&lt;p&gt;لا، لذا يُرجع إلى التعليمات المدونة على العبوة لمعرفة تفاصيل التطبيق.&lt;/p&gt;</t>
+          <t>&lt;p&gt;كريم بالمرز لعلامات تمدد الجلد 125 جم، Palmer's Stretch Marks Cream، من علامة بالمرز، كريم للعناية بالجسم بحجم 125 جم.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | كريم بالمرز لعلامات تمدد الجلد&lt;/li&gt;&lt;li&gt;النوع | كريم للجسم&lt;/li&gt;&lt;li&gt;الحجم | 125 جم&lt;/li&gt;&lt;li&gt;العلامة التجارية | بالمرز&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;كريم للعناية بالجسم يرد في اسمه ارتباطه بعلامات تمدد الجلد، وتقدمه علامة بالمرز بعبوة وزنها 125 جم. يتيح شكل الكريم توزيعه على البشرة ضمن خطوات العناية المعتادة، مع الالتزام بما توضحه العبوة بشأن مواضع الاستخدام وطريقته.&lt;/p&gt;&lt;p&gt;اختيرت صياغة هذا الوصف لتوضيح هوية المنتج من دون إضافة وعود أو نتائج غير مذكورة في الاسم. يمكن تخصيصه للعناية بالمناطق التي يرغب المستخدم في إدراجها ضمن روتينه، مع مراعاة اختلاف احتياجات البشرة واتباع الإرشادات المدونة على المنتج.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;كريم للعناية ببشرة الجسم.&lt;/li&gt;&lt;li&gt;يرتبط اسمه بعلامات تمدد الجلد.&lt;/li&gt;&lt;li&gt;عبوة بوزن 125 جم.&lt;/li&gt;&lt;li&gt;صيغة كريمية قابلة للتوزيع على البشرة.&lt;/li&gt;&lt;li&gt;يمكن إضافته إلى روتين العناية الشخصي.&lt;/li&gt;&lt;li&gt;يحمل علامة بالمرز التجارية.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحثون عن كريم جسم يذكر علامات تمدد الجلد في اسمه.&lt;/li&gt;&lt;li&gt;للراغبين في إضافة مستحضر كريمي إلى عناية الجسم.&lt;/li&gt;&lt;li&gt;لمن يفضلون اختيار منتجاتهم بحسب المنطقة المراد العناية بها.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;تُتبع التعليمات المثبتة على العبوة لتحديد موضع الاستخدام وتكراره. عند الاستخدام، توزع كمية مناسبة على بشرة نظيفة وتدلك برفق حتى تنتشر على المنطقة المرغوبة. يُنصح بالبدء على مساحة صغيرة إذا كانت هذه أول مرة لاستخدام المنتج، والتوقف عند ظهور انزعاج.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط؛ تجنب ملامسة العينين. أبقِ العبوة بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;بالمرز هو الاسم العربي للعلامة Palmer's الظاهر على هذا المنتج. يقدم هذا الإصدار في صورة كريم للعناية بالجسم وبحجم 125 جم، بينما تُراجع تفاصيل الاستخدام على العبوة الأصلية.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما المقصود باستخدام الكريم بحسب اسمه؟&lt;/p&gt;&lt;p&gt;يرتبط اسم المنتج بالعناية بالبشرة التي تظهر عليها علامات تمدد الجلد، من دون أن يحدد الاسم نتيجة بعينها.&lt;/p&gt;&lt;p&gt;كم يبلغ وزن العبوة؟&lt;/p&gt;&lt;p&gt;وزن المنتج المذكور هو 125 جم.&lt;/p&gt;&lt;p&gt;هل هو مستحضر للوجه؟&lt;/p&gt;&lt;p&gt;يُصنف بوصفه كريماً للعناية بالجسم، وتُحدد العبوة مواضع الاستخدام المناسبة.&lt;/p&gt;&lt;p&gt;أين أجد إرشادات الاستعمال؟&lt;/p&gt;&lt;p&gt;راجعي الملصق المرفق بالعبوة لمعرفة الطريقة والتكرار الموصى بهما من الشركة.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5472,7 +5482,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>MNT-R60</t>
+          <t>MNT-R62</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5509,7 +5519,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>بالمرز كريم زبدة كاكاو 200 جرام</t>
+          <t>بالمرز كريم رضاعة مع زبدة الكاكاو 30 جرام</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5519,12 +5529,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0749/1387/4134/files/4008_Front.webp?v=1762800446&amp;width=1000&amp;height=1000&amp;crop=center</t>
+          <t>https://cdn.shopify.com/s/files/1/0749/1387/4134/files/3595.jpg?v=1748505420&amp;width=1000&amp;height=1000&amp;crop=center</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>بالمرز كريم زبدة كاكاو 200 جرام</t>
+          <t>بالمرز كريم رضاعة مع زبدة الكاكاو 30 جرام</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -5534,12 +5544,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>&lt;p&gt;كريم بالمرز بزبدة الكاكاو 200 جرام، Palmer's Cocoa Butter Cream، من علامة بالمرز، كريم للعناية بالجسم بحجم 200 جرام.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | كريم بالمرز بزبدة الكاكاو&lt;/li&gt;&lt;li&gt;النوع | كريم جسم&lt;/li&gt;&lt;li&gt;الحجم | 200 جرام&lt;/li&gt;&lt;li&gt;العلامة التجارية | بالمرز&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;كريم للجسم يحمل زبدة الكاكاو في اسمه، ويأتي من بالمرز في عبوة 200 جرام. صيغته الكريمية مخصصة للعناية ببشرة الجسم، ويمكن إدراجه ضمن خطوات العناية اليومية وفق الحاجة وطريقة الاستخدام الموضحة على العبوة.&lt;/p&gt;&lt;p&gt;يمنحك حجمه مساحة مناسبة للاستخدام ضمن روتينك المعتاد، سواء خصصتِ له وقتاً بعد الاستحمام أو جعلتِه جزءاً من عنايتك بالبشرة في أي وقت آخر. يظل وصف المنتج محصوراً في اسمه ونوعه وحجمه، لذا يُرجى الرجوع إلى بيانات العبوة للتفاصيل الإضافية.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;كريم مخصص للعناية ببشرة الجسم.&lt;/li&gt;&lt;li&gt;يحمل اسم زبدة الكاكاو ضمن تعريف المنتج.&lt;/li&gt;&lt;li&gt;عبوة بحجم 200 جرام.&lt;/li&gt;&lt;li&gt;يمكن إدراجه في روتين العناية اليومي.&lt;/li&gt;&lt;li&gt;قوام كريمي سهل التوزيع على البشرة.&lt;/li&gt;&lt;li&gt;من علامة بالمرز.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يفضلن مستحضرات العناية بالجسم بصيغة الكريم.&lt;/li&gt;&lt;li&gt;للمهتمين باختيار منتج يحمل زبدة الكاكاو في اسمه.&lt;/li&gt;&lt;li&gt;لمن يرغبون بإضافة كريم جسم إلى روتين العناية المعتاد.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;يُوزع مقدار مناسب على بشرة الجسم النظيفة، ثم يُدلك بلطف حتى يتوزع. يُستخدم وفق تعليمات العبوة، ويمكن تكرار الاستخدام بحسب ما توضحه الجهة المصنّعة. تجنبي وضعه على بشرة متهيجة أو غير سليمة، وتحققي من ملاءمته لبشرتك قبل إدخاله في روتينك.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، مع تجنب ملامسة العينين. يُحفظ بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;بالمرز هي العلامة التجارية الظاهرة على عبوة هذا الكريم، ويُعرف المنتج باسم كريم زبدة الكاكاو. يأتي هذا الإصدار بوزن 200 جرام، وتُستكمل تفاصيله من المعلومات المطبوعة على العبوة.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع هذا المنتج؟&lt;/p&gt;&lt;p&gt;هو كريم مخصص للعناية ببشرة الجسم، ويُعرف في الاسم بزبدة الكاكاو.&lt;/p&gt;&lt;p&gt;ما حجم العبوة؟&lt;/p&gt;&lt;p&gt;تحتوي العبوة على 200 جرام من المنتج.&lt;/p&gt;&lt;p&gt;كيف يُستخدم؟&lt;/p&gt;&lt;p&gt;يوزع على بشرة الجسم النظيفة مع اتباع الإرشادات المكتوبة على العبوة.&lt;/p&gt;&lt;p&gt;هل يحتوي الاسم على درجة لونية؟&lt;/p&gt;&lt;p&gt;لا، لا ترد درجة لونية ضمن اسم المنتج؛ فهو كريم للجسم وليس منتج مكياج بدرجة محددة.&lt;/p&gt;</t>
+          <t>&lt;p&gt;كريم بالمرز للرضاعة مع زبدة الكاكاو 30 جرام، Palmer's Nursing Cream with Cocoa Butter، من علامة بالمرز، كريم عناية بحجم 30 جرام.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | كريم بالمرز للرضاعة مع زبدة الكاكاو&lt;/li&gt;&lt;li&gt;النوع | كريم عناية&lt;/li&gt;&lt;li&gt;الحجم | 30 جرام&lt;/li&gt;&lt;li&gt;العلامة التجارية | بالمرز&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;كريم يحمل في اسمه الإشارة إلى الرضاعة وزبدة الكاكاو، وتقدمه بالمرز بعبوة صغيرة وزنها 30 جراماً. يُصنف ضمن مستحضرات العناية الشخصية ذات الاستخدام الموضعي، وتُعتمد تعليمات العبوة لتحديد موضع الاستخدام وطريقته، ولا سيما في هذه المرحلة التي تتطلب مراعاة الإرشادات الخاصة بالمنتج.&lt;/p&gt;&lt;p&gt;تُعرض العبوة بحجم عملي يسهل الاحتفاظ به ضمن مستلزمات العناية، مع ضرورة قراءة الملصق كاملاً قبل الاستعمال. لا يذكر الاسم تفاصيل إضافية عن الاستخدام أو أي خصائص أخرى؛ لذا يُكتفى بالمعلومات المتاحة على العبوة، ويُستحسن الاستفسار من مختص عند وجود أي تساؤل متعلق باستخدام مستحضر في فترة الرضاعة.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;كريم عناية مرتبط بالرضاعة بحسب الاسم.&lt;/li&gt;&lt;li&gt;يتضمن اسم المنتج زبدة الكاكاو.&lt;/li&gt;&lt;li&gt;عبوة صغيرة بوزن 30 جراماً.&lt;/li&gt;&lt;li&gt;صيغة موضعية للاستخدام وفق الملصق.&lt;/li&gt;&lt;li&gt;يمكن حمل العبوة مع مستلزمات العناية الشخصية.&lt;/li&gt;&lt;li&gt;من علامة بالمرز التجارية.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحثن عن المنتج المسمى كريم بالمرز للرضاعة.&lt;/li&gt;&lt;li&gt;لمن يفضلن عبوة عناية صغيرة بحجم 30 جراماً.&lt;/li&gt;&lt;li&gt;لمن يرغبن في مراجعة تعليمات الاستخدام الخاصة بالمنتج قبل الاستعمال.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;اقرئي التعليمات المطبوعة على العبوة بعناية قبل الاستخدام، واتبعيها كما هي من حيث الموضع والكمية والتوقيت. لا يُفترض من الاسم وحده تحديد ما إذا كان يلزم إزالة المنتج قبل الرضاعة؛ لذلك تُراجع تعليمات الشركة أو يُستفسر من مختص عند الحاجة. لا تستخدميه بطريقة تخالف الملصق.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. يُحفظ بعيداً عن متناول الأطفال، وتُراجع تعليمات العبوة قبل الاستعمال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;بالمرز هي العلامة التجارية المسجلة على المنتج، ويظهر اسم Palmer's إلى جانب وصفه المرتبط بالرضاعة وزبدة الكاكاو. تتوفر هذه العبوة بوزن 30 جراماً، وتظل المعلومات التفصيلية للاستخدام كما وردت على الملصق.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما حجم كريم بالمرز للرضاعة؟&lt;/p&gt;&lt;p&gt;تحتوي العبوة على 30 جراماً من الكريم.&lt;/p&gt;&lt;p&gt;ما الذي يذكره اسم المنتج؟&lt;/p&gt;&lt;p&gt;يشير الاسم إلى كريم للرضاعة مع زبدة الكاكاو.&lt;/p&gt;&lt;p&gt;هل يوضح الاسم وحده طريقة الاستخدام؟&lt;/p&gt;&lt;p&gt;لا، يجب الرجوع إلى الإرشادات المطبوعة على العبوة لمعرفة طريقة الاستخدام وموضعه.&lt;/p&gt;&lt;p&gt;هل توجد معلومات عن إزالة الكريم قبل الرضاعة؟&lt;/p&gt;&lt;p&gt;لا يوضح الاسم هذه المعلومة؛ يرجى قراءة الملصق أو سؤال مختص قبل الاستخدام عند الحاجة.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5549,7 +5559,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>MNT-R61</t>
+          <t>MNT-R63</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5586,7 +5596,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>كريم بالمرز لعلامات تمدد الجلد 125جم</t>
+          <t>بالمرز كريم الصدر 125 جرام</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5596,12 +5606,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71S2urregML.jpg</t>
+          <t>https://m.media-amazon.com/images/I/81NBRkl-lBL.jpg</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>كريم بالمرز لعلامات تمدد الجلد 125جم</t>
+          <t>بالمرز كريم الصدر 125 جرام</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5611,12 +5621,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>39</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>&lt;p&gt;كريم بالمرز لعلامات تمدد الجلد 125 جم، Palmer's Stretch Marks Cream، من علامة بالمرز، كريم للعناية بالجسم بحجم 125 جم.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | كريم بالمرز لعلامات تمدد الجلد&lt;/li&gt;&lt;li&gt;النوع | كريم للجسم&lt;/li&gt;&lt;li&gt;الحجم | 125 جم&lt;/li&gt;&lt;li&gt;العلامة التجارية | بالمرز&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;كريم للعناية بالجسم يرد في اسمه ارتباطه بعلامات تمدد الجلد، وتقدمه علامة بالمرز بعبوة وزنها 125 جم. يتيح شكل الكريم توزيعه على البشرة ضمن خطوات العناية المعتادة، مع الالتزام بما توضحه العبوة بشأن مواضع الاستخدام وطريقته.&lt;/p&gt;&lt;p&gt;اختيرت صياغة هذا الوصف لتوضيح هوية المنتج من دون إضافة وعود أو نتائج غير مذكورة في الاسم. يمكن تخصيصه للعناية بالمناطق التي يرغب المستخدم في إدراجها ضمن روتينه، مع مراعاة اختلاف احتياجات البشرة واتباع الإرشادات المدونة على المنتج.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;كريم للعناية ببشرة الجسم.&lt;/li&gt;&lt;li&gt;يرتبط اسمه بعلامات تمدد الجلد.&lt;/li&gt;&lt;li&gt;عبوة بوزن 125 جم.&lt;/li&gt;&lt;li&gt;صيغة كريمية قابلة للتوزيع على البشرة.&lt;/li&gt;&lt;li&gt;يمكن إضافته إلى روتين العناية الشخصي.&lt;/li&gt;&lt;li&gt;يحمل علامة بالمرز التجارية.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحثون عن كريم جسم يذكر علامات تمدد الجلد في اسمه.&lt;/li&gt;&lt;li&gt;للراغبين في إضافة مستحضر كريمي إلى عناية الجسم.&lt;/li&gt;&lt;li&gt;لمن يفضلون اختيار منتجاتهم بحسب المنطقة المراد العناية بها.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;تُتبع التعليمات المثبتة على العبوة لتحديد موضع الاستخدام وتكراره. عند الاستخدام، توزع كمية مناسبة على بشرة نظيفة وتدلك برفق حتى تنتشر على المنطقة المرغوبة. يُنصح بالبدء على مساحة صغيرة إذا كانت هذه أول مرة لاستخدام المنتج، والتوقف عند ظهور انزعاج.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط؛ تجنب ملامسة العينين. أبقِ العبوة بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;بالمرز هو الاسم العربي للعلامة Palmer's الظاهر على هذا المنتج. يقدم هذا الإصدار في صورة كريم للعناية بالجسم وبحجم 125 جم، بينما تُراجع تفاصيل الاستخدام على العبوة الأصلية.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما المقصود باستخدام الكريم بحسب اسمه؟&lt;/p&gt;&lt;p&gt;يرتبط اسم المنتج بالعناية بالبشرة التي تظهر عليها علامات تمدد الجلد، من دون أن يحدد الاسم نتيجة بعينها.&lt;/p&gt;&lt;p&gt;كم يبلغ وزن العبوة؟&lt;/p&gt;&lt;p&gt;وزن المنتج المذكور هو 125 جم.&lt;/p&gt;&lt;p&gt;هل هو مستحضر للوجه؟&lt;/p&gt;&lt;p&gt;يُصنف بوصفه كريماً للعناية بالجسم، وتُحدد العبوة مواضع الاستخدام المناسبة.&lt;/p&gt;&lt;p&gt;أين أجد إرشادات الاستعمال؟&lt;/p&gt;&lt;p&gt;راجعي الملصق المرفق بالعبوة لمعرفة الطريقة والتكرار الموصى بهما من الشركة.&lt;/p&gt;</t>
+          <t>&lt;p&gt;كريم بالمرز للصدر 125 جرام، Palmer's Bust Cream، من علامة بالمرز، كريم عناية بالجسم بحجم 125 جرام.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | كريم بالمرز للصدر&lt;/li&gt;&lt;li&gt;النوع | كريم جسم&lt;/li&gt;&lt;li&gt;الحجم | 125 جرام&lt;/li&gt;&lt;li&gt;العلامة التجارية | بالمرز&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;كريم للعناية بالجسم يُعرّف باسمه على أنه مخصص لمنطقة الصدر، وتأتي العبوة من بالمرز بوزن 125 جراماً. يساعد وضوح التسمية على تمييز المنتج ضمن مستحضرات العناية الموضعية، مع ضرورة الرجوع إلى ملصق العبوة لمعرفة التفاصيل الدقيقة المتعلقة بمناطق الاستعمال وطريقته.&lt;/p&gt;&lt;p&gt;يمكن إدراجه ضمن روتين العناية الشخصية لمن يبحث عن كريم يحمل هذا الوصف تحديداً. لا يتضمن الاسم درجة أو نتيجة معلنة، لذلك يقتصر التعريف هنا على نوع المستحضر وحجمه والمنطقة المذكورة في اسمه. يُستخدم وفق إرشادات العبوة، مع مراعاة طبيعة البشرة وتجنب وضعه على مناطق غير موصى بها.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;كريم عناية للجسم يحمل وصف الصدر في اسمه.&lt;/li&gt;&lt;li&gt;عبوة بوزن 125 جراماً.&lt;/li&gt;&lt;li&gt;صيغة كريم قابلة للتوزيع الموضعي.&lt;/li&gt;&lt;li&gt;يمكن تخصيصه ضمن روتين العناية الشخصية.&lt;/li&gt;&lt;li&gt;لا يتضمن الاسم درجة لونية.&lt;/li&gt;&lt;li&gt;من علامة بالمرز Palmer's.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحثون عن كريم عناية مذكور للصدر في اسم المنتج.&lt;/li&gt;&lt;li&gt;للمهتمين بمستحضرات الجسم ذات الاستخدام الموضعي.&lt;/li&gt;&lt;li&gt;لمن يحرصون على اختيار المنتج بحسب المنطقة الموضحة على العبوة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;راجعي العبوة أولاً لتأكيد موضع الاستخدام وطريقة تطبيق الكريم. إذا كانت التعليمات تسمح باستخدامه على المنطقة المقصودة، توزع كمية مناسبة على بشرة نظيفة وتدلك برفق. لا يوضع على مناطق أخرى لم يشر إليها الملصق، ويُوقف الاستخدام عند حدوث انزعاج أو تهيج.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط؛ احرصي على عدم ملامسة العينين. يُحفظ في مكان لا يصل إليه الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;بالمرز هي العلامة الظاهرة على هذا الكريم، ويقابلها اسم Palmer's بالإنجليزية. يقدم المنتج هنا بوصفه كريم عناية للجسم في عبوة 125 جراماً، وتُراجع بيانات العبوة لاستكمال معلومات الاستعمال.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما المنطقة المذكورة في اسم الكريم؟&lt;/p&gt;&lt;p&gt;يشير الاسم إلى الصدر، وتبقى تعليمات الملصق المرجع لتحديد الاستعمال.&lt;/p&gt;&lt;p&gt;كم وزن المنتج؟&lt;/p&gt;&lt;p&gt;العبوة المذكورة في الاسم بوزن 125 جراماً.&lt;/p&gt;&lt;p&gt;هل هو كريم للوجه؟&lt;/p&gt;&lt;p&gt;لا يذكر الاسم الوجه؛ بل يقدمه بوصفه كريماً للصدر ضمن العناية بالجسم.&lt;/p&gt;&lt;p&gt;كيف أحدد طريقة تطبيقه؟&lt;/p&gt;&lt;p&gt;اتبعي إرشادات العبوة الخاصة بموضع الاستخدام والكمية وطريقة التطبيق.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5626,7 +5636,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>MNT-R62</t>
+          <t>MNT-R64</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5663,7 +5673,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>بالمرز كريم رضاعة مع زبدة الكاكاو 30 جرام</t>
+          <t>بالمرز لعلامات التمدد 125 جرام</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5673,12 +5683,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0749/1387/4134/files/3595.jpg?v=1748505420&amp;width=1000&amp;height=1000&amp;crop=center</t>
+          <t>https://m.media-amazon.com/images/I/71S2urregML.jpg</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>بالمرز كريم رضاعة مع زبدة الكاكاو 30 جرام</t>
+          <t>بالمرز لعلامات التمدد 125 جرام</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5688,12 +5698,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>&lt;p&gt;كريم بالمرز للرضاعة مع زبدة الكاكاو 30 جرام، Palmer's Nursing Cream with Cocoa Butter، من علامة بالمرز، كريم عناية بحجم 30 جرام.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | كريم بالمرز للرضاعة مع زبدة الكاكاو&lt;/li&gt;&lt;li&gt;النوع | كريم عناية&lt;/li&gt;&lt;li&gt;الحجم | 30 جرام&lt;/li&gt;&lt;li&gt;العلامة التجارية | بالمرز&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;كريم يحمل في اسمه الإشارة إلى الرضاعة وزبدة الكاكاو، وتقدمه بالمرز بعبوة صغيرة وزنها 30 جراماً. يُصنف ضمن مستحضرات العناية الشخصية ذات الاستخدام الموضعي، وتُعتمد تعليمات العبوة لتحديد موضع الاستخدام وطريقته، ولا سيما في هذه المرحلة التي تتطلب مراعاة الإرشادات الخاصة بالمنتج.&lt;/p&gt;&lt;p&gt;تُعرض العبوة بحجم عملي يسهل الاحتفاظ به ضمن مستلزمات العناية، مع ضرورة قراءة الملصق كاملاً قبل الاستعمال. لا يذكر الاسم تفاصيل إضافية عن الاستخدام أو أي خصائص أخرى؛ لذا يُكتفى بالمعلومات المتاحة على العبوة، ويُستحسن الاستفسار من مختص عند وجود أي تساؤل متعلق باستخدام مستحضر في فترة الرضاعة.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;كريم عناية مرتبط بالرضاعة بحسب الاسم.&lt;/li&gt;&lt;li&gt;يتضمن اسم المنتج زبدة الكاكاو.&lt;/li&gt;&lt;li&gt;عبوة صغيرة بوزن 30 جراماً.&lt;/li&gt;&lt;li&gt;صيغة موضعية للاستخدام وفق الملصق.&lt;/li&gt;&lt;li&gt;يمكن حمل العبوة مع مستلزمات العناية الشخصية.&lt;/li&gt;&lt;li&gt;من علامة بالمرز التجارية.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحثن عن المنتج المسمى كريم بالمرز للرضاعة.&lt;/li&gt;&lt;li&gt;لمن يفضلن عبوة عناية صغيرة بحجم 30 جراماً.&lt;/li&gt;&lt;li&gt;لمن يرغبن في مراجعة تعليمات الاستخدام الخاصة بالمنتج قبل الاستعمال.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;اقرئي التعليمات المطبوعة على العبوة بعناية قبل الاستخدام، واتبعيها كما هي من حيث الموضع والكمية والتوقيت. لا يُفترض من الاسم وحده تحديد ما إذا كان يلزم إزالة المنتج قبل الرضاعة؛ لذلك تُراجع تعليمات الشركة أو يُستفسر من مختص عند الحاجة. لا تستخدميه بطريقة تخالف الملصق.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. يُحفظ بعيداً عن متناول الأطفال، وتُراجع تعليمات العبوة قبل الاستعمال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;بالمرز هي العلامة التجارية المسجلة على المنتج، ويظهر اسم Palmer's إلى جانب وصفه المرتبط بالرضاعة وزبدة الكاكاو. تتوفر هذه العبوة بوزن 30 جراماً، وتظل المعلومات التفصيلية للاستخدام كما وردت على الملصق.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما حجم كريم بالمرز للرضاعة؟&lt;/p&gt;&lt;p&gt;تحتوي العبوة على 30 جراماً من الكريم.&lt;/p&gt;&lt;p&gt;ما الذي يذكره اسم المنتج؟&lt;/p&gt;&lt;p&gt;يشير الاسم إلى كريم للرضاعة مع زبدة الكاكاو.&lt;/p&gt;&lt;p&gt;هل يوضح الاسم وحده طريقة الاستخدام؟&lt;/p&gt;&lt;p&gt;لا، يجب الرجوع إلى الإرشادات المطبوعة على العبوة لمعرفة طريقة الاستخدام وموضعه.&lt;/p&gt;&lt;p&gt;هل توجد معلومات عن إزالة الكريم قبل الرضاعة؟&lt;/p&gt;&lt;p&gt;لا يوضح الاسم هذه المعلومة؛ يرجى قراءة الملصق أو سؤال مختص قبل الاستخدام عند الحاجة.&lt;/p&gt;</t>
+          <t>&lt;p&gt;كريم بالمرز لعلامات التمدد 125 جرام، Palmer's Stretch Marks Cream، من علامة بالمرز، كريم جسم بحجم 125 جرام.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | كريم بالمرز لعلامات التمدد&lt;/li&gt;&lt;li&gt;النوع | كريم جسم&lt;/li&gt;&lt;li&gt;الحجم | 125 جرام&lt;/li&gt;&lt;li&gt;العلامة التجارية | بالمرز&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;يأتي هذا المنتج من بالمرز في صورة كريم للجسم، ويشير اسمه إلى علامات التمدد بوصفها مجال العناية المرتبط به. تحتوي العبوة على 125 جراماً، ما يجعلها خياراً واضحاً لمن يبحثون عن كريم بهذا الاسم والحجم ضمن مستحضرات العناية الشخصية.&lt;/p&gt;&lt;p&gt;يمكن تخصيصه لخطوات العناية بالبشرة وفق تعليمات العبوة، مع عدم افتراض نتائج أو خصائص غير واردة في المعلومات المتاحة. تختلف طريقة الاستخدام بحسب إرشادات المنتج، لذلك يُنصح بقراءتها قبل البدء، خصوصاً عند استخدامه للمرة الأولى أو عند إدخاله في روتين قائم.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;كريم جسم يرتبط اسمه بعلامات التمدد.&lt;/li&gt;&lt;li&gt;وزن العبوة 125 جراماً.&lt;/li&gt;&lt;li&gt;صيغة كريمية للاستخدام الموضعي على البشرة.&lt;/li&gt;&lt;li&gt;يناسب إدراجه ضمن روتين العناية بالجسم.&lt;/li&gt;&lt;li&gt;يحمل علامة بالمرز التجارية.&lt;/li&gt;&lt;li&gt;لا يذكر الاسم درجة لونية أو قياساً آخر.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يفضلون كريمات الجسم المخصصة للعناية بالبشرة.&lt;/li&gt;&lt;li&gt;لمن يبحثون عن منتج يحمل علامات التمدد في تسميته.&lt;/li&gt;&lt;li&gt;للراغبين في اختيار عبوة بوزن 125 جراماً.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;اتبعي إرشادات العبوة بشأن الكمية والمواضع المقترحة وتكرار الاستخدام. عند التطبيق، وزعي الكريم برفق على بشرة نظيفة في المنطقة المراد العناية بها، من دون الضغط أو الفرك القوي. تجنبي استعماله على مناطق لم ترد ضمن التعليمات، وأوقفي الاستخدام إذا ظهر تهيج.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;مخصص للاستعمال الخارجي فقط، ويجب تجنب وصوله إلى العينين. يُحفظ بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;يظهر اسم بالمرز بالعربية وPalmer's بالإنجليزية على تعريف المنتج. هذا الإصدار هو كريم للجسم مرتبط اسمه بعلامات التمدد، ويتوفر بوزن 125 جراماً؛ أما إرشادات الاستعمال التفصيلية فتُراجع على العبوة.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;هل يختلف هذا المنتج عن كريم بالمرز لعلامات تمدد الجلد؟&lt;/p&gt;&lt;p&gt;الاسمان يصفان كريم بالمرز المرتبط بعلامات التمدد، والعبوة المحددة هنا بوزن 125 جراماً.&lt;/p&gt;&lt;p&gt;هل يمكن استخدامه على كل مناطق الجسم؟&lt;/p&gt;&lt;p&gt;يُرجى تحديد مواضع الاستعمال بالرجوع إلى تعليمات المنتج المطبوعة على العبوة.&lt;/p&gt;&lt;p&gt;هل يحتوي المنتج على درجة؟&lt;/p&gt;&lt;p&gt;لا توجد درجة لونية في الاسم؛ فهو كريم للعناية بالجسم.&lt;/p&gt;&lt;p&gt;ما أهم معلومة قبل الاستخدام؟&lt;/p&gt;&lt;p&gt;قراءة الملصق للتحقق من طريقة التطبيق والموضع والتكرار الموصى به.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5703,7 +5713,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>MNT-R63</t>
+          <t>MNT-R65</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -5740,7 +5750,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>بالمرز كريم الصدر 125 جرام</t>
+          <t>بالمرز زيت بزبدة الكاكاو 150 مل</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5750,12 +5760,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/81NBRkl-lBL.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0749/1387/4134/files/4153_Front_4cee072f-ab2c-4c9e-8475-f1c4eeb5e991.webp?v=1758903849&amp;width=1000&amp;height=1000&amp;crop=center</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>بالمرز كريم الصدر 125 جرام</t>
+          <t>بالمرز زيت بزبدة الكاكاو 150 مل</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -5765,12 +5775,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>58</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>&lt;p&gt;كريم بالمرز للصدر 125 جرام، Palmer's Bust Cream، من علامة بالمرز، كريم عناية بالجسم بحجم 125 جرام.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | كريم بالمرز للصدر&lt;/li&gt;&lt;li&gt;النوع | كريم جسم&lt;/li&gt;&lt;li&gt;الحجم | 125 جرام&lt;/li&gt;&lt;li&gt;العلامة التجارية | بالمرز&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;كريم للعناية بالجسم يُعرّف باسمه على أنه مخصص لمنطقة الصدر، وتأتي العبوة من بالمرز بوزن 125 جراماً. يساعد وضوح التسمية على تمييز المنتج ضمن مستحضرات العناية الموضعية، مع ضرورة الرجوع إلى ملصق العبوة لمعرفة التفاصيل الدقيقة المتعلقة بمناطق الاستعمال وطريقته.&lt;/p&gt;&lt;p&gt;يمكن إدراجه ضمن روتين العناية الشخصية لمن يبحث عن كريم يحمل هذا الوصف تحديداً. لا يتضمن الاسم درجة أو نتيجة معلنة، لذلك يقتصر التعريف هنا على نوع المستحضر وحجمه والمنطقة المذكورة في اسمه. يُستخدم وفق إرشادات العبوة، مع مراعاة طبيعة البشرة وتجنب وضعه على مناطق غير موصى بها.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;كريم عناية للجسم يحمل وصف الصدر في اسمه.&lt;/li&gt;&lt;li&gt;عبوة بوزن 125 جراماً.&lt;/li&gt;&lt;li&gt;صيغة كريم قابلة للتوزيع الموضعي.&lt;/li&gt;&lt;li&gt;يمكن تخصيصه ضمن روتين العناية الشخصية.&lt;/li&gt;&lt;li&gt;لا يتضمن الاسم درجة لونية.&lt;/li&gt;&lt;li&gt;من علامة بالمرز Palmer's.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحثون عن كريم عناية مذكور للصدر في اسم المنتج.&lt;/li&gt;&lt;li&gt;للمهتمين بمستحضرات الجسم ذات الاستخدام الموضعي.&lt;/li&gt;&lt;li&gt;لمن يحرصون على اختيار المنتج بحسب المنطقة الموضحة على العبوة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;راجعي العبوة أولاً لتأكيد موضع الاستخدام وطريقة تطبيق الكريم. إذا كانت التعليمات تسمح باستخدامه على المنطقة المقصودة، توزع كمية مناسبة على بشرة نظيفة وتدلك برفق. لا يوضع على مناطق أخرى لم يشر إليها الملصق، ويُوقف الاستخدام عند حدوث انزعاج أو تهيج.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط؛ احرصي على عدم ملامسة العينين. يُحفظ في مكان لا يصل إليه الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;بالمرز هي العلامة الظاهرة على هذا الكريم، ويقابلها اسم Palmer's بالإنجليزية. يقدم المنتج هنا بوصفه كريم عناية للجسم في عبوة 125 جراماً، وتُراجع بيانات العبوة لاستكمال معلومات الاستعمال.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما المنطقة المذكورة في اسم الكريم؟&lt;/p&gt;&lt;p&gt;يشير الاسم إلى الصدر، وتبقى تعليمات الملصق المرجع لتحديد الاستعمال.&lt;/p&gt;&lt;p&gt;كم وزن المنتج؟&lt;/p&gt;&lt;p&gt;العبوة المذكورة في الاسم بوزن 125 جراماً.&lt;/p&gt;&lt;p&gt;هل هو كريم للوجه؟&lt;/p&gt;&lt;p&gt;لا يذكر الاسم الوجه؛ بل يقدمه بوصفه كريماً للصدر ضمن العناية بالجسم.&lt;/p&gt;&lt;p&gt;كيف أحدد طريقة تطبيقه؟&lt;/p&gt;&lt;p&gt;اتبعي إرشادات العبوة الخاصة بموضع الاستخدام والكمية وطريقة التطبيق.&lt;/p&gt;</t>
+          <t>&lt;p&gt;زيت بالمرز بزبدة الكاكاو 150 مل، Palmer's Cocoa Butter Oil، من علامة بالمرز، زيت للعناية بالجسم بحجم 150 مل.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | زيت بالمرز بزبدة الكاكاو&lt;/li&gt;&lt;li&gt;النوع | زيت جسم&lt;/li&gt;&lt;li&gt;الحجم | 150 مل&lt;/li&gt;&lt;li&gt;العلامة التجارية | بالمرز&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;زيت عناية للجسم يحمل زبدة الكاكاو ضمن اسمه، ويأتي من بالمرز في عبوة حجمها 150 مل. تمنح صيغة الزيت طريقة مختلفة عن الكريمات في تطبيق مستحضرات الجسم، ويمكن تخصيصه لخطوة العناية التي تناسب تفضيلاتك، مع الرجوع إلى الملصق لمعرفة التعليمات التفصيلية.&lt;/p&gt;&lt;p&gt;العبوة ذات الحجم المحدد تتيح التعرف بسهولة على كمية المنتج قبل الاختيار. يظل وصفه هنا مرتبطاً بما يورده الاسم: زيت من بالمرز، بزبدة الكاكاو، مخصص للعناية بالجسم. لا تُفترض خصائص أو مكونات إضافية غير مذكورة، وتُراعى احتياجات البشرة عند إدخاله في الروتين.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;زيت للعناية ببشرة الجسم.&lt;/li&gt;&lt;li&gt;يتضمن الاسم زبدة الكاكاو.&lt;/li&gt;&lt;li&gt;عبوة بحجم 150 مل.&lt;/li&gt;&lt;li&gt;صيغة زيت للاستخدام الموضعي وفق الملصق.&lt;/li&gt;&lt;li&gt;بديل بصيغة الزيت لمن يختارون مستحضرات الجسم السائلة.&lt;/li&gt;&lt;li&gt;من علامة بالمرز.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يفضلون الزيوت في روتين العناية بالجسم.&lt;/li&gt;&lt;li&gt;للمهتمين بمنتج يذكر زبدة الكاكاو في اسمه.&lt;/li&gt;&lt;li&gt;لمن يبحثون عن عبوة زيت بحجم 150 مل.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;يُستخدم الزيت وفق التعليمات الواردة على العبوة. إذا سمحت الإرشادات بذلك، توضع كمية مناسبة على البشرة وتوزع برفق، مع تجنب الإفراط في الكمية لتفادي بقاء فائض على الجلد أو الأسطح. تأكدي من ملاءمته للمنطقة المراد استخدامها قبل تطبيقه على مساحة واسعة.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستعمال الخارجي فقط، وتجنبي ملامسة العينين. أبقي العبوة في مكان بعيد عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;بالمرز هي العلامة الظاهرة على عبوة زيت زبدة الكاكاو، ويُكتب اسمها بالإنجليزية Palmer's. يتوفر المنتج في هذا الإصدار بحجم 150 مل، وتُراجع معلومات الاستعمال الإضافية على العبوة.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;هل يأتي المنتج على هيئة كريم؟&lt;/p&gt;&lt;p&gt;لا، تصفه التسمية بأنه زيت للعناية بالجسم.&lt;/p&gt;&lt;p&gt;ما الحجم الوارد في الاسم؟&lt;/p&gt;&lt;p&gt;حجم العبوة 150 مل.&lt;/p&gt;&lt;p&gt;ما المعلومة المرتبطة بزبدة الكاكاو؟&lt;/p&gt;&lt;p&gt;ترد زبدة الكاكاو في اسم المنتج، من دون تفاصيل أخرى عن تركيبته في الاسم المعروض.&lt;/p&gt;&lt;p&gt;هل يصلح استخدامه على الوجه؟&lt;/p&gt;&lt;p&gt;يُصنف هنا زيتاً للجسم؛ راجعي العبوة قبل استخدامه على أي منطقة أخرى.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5780,7 +5790,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>MNT-R64</t>
+          <t>MNT-R66</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -5817,22 +5827,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>بالمرز لعلامات التمدد 125 جرام</t>
+          <t>بالمرز زيت العناية بالبشرة عطر ثمر الورد 60مل</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>العناية والجمال &gt; العناية بالجسم</t>
+          <t>العناية والجمال &gt; العناية بالبشرة &gt; زيوت وزبدات</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71S2urregML.jpg</t>
+          <t>https://m.media-amazon.com/images/I/5173EMbdpfL.jpg</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>بالمرز لعلامات التمدد 125 جرام</t>
+          <t>بالمرز زيت العناية بالبشرة عطر ثمر الورد 60مل</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -5842,12 +5852,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>&lt;p&gt;كريم بالمرز لعلامات التمدد 125 جرام، Palmer's Stretch Marks Cream، من علامة بالمرز، كريم جسم بحجم 125 جرام.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | كريم بالمرز لعلامات التمدد&lt;/li&gt;&lt;li&gt;النوع | كريم جسم&lt;/li&gt;&lt;li&gt;الحجم | 125 جرام&lt;/li&gt;&lt;li&gt;العلامة التجارية | بالمرز&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;يأتي هذا المنتج من بالمرز في صورة كريم للجسم، ويشير اسمه إلى علامات التمدد بوصفها مجال العناية المرتبط به. تحتوي العبوة على 125 جراماً، ما يجعلها خياراً واضحاً لمن يبحثون عن كريم بهذا الاسم والحجم ضمن مستحضرات العناية الشخصية.&lt;/p&gt;&lt;p&gt;يمكن تخصيصه لخطوات العناية بالبشرة وفق تعليمات العبوة، مع عدم افتراض نتائج أو خصائص غير واردة في المعلومات المتاحة. تختلف طريقة الاستخدام بحسب إرشادات المنتج، لذلك يُنصح بقراءتها قبل البدء، خصوصاً عند استخدامه للمرة الأولى أو عند إدخاله في روتين قائم.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;كريم جسم يرتبط اسمه بعلامات التمدد.&lt;/li&gt;&lt;li&gt;وزن العبوة 125 جراماً.&lt;/li&gt;&lt;li&gt;صيغة كريمية للاستخدام الموضعي على البشرة.&lt;/li&gt;&lt;li&gt;يناسب إدراجه ضمن روتين العناية بالجسم.&lt;/li&gt;&lt;li&gt;يحمل علامة بالمرز التجارية.&lt;/li&gt;&lt;li&gt;لا يذكر الاسم درجة لونية أو قياساً آخر.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يفضلون كريمات الجسم المخصصة للعناية بالبشرة.&lt;/li&gt;&lt;li&gt;لمن يبحثون عن منتج يحمل علامات التمدد في تسميته.&lt;/li&gt;&lt;li&gt;للراغبين في اختيار عبوة بوزن 125 جراماً.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;اتبعي إرشادات العبوة بشأن الكمية والمواضع المقترحة وتكرار الاستخدام. عند التطبيق، وزعي الكريم برفق على بشرة نظيفة في المنطقة المراد العناية بها، من دون الضغط أو الفرك القوي. تجنبي استعماله على مناطق لم ترد ضمن التعليمات، وأوقفي الاستخدام إذا ظهر تهيج.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;مخصص للاستعمال الخارجي فقط، ويجب تجنب وصوله إلى العينين. يُحفظ بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;يظهر اسم بالمرز بالعربية وPalmer's بالإنجليزية على تعريف المنتج. هذا الإصدار هو كريم للجسم مرتبط اسمه بعلامات التمدد، ويتوفر بوزن 125 جراماً؛ أما إرشادات الاستعمال التفصيلية فتُراجع على العبوة.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;هل يختلف هذا المنتج عن كريم بالمرز لعلامات تمدد الجلد؟&lt;/p&gt;&lt;p&gt;الاسمان يصفان كريم بالمرز المرتبط بعلامات التمدد، والعبوة المحددة هنا بوزن 125 جراماً.&lt;/p&gt;&lt;p&gt;هل يمكن استخدامه على كل مناطق الجسم؟&lt;/p&gt;&lt;p&gt;يُرجى تحديد مواضع الاستعمال بالرجوع إلى تعليمات المنتج المطبوعة على العبوة.&lt;/p&gt;&lt;p&gt;هل يحتوي المنتج على درجة؟&lt;/p&gt;&lt;p&gt;لا توجد درجة لونية في الاسم؛ فهو كريم للعناية بالجسم.&lt;/p&gt;&lt;p&gt;ما أهم معلومة قبل الاستخدام؟&lt;/p&gt;&lt;p&gt;قراءة الملصق للتحقق من طريقة التطبيق والموضع والتكرار الموصى به.&lt;/p&gt;</t>
+          <t>&lt;p&gt;زيت بالمرز للعناية بالبشرة بعطر ثمر الورد 60 مل، Palmer's Skin Care Oil Rosehip Fragrance، من علامة بالمرز، زيت عناية بحجم 60 مل.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | زيت بالمرز للعناية بالبشرة بعطر ثمر الورد&lt;/li&gt;&lt;li&gt;النوع | زيت عناية بالبشرة&lt;/li&gt;&lt;li&gt;الحجم | 60 مل&lt;/li&gt;&lt;li&gt;العلامة التجارية | بالمرز&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;زيت من بالمرز للعناية بالبشرة، يرد عطر ثمر الورد في اسمه، ويتوفر بعبوة 60 مل. يجمع تعريفه بين صيغة الزيت ووصف الرائحة المذكور في التسمية، من دون افتراض مكونات أو خصائص أخرى غير موضحة في الاسم. يمكن إدراجه ضمن روتين العناية بالبشرة بحسب تعليمات العبوة.&lt;/p&gt;&lt;p&gt;يُعد الحجم الصغير تفصيلاً عملياً عند المقارنة بين مستحضرات العناية، كما تتيح صيغة الزيت اختيار أسلوب تطبيق يناسب المستخدم. قبل الاستخدام، راجعي بيانات العبوة لمعرفة المناطق المقترحة وطريقة التوزيع، وجرّبي المنتج على مساحة محدودة إذا لم يسبق لك استخدامه.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;زيت مخصص للعناية بالبشرة.&lt;/li&gt;&lt;li&gt;يذكر الاسم عطر ثمر الورد.&lt;/li&gt;&lt;li&gt;عبوة بحجم 60 مل.&lt;/li&gt;&lt;li&gt;صيغة زيت للاستخدام الخارجي وفق التعليمات.&lt;/li&gt;&lt;li&gt;يمكن إضافته إلى روتين العناية بالبشرة.&lt;/li&gt;&lt;li&gt;من علامة بالمرز التجارية.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يفضلون مستحضرات العناية بالبشرة بصيغة الزيت.&lt;/li&gt;&lt;li&gt;لمن يبحثون عن منتج يذكر عطر ثمر الورد في اسمه.&lt;/li&gt;&lt;li&gt;للمهتمين بعبوة عناية بحجم 60 مل.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;اتبعي إرشادات العبوة قبل وضع الزيت، ولا تستخدميه على الوجه أو الجسم إلا إذا كانت التعليمات تشير إلى ذلك. توزع كمية قليلة على البشرة بالطريقة الموضحة على الملصق، مع تجنب ملامسة العينين والأغشية الحساسة. اتركيه للاستخدام المحدد على العبوة، ولا تخلطيه مع منتجات أخرى ما لم تسمح التعليمات بذلك.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، مع الحرص على عدم وصوله إلى العينين. يُحفظ بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;يحمل المنتج اسم بالمرز بالعربية وPalmer's بالإنجليزية، ويُعرض هنا كزيت للعناية بالبشرة بحجم 60 مل. يرد وصف عطر ثمر الورد ضمن اسم هذا الإصدار، وتُراجع العبوة لمعرفة بياناته الإضافية.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما صيغة المنتج؟&lt;/p&gt;&lt;p&gt;هو زيت للعناية بالبشرة، وليس كريماً أو لوشناً بحسب الاسم الوارد.&lt;/p&gt;&lt;p&gt;هل يذكر الاسم رائحة؟&lt;/p&gt;&lt;p&gt;نعم، يرد عطر ثمر الورد ضمن تسمية المنتج.&lt;/p&gt;&lt;p&gt;ما الحجم المتوفر؟&lt;/p&gt;&lt;p&gt;يأتي هذا الإصدار بعبوة حجمها 60 مل.&lt;/p&gt;&lt;p&gt;هل يمكن استعماله على الوجه؟&lt;/p&gt;&lt;p&gt;لا يحدد الاسم موضع التطبيق؛ تحققي من تعليمات العبوة قبل استخدامه على الوجه.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -5857,7 +5867,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>MNT-R65</t>
+          <t>MNT-R67</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -5894,7 +5904,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>بالمرز زيت بزبدة الكاكاو 150 مل</t>
+          <t>زيت مرطب للجسم من بالمرز 250 مل</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5904,12 +5914,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0749/1387/4134/files/4153_Front_4cee072f-ab2c-4c9e-8475-f1c4eeb5e991.webp?v=1758903849&amp;width=1000&amp;height=1000&amp;crop=center</t>
+          <t>https://cdn.shopify.com/s/files/1/0749/1387/4134/files/3227.jpg?v=1748505207</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>بالمرز زيت بزبدة الكاكاو 150 مل</t>
+          <t>زيت مرطب للجسم من بالمرز 250 مل</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -5919,12 +5929,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>&lt;p&gt;زيت بالمرز بزبدة الكاكاو 150 مل، Palmer's Cocoa Butter Oil، من علامة بالمرز، زيت للعناية بالجسم بحجم 150 مل.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | زيت بالمرز بزبدة الكاكاو&lt;/li&gt;&lt;li&gt;النوع | زيت جسم&lt;/li&gt;&lt;li&gt;الحجم | 150 مل&lt;/li&gt;&lt;li&gt;العلامة التجارية | بالمرز&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;زيت عناية للجسم يحمل زبدة الكاكاو ضمن اسمه، ويأتي من بالمرز في عبوة حجمها 150 مل. تمنح صيغة الزيت طريقة مختلفة عن الكريمات في تطبيق مستحضرات الجسم، ويمكن تخصيصه لخطوة العناية التي تناسب تفضيلاتك، مع الرجوع إلى الملصق لمعرفة التعليمات التفصيلية.&lt;/p&gt;&lt;p&gt;العبوة ذات الحجم المحدد تتيح التعرف بسهولة على كمية المنتج قبل الاختيار. يظل وصفه هنا مرتبطاً بما يورده الاسم: زيت من بالمرز، بزبدة الكاكاو، مخصص للعناية بالجسم. لا تُفترض خصائص أو مكونات إضافية غير مذكورة، وتُراعى احتياجات البشرة عند إدخاله في الروتين.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;زيت للعناية ببشرة الجسم.&lt;/li&gt;&lt;li&gt;يتضمن الاسم زبدة الكاكاو.&lt;/li&gt;&lt;li&gt;عبوة بحجم 150 مل.&lt;/li&gt;&lt;li&gt;صيغة زيت للاستخدام الموضعي وفق الملصق.&lt;/li&gt;&lt;li&gt;بديل بصيغة الزيت لمن يختارون مستحضرات الجسم السائلة.&lt;/li&gt;&lt;li&gt;من علامة بالمرز.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يفضلون الزيوت في روتين العناية بالجسم.&lt;/li&gt;&lt;li&gt;للمهتمين بمنتج يذكر زبدة الكاكاو في اسمه.&lt;/li&gt;&lt;li&gt;لمن يبحثون عن عبوة زيت بحجم 150 مل.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;يُستخدم الزيت وفق التعليمات الواردة على العبوة. إذا سمحت الإرشادات بذلك، توضع كمية مناسبة على البشرة وتوزع برفق، مع تجنب الإفراط في الكمية لتفادي بقاء فائض على الجلد أو الأسطح. تأكدي من ملاءمته للمنطقة المراد استخدامها قبل تطبيقه على مساحة واسعة.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستعمال الخارجي فقط، وتجنبي ملامسة العينين. أبقي العبوة في مكان بعيد عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;بالمرز هي العلامة الظاهرة على عبوة زيت زبدة الكاكاو، ويُكتب اسمها بالإنجليزية Palmer's. يتوفر المنتج في هذا الإصدار بحجم 150 مل، وتُراجع معلومات الاستعمال الإضافية على العبوة.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;هل يأتي المنتج على هيئة كريم؟&lt;/p&gt;&lt;p&gt;لا، تصفه التسمية بأنه زيت للعناية بالجسم.&lt;/p&gt;&lt;p&gt;ما الحجم الوارد في الاسم؟&lt;/p&gt;&lt;p&gt;حجم العبوة 150 مل.&lt;/p&gt;&lt;p&gt;ما المعلومة المرتبطة بزبدة الكاكاو؟&lt;/p&gt;&lt;p&gt;ترد زبدة الكاكاو في اسم المنتج، من دون تفاصيل أخرى عن تركيبته في الاسم المعروض.&lt;/p&gt;&lt;p&gt;هل يصلح استخدامه على الوجه؟&lt;/p&gt;&lt;p&gt;يُصنف هنا زيتاً للجسم؛ راجعي العبوة قبل استخدامه على أي منطقة أخرى.&lt;/p&gt;</t>
+          <t>&lt;p&gt;زيت مرطب للجسم من بالمرز 250 مل، Palmer's Moisturizing Body Oil، من علامة بالمرز، زيت للجسم بحجم 250 مل.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | زيت مرطب للجسم من بالمرز&lt;/li&gt;&lt;li&gt;النوع | زيت جسم&lt;/li&gt;&lt;li&gt;الحجم | 250 مل&lt;/li&gt;&lt;li&gt;العلامة التجارية | بالمرز&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;زيت للجسم يحمل وصف المرطب ضمن اسمه، وتقدمه علامة بالمرز بحجم 250 مل. تمنح تسمية المنتج دلالة واضحة على صيغته واستخدامه المعلن للعناية بالجسم، فيما توفر العبوة حجماً محدداً يسهل أخذه في الحسبان عند تنظيم مستحضرات العناية اليومية.&lt;/p&gt;&lt;p&gt;يمكن توزيع الزيت على البشرة بالطريقة التي توضحها الشركة على العبوة، مع الانتباه إلى أن صيغة الزيت تختلف في طريقة التعامل معها عن الكريمات. لا ترد في الاسم معلومات أخرى عن الرائحة أو المكونات أو خصائص إضافية، لذا يُعتمد على الملصق لاستكمال التفاصيل قبل الاستخدام.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;زيت موصوف بأنه مرطب للجسم ضمن الاسم.&lt;/li&gt;&lt;li&gt;عبوة كبيرة نسبياً بحجم 250 مل.&lt;/li&gt;&lt;li&gt;صيغة زيت للعناية بالبشرة.&lt;/li&gt;&lt;li&gt;يمكن إدراجه ضمن خطوات العناية بالجسم.&lt;/li&gt;&lt;li&gt;يوضح الاسم مجال استخدام المنتج.&lt;/li&gt;&lt;li&gt;من علامة بالمرز.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يفضلون الزيوت ضمن مستحضرات العناية بالجسم.&lt;/li&gt;&lt;li&gt;للمهتمين بمنتج يحمل وصف الترطيب للجسم في اسمه.&lt;/li&gt;&lt;li&gt;لمن يبحثون عن عبوة بحجم 250 مل.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;يُستخدم بحسب الإرشادات المكتوبة على العبوة. يمكن توزيع كمية مناسبة على البشرة بالطريقة الموضحة، مع مراعاة أن الزيت قد يترك أثراً على الملابس أو الأسطح قبل جفافه، لذلك يُنتظر وفق تعليمات المنتج قبل ارتداء الملابس. تجنبي استخدام كمية أكبر من الحاجة، ولا يوضع على الوجه إلا إذا ورد ذلك على الملصق.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط؛ تجنبي ملامسة العينين. احفظي العبوة بعيداً عن متناول الأطفال وأغلقيها بعد الاستخدام.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;بالمرز هي العلامة التي يحملها هذا الزيت المخصص للجسم، ويظهر اسمها بالإنجليزية Palmer's. يتوفر المنتج بعبوة 250 مل، ويمكن الرجوع إلى المعلومات المطبوعة عليها لمعرفة بيانات الاستخدام الأخرى.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع هذا المستحضر؟&lt;/p&gt;&lt;p&gt;زيت للجسم، ويذكر الاسم وصف الترطيب.&lt;/p&gt;&lt;p&gt;ما حجم العبوة؟&lt;/p&gt;&lt;p&gt;يبلغ حجمها 250 مل.&lt;/p&gt;&lt;p&gt;هل يذكر الاسم عطرًا محدداً؟&lt;/p&gt;&lt;p&gt;لا، لا يذكر الاسم المعروض رائحة أو عطراً بعينه.&lt;/p&gt;&lt;p&gt;كيف أتعرف على طريقة الاستخدام؟&lt;/p&gt;&lt;p&gt;راجعي الملصق المرفق بالعبوة لمعرفة كيفية التوزيع وأي توجيهات خاصة بالاستعمال.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -5934,7 +5944,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>MNT-R66</t>
+          <t>MNT-R68</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -5971,22 +5981,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>بالمرز زيت العناية بالبشرة عطر ثمر الورد 60مل</t>
+          <t>بالمرز زيت الجسم بزبدة الكاكو ثمرة الورد150مل</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>العناية والجمال &gt; العناية بالبشرة &gt; زيوت وزبدات</t>
+          <t>العناية والجمال &gt; العناية بالجسم</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/5173EMbdpfL.jpg</t>
+          <t>https://m.media-amazon.com/images/I/712ePqXZqUL.jpg</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>بالمرز زيت العناية بالبشرة عطر ثمر الورد 60مل</t>
+          <t>بالمرز زيت الجسم بزبدة الكاكو ثمرة الورد150مل</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5996,12 +6006,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>58</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>&lt;p&gt;زيت بالمرز للعناية بالبشرة بعطر ثمر الورد 60 مل، Palmer's Skin Care Oil Rosehip Fragrance، من علامة بالمرز، زيت عناية بحجم 60 مل.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | زيت بالمرز للعناية بالبشرة بعطر ثمر الورد&lt;/li&gt;&lt;li&gt;النوع | زيت عناية بالبشرة&lt;/li&gt;&lt;li&gt;الحجم | 60 مل&lt;/li&gt;&lt;li&gt;العلامة التجارية | بالمرز&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;زيت من بالمرز للعناية بالبشرة، يرد عطر ثمر الورد في اسمه، ويتوفر بعبوة 60 مل. يجمع تعريفه بين صيغة الزيت ووصف الرائحة المذكور في التسمية، من دون افتراض مكونات أو خصائص أخرى غير موضحة في الاسم. يمكن إدراجه ضمن روتين العناية بالبشرة بحسب تعليمات العبوة.&lt;/p&gt;&lt;p&gt;يُعد الحجم الصغير تفصيلاً عملياً عند المقارنة بين مستحضرات العناية، كما تتيح صيغة الزيت اختيار أسلوب تطبيق يناسب المستخدم. قبل الاستخدام، راجعي بيانات العبوة لمعرفة المناطق المقترحة وطريقة التوزيع، وجرّبي المنتج على مساحة محدودة إذا لم يسبق لك استخدامه.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;زيت مخصص للعناية بالبشرة.&lt;/li&gt;&lt;li&gt;يذكر الاسم عطر ثمر الورد.&lt;/li&gt;&lt;li&gt;عبوة بحجم 60 مل.&lt;/li&gt;&lt;li&gt;صيغة زيت للاستخدام الخارجي وفق التعليمات.&lt;/li&gt;&lt;li&gt;يمكن إضافته إلى روتين العناية بالبشرة.&lt;/li&gt;&lt;li&gt;من علامة بالمرز التجارية.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يفضلون مستحضرات العناية بالبشرة بصيغة الزيت.&lt;/li&gt;&lt;li&gt;لمن يبحثون عن منتج يذكر عطر ثمر الورد في اسمه.&lt;/li&gt;&lt;li&gt;للمهتمين بعبوة عناية بحجم 60 مل.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;اتبعي إرشادات العبوة قبل وضع الزيت، ولا تستخدميه على الوجه أو الجسم إلا إذا كانت التعليمات تشير إلى ذلك. توزع كمية قليلة على البشرة بالطريقة الموضحة على الملصق، مع تجنب ملامسة العينين والأغشية الحساسة. اتركيه للاستخدام المحدد على العبوة، ولا تخلطيه مع منتجات أخرى ما لم تسمح التعليمات بذلك.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، مع الحرص على عدم وصوله إلى العينين. يُحفظ بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;يحمل المنتج اسم بالمرز بالعربية وPalmer's بالإنجليزية، ويُعرض هنا كزيت للعناية بالبشرة بحجم 60 مل. يرد وصف عطر ثمر الورد ضمن اسم هذا الإصدار، وتُراجع العبوة لمعرفة بياناته الإضافية.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما صيغة المنتج؟&lt;/p&gt;&lt;p&gt;هو زيت للعناية بالبشرة، وليس كريماً أو لوشناً بحسب الاسم الوارد.&lt;/p&gt;&lt;p&gt;هل يذكر الاسم رائحة؟&lt;/p&gt;&lt;p&gt;نعم، يرد عطر ثمر الورد ضمن تسمية المنتج.&lt;/p&gt;&lt;p&gt;ما الحجم المتوفر؟&lt;/p&gt;&lt;p&gt;يأتي هذا الإصدار بعبوة حجمها 60 مل.&lt;/p&gt;&lt;p&gt;هل يمكن استعماله على الوجه؟&lt;/p&gt;&lt;p&gt;لا يحدد الاسم موضع التطبيق؛ تحققي من تعليمات العبوة قبل استخدامه على الوجه.&lt;/p&gt;</t>
+          <t>&lt;p&gt;زيت الجسم بالمرز بزبدة الكاكاو وثمرة الورد 150 مل، Palmer's Cocoa Butter Rosehip Body Oil، من علامة بالمرز، زيت جسم بحجم 150 مل.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | زيت الجسم بالمرز بزبدة الكاكاو وثمرة الورد&lt;/li&gt;&lt;li&gt;النوع | زيت جسم&lt;/li&gt;&lt;li&gt;الحجم | 150 مل&lt;/li&gt;&lt;li&gt;العلامة التجارية | بالمرز&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;زيت للجسم من بالمرز، يذكر في اسمه زبدة الكاكاو وثمرة الورد، ويتوفر بحجم 150 مل. يساعد هذا الوصف على تمييزه عن زيوت الجسم الأخرى في المجموعة، من دون إضافة تفاصيل عن مكونات أو خصائص لم يوردها الاسم المعروض. تُعتمد معلومات العبوة لمعرفة طريقة الاستخدام المحددة.&lt;/p&gt;&lt;p&gt;تتيح صيغة الزيت إدراجه في روتين العناية بالجسم لمن يفضلون المستحضرات السائلة، ويُراعى عند استعماله توزيع كمية مناسبة بحسب الإرشادات. لا يذكر الاسم درجة أو لوناً، كما لا يوضح تفاصيل إضافية عن العطر؛ لذا تظل المعلومات المطبوعة على العبوة المرجع لاستكمال البيانات.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;زيت مخصص للعناية بالجسم.&lt;/li&gt;&lt;li&gt;يذكر الاسم زبدة الكاكاو وثمرة الورد.&lt;/li&gt;&lt;li&gt;عبوة بحجم 150 مل.&lt;/li&gt;&lt;li&gt;صيغة زيت قابلة للتوزيع على البشرة وفق الملصق.&lt;/li&gt;&lt;li&gt;يمكن إدخاله ضمن خطوات العناية الشخصية.&lt;/li&gt;&lt;li&gt;يحمل علامة بالمرز التجارية.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يختارون زيوت الجسم ضمن روتين العناية.&lt;/li&gt;&lt;li&gt;للمهتمين بمنتج يذكر زبدة الكاكاو وثمرة الورد في اسمه.&lt;/li&gt;&lt;li&gt;لمن يرغبون في عبوة بحجم 150 مل.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;اتبعي التعليمات المدونة على العبوة لتحديد طريقة وضع الزيت والمواضع المناسبة. توزع كمية ملائمة على البشرة وفق الإرشادات، مع الحرص على عدم ملامسة العينين وغسل اليدين بعد التطبيق إذا اقتضت الحاجة. يفضل التأكد من ملاءمته للبشرة على مساحة صغيرة قبل إدخاله في الاستخدام المعتاد.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. يُحفظ المنتج بعيداً عن متناول الأطفال، وتُغلق العبوة بإحكام بعد الاستخدام.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;يحمل هذا المنتج علامة بالمرز، ويظهر اسمها بالإنجليزية Palmer's. هذا الإصدار زيت جسم بحجم 150 مل، وترد زبدة الكاكاو وثمرة الورد ضمن اسمه كما هو معروض.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما صيغة المنتج؟&lt;/p&gt;&lt;p&gt;هو زيت مخصص للجسم، وليس كريماً بحسب الاسم الوارد.&lt;/p&gt;&lt;p&gt;ما العناصر التي يذكرها اسمه؟&lt;/p&gt;&lt;p&gt;يذكر زبدة الكاكاو وثمرة الورد ضمن التسمية، من دون تفاصيل إضافية في الاسم.&lt;/p&gt;&lt;p&gt;كم يبلغ حجم العبوة؟&lt;/p&gt;&lt;p&gt;حجم المنتج المذكور هو 150 مل.&lt;/p&gt;&lt;p&gt;هل يوضح الاسم مواضع الاستخدام؟&lt;/p&gt;&lt;p&gt;يصفه الاسم بأنه زيت للجسم، وتُراجع العبوة لمعرفة طريقة التطبيق والمواضع المحددة بالتفصيل.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6011,7 +6021,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>MNT-R67</t>
+          <t>MNT-R70</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6048,7 +6058,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>زيت مرطب للجسم من بالمرز 250 مل</t>
+          <t>بالمرز كريم القدمين ماجيك 60 جرام</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -6058,12 +6068,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0749/1387/4134/files/3227.jpg?v=1748505207</t>
+          <t>https://m.media-amazon.com/images/I/61RW8oipciL.jpg</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>زيت مرطب للجسم من بالمرز 250 مل</t>
+          <t>بالمرز كريم القدمين ماجيك 60 جرام</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -6073,12 +6083,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>&lt;p&gt;زيت مرطب للجسم من بالمرز 250 مل، Palmer's Moisturizing Body Oil، من علامة بالمرز، زيت للجسم بحجم 250 مل.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | زيت مرطب للجسم من بالمرز&lt;/li&gt;&lt;li&gt;النوع | زيت جسم&lt;/li&gt;&lt;li&gt;الحجم | 250 مل&lt;/li&gt;&lt;li&gt;العلامة التجارية | بالمرز&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;زيت للجسم يحمل وصف المرطب ضمن اسمه، وتقدمه علامة بالمرز بحجم 250 مل. تمنح تسمية المنتج دلالة واضحة على صيغته واستخدامه المعلن للعناية بالجسم، فيما توفر العبوة حجماً محدداً يسهل أخذه في الحسبان عند تنظيم مستحضرات العناية اليومية.&lt;/p&gt;&lt;p&gt;يمكن توزيع الزيت على البشرة بالطريقة التي توضحها الشركة على العبوة، مع الانتباه إلى أن صيغة الزيت تختلف في طريقة التعامل معها عن الكريمات. لا ترد في الاسم معلومات أخرى عن الرائحة أو المكونات أو خصائص إضافية، لذا يُعتمد على الملصق لاستكمال التفاصيل قبل الاستخدام.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;زيت موصوف بأنه مرطب للجسم ضمن الاسم.&lt;/li&gt;&lt;li&gt;عبوة كبيرة نسبياً بحجم 250 مل.&lt;/li&gt;&lt;li&gt;صيغة زيت للعناية بالبشرة.&lt;/li&gt;&lt;li&gt;يمكن إدراجه ضمن خطوات العناية بالجسم.&lt;/li&gt;&lt;li&gt;يوضح الاسم مجال استخدام المنتج.&lt;/li&gt;&lt;li&gt;من علامة بالمرز.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يفضلون الزيوت ضمن مستحضرات العناية بالجسم.&lt;/li&gt;&lt;li&gt;للمهتمين بمنتج يحمل وصف الترطيب للجسم في اسمه.&lt;/li&gt;&lt;li&gt;لمن يبحثون عن عبوة بحجم 250 مل.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;يُستخدم بحسب الإرشادات المكتوبة على العبوة. يمكن توزيع كمية مناسبة على البشرة بالطريقة الموضحة، مع مراعاة أن الزيت قد يترك أثراً على الملابس أو الأسطح قبل جفافه، لذلك يُنتظر وفق تعليمات المنتج قبل ارتداء الملابس. تجنبي استخدام كمية أكبر من الحاجة، ولا يوضع على الوجه إلا إذا ورد ذلك على الملصق.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط؛ تجنبي ملامسة العينين. احفظي العبوة بعيداً عن متناول الأطفال وأغلقيها بعد الاستخدام.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;بالمرز هي العلامة التي يحملها هذا الزيت المخصص للجسم، ويظهر اسمها بالإنجليزية Palmer's. يتوفر المنتج بعبوة 250 مل، ويمكن الرجوع إلى المعلومات المطبوعة عليها لمعرفة بيانات الاستخدام الأخرى.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع هذا المستحضر؟&lt;/p&gt;&lt;p&gt;زيت للجسم، ويذكر الاسم وصف الترطيب.&lt;/p&gt;&lt;p&gt;ما حجم العبوة؟&lt;/p&gt;&lt;p&gt;يبلغ حجمها 250 مل.&lt;/p&gt;&lt;p&gt;هل يذكر الاسم عطرًا محدداً؟&lt;/p&gt;&lt;p&gt;لا، لا يذكر الاسم المعروض رائحة أو عطراً بعينه.&lt;/p&gt;&lt;p&gt;كيف أتعرف على طريقة الاستخدام؟&lt;/p&gt;&lt;p&gt;راجعي الملصق المرفق بالعبوة لمعرفة كيفية التوزيع وأي توجيهات خاصة بالاستعمال.&lt;/p&gt;</t>
+          <t>كريم القدمين ماجيك من بالمرز Palmer's Magic Foot Cream، كريم للقدمين بحجم 60 جرام. يحمل الاسم وصف ماجيك، ويقدّم في عبوة مخصصة للعناية بالقدمين، مع تحديد العلامة التجارية والحجم في اسم المنتج.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | كريم القدمين ماجيك&lt;/li&gt;&lt;li&gt;النوع | كريم للقدمين&lt;/li&gt;&lt;li&gt;الحجم | 60 جرام&lt;/li&gt;&lt;li&gt;العلامة التجارية | بالمرز Palmer's&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;اختيار عملي ضمن مستحضرات العناية بالجسم، صُمم على هيئة كريم للقدمين ليدخل بسهولة في روتين العناية اليومي. يأتي باسم ماجيك من بالمرز، وتوضح بياناته الأساسية نوع المنتج وحجمه بوضوح، لتتمكني من التعرف إلى العبوة ومحتواها قبل الاستخدام.&lt;/p&gt;&lt;p&gt;يمكن توزيع الكريم على بشرة القدمين النظيفة مع تدليك لطيف حتى يتوزع على المنطقة المراد العناية بها. لا يتضمن الاسم تفاصيل إضافية عن مكونات المنتج أو درجة محددة، لذلك يُرجى الرجوع إلى بيانات العبوة للاطلاع على أي إرشادات أو معلومات تفصيلية أخرى.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;كريم مخصص للعناية بالقدمين.&lt;/li&gt;&lt;li&gt;يحمل اسم ماجيك كما ورد في المنتج.&lt;/li&gt;&lt;li&gt;يأتي من علامة بالمرز.&lt;/li&gt;&lt;li&gt;حجم العبوة محدد بـ 60 جرام.&lt;/li&gt;&lt;li&gt;يمكن إدراجه ضمن روتين العناية بالجسم.&lt;/li&gt;&lt;li&gt;قوام الكريم مناسب للتوزيع بالتدليك على القدمين.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن كريم مخصص لمنطقة القدمين.&lt;/li&gt;&lt;li&gt;لمن يفضل إضافة مستحضر للقدمين إلى روتين العناية الشخصي.&lt;/li&gt;&lt;li&gt;لمن يرغب في اختيار عبوة بحجم 60 جرام.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;توضع كمية مناسبة على بشرة القدمين النظيفة، ثم توزع بتدليك لطيف حتى تغطي المنطقة المطلوبة. يُستخدم وفق الإرشادات المدونة على العبوة، مع تجنب وضعه على المناطق التي لا تذكرها تعليمات المنتج.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، تجنب ملامسة العينين، وأبعد المنتج عن متناول الأطفال. أوقف الاستخدام عند ظهور تهيج، واتبع تعليمات العبوة.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;بالمرز هي العلامة التجارية المذكورة على هذا المنتج. يظهر اسمها مع كريم القدمين ماجيك في عبوة تحمل حجم 60 جرام.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع هذا المنتج؟&lt;/p&gt;&lt;p&gt;هو كريم للقدمين، ويظهر اسم ماجيك ضمن اسمه التجاري.&lt;/p&gt;&lt;p&gt;ما حجم العبوة؟&lt;/p&gt;&lt;p&gt;الحجم المذكور في اسم المنتج هو 60 جرام.&lt;/p&gt;&lt;p&gt;كيف أستخدم الكريم؟&lt;/p&gt;&lt;p&gt;يوزع على بشرة القدمين النظيفة مع تدليك لطيف، مع مراعاة تعليمات العبوة.&lt;/p&gt;&lt;p&gt;هل يحتوي الاسم على معلومات عن المكونات؟&lt;/p&gt;&lt;p&gt;لا يذكر الاسم مكونات محددة؛ يُرجى مراجعة العبوة للاطلاع على تفاصيل المنتج.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6088,7 +6098,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>MNT-R68</t>
+          <t>MNT-R71</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6125,7 +6135,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>بالمرز زيت الجسم بزبدة الكاكو ثمرة الورد150مل</t>
+          <t>بالمرز لوشن الجسم زبدة الشيا 250 مل</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -6135,12 +6145,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/712ePqXZqUL.jpg</t>
+          <t>https://m.media-amazon.com/images/I/61zej-kYbaL.jpg</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>بالمرز زيت الجسم بزبدة الكاكو ثمرة الورد150مل</t>
+          <t>بالمرز لوشن الجسم زبدة الشيا 250 مل</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -6150,12 +6160,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>&lt;p&gt;زيت الجسم بالمرز بزبدة الكاكاو وثمرة الورد 150 مل، Palmer's Cocoa Butter Rosehip Body Oil، من علامة بالمرز، زيت جسم بحجم 150 مل.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | زيت الجسم بالمرز بزبدة الكاكاو وثمرة الورد&lt;/li&gt;&lt;li&gt;النوع | زيت جسم&lt;/li&gt;&lt;li&gt;الحجم | 150 مل&lt;/li&gt;&lt;li&gt;العلامة التجارية | بالمرز&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;زيت للجسم من بالمرز، يذكر في اسمه زبدة الكاكاو وثمرة الورد، ويتوفر بحجم 150 مل. يساعد هذا الوصف على تمييزه عن زيوت الجسم الأخرى في المجموعة، من دون إضافة تفاصيل عن مكونات أو خصائص لم يوردها الاسم المعروض. تُعتمد معلومات العبوة لمعرفة طريقة الاستخدام المحددة.&lt;/p&gt;&lt;p&gt;تتيح صيغة الزيت إدراجه في روتين العناية بالجسم لمن يفضلون المستحضرات السائلة، ويُراعى عند استعماله توزيع كمية مناسبة بحسب الإرشادات. لا يذكر الاسم درجة أو لوناً، كما لا يوضح تفاصيل إضافية عن العطر؛ لذا تظل المعلومات المطبوعة على العبوة المرجع لاستكمال البيانات.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;زيت مخصص للعناية بالجسم.&lt;/li&gt;&lt;li&gt;يذكر الاسم زبدة الكاكاو وثمرة الورد.&lt;/li&gt;&lt;li&gt;عبوة بحجم 150 مل.&lt;/li&gt;&lt;li&gt;صيغة زيت قابلة للتوزيع على البشرة وفق الملصق.&lt;/li&gt;&lt;li&gt;يمكن إدخاله ضمن خطوات العناية الشخصية.&lt;/li&gt;&lt;li&gt;يحمل علامة بالمرز التجارية.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يختارون زيوت الجسم ضمن روتين العناية.&lt;/li&gt;&lt;li&gt;للمهتمين بمنتج يذكر زبدة الكاكاو وثمرة الورد في اسمه.&lt;/li&gt;&lt;li&gt;لمن يرغبون في عبوة بحجم 150 مل.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;اتبعي التعليمات المدونة على العبوة لتحديد طريقة وضع الزيت والمواضع المناسبة. توزع كمية ملائمة على البشرة وفق الإرشادات، مع الحرص على عدم ملامسة العينين وغسل اليدين بعد التطبيق إذا اقتضت الحاجة. يفضل التأكد من ملاءمته للبشرة على مساحة صغيرة قبل إدخاله في الاستخدام المعتاد.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. يُحفظ المنتج بعيداً عن متناول الأطفال، وتُغلق العبوة بإحكام بعد الاستخدام.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;يحمل هذا المنتج علامة بالمرز، ويظهر اسمها بالإنجليزية Palmer's. هذا الإصدار زيت جسم بحجم 150 مل، وترد زبدة الكاكاو وثمرة الورد ضمن اسمه كما هو معروض.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما صيغة المنتج؟&lt;/p&gt;&lt;p&gt;هو زيت مخصص للجسم، وليس كريماً بحسب الاسم الوارد.&lt;/p&gt;&lt;p&gt;ما العناصر التي يذكرها اسمه؟&lt;/p&gt;&lt;p&gt;يذكر زبدة الكاكاو وثمرة الورد ضمن التسمية، من دون تفاصيل إضافية في الاسم.&lt;/p&gt;&lt;p&gt;كم يبلغ حجم العبوة؟&lt;/p&gt;&lt;p&gt;حجم المنتج المذكور هو 150 مل.&lt;/p&gt;&lt;p&gt;هل يوضح الاسم مواضع الاستخدام؟&lt;/p&gt;&lt;p&gt;يصفه الاسم بأنه زيت للجسم، وتُراجع العبوة لمعرفة طريقة التطبيق والمواضع المحددة بالتفصيل.&lt;/p&gt;</t>
+          <t>لوشن الجسم بزبدة الشيا من بالمرز Palmer's Shea Butter Body Lotion، لوشن للجسم بحجم 250 مل. يذكر اسم المنتج زبدة الشيا بوصفها جزءًا من اسمه، ويحدد شكل المستحضر وحجمه والعلامة التجارية.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | لوشن الجسم بزبدة الشيا&lt;/li&gt;&lt;li&gt;النوع | لوشن للجسم&lt;/li&gt;&lt;li&gt;الحجم | 250 مل&lt;/li&gt;&lt;li&gt;العلامة التجارية | بالمرز Palmer's&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;يأتي هذا المستحضر من بالمرز بصيغة لوشن مخصص للجسم، ويحمل اسم زبدة الشيا كما ورد في بيانات المنتج. يتيح شكل اللوشن توزيعه على البشرة ضمن روتين العناية المعتاد، فيما تساعد معلومات الحجم والعلامة التجارية على تمييز العبوة عند اختيار مستحضرات الجسم.&lt;/p&gt;&lt;p&gt;يمكن استخدامه على بشرة الجسم بالطريقة الموضحة على العبوة، مع توزيع كمية مناسبة على المنطقة المطلوبة. لا يحدد الاسم تفاصيل عن نسبة زبدة الشيا أو مكونات أخرى، لذلك تظل بيانات العبوة المرجع لمعرفة أي معلومات إضافية تخص المنتج.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لوشن مخصص للاستخدام على الجسم.&lt;/li&gt;&lt;li&gt;يحمل اسم زبدة الشيا ضمن وصف المنتج.&lt;/li&gt;&lt;li&gt;من علامة بالمرز التجارية.&lt;/li&gt;&lt;li&gt;يأتي في عبوة بحجم 250 مل.&lt;/li&gt;&lt;li&gt;يمكن إدخاله ضمن روتين العناية اليومية بالجسم.&lt;/li&gt;&lt;li&gt;صيغة اللوشن تتيح توزيعه على البشرة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يفضل استخدام اللوشن ضمن روتين العناية بالجسم.&lt;/li&gt;&lt;li&gt;لمن يبحث عن منتج يذكر زبدة الشيا في اسمه.&lt;/li&gt;&lt;li&gt;لمن يرغب في عبوة بحجم 250 مل من بالمرز.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;يوزع مقدار مناسب على بشرة الجسم، ثم يمرر بلطف على المنطقة المراد العناية بها. يُستخدم بحسب إرشادات العبوة، ويُترك أو يُغسل وفق ما توضحه تعليمات المنتج، إذ لا يذكر الاسم طريقة تفصيلية للاستخدام.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، تجنب ملامسة العينين، وأبعد المنتج عن متناول الأطفال. راجعي تعليمات العبوة قبل الاستخدام، وتوقفي عنه عند حدوث تهيج.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;بالمرز هي العلامة التجارية الواردة في اسم هذا اللوشن. يظهر المنتج تحت اسمها مع الإشارة إلى زبدة الشيا وحجم العبوة البالغ 250 مل.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع المستحضر؟&lt;/p&gt;&lt;p&gt;هو لوشن للجسم، ويذكر اسم زبدة الشيا ضمن تعريف المنتج.&lt;/p&gt;&lt;p&gt;ما الحجم المكتوب للعبوة؟&lt;/p&gt;&lt;p&gt;الحجم الوارد في اسم المنتج هو 250 مل.&lt;/p&gt;&lt;p&gt;هل يذكر الاسم مكونات أخرى؟&lt;/p&gt;&lt;p&gt;لا يحدد الاسم مكونات أخرى أو نسبًا، ويُرجى الرجوع إلى بيانات العبوة للتفاصيل.&lt;/p&gt;&lt;p&gt;كيف يوضع اللوشن؟&lt;/p&gt;&lt;p&gt;يوزع على بشرة الجسم وفق طريقة الاستخدام الموضحة على العبوة.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6165,7 +6175,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>MNT-R70</t>
+          <t>MNT-R72</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6202,22 +6212,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>بالمرز كريم القدمين ماجيك 60 جرام</t>
+          <t>كريم مغذي للشعر ضد القشره من بالمرز - 150 جم</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>العناية والجمال &gt; العناية بالجسم</t>
+          <t>العناية والجمال &gt; العناية بالشعر</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/61RW8oipciL.jpg</t>
+          <t>https://m.media-amazon.com/images/I/71BLb2r6SBL.jpg</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>بالمرز كريم القدمين ماجيك 60 جرام</t>
+          <t>كريم مغذي للشعر ضد القشره من بالمرز - 150 جم</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -6227,12 +6237,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>كريم القدمين ماجيك من بالمرز Palmer's Magic Foot Cream، كريم للقدمين بحجم 60 جرام. يحمل الاسم وصف ماجيك، ويقدّم في عبوة مخصصة للعناية بالقدمين، مع تحديد العلامة التجارية والحجم في اسم المنتج.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | كريم القدمين ماجيك&lt;/li&gt;&lt;li&gt;النوع | كريم للقدمين&lt;/li&gt;&lt;li&gt;الحجم | 60 جرام&lt;/li&gt;&lt;li&gt;العلامة التجارية | بالمرز Palmer's&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;اختيار عملي ضمن مستحضرات العناية بالجسم، صُمم على هيئة كريم للقدمين ليدخل بسهولة في روتين العناية اليومي. يأتي باسم ماجيك من بالمرز، وتوضح بياناته الأساسية نوع المنتج وحجمه بوضوح، لتتمكني من التعرف إلى العبوة ومحتواها قبل الاستخدام.&lt;/p&gt;&lt;p&gt;يمكن توزيع الكريم على بشرة القدمين النظيفة مع تدليك لطيف حتى يتوزع على المنطقة المراد العناية بها. لا يتضمن الاسم تفاصيل إضافية عن مكونات المنتج أو درجة محددة، لذلك يُرجى الرجوع إلى بيانات العبوة للاطلاع على أي إرشادات أو معلومات تفصيلية أخرى.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;كريم مخصص للعناية بالقدمين.&lt;/li&gt;&lt;li&gt;يحمل اسم ماجيك كما ورد في المنتج.&lt;/li&gt;&lt;li&gt;يأتي من علامة بالمرز.&lt;/li&gt;&lt;li&gt;حجم العبوة محدد بـ 60 جرام.&lt;/li&gt;&lt;li&gt;يمكن إدراجه ضمن روتين العناية بالجسم.&lt;/li&gt;&lt;li&gt;قوام الكريم مناسب للتوزيع بالتدليك على القدمين.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن كريم مخصص لمنطقة القدمين.&lt;/li&gt;&lt;li&gt;لمن يفضل إضافة مستحضر للقدمين إلى روتين العناية الشخصي.&lt;/li&gt;&lt;li&gt;لمن يرغب في اختيار عبوة بحجم 60 جرام.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;توضع كمية مناسبة على بشرة القدمين النظيفة، ثم توزع بتدليك لطيف حتى تغطي المنطقة المطلوبة. يُستخدم وفق الإرشادات المدونة على العبوة، مع تجنب وضعه على المناطق التي لا تذكرها تعليمات المنتج.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، تجنب ملامسة العينين، وأبعد المنتج عن متناول الأطفال. أوقف الاستخدام عند ظهور تهيج، واتبع تعليمات العبوة.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;بالمرز هي العلامة التجارية المذكورة على هذا المنتج. يظهر اسمها مع كريم القدمين ماجيك في عبوة تحمل حجم 60 جرام.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع هذا المنتج؟&lt;/p&gt;&lt;p&gt;هو كريم للقدمين، ويظهر اسم ماجيك ضمن اسمه التجاري.&lt;/p&gt;&lt;p&gt;ما حجم العبوة؟&lt;/p&gt;&lt;p&gt;الحجم المذكور في اسم المنتج هو 60 جرام.&lt;/p&gt;&lt;p&gt;كيف أستخدم الكريم؟&lt;/p&gt;&lt;p&gt;يوزع على بشرة القدمين النظيفة مع تدليك لطيف، مع مراعاة تعليمات العبوة.&lt;/p&gt;&lt;p&gt;هل يحتوي الاسم على معلومات عن المكونات؟&lt;/p&gt;&lt;p&gt;لا يذكر الاسم مكونات محددة؛ يُرجى مراجعة العبوة للاطلاع على تفاصيل المنتج.&lt;/p&gt;</t>
+          <t>كريم مغذي للشعر ضد القشرة من بالمرز Palmer's Nourishing Anti-Dandruff Hair Cream، كريم للشعر بحجم 150 جم. يجمع اسم المنتج بين وصف مغذٍ للشعر والإشارة إلى القشرة، من دون أن يحدد تفاصيل عن مكونات الكريم أو طريقة استخدامه الدقيقة.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | كريم مغذي للشعر ضد القشرة&lt;/li&gt;&lt;li&gt;النوع | كريم للشعر&lt;/li&gt;&lt;li&gt;الحجم | 150 جم&lt;/li&gt;&lt;li&gt;العلامة التجارية | بالمرز Palmer's&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;يأتي هذا الكريم من بالمرز ضمن مستحضرات العناية بالشعر، ويحمل في اسمه وصفًا مغذيًا وإشارة إلى القشرة. يوضح الاسم حجم العبوة، 150 جم، ونوع المنتج بوصفه كريمًا، بينما تبقى تفاصيل التركيبة وطريقة التطبيق الدقيقة مرتبطة بما هو مدون على العبوة.&lt;/p&gt;&lt;p&gt;يمكن استخدامه للعناية بالشعر وفق التعليمات المرفقة بالمنتج. ولأن الاسم لا يحدد موضع وضع الكريم أو مدة بقائه أو عدد مرات الاستخدام، فمن الأفضل الرجوع إلى بيانات العبوة قبل إدخاله في الروتين. يصف الاسم المنتج بأنه ضد القشرة، من دون إضافة ادعاءات علاجية أو معلومات غير واردة فيه.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;كريم مخصص للعناية بالشعر.&lt;/li&gt;&lt;li&gt;يذكر الاسم وصفًا مغذيًا للشعر.&lt;/li&gt;&lt;li&gt;يتضمن الاسم إشارة إلى القشرة.&lt;/li&gt;&lt;li&gt;من علامة بالمرز التجارية.&lt;/li&gt;&lt;li&gt;حجم العبوة المحدد 150 جم.&lt;/li&gt;&lt;li&gt;يمكن استخدامه وفق طريقة الاستعمال الموضحة على العبوة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن كريم للعناية بالشعر.&lt;/li&gt;&lt;li&gt;لمن يفضل منتجًا يذكر القشرة في اسمه.&lt;/li&gt;&lt;li&gt;لمن يرغب في عبوة بحجم 150 جم من بالمرز.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;يستخدم على الشعر وفق الإرشادات المدونة على العبوة، مع الالتزام بموضع التطبيق والكمية وطريقة التوزيع المحددة للمنتج. لا يحدد الاسم ما إذا كان الكريم يُشطف أو يُترك على الشعر.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، تجنب ملامسة العينين، وأبعد المنتج عن متناول الأطفال. اتبعي تعليمات العبوة، وتوقفي عن الاستخدام عند ظهور تهيج.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;بالمرز هي العلامة التجارية الظاهرة لمنتج كريم الشعر هذا. يرد اسمها على العبوة مع وصف المنتج وحجمه البالغ 150 جم.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع المنتج؟&lt;/p&gt;&lt;p&gt;هو كريم للشعر، ويصفه الاسم بأنه مغذٍ ويشير إلى القشرة.&lt;/p&gt;&lt;p&gt;ما حجم العبوة؟&lt;/p&gt;&lt;p&gt;العبوة محددة بحجم 150 جم.&lt;/p&gt;&lt;p&gt;هل يوضح الاسم طريقة الاستخدام؟&lt;/p&gt;&lt;p&gt;لا يورد الاسم تفاصيل التطبيق أو الشطف، لذلك تُراجع تعليمات العبوة.&lt;/p&gt;&lt;p&gt;هل يذكر الاسم مكونات محددة؟&lt;/p&gt;&lt;p&gt;لا يحدد الاسم مكونات أو نسبًا؛ يمكن الاطلاع على العبوة لمعرفة بيانات التركيبة.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6242,7 +6252,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>MNT-R71</t>
+          <t>MNT-R75</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6279,7 +6289,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>بالمرز لوشن الجسم زبدة الشيا 250 مل</t>
+          <t>بالمرز صابون زبدة الكاكاو مع فيتامين 133 جم</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -6289,12 +6299,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/61zej-kYbaL.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0749/1387/4134/files/3543.jpg?v=1748505319&amp;width=1000&amp;height=1000&amp;crop=center</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>بالمرز لوشن الجسم زبدة الشيا 250 مل</t>
+          <t>بالمرز صابون زبدة الكاكاو مع فيتامين 133 جم</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -6304,12 +6314,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>لوشن الجسم بزبدة الشيا من بالمرز Palmer's Shea Butter Body Lotion، لوشن للجسم بحجم 250 مل. يذكر اسم المنتج زبدة الشيا بوصفها جزءًا من اسمه، ويحدد شكل المستحضر وحجمه والعلامة التجارية.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | لوشن الجسم بزبدة الشيا&lt;/li&gt;&lt;li&gt;النوع | لوشن للجسم&lt;/li&gt;&lt;li&gt;الحجم | 250 مل&lt;/li&gt;&lt;li&gt;العلامة التجارية | بالمرز Palmer's&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;يأتي هذا المستحضر من بالمرز بصيغة لوشن مخصص للجسم، ويحمل اسم زبدة الشيا كما ورد في بيانات المنتج. يتيح شكل اللوشن توزيعه على البشرة ضمن روتين العناية المعتاد، فيما تساعد معلومات الحجم والعلامة التجارية على تمييز العبوة عند اختيار مستحضرات الجسم.&lt;/p&gt;&lt;p&gt;يمكن استخدامه على بشرة الجسم بالطريقة الموضحة على العبوة، مع توزيع كمية مناسبة على المنطقة المطلوبة. لا يحدد الاسم تفاصيل عن نسبة زبدة الشيا أو مكونات أخرى، لذلك تظل بيانات العبوة المرجع لمعرفة أي معلومات إضافية تخص المنتج.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لوشن مخصص للاستخدام على الجسم.&lt;/li&gt;&lt;li&gt;يحمل اسم زبدة الشيا ضمن وصف المنتج.&lt;/li&gt;&lt;li&gt;من علامة بالمرز التجارية.&lt;/li&gt;&lt;li&gt;يأتي في عبوة بحجم 250 مل.&lt;/li&gt;&lt;li&gt;يمكن إدخاله ضمن روتين العناية اليومية بالجسم.&lt;/li&gt;&lt;li&gt;صيغة اللوشن تتيح توزيعه على البشرة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يفضل استخدام اللوشن ضمن روتين العناية بالجسم.&lt;/li&gt;&lt;li&gt;لمن يبحث عن منتج يذكر زبدة الشيا في اسمه.&lt;/li&gt;&lt;li&gt;لمن يرغب في عبوة بحجم 250 مل من بالمرز.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;يوزع مقدار مناسب على بشرة الجسم، ثم يمرر بلطف على المنطقة المراد العناية بها. يُستخدم بحسب إرشادات العبوة، ويُترك أو يُغسل وفق ما توضحه تعليمات المنتج، إذ لا يذكر الاسم طريقة تفصيلية للاستخدام.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، تجنب ملامسة العينين، وأبعد المنتج عن متناول الأطفال. راجعي تعليمات العبوة قبل الاستخدام، وتوقفي عنه عند حدوث تهيج.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;بالمرز هي العلامة التجارية الواردة في اسم هذا اللوشن. يظهر المنتج تحت اسمها مع الإشارة إلى زبدة الشيا وحجم العبوة البالغ 250 مل.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع المستحضر؟&lt;/p&gt;&lt;p&gt;هو لوشن للجسم، ويذكر اسم زبدة الشيا ضمن تعريف المنتج.&lt;/p&gt;&lt;p&gt;ما الحجم المكتوب للعبوة؟&lt;/p&gt;&lt;p&gt;الحجم الوارد في اسم المنتج هو 250 مل.&lt;/p&gt;&lt;p&gt;هل يذكر الاسم مكونات أخرى؟&lt;/p&gt;&lt;p&gt;لا يحدد الاسم مكونات أخرى أو نسبًا، ويُرجى الرجوع إلى بيانات العبوة للتفاصيل.&lt;/p&gt;&lt;p&gt;كيف يوضع اللوشن؟&lt;/p&gt;&lt;p&gt;يوزع على بشرة الجسم وفق طريقة الاستخدام الموضحة على العبوة.&lt;/p&gt;</t>
+          <t>صابون زبدة الكاكاو مع فيتامين من بالمرز Palmer's Cocoa Butter Soap with Vitamin، صابون للجسم بحجم 133 جم. يذكر الاسم زبدة الكاكاو وفيتامين من دون تحديد نوع الفيتامين، كما يوضح العلامة التجارية وحجم قطعة الصابون.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | صابون زبدة الكاكاو مع فيتامين&lt;/li&gt;&lt;li&gt;النوع | صابون للجسم&lt;/li&gt;&lt;li&gt;الحجم | 133 جم&lt;/li&gt;&lt;li&gt;العلامة التجارية | بالمرز Palmer's&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;قطعة صابون للعناية بالجسم من بالمرز، يحمل اسمها زبدة الكاكاو مع فيتامين. يحدد الاسم شكل المنتج وحجمه البالغ 133 جم، ويتيح تمييزه ضمن مستحضرات التنظيف والعناية الشخصية. لا يذكر اسم المنتج نوع الفيتامين أو تفاصيل تركيبته، لذا تُراجع بيانات العبوة لأي معلومات إضافية.&lt;/p&gt;&lt;p&gt;يمكن استعمال الصابون لتنظيف الجسم بالطريقة المعتادة، مع ترطيب القطعة بالماء وتكوين رغوة ثم شطف البشرة جيدًا. تبقى تعليمات الاستخدام المطبوعة على المنتج هي المرجع، خصوصًا إذا كانت هناك توجيهات خاصة بطريقة الاستعمال أو مناطق الاستخدام.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;صابون مخصص للاستخدام على الجسم.&lt;/li&gt;&lt;li&gt;يذكر زبدة الكاكاو ضمن اسم المنتج.&lt;/li&gt;&lt;li&gt;يتضمن الاسم إشارة إلى فيتامين من دون تحديد نوعه.&lt;/li&gt;&lt;li&gt;من علامة بالمرز التجارية.&lt;/li&gt;&lt;li&gt;وزن العبوة المحدد هو 133 جم.&lt;/li&gt;&lt;li&gt;يأتي في هيئة قطعة صابون للاستخدام مع الماء.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يفضل الصابون ضمن روتين تنظيف الجسم.&lt;/li&gt;&lt;li&gt;لمن يبحث عن منتج يذكر زبدة الكاكاو في اسمه.&lt;/li&gt;&lt;li&gt;لمن يرغب في قطعة صابون بوزن 133 جم من بالمرز.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;تبلل البشرة وقطعة الصابون بالماء، ثم تمرر القطعة لتكوين رغوة على المنطقة المراد تنظيفها، وبعد ذلك تشطف البشرة جيدًا. يُستخدم وفق ما توضحه العبوة، مع تجنب المناطق التي لا توصي التعليمات باستخدامه عليها.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، تجنب ملامسة العينين، وأبعد المنتج عن متناول الأطفال. في حال ملامسة العينين تُشطفان بالماء، ويوقف الاستخدام عند حدوث تهيج.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;بالمرز هي العلامة التجارية المذكورة على صابون زبدة الكاكاو. يحمل هذا المنتج اسمها ويأتي بوزن 133 جم.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع هذا المنتج؟&lt;/p&gt;&lt;p&gt;هو صابون للجسم، ويذكر الاسم زبدة الكاكاو مع فيتامين.&lt;/p&gt;&lt;p&gt;ما الوزن المذكور؟&lt;/p&gt;&lt;p&gt;وزن العبوة المحدد في الاسم هو 133 جم.&lt;/p&gt;&lt;p&gt;هل يحدد الاسم نوع الفيتامين؟&lt;/p&gt;&lt;p&gt;لا، يذكر فيتامينًا من دون تحديد نوعه؛ تُراجع العبوة للاطلاع على بيانات التركيبة.&lt;/p&gt;&lt;p&gt;كيف يستخدم الصابون؟&lt;/p&gt;&lt;p&gt;يستخدم مع الماء لتكوين رغوة على البشرة، ثم تشطف البشرة وفق إرشادات العبوة.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6319,7 +6329,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>MNT-R72</t>
+          <t>MNT-R76</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6356,22 +6366,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>كريم شعر بالمرز بالفيتامينات 250 جم</t>
+          <t>دوف مقشر جسم بحليب الأرز 298</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>العناية والجمال &gt; العناية بالشعر</t>
+          <t>العناية والجمال &gt; العناية بالجسم</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://sa.palmers.com/cdn/shop/files/hair_food.jpg?v=1780119467&amp;width=1780</t>
+          <t>https://m.media-amazon.com/images/I/51AAcZlz7hL.jpg</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>كريم شعر بالمرز بالفيتامينات 250 جم</t>
+          <t>دوف مقشر جسم بحليب الأرز 298</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -6381,12 +6391,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>كريم الشعر بالفيتامينات من بالمرز Palmer's Vitamin Hair Cream، كريم للشعر بحجم 250 جم. يوضح الاسم أن المنتج كريم للشعر ويذكر الفيتامينات ضمن تعريفه، من دون تحديد نوع الفيتامين أو تفاصيل أخرى عن التركيبة.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | كريم الشعر بالفيتامينات&lt;/li&gt;&lt;li&gt;النوع | كريم للشعر&lt;/li&gt;&lt;li&gt;الحجم | 250 جم&lt;/li&gt;&lt;li&gt;العلامة التجارية | بالمرز Palmer's&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;مستحضر من بالمرز مخصص للعناية بالشعر، يأتي بصيغة كريم ويحمل وصف بالفيتامينات في اسمه. يحدد الاسم طبيعة المنتج وحجمه البالغ 250 جم، ليكون التعرف إلى العبوة ومجال استخدامها واضحًا عند تنظيم مستحضرات العناية بالشعر.&lt;/p&gt;&lt;p&gt;يمكن توزيع كمية مناسبة من الكريم على الشعر بالطريقة التي توضحها العبوة، مع مراعاة التعليمات الخاصة بموضع التطبيق وطريقة الاستخدام. لا يذكر الاسم أنواع الفيتامينات أو نسبها، ولا يحدد ما إذا كان الاستخدام على الشعر الرطب أو الجاف؛ لذا يُعتمد على بيانات المنتج المطبوعة لمعرفة ذلك.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;كريم مخصص للعناية بالشعر.&lt;/li&gt;&lt;li&gt;يذكر الفيتامينات ضمن اسم المنتج.&lt;/li&gt;&lt;li&gt;من علامة بالمرز التجارية.&lt;/li&gt;&lt;li&gt;حجم العبوة المحدد هو 250 جم.&lt;/li&gt;&lt;li&gt;يمكن إدراجه ضمن روتين العناية بالشعر.&lt;/li&gt;&lt;li&gt;يأتي بصيغة كريم سهلة التوزيع بحسب إرشادات العبوة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن كريم مخصص للشعر.&lt;/li&gt;&lt;li&gt;لمن يفضل منتجًا يذكر الفيتامينات في اسمه.&lt;/li&gt;&lt;li&gt;لمن يرغب في عبوة شعر بحجم 250 جم من بالمرز.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;يوضع مقدار مناسب على الشعر وفق التعليمات الموجودة على العبوة، ثم يوزع بالطريقة المحددة للمنتج. لا تفترضي موضعًا أو توقيتًا معينًا للتطبيق قبل مراجعة الإرشادات، لأن الاسم لا يوضح هذه التفاصيل.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، تجنب ملامسة العينين، وأبعد المنتج عن متناول الأطفال. التزمي بإرشادات العبوة، وأوقفي الاستخدام إذا ظهر تهيج.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;بالمرز هي العلامة التجارية المسجلة في اسم هذا المستحضر. يحمل المنتج وصف كريم للشعر بالفيتامينات، ويأتي بحجم 250 جم.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما طبيعة هذا المنتج؟&lt;/p&gt;&lt;p&gt;هو كريم مخصص للشعر، وترد الفيتامينات ضمن الاسم التجاري للمنتج.&lt;/p&gt;&lt;p&gt;كم يبلغ حجم العبوة؟&lt;/p&gt;&lt;p&gt;الحجم المذكور هو 250 جم.&lt;/p&gt;&lt;p&gt;هل يحدد الاسم أنواع الفيتامينات؟&lt;/p&gt;&lt;p&gt;لا، لا يذكر الاسم أنواعًا أو نسبًا محددة؛ راجعي بيانات العبوة لمعلومات التركيبة.&lt;/p&gt;&lt;p&gt;هل يوضع على شعر رطب أم جاف؟&lt;/p&gt;&lt;p&gt;الاسم لا يحدد ذلك، لذا تُتبع طريقة الاستخدام المدونة على العبوة.&lt;/p&gt;</t>
+          <t>مقشر الجسم بحليب الأرز من دوف Dove Rice Milk Body Scrub، مقشر للجسم بحجم 298. يذكر اسم المنتج حليب الأرز، ويحدد نوع المستحضر بوصفه مقشرًا للجسم، بينما يرد الحجم بالرقم 298 من دون وحدة في الاسم.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | مقشر الجسم بحليب الأرز&lt;/li&gt;&lt;li&gt;النوع | مقشر للجسم&lt;/li&gt;&lt;li&gt;الحجم | 298&lt;/li&gt;&lt;li&gt;العلامة التجارية | دوف Dove&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;مقشر للجسم من دوف يحمل حليب الأرز ضمن اسمه، ويأتي ضمن مستحضرات العناية المخصصة للجسم. يوضح الاسم العلامة التجارية ونوع المنتج، كما يذكر الرقم 298 للحجم من دون إظهار وحدة قياس؛ لذلك لا تُضاف وحدة غير واردة في بياناته.&lt;/p&gt;&lt;p&gt;يمكن استخدام المقشر على بشرة الجسم وفق التعليمات المدونة على العبوة. يوزع بلطف على المنطقة المطلوبة ثم يشطف إذا كانت تعليمات المنتج تنص على ذلك. لا يحدد الاسم طريقة التدليك أو عدد مرات الاستخدام أو مكونات أخرى، ولهذا ينبغي الرجوع إلى العبوة لمعرفة التفاصيل المرتبطة بالاستخدام.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مقشر مخصص للعناية بالجسم.&lt;/li&gt;&lt;li&gt;يذكر حليب الأرز ضمن اسم المنتج.&lt;/li&gt;&lt;li&gt;من علامة دوف التجارية.&lt;/li&gt;&lt;li&gt;الحجم مذكور بالرقم 298 من دون وحدة في الاسم.&lt;/li&gt;&lt;li&gt;يمكن إدراجه ضمن روتين العناية بالجسم.&lt;/li&gt;&lt;li&gt;تعتمد طريقة الاستعمال على تعليمات العبوة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن مقشر مخصص للجسم.&lt;/li&gt;&lt;li&gt;لمن يفضل منتجًا يذكر حليب الأرز في اسمه.&lt;/li&gt;&lt;li&gt;لمن يرغب في اختيار منتج من علامة دوف.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;يوضع المقشر على بشرة الجسم وفق إرشادات العبوة، ويدلك بلطف إذا أوصت التعليمات بذلك، ثم يشطف بالطريقة المحددة للمنتج. راجعي طريقة الاستخدام المطبوعة قبل الاستعمال، إذ لا يحدد الاسم تفاصيل التكرار أو مدة التدليك.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، تجنب ملامسة العينين، وأبعد المنتج عن متناول الأطفال. لا يستخدم على مواضع لا تسمح بها تعليمات العبوة.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;دوف هي العلامة التجارية المذكورة على هذا المقشر. يظهر اسمها مع وصف المنتج بحليب الأرز ومع الرقم 298 الوارد للحجم.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع المنتج؟&lt;/p&gt;&lt;p&gt;هو مقشر للجسم، ويذكر حليب الأرز ضمن اسمه.&lt;/p&gt;&lt;p&gt;ما الحجم المكتوب؟&lt;/p&gt;&lt;p&gt;ورد الرقم 298 في اسم المنتج من دون تحديد وحدة قياس.&lt;/p&gt;&lt;p&gt;هل يذكر الاسم مكونات أخرى؟&lt;/p&gt;&lt;p&gt;لا، الاسم يذكر حليب الأرز فقط؛ تراجع العبوة لمعرفة تفاصيل إضافية.&lt;/p&gt;&lt;p&gt;كيف يستخدم المقشر؟&lt;/p&gt;&lt;p&gt;يستخدم على الجسم وفق طريقة الاستعمال والتحذيرات المكتوبة على العبوة.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6396,7 +6406,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>MNT-R74</t>
+          <t>MNT-R77</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -6411,7 +6421,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>Palmer's</t>
+          <t>Dove</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -6433,22 +6443,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>كريم مغذي للشعر ضد القشره من بالمرز - 150 جم</t>
+          <t>دوف مقشر الجسم بخلاصة بذور الرمان 298 جم</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>العناية والجمال &gt; العناية بالشعر</t>
+          <t>العناية والجمال &gt; العناية بالجسم</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71BLb2r6SBL.jpg</t>
+          <t>https://assets.unileversolutions.com/v1/111353190.png?im=AspectCrop=(1000,1000)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>كريم مغذي للشعر ضد القشره من بالمرز - 150 جم</t>
+          <t>دوف مقشر الجسم بخلاصة بذور الرمان 298 جم</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -6458,12 +6468,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>كريم مغذي للشعر ضد القشرة من بالمرز Palmer's Nourishing Anti-Dandruff Hair Cream، كريم للشعر بحجم 150 جم. يجمع اسم المنتج بين وصف مغذٍ للشعر والإشارة إلى القشرة، من دون أن يحدد تفاصيل عن مكونات الكريم أو طريقة استخدامه الدقيقة.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | كريم مغذي للشعر ضد القشرة&lt;/li&gt;&lt;li&gt;النوع | كريم للشعر&lt;/li&gt;&lt;li&gt;الحجم | 150 جم&lt;/li&gt;&lt;li&gt;العلامة التجارية | بالمرز Palmer's&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;يأتي هذا الكريم من بالمرز ضمن مستحضرات العناية بالشعر، ويحمل في اسمه وصفًا مغذيًا وإشارة إلى القشرة. يوضح الاسم حجم العبوة، 150 جم، ونوع المنتج بوصفه كريمًا، بينما تبقى تفاصيل التركيبة وطريقة التطبيق الدقيقة مرتبطة بما هو مدون على العبوة.&lt;/p&gt;&lt;p&gt;يمكن استخدامه للعناية بالشعر وفق التعليمات المرفقة بالمنتج. ولأن الاسم لا يحدد موضع وضع الكريم أو مدة بقائه أو عدد مرات الاستخدام، فمن الأفضل الرجوع إلى بيانات العبوة قبل إدخاله في الروتين. يصف الاسم المنتج بأنه ضد القشرة، من دون إضافة ادعاءات علاجية أو معلومات غير واردة فيه.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;كريم مخصص للعناية بالشعر.&lt;/li&gt;&lt;li&gt;يذكر الاسم وصفًا مغذيًا للشعر.&lt;/li&gt;&lt;li&gt;يتضمن الاسم إشارة إلى القشرة.&lt;/li&gt;&lt;li&gt;من علامة بالمرز التجارية.&lt;/li&gt;&lt;li&gt;حجم العبوة المحدد 150 جم.&lt;/li&gt;&lt;li&gt;يمكن استخدامه وفق طريقة الاستعمال الموضحة على العبوة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن كريم للعناية بالشعر.&lt;/li&gt;&lt;li&gt;لمن يفضل منتجًا يذكر القشرة في اسمه.&lt;/li&gt;&lt;li&gt;لمن يرغب في عبوة بحجم 150 جم من بالمرز.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;يستخدم على الشعر وفق الإرشادات المدونة على العبوة، مع الالتزام بموضع التطبيق والكمية وطريقة التوزيع المحددة للمنتج. لا يحدد الاسم ما إذا كان الكريم يُشطف أو يُترك على الشعر.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، تجنب ملامسة العينين، وأبعد المنتج عن متناول الأطفال. اتبعي تعليمات العبوة، وتوقفي عن الاستخدام عند ظهور تهيج.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;بالمرز هي العلامة التجارية الظاهرة لمنتج كريم الشعر هذا. يرد اسمها على العبوة مع وصف المنتج وحجمه البالغ 150 جم.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع المنتج؟&lt;/p&gt;&lt;p&gt;هو كريم للشعر، ويصفه الاسم بأنه مغذٍ ويشير إلى القشرة.&lt;/p&gt;&lt;p&gt;ما حجم العبوة؟&lt;/p&gt;&lt;p&gt;العبوة محددة بحجم 150 جم.&lt;/p&gt;&lt;p&gt;هل يوضح الاسم طريقة الاستخدام؟&lt;/p&gt;&lt;p&gt;لا يورد الاسم تفاصيل التطبيق أو الشطف، لذلك تُراجع تعليمات العبوة.&lt;/p&gt;&lt;p&gt;هل يذكر الاسم مكونات محددة؟&lt;/p&gt;&lt;p&gt;لا يحدد الاسم مكونات أو نسبًا؛ يمكن الاطلاع على العبوة لمعرفة بيانات التركيبة.&lt;/p&gt;</t>
+          <t>مقشر الجسم بخلاصة بذور الرمان من دوف Dove Pomegranate Seed Body Scrub، مقشر للجسم بحجم 298 جم. يحدد اسم المنتج خلاصة بذور الرمان، ويبين نوع المستحضر والعلامة التجارية والوزن الوارد على العبوة.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | مقشر الجسم بخلاصة بذور الرمان&lt;/li&gt;&lt;li&gt;النوع | مقشر للجسم&lt;/li&gt;&lt;li&gt;الحجم | 298 جم&lt;/li&gt;&lt;li&gt;العلامة التجارية | دوف Dove&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;هذا مقشر للجسم من دوف، يحمل خلاصة بذور الرمان ضمن اسمه ويأتي بوزن 298 جم. يوضح وصفه أنه مخصص للعناية بالجسم، فيما توفر بيانات الاسم معلومات مباشرة عن العلامة التجارية والمادة المذكورة والحجم، من دون تحديد مكونات أخرى أو نسبها.&lt;/p&gt;&lt;p&gt;يستخدم المقشر على الجسم وفق التعليمات الموجودة على العبوة. يمكن توزيعه بلطف على البشرة بالطريقة التي توصي بها الشركة، ثم شطفه إذا كانت تعليمات المنتج تنص على ذلك. لا يحدد الاسم عدد مرات الاستخدام أو مدة التدليك، لذا تُتبع الإرشادات المرفقة بدل افتراض روتين ثابت.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مقشر مخصص للاستخدام على الجسم.&lt;/li&gt;&lt;li&gt;يذكر خلاصة بذور الرمان في اسمه.&lt;/li&gt;&lt;li&gt;من علامة دوف التجارية.&lt;/li&gt;&lt;li&gt;يأتي بوزن 298 جم.&lt;/li&gt;&lt;li&gt;يمكن إدراجه ضمن روتين العناية بالجسم.&lt;/li&gt;&lt;li&gt;توضح بياناته نوع المنتج والعلامة التجارية والحجم.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن مقشر للجسم.&lt;/li&gt;&lt;li&gt;لمن يفضل منتجًا يذكر خلاصة بذور الرمان في اسمه.&lt;/li&gt;&lt;li&gt;لمن يرغب في عبوة من دوف بوزن 298 جم.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;يوضع على بشرة الجسم بالطريقة المحددة على العبوة، ويوزع بتدليك لطيف إذا ورد ذلك ضمن التعليمات، ثم يشطف وفق الإرشادات. راجعي العبوة لمعرفة طريقة الاستخدام كاملة وتفاصيل التكرار المناسبة للمنتج.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، تجنب ملامسة العينين، وأبعد المنتج عن متناول الأطفال. تجنبي استخدامه على مناطق لا تسمح بها تعليمات العبوة.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;دوف هي العلامة التجارية المذكورة في بيانات هذا المقشر. يرد اسمها مع وصف خلاصة بذور الرمان والوزن المحدد للعبوة.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما فئة هذا المنتج؟&lt;/p&gt;&lt;p&gt;هو مقشر للجسم من دوف، ويذكر خلاصة بذور الرمان ضمن اسمه.&lt;/p&gt;&lt;p&gt;كم وزن العبوة؟&lt;/p&gt;&lt;p&gt;الوزن الوارد في الاسم هو 298 جم.&lt;/p&gt;&lt;p&gt;هل يحدد الاسم جميع مكونات المنتج؟&lt;/p&gt;&lt;p&gt;لا، يذكر خلاصة بذور الرمان فقط؛ وتعرض العبوة المعلومات التفصيلية عن المكونات.&lt;/p&gt;&lt;p&gt;هل توجد طريقة استخدام محددة؟&lt;/p&gt;&lt;p&gt;تُتبع تعليمات الاستعمال المطبوعة على العبوة، إذ لا يحدد الاسم وحده التفاصيل.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6473,7 +6483,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>MNT-R75</t>
+          <t>MNT-R78</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -6488,7 +6498,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>Palmer's</t>
+          <t>Dove</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -6510,7 +6520,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>بالمرز صابون زبدة الكاكاو مع فيتامين 133 جم</t>
+          <t>مقشر الجسم دوف باللافندر وحليب جوز الهند 298</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -6520,12 +6530,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0749/1387/4134/files/3543.jpg?v=1748505319&amp;width=1000&amp;height=1000&amp;crop=center</t>
+          <t>https://m.media-amazon.com/images/I/51-bWlqiSfL.jpg</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>بالمرز صابون زبدة الكاكاو مع فيتامين 133 جم</t>
+          <t>مقشر الجسم دوف باللافندر وحليب جوز الهند 298</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -6535,12 +6545,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>صابون زبدة الكاكاو مع فيتامين من بالمرز Palmer's Cocoa Butter Soap with Vitamin، صابون للجسم بحجم 133 جم. يذكر الاسم زبدة الكاكاو وفيتامين من دون تحديد نوع الفيتامين، كما يوضح العلامة التجارية وحجم قطعة الصابون.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | صابون زبدة الكاكاو مع فيتامين&lt;/li&gt;&lt;li&gt;النوع | صابون للجسم&lt;/li&gt;&lt;li&gt;الحجم | 133 جم&lt;/li&gt;&lt;li&gt;العلامة التجارية | بالمرز Palmer's&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;قطعة صابون للعناية بالجسم من بالمرز، يحمل اسمها زبدة الكاكاو مع فيتامين. يحدد الاسم شكل المنتج وحجمه البالغ 133 جم، ويتيح تمييزه ضمن مستحضرات التنظيف والعناية الشخصية. لا يذكر اسم المنتج نوع الفيتامين أو تفاصيل تركيبته، لذا تُراجع بيانات العبوة لأي معلومات إضافية.&lt;/p&gt;&lt;p&gt;يمكن استعمال الصابون لتنظيف الجسم بالطريقة المعتادة، مع ترطيب القطعة بالماء وتكوين رغوة ثم شطف البشرة جيدًا. تبقى تعليمات الاستخدام المطبوعة على المنتج هي المرجع، خصوصًا إذا كانت هناك توجيهات خاصة بطريقة الاستعمال أو مناطق الاستخدام.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;صابون مخصص للاستخدام على الجسم.&lt;/li&gt;&lt;li&gt;يذكر زبدة الكاكاو ضمن اسم المنتج.&lt;/li&gt;&lt;li&gt;يتضمن الاسم إشارة إلى فيتامين من دون تحديد نوعه.&lt;/li&gt;&lt;li&gt;من علامة بالمرز التجارية.&lt;/li&gt;&lt;li&gt;وزن العبوة المحدد هو 133 جم.&lt;/li&gt;&lt;li&gt;يأتي في هيئة قطعة صابون للاستخدام مع الماء.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يفضل الصابون ضمن روتين تنظيف الجسم.&lt;/li&gt;&lt;li&gt;لمن يبحث عن منتج يذكر زبدة الكاكاو في اسمه.&lt;/li&gt;&lt;li&gt;لمن يرغب في قطعة صابون بوزن 133 جم من بالمرز.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;تبلل البشرة وقطعة الصابون بالماء، ثم تمرر القطعة لتكوين رغوة على المنطقة المراد تنظيفها، وبعد ذلك تشطف البشرة جيدًا. يُستخدم وفق ما توضحه العبوة، مع تجنب المناطق التي لا توصي التعليمات باستخدامه عليها.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، تجنب ملامسة العينين، وأبعد المنتج عن متناول الأطفال. في حال ملامسة العينين تُشطفان بالماء، ويوقف الاستخدام عند حدوث تهيج.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;بالمرز هي العلامة التجارية المذكورة على صابون زبدة الكاكاو. يحمل هذا المنتج اسمها ويأتي بوزن 133 جم.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع هذا المنتج؟&lt;/p&gt;&lt;p&gt;هو صابون للجسم، ويذكر الاسم زبدة الكاكاو مع فيتامين.&lt;/p&gt;&lt;p&gt;ما الوزن المذكور؟&lt;/p&gt;&lt;p&gt;وزن العبوة المحدد في الاسم هو 133 جم.&lt;/p&gt;&lt;p&gt;هل يحدد الاسم نوع الفيتامين؟&lt;/p&gt;&lt;p&gt;لا، يذكر فيتامينًا من دون تحديد نوعه؛ تُراجع العبوة للاطلاع على بيانات التركيبة.&lt;/p&gt;&lt;p&gt;كيف يستخدم الصابون؟&lt;/p&gt;&lt;p&gt;يستخدم مع الماء لتكوين رغوة على البشرة، ثم تشطف البشرة وفق إرشادات العبوة.&lt;/p&gt;</t>
+          <t>مقشر الجسم باللافندر وحليب جوز الهند من دوف Dove Lavender and Coconut Milk Body Scrub، مقشر للجسم بحجم 298. يذكر الاسم اللافندر وحليب جوز الهند، ويحدد نوع المنتج والعلامة التجارية، بينما لا يورد وحدة قياس للرقم 298.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | مقشر الجسم باللافندر وحليب جوز الهند&lt;/li&gt;&lt;li&gt;النوع | مقشر للجسم&lt;/li&gt;&lt;li&gt;الحجم | 298&lt;/li&gt;&lt;li&gt;العلامة التجارية | دوف Dove&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;مقشر للجسم من دوف، يجمع اسمه بين اللافندر وحليب جوز الهند كما وردا في بيانات المنتج. يندرج ضمن مستحضرات العناية بالجسم، ويأتي الرقم 298 ضمن الاسم من دون وحدة قياس، لذلك يُنقل الحجم كما ورد من غير افتراض جرام أو مل.&lt;/p&gt;&lt;p&gt;تُستخدم المقشرات على الجسم وفق تعليمات العبوة، مع الالتزام بطريقة التوزيع والشطف المحددة للمنتج. لا يوضح الاسم تفاصيل عن التركيبة أو نسب المكونات، كما لا يحدد مدة التدليك أو عدد مرات الاستخدام. تساعد قراءة بيانات العبوة على معرفة الإرشادات الخاصة بهذا المنتج قبل إضافته إلى روتين العناية.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مقشر مخصص للجسم.&lt;/li&gt;&lt;li&gt;يذكر اللافندر ضمن اسم المنتج.&lt;/li&gt;&lt;li&gt;يتضمن الاسم حليب جوز الهند.&lt;/li&gt;&lt;li&gt;من علامة دوف التجارية.&lt;/li&gt;&lt;li&gt;يرد الرقم 298 للحجم من دون وحدة قياس في الاسم.&lt;/li&gt;&lt;li&gt;يمكن استخدامه ضمن روتين العناية بالجسم وفق التعليمات.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن مستحضر مقشر للجسم.&lt;/li&gt;&lt;li&gt;لمن يفضل منتجًا يذكر اللافندر وحليب جوز الهند في اسمه.&lt;/li&gt;&lt;li&gt;لمن يرغب في اختيار مقشر من علامة دوف.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;يوزع على بشرة الجسم بالطريقة المذكورة على العبوة، مع تدليك لطيف فقط إذا كانت التعليمات توصي بذلك، ثم يشطف وفق الإرشادات. لا يحدد الاسم تواتر الاستخدام أو مدة التدليك، لذا يرجى الرجوع إلى تعليمات المنتج.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، تجنب ملامسة العينين، وأبعد المنتج عن متناول الأطفال. اتبعي الإرشادات المكتوبة على العبوة وتجنبي الاستخدام في المواضع غير المحددة.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;دوف هي العلامة التجارية المذكورة لهذا المقشر. يرد اسمها مع إشارات اللافندر وحليب جوز الهند والرقم 298 الوارد في اسم المنتج.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع المستحضر؟&lt;/p&gt;&lt;p&gt;هو مقشر للجسم من دوف.&lt;/p&gt;&lt;p&gt;ما العناصر المذكورة في اسمه؟&lt;/p&gt;&lt;p&gt;يذكر الاسم اللافندر وحليب جوز الهند.&lt;/p&gt;&lt;p&gt;هل الرقم 298 محدد بوحدة؟&lt;/p&gt;&lt;p&gt;لا ترد وحدة قياس بعد الرقم في الاسم؛ راجعي العبوة للتأكد من الحجم.&lt;/p&gt;&lt;p&gt;كيف أستخدمه؟&lt;/p&gt;&lt;p&gt;تُتبع طريقة الاستعمال المدوّنة على العبوة، بما في ذلك ما يتعلق بالتوزيع والشطف.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -6550,7 +6560,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>MNT-R76</t>
+          <t>MNT-R79</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -6565,7 +6575,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>Palmer's</t>
+          <t>Dove</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -6587,7 +6597,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>دوف مقشر جسم بحليب الأرز 298</t>
+          <t>دوف مقشر الجسم بزبدة اللوز والمانجو298جم</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -6597,12 +6607,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/51AAcZlz7hL.jpg</t>
+          <t>https://m.media-amazon.com/images/I/51UW3T0xcNL.jpg</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>دوف مقشر جسم بحليب الأرز 298</t>
+          <t>دوف مقشر الجسم بزبدة اللوز والمانجو298جم</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -6612,12 +6622,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>مقشر الجسم بحليب الأرز من دوف Dove Rice Milk Body Scrub، مقشر للجسم بحجم 298. يذكر اسم المنتج حليب الأرز، ويحدد نوع المستحضر بوصفه مقشرًا للجسم، بينما يرد الحجم بالرقم 298 من دون وحدة في الاسم.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | مقشر الجسم بحليب الأرز&lt;/li&gt;&lt;li&gt;النوع | مقشر للجسم&lt;/li&gt;&lt;li&gt;الحجم | 298&lt;/li&gt;&lt;li&gt;العلامة التجارية | دوف Dove&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;مقشر للجسم من دوف يحمل حليب الأرز ضمن اسمه، ويأتي ضمن مستحضرات العناية المخصصة للجسم. يوضح الاسم العلامة التجارية ونوع المنتج، كما يذكر الرقم 298 للحجم من دون إظهار وحدة قياس؛ لذلك لا تُضاف وحدة غير واردة في بياناته.&lt;/p&gt;&lt;p&gt;يمكن استخدام المقشر على بشرة الجسم وفق التعليمات المدونة على العبوة. يوزع بلطف على المنطقة المطلوبة ثم يشطف إذا كانت تعليمات المنتج تنص على ذلك. لا يحدد الاسم طريقة التدليك أو عدد مرات الاستخدام أو مكونات أخرى، ولهذا ينبغي الرجوع إلى العبوة لمعرفة التفاصيل المرتبطة بالاستخدام.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مقشر مخصص للعناية بالجسم.&lt;/li&gt;&lt;li&gt;يذكر حليب الأرز ضمن اسم المنتج.&lt;/li&gt;&lt;li&gt;من علامة دوف التجارية.&lt;/li&gt;&lt;li&gt;الحجم مذكور بالرقم 298 من دون وحدة في الاسم.&lt;/li&gt;&lt;li&gt;يمكن إدراجه ضمن روتين العناية بالجسم.&lt;/li&gt;&lt;li&gt;تعتمد طريقة الاستعمال على تعليمات العبوة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن مقشر مخصص للجسم.&lt;/li&gt;&lt;li&gt;لمن يفضل منتجًا يذكر حليب الأرز في اسمه.&lt;/li&gt;&lt;li&gt;لمن يرغب في اختيار منتج من علامة دوف.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;يوضع المقشر على بشرة الجسم وفق إرشادات العبوة، ويدلك بلطف إذا أوصت التعليمات بذلك، ثم يشطف بالطريقة المحددة للمنتج. راجعي طريقة الاستخدام المطبوعة قبل الاستعمال، إذ لا يحدد الاسم تفاصيل التكرار أو مدة التدليك.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، تجنب ملامسة العينين، وأبعد المنتج عن متناول الأطفال. لا يستخدم على مواضع لا تسمح بها تعليمات العبوة.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;دوف هي العلامة التجارية المذكورة على هذا المقشر. يظهر اسمها مع وصف المنتج بحليب الأرز ومع الرقم 298 الوارد للحجم.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع المنتج؟&lt;/p&gt;&lt;p&gt;هو مقشر للجسم، ويذكر حليب الأرز ضمن اسمه.&lt;/p&gt;&lt;p&gt;ما الحجم المكتوب؟&lt;/p&gt;&lt;p&gt;ورد الرقم 298 في اسم المنتج من دون تحديد وحدة قياس.&lt;/p&gt;&lt;p&gt;هل يذكر الاسم مكونات أخرى؟&lt;/p&gt;&lt;p&gt;لا، الاسم يذكر حليب الأرز فقط؛ تراجع العبوة لمعرفة تفاصيل إضافية.&lt;/p&gt;&lt;p&gt;كيف يستخدم المقشر؟&lt;/p&gt;&lt;p&gt;يستخدم على الجسم وفق طريقة الاستعمال والتحذيرات المكتوبة على العبوة.&lt;/p&gt;</t>
+          <t>مقشر الجسم بزبدة اللوز والمانجو من دوف Dove Almond Butter and Mango Body Scrub، مقشر للجسم بحجم 298 جم. يذكر الاسم زبدة اللوز والمانجو، ويحدد وزن العبوة والعلامة التجارية ونوع المستحضر.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | مقشر الجسم بزبدة اللوز والمانجو&lt;/li&gt;&lt;li&gt;النوع | مقشر للجسم&lt;/li&gt;&lt;li&gt;الحجم | 298 جم&lt;/li&gt;&lt;li&gt;العلامة التجارية | دوف Dove&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;مقشر للجسم من دوف، يحمل زبدة اللوز والمانجو في اسمه، ويأتي بوزن 298 جم. يوضح الاسم طبيعة المستحضر المخصص للجسم والعلامة التجارية، كما يورد العناصر المذكورة في تعريف المنتج من دون عرض قائمة كاملة بالمكونات أو نسبها.&lt;/p&gt;&lt;p&gt;يمكن إدخال المقشر ضمن روتين العناية بالجسم، مع استخدامه بالطريقة التي توضحها العبوة. يوزع على المنطقة المطلوبة وفق التعليمات، ويشطف إذا كانت الإرشادات تنص على ذلك. لا يحدد الاسم عدد مرات الاستخدام أو تفاصيل التدليك، لذا تُتبع المعلومات المدونة على العبوة ولا يُفترض برنامج استخدام ثابت.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مقشر مخصص للعناية بالجسم.&lt;/li&gt;&lt;li&gt;يذكر زبدة اللوز ضمن اسم المنتج.&lt;/li&gt;&lt;li&gt;يتضمن الاسم المانجو.&lt;/li&gt;&lt;li&gt;من علامة دوف التجارية.&lt;/li&gt;&lt;li&gt;يأتي بوزن 298 جم.&lt;/li&gt;&lt;li&gt;تساعد بيانات الاسم على معرفة النوع والحجم والعلامة التجارية.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن مقشر للجسم.&lt;/li&gt;&lt;li&gt;لمن يفضل منتجًا يذكر زبدة اللوز والمانجو في اسمه.&lt;/li&gt;&lt;li&gt;لمن يرغب في عبوة من دوف بوزن 298 جم.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;يستخدم على بشرة الجسم وفق التعليمات المطبوعة على العبوة. يوزع بلطف على المنطقة المطلوبة، ثم يشطف إذا نصت الإرشادات على ذلك. راجعي تفاصيل الاستعمال قبل الاستخدام لمعرفة التكرار وطريقة التطبيق الخاصة بالمنتج.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، تجنب ملامسة العينين، وأبعد المنتج عن متناول الأطفال. يُراعى اتباع تحذيرات العبوة وعدم استخدامه على مناطق غير موصى بها.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;دوف هي العلامة التجارية الواردة على هذا المقشر. يظهر اسمها مع وصف زبدة اللوز والمانجو ووزن العبوة المحدد بـ 298 جم.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما استخدام هذا المنتج؟&lt;/p&gt;&lt;p&gt;هو مقشر للجسم، ويستخدم وفق الإرشادات الخاصة به على العبوة.&lt;/p&gt;&lt;p&gt;ما العناصر المذكورة في الاسم؟&lt;/p&gt;&lt;p&gt;يذكر الاسم زبدة اللوز والمانجو.&lt;/p&gt;&lt;p&gt;ما وزن العبوة؟&lt;/p&gt;&lt;p&gt;الوزن المذكور هو 298 جم.&lt;/p&gt;&lt;p&gt;هل يوضح الاسم طريقة الاستعمال كاملة؟&lt;/p&gt;&lt;p&gt;لا، لذلك تُراجع العبوة لمعرفة طريقة التطبيق والتكرار والشطف.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -6627,7 +6637,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>MNT-R77</t>
+          <t>MNT-R80</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -6664,7 +6674,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>دوف مقشر الجسم بخلاصة بذور الرمان 298 جم</t>
+          <t>دوف مقشر الجسم بملح الهيمالايا وزيت الورد425ج</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -6674,12 +6684,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://assets.unileversolutions.com/v1/111353190.png?im=AspectCrop=(1000,1000)</t>
+          <t>https://m.media-amazon.com/images/I/71F1CH9-7wL.jpg</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>دوف مقشر الجسم بخلاصة بذور الرمان 298 جم</t>
+          <t>دوف مقشر الجسم بملح الهيمالايا وزيت الورد425ج</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -6689,12 +6699,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>مقشر الجسم بخلاصة بذور الرمان من دوف Dove Pomegranate Seed Body Scrub، مقشر للجسم بحجم 298 جم. يحدد اسم المنتج خلاصة بذور الرمان، ويبين نوع المستحضر والعلامة التجارية والوزن الوارد على العبوة.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | مقشر الجسم بخلاصة بذور الرمان&lt;/li&gt;&lt;li&gt;النوع | مقشر للجسم&lt;/li&gt;&lt;li&gt;الحجم | 298 جم&lt;/li&gt;&lt;li&gt;العلامة التجارية | دوف Dove&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;هذا مقشر للجسم من دوف، يحمل خلاصة بذور الرمان ضمن اسمه ويأتي بوزن 298 جم. يوضح وصفه أنه مخصص للعناية بالجسم، فيما توفر بيانات الاسم معلومات مباشرة عن العلامة التجارية والمادة المذكورة والحجم، من دون تحديد مكونات أخرى أو نسبها.&lt;/p&gt;&lt;p&gt;يستخدم المقشر على الجسم وفق التعليمات الموجودة على العبوة. يمكن توزيعه بلطف على البشرة بالطريقة التي توصي بها الشركة، ثم شطفه إذا كانت تعليمات المنتج تنص على ذلك. لا يحدد الاسم عدد مرات الاستخدام أو مدة التدليك، لذا تُتبع الإرشادات المرفقة بدل افتراض روتين ثابت.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مقشر مخصص للاستخدام على الجسم.&lt;/li&gt;&lt;li&gt;يذكر خلاصة بذور الرمان في اسمه.&lt;/li&gt;&lt;li&gt;من علامة دوف التجارية.&lt;/li&gt;&lt;li&gt;يأتي بوزن 298 جم.&lt;/li&gt;&lt;li&gt;يمكن إدراجه ضمن روتين العناية بالجسم.&lt;/li&gt;&lt;li&gt;توضح بياناته نوع المنتج والعلامة التجارية والحجم.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن مقشر للجسم.&lt;/li&gt;&lt;li&gt;لمن يفضل منتجًا يذكر خلاصة بذور الرمان في اسمه.&lt;/li&gt;&lt;li&gt;لمن يرغب في عبوة من دوف بوزن 298 جم.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;يوضع على بشرة الجسم بالطريقة المحددة على العبوة، ويوزع بتدليك لطيف إذا ورد ذلك ضمن التعليمات، ثم يشطف وفق الإرشادات. راجعي العبوة لمعرفة طريقة الاستخدام كاملة وتفاصيل التكرار المناسبة للمنتج.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، تجنب ملامسة العينين، وأبعد المنتج عن متناول الأطفال. تجنبي استخدامه على مناطق لا تسمح بها تعليمات العبوة.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;دوف هي العلامة التجارية المذكورة في بيانات هذا المقشر. يرد اسمها مع وصف خلاصة بذور الرمان والوزن المحدد للعبوة.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما فئة هذا المنتج؟&lt;/p&gt;&lt;p&gt;هو مقشر للجسم من دوف، ويذكر خلاصة بذور الرمان ضمن اسمه.&lt;/p&gt;&lt;p&gt;كم وزن العبوة؟&lt;/p&gt;&lt;p&gt;الوزن الوارد في الاسم هو 298 جم.&lt;/p&gt;&lt;p&gt;هل يحدد الاسم جميع مكونات المنتج؟&lt;/p&gt;&lt;p&gt;لا، يذكر خلاصة بذور الرمان فقط؛ وتعرض العبوة المعلومات التفصيلية عن المكونات.&lt;/p&gt;&lt;p&gt;هل توجد طريقة استخدام محددة؟&lt;/p&gt;&lt;p&gt;تُتبع تعليمات الاستعمال المطبوعة على العبوة، إذ لا يحدد الاسم وحده التفاصيل.&lt;/p&gt;</t>
+          <t>&lt;p&gt;دوف مقشر الجسم بملح الهيمالايا وزيت الورد Dove Himalayan Salt and Rose Oil Body Scrub من دوف، نوعه مقشر جسم، بحجم 425 جم.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | مقشر الجسم بملح الهيمالايا وزيت الورد&lt;/li&gt;&lt;li&gt;النوع | مقشر جسم&lt;/li&gt;&lt;li&gt;الحجم | 425 جم&lt;/li&gt;&lt;li&gt;العلامة التجارية | دوف&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;مقشر جسم من دوف يجمع في اسمه بين ملح الهيمالايا وزيت الورد، ليكون خطوة مخصصة لتقشير بشرة الجسم ضمن روتين العناية. يأتي المنتج بعبوة وزنها 425 جم، ويمكن إدراجه في روتين الاستحمام مع مراعاة طريقة الاستخدام الموضحة على العبوة.&lt;/p&gt;&lt;p&gt;تمنحك تسمية المنتج تصوراً واضحاً عن طابعه: مقشر للجسم بتركيبة يرد فيها ملح الهيمالايا وزيت الورد. اختاريه عندما ترغبين في تخصيص خطوة للتقشير، مع استخدام لطيف وتجنب الضغط الشديد على البشرة.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مخصص لتقشير بشرة الجسم.&lt;/li&gt;&lt;li&gt;يحتوي اسم المنتج على ملح الهيمالايا وزيت الورد.&lt;/li&gt;&lt;li&gt;يندرج ضمن منتجات العناية بالجسم من دوف.&lt;/li&gt;&lt;li&gt;عبوة بوزن 425 جم.&lt;/li&gt;&lt;li&gt;يمكن إدخاله في روتين الاستحمام وفق تعليمات العبوة.&lt;/li&gt;&lt;li&gt;خطوة عناية مستقلة يمكن تنسيقها مع بقية روتين الجسم.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن مقشر مخصص للجسم.&lt;/li&gt;&lt;li&gt;لمن يفضل منتجات دوف للعناية الشخصية.&lt;/li&gt;&lt;li&gt;لمن يرغب في إضافة خطوة تقشير إلى روتينه.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;اتبعي الإرشادات المطبوعة على العبوة. يوزع المقشر على بشرة الجسم بالطريقة المحددة للمنتج، مع تدليك لطيف ثم الشطف إذا كانت تعليمات العبوة تنص على ذلك. تجنبي استخدامه على البشرة المتهيجة أو المجروحة، ولا تكثري من الضغط أثناء التدليك.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، تجنبي ملامسة العينين، وأبقي المنتج بعيداً عن متناول الأطفال. أوقفي الاستخدام عند ظهور انزعاج، وراجعي تعليمات العبوة قبل الاستعمال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;دوف علامة تجارية معروفة بمنتجات العناية الشخصية والجسم. تقدم العلامة أصنافاً متعددة تدخل في الروتين اليومي، ويأتي هذا المقشر ضمن مجموعة منتجاتها المخصصة للعناية بالجسم.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;س: ما نوع هذا المنتج؟&lt;/p&gt;&lt;p&gt;ج: هو مقشر مخصص لبشرة الجسم.&lt;/p&gt;&lt;p&gt;س: ما المكونات المذكورة في اسم المنتج؟&lt;/p&gt;&lt;p&gt;ج: يذكر الاسم ملح الهيمالايا وزيت الورد.&lt;/p&gt;&lt;p&gt;س: ما وزن العبوة؟&lt;/p&gt;&lt;p&gt;ج: وزن العبوة المذكور هو 425 جم.&lt;/p&gt;&lt;p&gt;س: كيف أستخدم المقشر؟&lt;/p&gt;&lt;p&gt;ج: اتبعي طريقة الاستخدام والتحذيرات المكتوبة على العبوة، واستخدميه بلطف.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -6704,7 +6714,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>MNT-R78</t>
+          <t>MNT-R81</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -6741,7 +6751,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>مقشر الجسم دوف باللافندر وحليب جوز الهند 298</t>
+          <t>دوف, مقشر جسم بالكرز, وحليب الشيا , 425جم</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -6751,12 +6761,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/51-bWlqiSfL.jpg</t>
+          <t>https://m.media-amazon.com/images/I/71j5Ygp9esL.jpg</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>مقشر الجسم دوف باللافندر وحليب جوز الهند 298</t>
+          <t>دوف, مقشر جسم بالكرز, وحليب الشيا , 425جم</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -6766,12 +6776,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>مقشر الجسم باللافندر وحليب جوز الهند من دوف Dove Lavender and Coconut Milk Body Scrub، مقشر للجسم بحجم 298. يذكر الاسم اللافندر وحليب جوز الهند، ويحدد نوع المنتج والعلامة التجارية، بينما لا يورد وحدة قياس للرقم 298.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | مقشر الجسم باللافندر وحليب جوز الهند&lt;/li&gt;&lt;li&gt;النوع | مقشر للجسم&lt;/li&gt;&lt;li&gt;الحجم | 298&lt;/li&gt;&lt;li&gt;العلامة التجارية | دوف Dove&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;مقشر للجسم من دوف، يجمع اسمه بين اللافندر وحليب جوز الهند كما وردا في بيانات المنتج. يندرج ضمن مستحضرات العناية بالجسم، ويأتي الرقم 298 ضمن الاسم من دون وحدة قياس، لذلك يُنقل الحجم كما ورد من غير افتراض جرام أو مل.&lt;/p&gt;&lt;p&gt;تُستخدم المقشرات على الجسم وفق تعليمات العبوة، مع الالتزام بطريقة التوزيع والشطف المحددة للمنتج. لا يوضح الاسم تفاصيل عن التركيبة أو نسب المكونات، كما لا يحدد مدة التدليك أو عدد مرات الاستخدام. تساعد قراءة بيانات العبوة على معرفة الإرشادات الخاصة بهذا المنتج قبل إضافته إلى روتين العناية.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مقشر مخصص للجسم.&lt;/li&gt;&lt;li&gt;يذكر اللافندر ضمن اسم المنتج.&lt;/li&gt;&lt;li&gt;يتضمن الاسم حليب جوز الهند.&lt;/li&gt;&lt;li&gt;من علامة دوف التجارية.&lt;/li&gt;&lt;li&gt;يرد الرقم 298 للحجم من دون وحدة قياس في الاسم.&lt;/li&gt;&lt;li&gt;يمكن استخدامه ضمن روتين العناية بالجسم وفق التعليمات.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن مستحضر مقشر للجسم.&lt;/li&gt;&lt;li&gt;لمن يفضل منتجًا يذكر اللافندر وحليب جوز الهند في اسمه.&lt;/li&gt;&lt;li&gt;لمن يرغب في اختيار مقشر من علامة دوف.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;يوزع على بشرة الجسم بالطريقة المذكورة على العبوة، مع تدليك لطيف فقط إذا كانت التعليمات توصي بذلك، ثم يشطف وفق الإرشادات. لا يحدد الاسم تواتر الاستخدام أو مدة التدليك، لذا يرجى الرجوع إلى تعليمات المنتج.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، تجنب ملامسة العينين، وأبعد المنتج عن متناول الأطفال. اتبعي الإرشادات المكتوبة على العبوة وتجنبي الاستخدام في المواضع غير المحددة.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;دوف هي العلامة التجارية المذكورة لهذا المقشر. يرد اسمها مع إشارات اللافندر وحليب جوز الهند والرقم 298 الوارد في اسم المنتج.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع المستحضر؟&lt;/p&gt;&lt;p&gt;هو مقشر للجسم من دوف.&lt;/p&gt;&lt;p&gt;ما العناصر المذكورة في اسمه؟&lt;/p&gt;&lt;p&gt;يذكر الاسم اللافندر وحليب جوز الهند.&lt;/p&gt;&lt;p&gt;هل الرقم 298 محدد بوحدة؟&lt;/p&gt;&lt;p&gt;لا ترد وحدة قياس بعد الرقم في الاسم؛ راجعي العبوة للتأكد من الحجم.&lt;/p&gt;&lt;p&gt;كيف أستخدمه؟&lt;/p&gt;&lt;p&gt;تُتبع طريقة الاستعمال المدوّنة على العبوة، بما في ذلك ما يتعلق بالتوزيع والشطف.&lt;/p&gt;</t>
+          <t>&lt;p&gt;دوف مقشر الجسم بالكرز وحليب الشيا Dove Cherry and Shea Milk Body Scrub من دوف، نوعه مقشر جسم، بحجم 425 جم.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | مقشر الجسم بالكرز وحليب الشيا&lt;/li&gt;&lt;li&gt;النوع | مقشر جسم&lt;/li&gt;&lt;li&gt;الحجم | 425 جم&lt;/li&gt;&lt;li&gt;العلامة التجارية | دوف&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;يأتي هذا المقشر من دوف مخصصاً للعناية ببشرة الجسم، ويحمل في اسمه الكرز وحليب الشيا. ويبلغ وزن العبوة 425 جم، ما يتيح إدراجه ضمن مستلزمات العناية بالجسم والاستحمام. استخدميه وفق الطريقة المبيّنة على العبوة، مع مراعاة احتياجات بشرتك وتجنب الفرك القوي.&lt;/p&gt;&lt;p&gt;يجمع الاسم بين طابع الفاكهة وإشارة حليب الشيا، مع تحديد واضح لوظيفة المنتج كمقشر للجسم. ويمكن تخصيصه لخطوة التقشير في روتينك، على أن تظل تفاصيل الاستخدام وعدد مرات التكرار مرتبطة بتوجيهات العبوة.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مقشر مخصص لبشرة الجسم.&lt;/li&gt;&lt;li&gt;يذكر اسم المنتج الكرز وحليب الشيا.&lt;/li&gt;&lt;li&gt;من منتجات دوف للعناية بالجسم.&lt;/li&gt;&lt;li&gt;وزن العبوة 425 جم.&lt;/li&gt;&lt;li&gt;يمكن إدراجه في روتين الاستحمام.&lt;/li&gt;&lt;li&gt;يوفر خياراً لمن يفضل منتجات التقشير ضمن العناية بالجسم.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يرغب في إضافة مقشر إلى روتين الجسم.&lt;/li&gt;&lt;li&gt;لمن يبحث عن منتج يحمل اسم الكرز وحليب الشيا.&lt;/li&gt;&lt;li&gt;لمستخدمي منتجات دوف للعناية الشخصية.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;راجعي تعليمات الاستخدام على العبوة قبل البدء. استخدمي المقشر على الجسم بالطريقة الموضحة، ودلكي بلطف دون ضغط زائد، ثم اشطفيه إذا كانت طريقة الاستخدام تنص على ذلك. تجنبي وضعه على البشرة المتضررة أو شديدة التحسس، ولا تستخدميه أكثر مما توصي به العبوة.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، تجنبي ملامسة العينين، واحفظيه بعيداً عن متناول الأطفال. أوقفي الاستخدام إذا سبب انزعاجاً، والتزمي بالإرشادات المرفقة بالمنتج.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;دوف علامة تجارية تقدم منتجات للعناية الشخصية والجسم. تتنوع منتجاتها بين أصناف للاستخدام اليومي وخطوات العناية، وهذا المقشر أحد منتجاتها الموجهة للعناية بالجسم.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;س: هل المنتج مخصص للجسم؟&lt;/p&gt;&lt;p&gt;ج: نعم، هو مقشر جسم بحسب اسم المنتج وتصنيفه.&lt;/p&gt;&lt;p&gt;س: ما الذي يرد في اسم المقشر؟&lt;/p&gt;&lt;p&gt;ج: يرد فيه الكرز وحليب الشيا.&lt;/p&gt;&lt;p&gt;س: ما وزن العبوة؟&lt;/p&gt;&lt;p&gt;ج: العبوة بوزن 425 جم.&lt;/p&gt;&lt;p&gt;س: أين أجد طريقة الاستخدام؟&lt;/p&gt;&lt;p&gt;ج: اتبعي تعليمات الاستخدام المطبوعة على العبوة.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -6781,7 +6791,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>MNT-R79</t>
+          <t>MNT-R82</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -6818,22 +6828,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>دوف مقشر الجسم بزبدة اللوز والمانجو298جم</t>
+          <t>سنسوداين معجون اسنان إنتعاش زائد 50 مل</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>العناية والجمال &gt; العناية بالجسم</t>
+          <t>العناية والجمال &gt; العناية الشخصية</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/51UW3T0xcNL.jpg</t>
+          <t>https://ecombe.nahdionline.com/media/catalog/product/1/0/100589334_63bbffcd646319bc6_19139.jpg?width=1050&amp;height=1050&amp;canvas=1050,1050&amp;optimize=high&amp;bg-color=255,255,255&amp;fit=bounds</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>دوف مقشر الجسم بزبدة اللوز والمانجو298جم</t>
+          <t>سنسوداين معجون اسنان إنتعاش زائد 50 مل</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -6843,12 +6853,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>مقشر الجسم بزبدة اللوز والمانجو من دوف Dove Almond Butter and Mango Body Scrub، مقشر للجسم بحجم 298 جم. يذكر الاسم زبدة اللوز والمانجو، ويحدد وزن العبوة والعلامة التجارية ونوع المستحضر.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | مقشر الجسم بزبدة اللوز والمانجو&lt;/li&gt;&lt;li&gt;النوع | مقشر للجسم&lt;/li&gt;&lt;li&gt;الحجم | 298 جم&lt;/li&gt;&lt;li&gt;العلامة التجارية | دوف Dove&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;مقشر للجسم من دوف، يحمل زبدة اللوز والمانجو في اسمه، ويأتي بوزن 298 جم. يوضح الاسم طبيعة المستحضر المخصص للجسم والعلامة التجارية، كما يورد العناصر المذكورة في تعريف المنتج من دون عرض قائمة كاملة بالمكونات أو نسبها.&lt;/p&gt;&lt;p&gt;يمكن إدخال المقشر ضمن روتين العناية بالجسم، مع استخدامه بالطريقة التي توضحها العبوة. يوزع على المنطقة المطلوبة وفق التعليمات، ويشطف إذا كانت الإرشادات تنص على ذلك. لا يحدد الاسم عدد مرات الاستخدام أو تفاصيل التدليك، لذا تُتبع المعلومات المدونة على العبوة ولا يُفترض برنامج استخدام ثابت.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مقشر مخصص للعناية بالجسم.&lt;/li&gt;&lt;li&gt;يذكر زبدة اللوز ضمن اسم المنتج.&lt;/li&gt;&lt;li&gt;يتضمن الاسم المانجو.&lt;/li&gt;&lt;li&gt;من علامة دوف التجارية.&lt;/li&gt;&lt;li&gt;يأتي بوزن 298 جم.&lt;/li&gt;&lt;li&gt;تساعد بيانات الاسم على معرفة النوع والحجم والعلامة التجارية.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن مقشر للجسم.&lt;/li&gt;&lt;li&gt;لمن يفضل منتجًا يذكر زبدة اللوز والمانجو في اسمه.&lt;/li&gt;&lt;li&gt;لمن يرغب في عبوة من دوف بوزن 298 جم.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;يستخدم على بشرة الجسم وفق التعليمات المطبوعة على العبوة. يوزع بلطف على المنطقة المطلوبة، ثم يشطف إذا نصت الإرشادات على ذلك. راجعي تفاصيل الاستعمال قبل الاستخدام لمعرفة التكرار وطريقة التطبيق الخاصة بالمنتج.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، تجنب ملامسة العينين، وأبعد المنتج عن متناول الأطفال. يُراعى اتباع تحذيرات العبوة وعدم استخدامه على مناطق غير موصى بها.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;دوف هي العلامة التجارية الواردة على هذا المقشر. يظهر اسمها مع وصف زبدة اللوز والمانجو ووزن العبوة المحدد بـ 298 جم.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما استخدام هذا المنتج؟&lt;/p&gt;&lt;p&gt;هو مقشر للجسم، ويستخدم وفق الإرشادات الخاصة به على العبوة.&lt;/p&gt;&lt;p&gt;ما العناصر المذكورة في الاسم؟&lt;/p&gt;&lt;p&gt;يذكر الاسم زبدة اللوز والمانجو.&lt;/p&gt;&lt;p&gt;ما وزن العبوة؟&lt;/p&gt;&lt;p&gt;الوزن المذكور هو 298 جم.&lt;/p&gt;&lt;p&gt;هل يوضح الاسم طريقة الاستعمال كاملة؟&lt;/p&gt;&lt;p&gt;لا، لذلك تُراجع العبوة لمعرفة طريقة التطبيق والتكرار والشطف.&lt;/p&gt;</t>
+          <t>&lt;p&gt;سنسوداين معجون أسنان انتعاش زائد Sensodyne Extra Fresh Toothpaste من سنسوداين، نوعه معجون أسنان، بحجم 50 مل.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | معجون أسنان انتعاش زائد&lt;/li&gt;&lt;li&gt;النوع | معجون أسنان&lt;/li&gt;&lt;li&gt;الحجم | 50 مل&lt;/li&gt;&lt;li&gt;العلامة التجارية | سنسوداين&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;معجون أسنان من سنسوداين يحمل اسم انتعاش زائد، ويأتي بحجم 50 مل. يندرج ضمن منتجات العناية الشخصية المخصصة لتنظيف الأسنان، ويمكن استخدامه كجزء من روتين العناية بالفم وفق الإرشادات المدونة على العبوة.&lt;/p&gt;&lt;p&gt;يوضح الاسم نوع المنتج واسمه التجاري دون الإشارة إلى درجة أو مقاس آخر. ولأن معاجين الأسنان تختلف في تعليمات الاستخدام والفئة العمرية المناسبة، ينبغي قراءة بيانات العبوة واتباعها، وعدم تجاوز الكمية أو الطريقة الموضحة من الشركة المصنّعة.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;معجون أسنان من علامة سنسوداين.&lt;/li&gt;&lt;li&gt;يحمل اسم انتعاش زائد.&lt;/li&gt;&lt;li&gt;حجم العبوة 50 مل.&lt;/li&gt;&lt;li&gt;مخصص لروتين تنظيف الأسنان.&lt;/li&gt;&lt;li&gt;يمكن وضعه ضمن مستلزمات العناية اليومية بالفم.&lt;/li&gt;&lt;li&gt;توضح العبوة بيانات المنتج وإرشادات استخدامه.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن معجون أسنان بحجم 50 مل.&lt;/li&gt;&lt;li&gt;لمستخدمي منتجات العناية بالفم من سنسوداين.&lt;/li&gt;&lt;li&gt;لمن يرغب في إضافة معجون إلى مستلزمات تنظيف الأسنان.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;استخدمي المعجون وفق الإرشادات المطبوعة على العبوة، وبالطريقة المناسبة للعمر المحدد في بيانات المنتج. لا تبتلعي المعجون، واحرصي على إغلاق العبوة بعد الاستخدام. عند وجود استفسار حول ملاءمته أو طريقة استعماله، يمكن الرجوع إلى تعليمات الشركة أو سؤال مختص بالعناية بالأسنان.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;يحفظ بعيداً عن متناول الأطفال ويستخدم وفق تعليمات العبوة. لا يُبتلع، وتجنبي استعماله بطريقة تخالف الإرشادات المطبوعة على المنتج.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;سنسوداين علامة تجارية لمنتجات العناية بالفم والأسنان. يندرج هذا المنتج ضمن معاجين الأسنان التي تحمل اسم العلامة، وتبقى تفاصيل الاستخدام والفئة العمرية مرتبطة بما توضحه العبوة.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;س: ما نوع المنتج؟&lt;/p&gt;&lt;p&gt;ج: هو معجون أسنان باسم انتعاش زائد.&lt;/p&gt;&lt;p&gt;س: ما حجم العبوة؟&lt;/p&gt;&lt;p&gt;ج: الحجم المذكور هو 50 مل.&lt;/p&gt;&lt;p&gt;س: هل يحتوي الاسم على درجة أو لون؟&lt;/p&gt;&lt;p&gt;ج: لا يرد في الاسم المذكور لون أو درجة.&lt;/p&gt;&lt;p&gt;س: كيف أستخدمه؟&lt;/p&gt;&lt;p&gt;ج: اتبعي تعليمات العبوة الخاصة بالاستخدام والكمية المناسبة.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -6858,7 +6868,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>MNT-R80</t>
+          <t>MNT-R83</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -6873,7 +6883,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>Dove</t>
+          <t>Sensodyne</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -6895,22 +6905,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>دوف مقشر الجسم بملح الهيمالايا وزيت الورد425ج</t>
+          <t>بودرة كلينيك المضغوطة الشفافة غير اللامعة</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>العناية والجمال &gt; العناية بالجسم</t>
+          <t>العناية والجمال &gt; الوجه &gt; بودرة الوجه</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71F1CH9-7wL.jpg</t>
+          <t>https://cdn.beautybay.com/images/eoaaqxyywn6o/CLIQ0500F_1.jpg_s3.lmb_4pija/5eb7dc3dd4906118282d33236053753d/CLIQ0500F_1.jpg?w=1200&amp;fm=jpg&amp;q=90</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>دوف مقشر الجسم بملح الهيمالايا وزيت الورد425ج</t>
+          <t>بودرة كلينيك المضغوطة الشفافة غير اللامعة</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -6920,12 +6930,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>&lt;p&gt;دوف مقشر الجسم بملح الهيمالايا وزيت الورد Dove Himalayan Salt and Rose Oil Body Scrub من دوف، نوعه مقشر جسم، بحجم 425 جم.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | مقشر الجسم بملح الهيمالايا وزيت الورد&lt;/li&gt;&lt;li&gt;النوع | مقشر جسم&lt;/li&gt;&lt;li&gt;الحجم | 425 جم&lt;/li&gt;&lt;li&gt;العلامة التجارية | دوف&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;مقشر جسم من دوف يجمع في اسمه بين ملح الهيمالايا وزيت الورد، ليكون خطوة مخصصة لتقشير بشرة الجسم ضمن روتين العناية. يأتي المنتج بعبوة وزنها 425 جم، ويمكن إدراجه في روتين الاستحمام مع مراعاة طريقة الاستخدام الموضحة على العبوة.&lt;/p&gt;&lt;p&gt;تمنحك تسمية المنتج تصوراً واضحاً عن طابعه: مقشر للجسم بتركيبة يرد فيها ملح الهيمالايا وزيت الورد. اختاريه عندما ترغبين في تخصيص خطوة للتقشير، مع استخدام لطيف وتجنب الضغط الشديد على البشرة.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مخصص لتقشير بشرة الجسم.&lt;/li&gt;&lt;li&gt;يحتوي اسم المنتج على ملح الهيمالايا وزيت الورد.&lt;/li&gt;&lt;li&gt;يندرج ضمن منتجات العناية بالجسم من دوف.&lt;/li&gt;&lt;li&gt;عبوة بوزن 425 جم.&lt;/li&gt;&lt;li&gt;يمكن إدخاله في روتين الاستحمام وفق تعليمات العبوة.&lt;/li&gt;&lt;li&gt;خطوة عناية مستقلة يمكن تنسيقها مع بقية روتين الجسم.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن مقشر مخصص للجسم.&lt;/li&gt;&lt;li&gt;لمن يفضل منتجات دوف للعناية الشخصية.&lt;/li&gt;&lt;li&gt;لمن يرغب في إضافة خطوة تقشير إلى روتينه.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;اتبعي الإرشادات المطبوعة على العبوة. يوزع المقشر على بشرة الجسم بالطريقة المحددة للمنتج، مع تدليك لطيف ثم الشطف إذا كانت تعليمات العبوة تنص على ذلك. تجنبي استخدامه على البشرة المتهيجة أو المجروحة، ولا تكثري من الضغط أثناء التدليك.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، تجنبي ملامسة العينين، وأبقي المنتج بعيداً عن متناول الأطفال. أوقفي الاستخدام عند ظهور انزعاج، وراجعي تعليمات العبوة قبل الاستعمال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;دوف علامة تجارية معروفة بمنتجات العناية الشخصية والجسم. تقدم العلامة أصنافاً متعددة تدخل في الروتين اليومي، ويأتي هذا المقشر ضمن مجموعة منتجاتها المخصصة للعناية بالجسم.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;س: ما نوع هذا المنتج؟&lt;/p&gt;&lt;p&gt;ج: هو مقشر مخصص لبشرة الجسم.&lt;/p&gt;&lt;p&gt;س: ما المكونات المذكورة في اسم المنتج؟&lt;/p&gt;&lt;p&gt;ج: يذكر الاسم ملح الهيمالايا وزيت الورد.&lt;/p&gt;&lt;p&gt;س: ما وزن العبوة؟&lt;/p&gt;&lt;p&gt;ج: وزن العبوة المذكور هو 425 جم.&lt;/p&gt;&lt;p&gt;س: كيف أستخدم المقشر؟&lt;/p&gt;&lt;p&gt;ج: اتبعي طريقة الاستخدام والتحذيرات المكتوبة على العبوة، واستخدميه بلطف.&lt;/p&gt;</t>
+          <t>&lt;p&gt;بودرة كلينيك المضغوطة الشفافة غير اللامعة Clinique Transparent Matte Pressed Powder من كلينيك، نوعها بودرة وجه مضغوطة.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | بودرة كلينيك المضغوطة الشفافة غير اللامعة&lt;/li&gt;&lt;li&gt;النوع | بودرة وجه مضغوطة&lt;/li&gt;&lt;li&gt;العلامة التجارية | كلينيك&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;بودرة وجه مضغوطة من كلينيك، يحدد اسمها أنها شفافة وغير لامعة. تأتي بصيغة مضغوطة وتندرج ضمن منتجات مكياج الوجه. لا يذكر الاسم درجة لونية أو حجماً محدداً، لذلك يفضل مراجعة بيانات العبوة أو المنتج للتعرف على أي تفاصيل إضافية قبل الاختيار.&lt;/p&gt;&lt;p&gt;تتيح طبيعتها المضغوطة حملها واستخدامها ضمن روتين المكياج، مع إمكانية توزيعها بأداة نظيفة مناسبة. وللحفاظ على مظهر متوازن، توضع بكمية قليلة وتزاد تدريجياً عند الحاجة، مع اتباع تعليمات الاستخدام التي يوردها المنتج.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;بودرة مخصصة لمكياج الوجه.&lt;/li&gt;&lt;li&gt;تركيبة مضغوطة وفق اسم المنتج.&lt;/li&gt;&lt;li&gt;موصوفة بأنها شفافة وغير لامعة.&lt;/li&gt;&lt;li&gt;من علامة كلينيك.&lt;/li&gt;&lt;li&gt;يمكن إدراجها ضمن خطوات وضع المكياج.&lt;/li&gt;&lt;li&gt;لا يحدد الاسم درجة لونية أو حجماً، لذا يمكن مراجعة معلومات العبوة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن بودرة وجه مضغوطة.&lt;/li&gt;&lt;li&gt;لمن يفضل وصفاً شفافاً وغير لامع في بودرة الوجه.&lt;/li&gt;&lt;li&gt;لمستخدمي مستحضرات المكياج من كلينيك.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;استخدمي أداة مكياج نظيفة، وخذي كمية مناسبة ثم وزعيها برفق على الوجه وفق حاجتك. ابدئي بطبقة خفيفة، ويمكن زيادة الكمية تدريجياً. راجعي تعليمات العبوة، وأغلقيها بعد الاستخدام لحماية المنتج من التلوث أو الانسكاب.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، تجنبي ملامسة العينين، وأبقي المنتج بعيداً عن متناول الأطفال. لا تستخدميه على بشرة متهيجة، وتوقفي عن الاستخدام إذا ظهر انزعاج.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;كلينيك علامة تجارية تقدم مستحضرات للمكياج والعناية بالبشرة. ويأتي هذا المنتج ضمن مستحضرات الوجه التي تحمل اسمها، مع ضرورة الرجوع إلى العبوة لمعرفة التفاصيل غير الواردة في اسم المنتج.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;س: ما نوع هذه البودرة؟&lt;/p&gt;&lt;p&gt;ج: بودرة وجه مضغوطة.&lt;/p&gt;&lt;p&gt;س: كيف يصف الاسم مظهرها؟&lt;/p&gt;&lt;p&gt;ج: يصفها بأنها شفافة وغير لامعة.&lt;/p&gt;&lt;p&gt;س: هل يذكر الاسم درجة أو حجماً؟&lt;/p&gt;&lt;p&gt;ج: لا يذكر الاسم المتاح درجة لونية أو حجماً.&lt;/p&gt;&lt;p&gt;س: ما طريقة وضعها؟&lt;/p&gt;&lt;p&gt;ج: توزع بأداة نظيفة وفق تعليمات العبوة، ويفضل البدء بكمية قليلة.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -6935,7 +6945,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>MNT-R81</t>
+          <t>MNT-R84</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -6950,7 +6960,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>Dove</t>
+          <t>Clinique</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -6972,22 +6982,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>دوف, مقشر جسم بالكرز, وحليب الشيا , 425جم</t>
+          <t>بخاخ مويستشر سيرج للوجه 125 مل - كلينيك</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>العناية والجمال &gt; العناية بالجسم</t>
+          <t>العناية والجمال &gt; العناية بالبشرة &gt; مرطبات</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71j5Ygp9esL.jpg</t>
+          <t>https://m.media-amazon.com/images/I/51Ib5MaxK9L.jpg</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>دوف, مقشر جسم بالكرز, وحليب الشيا , 425جم</t>
+          <t>بخاخ مويستشر سيرج للوجه 125 مل - كلينيك</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -6997,12 +7007,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>&lt;p&gt;دوف مقشر الجسم بالكرز وحليب الشيا Dove Cherry and Shea Milk Body Scrub من دوف، نوعه مقشر جسم، بحجم 425 جم.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | مقشر الجسم بالكرز وحليب الشيا&lt;/li&gt;&lt;li&gt;النوع | مقشر جسم&lt;/li&gt;&lt;li&gt;الحجم | 425 جم&lt;/li&gt;&lt;li&gt;العلامة التجارية | دوف&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;يأتي هذا المقشر من دوف مخصصاً للعناية ببشرة الجسم، ويحمل في اسمه الكرز وحليب الشيا. ويبلغ وزن العبوة 425 جم، ما يتيح إدراجه ضمن مستلزمات العناية بالجسم والاستحمام. استخدميه وفق الطريقة المبيّنة على العبوة، مع مراعاة احتياجات بشرتك وتجنب الفرك القوي.&lt;/p&gt;&lt;p&gt;يجمع الاسم بين طابع الفاكهة وإشارة حليب الشيا، مع تحديد واضح لوظيفة المنتج كمقشر للجسم. ويمكن تخصيصه لخطوة التقشير في روتينك، على أن تظل تفاصيل الاستخدام وعدد مرات التكرار مرتبطة بتوجيهات العبوة.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مقشر مخصص لبشرة الجسم.&lt;/li&gt;&lt;li&gt;يذكر اسم المنتج الكرز وحليب الشيا.&lt;/li&gt;&lt;li&gt;من منتجات دوف للعناية بالجسم.&lt;/li&gt;&lt;li&gt;وزن العبوة 425 جم.&lt;/li&gt;&lt;li&gt;يمكن إدراجه في روتين الاستحمام.&lt;/li&gt;&lt;li&gt;يوفر خياراً لمن يفضل منتجات التقشير ضمن العناية بالجسم.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يرغب في إضافة مقشر إلى روتين الجسم.&lt;/li&gt;&lt;li&gt;لمن يبحث عن منتج يحمل اسم الكرز وحليب الشيا.&lt;/li&gt;&lt;li&gt;لمستخدمي منتجات دوف للعناية الشخصية.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;راجعي تعليمات الاستخدام على العبوة قبل البدء. استخدمي المقشر على الجسم بالطريقة الموضحة، ودلكي بلطف دون ضغط زائد، ثم اشطفيه إذا كانت طريقة الاستخدام تنص على ذلك. تجنبي وضعه على البشرة المتضررة أو شديدة التحسس، ولا تستخدميه أكثر مما توصي به العبوة.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، تجنبي ملامسة العينين، واحفظيه بعيداً عن متناول الأطفال. أوقفي الاستخدام إذا سبب انزعاجاً، والتزمي بالإرشادات المرفقة بالمنتج.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;دوف علامة تجارية تقدم منتجات للعناية الشخصية والجسم. تتنوع منتجاتها بين أصناف للاستخدام اليومي وخطوات العناية، وهذا المقشر أحد منتجاتها الموجهة للعناية بالجسم.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;س: هل المنتج مخصص للجسم؟&lt;/p&gt;&lt;p&gt;ج: نعم، هو مقشر جسم بحسب اسم المنتج وتصنيفه.&lt;/p&gt;&lt;p&gt;س: ما الذي يرد في اسم المقشر؟&lt;/p&gt;&lt;p&gt;ج: يرد فيه الكرز وحليب الشيا.&lt;/p&gt;&lt;p&gt;س: ما وزن العبوة؟&lt;/p&gt;&lt;p&gt;ج: العبوة بوزن 425 جم.&lt;/p&gt;&lt;p&gt;س: أين أجد طريقة الاستخدام؟&lt;/p&gt;&lt;p&gt;ج: اتبعي تعليمات الاستخدام المطبوعة على العبوة.&lt;/p&gt;</t>
+          <t>&lt;p&gt;بخاخ مويستشر سيرج للوجه Moisture Surge Face Spray من كلينيك، نوعه رذاذ ترطيب الوجه، بحجم 125 مل.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | بخاخ مويستشر سيرج للوجه&lt;/li&gt;&lt;li&gt;النوع | رذاذ ترطيب الوجه&lt;/li&gt;&lt;li&gt;الحجم | 125 مل&lt;/li&gt;&lt;li&gt;العلامة التجارية | كلينيك&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;رذاذ للوجه من مجموعة مويستشر سيرج من كلينيك، ويأتي بحجم 125 مل. يندرج ضمن منتجات الترطيب والعناية بالبشرة، وتمنح صيغة البخاخ طريقة استخدام مختلفة عن الكريمات أو المستحضرات التي توزع باليد. يمكن إدخاله في روتين الوجه وفق الإرشادات المدونة على العبوة.&lt;/p&gt;&lt;p&gt;يحمل المنتج اسماً يوضح ارتباطه بترطيب الوجه، من دون أن يذكر الاسم نوع البشرة أو مكونات محددة. لذلك احرصي على مراجعة بيانات العبوة للتعرف على تفاصيل المنتج وطريقة تطبيقه، واستخدميه بحذر مع إبعاد الرذاذ عن العينين.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;بخاخ مخصص للوجه.&lt;/li&gt;&lt;li&gt;ينتمي إلى مجموعة مويستشر سيرج من كلينيك.&lt;/li&gt;&lt;li&gt;يأتي بحجم 125 مل.&lt;/li&gt;&lt;li&gt;مصنف ضمن منتجات ترطيب البشرة.&lt;/li&gt;&lt;li&gt;صيغة رذاذ سهلة الإدراج في روتين الوجه.&lt;/li&gt;&lt;li&gt;يمكن استخدامه وفق تعليمات العبوة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن رذاذ للوجه من كلينيك.&lt;/li&gt;&lt;li&gt;لمن يفضل مستحضرات الترطيب بصيغة البخاخ.&lt;/li&gt;&lt;li&gt;لمن يرغب في إضافة خطوة ترطيب إلى روتين البشرة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;راجعي الإرشادات على العبوة قبل الاستعمال. عند الاستخدام، أغمضي العينين واتبعي الطريقة المحددة للرش، مع تجنب توجيه الرذاذ مباشرة إلى العينين أو استنشاقه. لا تستبدلي تعليمات الشركة بطريقة غير موضحة، وأغلقي العبوة بعد الانتهاء.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، تجنبي ملامسة العينين، واحفظي العبوة بعيداً عن متناول الأطفال. أوقفي الاستخدام عند حدوث انزعاج، والتزمي بإرشادات العبوة.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;كلينيك علامة تجارية لمستحضرات التجميل والعناية بالبشرة، وتضم منتجات للوجه بصيغ متعددة. يحمل هذا الرذاذ اسم مويستشر سيرج، ويأتي ضمن أصناف العناية التي تحمل اسم العلامة.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;س: ما نوع المنتج؟&lt;/p&gt;&lt;p&gt;ج: هو بخاخ مخصص للوجه ضمن منتجات الترطيب.&lt;/p&gt;&lt;p&gt;س: ما حجمه؟&lt;/p&gt;&lt;p&gt;ج: الحجم المذكور هو 125 مل.&lt;/p&gt;&lt;p&gt;س: هل يحدد الاسم نوع البشرة؟&lt;/p&gt;&lt;p&gt;ج: لا يحدد الاسم المتاح نوعاً معيناً للبشرة.&lt;/p&gt;&lt;p&gt;س: أين أجد طريقة الاستخدام؟&lt;/p&gt;&lt;p&gt;ج: راجعي الإرشادات المطبوعة على العبوة قبل الاستعمال.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7012,7 +7022,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>MNT-R82</t>
+          <t>MNT-R85</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7027,7 +7037,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>Dove</t>
+          <t>Clinique</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -7049,22 +7059,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>سنسوداين معجون اسنان إنتعاش زائد 50 مل</t>
+          <t>كلينيك بلسم تنظيف تيك ذا داي اوف للجنسين125مل</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>العناية والجمال &gt; العناية الشخصية</t>
+          <t>العناية والجمال &gt; العناية بالبشرة &gt; تنظيف الوجه</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://ecombe.nahdionline.com/media/catalog/product/1/0/100589334_63bbffcd646319bc6_19139.jpg?width=1050&amp;height=1050&amp;canvas=1050,1050&amp;optimize=high&amp;bg-color=255,255,255&amp;fit=bounds</t>
+          <t>https://m.media-amazon.com/images/I/61M-LA9OsgL.jpg</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>سنسوداين معجون اسنان إنتعاش زائد 50 مل</t>
+          <t>كلينيك بلسم تنظيف تيك ذا داي اوف للجنسين125مل</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -7074,12 +7084,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>&lt;p&gt;سنسوداين معجون أسنان انتعاش زائد Sensodyne Extra Fresh Toothpaste من سنسوداين، نوعه معجون أسنان، بحجم 50 مل.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | معجون أسنان انتعاش زائد&lt;/li&gt;&lt;li&gt;النوع | معجون أسنان&lt;/li&gt;&lt;li&gt;الحجم | 50 مل&lt;/li&gt;&lt;li&gt;العلامة التجارية | سنسوداين&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;معجون أسنان من سنسوداين يحمل اسم انتعاش زائد، ويأتي بحجم 50 مل. يندرج ضمن منتجات العناية الشخصية المخصصة لتنظيف الأسنان، ويمكن استخدامه كجزء من روتين العناية بالفم وفق الإرشادات المدونة على العبوة.&lt;/p&gt;&lt;p&gt;يوضح الاسم نوع المنتج واسمه التجاري دون الإشارة إلى درجة أو مقاس آخر. ولأن معاجين الأسنان تختلف في تعليمات الاستخدام والفئة العمرية المناسبة، ينبغي قراءة بيانات العبوة واتباعها، وعدم تجاوز الكمية أو الطريقة الموضحة من الشركة المصنّعة.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;معجون أسنان من علامة سنسوداين.&lt;/li&gt;&lt;li&gt;يحمل اسم انتعاش زائد.&lt;/li&gt;&lt;li&gt;حجم العبوة 50 مل.&lt;/li&gt;&lt;li&gt;مخصص لروتين تنظيف الأسنان.&lt;/li&gt;&lt;li&gt;يمكن وضعه ضمن مستلزمات العناية اليومية بالفم.&lt;/li&gt;&lt;li&gt;توضح العبوة بيانات المنتج وإرشادات استخدامه.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن معجون أسنان بحجم 50 مل.&lt;/li&gt;&lt;li&gt;لمستخدمي منتجات العناية بالفم من سنسوداين.&lt;/li&gt;&lt;li&gt;لمن يرغب في إضافة معجون إلى مستلزمات تنظيف الأسنان.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;استخدمي المعجون وفق الإرشادات المطبوعة على العبوة، وبالطريقة المناسبة للعمر المحدد في بيانات المنتج. لا تبتلعي المعجون، واحرصي على إغلاق العبوة بعد الاستخدام. عند وجود استفسار حول ملاءمته أو طريقة استعماله، يمكن الرجوع إلى تعليمات الشركة أو سؤال مختص بالعناية بالأسنان.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;يحفظ بعيداً عن متناول الأطفال ويستخدم وفق تعليمات العبوة. لا يُبتلع، وتجنبي استعماله بطريقة تخالف الإرشادات المطبوعة على المنتج.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;سنسوداين علامة تجارية لمنتجات العناية بالفم والأسنان. يندرج هذا المنتج ضمن معاجين الأسنان التي تحمل اسم العلامة، وتبقى تفاصيل الاستخدام والفئة العمرية مرتبطة بما توضحه العبوة.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;س: ما نوع المنتج؟&lt;/p&gt;&lt;p&gt;ج: هو معجون أسنان باسم انتعاش زائد.&lt;/p&gt;&lt;p&gt;س: ما حجم العبوة؟&lt;/p&gt;&lt;p&gt;ج: الحجم المذكور هو 50 مل.&lt;/p&gt;&lt;p&gt;س: هل يحتوي الاسم على درجة أو لون؟&lt;/p&gt;&lt;p&gt;ج: لا يرد في الاسم المذكور لون أو درجة.&lt;/p&gt;&lt;p&gt;س: كيف أستخدمه؟&lt;/p&gt;&lt;p&gt;ج: اتبعي تعليمات العبوة الخاصة بالاستخدام والكمية المناسبة.&lt;/p&gt;</t>
+          <t>&lt;p&gt;كلينيك بلسم تنظيف تيك ذا داي أوف Clinique Take The Day Off Cleansing Balm من كلينيك، نوعه بلسم تنظيف الوجه، بحجم 125 مل، ومذكور أنه للجنسين.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | بلسم تنظيف تيك ذا داي أوف&lt;/li&gt;&lt;li&gt;النوع | بلسم تنظيف الوجه&lt;/li&gt;&lt;li&gt;الحجم | 125 مل&lt;/li&gt;&lt;li&gt;العلامة التجارية | كلينيك&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;بلسم تنظيف للوجه من كلينيك يحمل اسم تيك ذا داي أوف، ويأتي بحجم 125 مل. ويشير الاسم الإنجليزي إلى بلسم للتنظيف، بينما يرد في بيانات المنتج أنه للجنسين. يمكن إدراجه في خطوات تنظيف الوجه، مع الرجوع إلى تعليمات العبوة لمعرفة كيفية تطبيقه وإزالته.&lt;/p&gt;&lt;p&gt;يقدم البلسم بديلاً بصيغة مختلفة عن الغسول السائل، ويتيح اختيار طريقة التنظيف وفق ما يلائم روتينك. لا يذكر الاسم نوع البشرة أو تفاصيل التركيبة؛ لذا من الأفضل مراجعة بيانات المنتج كاملة قبل الاستخدام، واتباع الخطوات الموضحة من العلامة.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;بلسم مخصص لتنظيف الوجه.&lt;/li&gt;&lt;li&gt;يحمل اسم تيك ذا داي أوف.&lt;/li&gt;&lt;li&gt;من علامة كلينيك.&lt;/li&gt;&lt;li&gt;حجم العبوة 125 مل.&lt;/li&gt;&lt;li&gt;مذكور أنه مناسب للجنسين.&lt;/li&gt;&lt;li&gt;صيغة بلسم ضمن خيارات تنظيف الوجه.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن بلسم لتنظيف الوجه.&lt;/li&gt;&lt;li&gt;للجنسين وفق بيانات المنتج المقدمة.&lt;/li&gt;&lt;li&gt;لمن يفضل إضافة منتج بصيغة البلسم إلى روتين التنظيف.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;اتبعي التعليمات المطبوعة على العبوة لمعرفة طريقة توزيع البلسم وإزالته. استخدميه على الوجه بالطريقة المحددة، ثم أكملي روتين التنظيف وفق احتياجك. تجنبي وضعه على محيط العينين ما لم توضح العبوة خلاف ذلك، واغسلي اليدين بعد الاستخدام.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، تجنبي ملامسة العينين، وأبقيه بعيداً عن متناول الأطفال. أوقفي الاستخدام عند حدوث انزعاج، وراجعي التعليمات قبل الاستعمال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;كلينيك علامة تجارية تقدم مستحضرات للمكياج والعناية بالبشرة. يشمل اسمها منتجات مخصصة لخطوات العناية بالوجه، وهذا البلسم أحد منتجات التنظيف التي تحمل اسمها.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;س: ما نوع منتج تيك ذا داي أوف؟&lt;/p&gt;&lt;p&gt;ج: هو بلسم تنظيف للوجه.&lt;/p&gt;&lt;p&gt;س: ما حجم العبوة؟&lt;/p&gt;&lt;p&gt;ج: العبوة بحجم 125 مل.&lt;/p&gt;&lt;p&gt;س: لمن يوجه المنتج؟&lt;/p&gt;&lt;p&gt;ج: يرد في بيانات المنتج أنه للجنسين.&lt;/p&gt;&lt;p&gt;س: كيف تتم إزالة البلسم؟&lt;/p&gt;&lt;p&gt;ج: اتبعي الطريقة الموضحة على العبوة للتطبيق والإزالة.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7089,7 +7099,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>MNT-R83</t>
+          <t>MNT-R86</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -7104,7 +7114,7 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>Sensodyne</t>
+          <t>Clinique</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -7126,22 +7136,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>بودرة كلينيك المضغوطة الشفافة غير اللامعة</t>
+          <t>كلينيك جل مرطب درامتكلي ديفرنت - 125 مل</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>العناية والجمال &gt; الوجه &gt; بودرة الوجه</t>
+          <t>العناية والجمال &gt; العناية بالبشرة &gt; مرطبات</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://cdn.beautybay.com/images/eoaaqxyywn6o/CLIQ0500F_1.jpg_s3.lmb_4pija/5eb7dc3dd4906118282d33236053753d/CLIQ0500F_1.jpg?w=1200&amp;fm=jpg&amp;q=90</t>
+          <t>https://m.media-amazon.com/images/I/61rjIWgNJoL.jpg</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>بودرة كلينيك المضغوطة الشفافة غير اللامعة</t>
+          <t>كلينيك جل مرطب درامتكلي ديفرنت - 125 مل</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -7151,12 +7161,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>80</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>&lt;p&gt;بودرة كلينيك المضغوطة الشفافة غير اللامعة Clinique Transparent Matte Pressed Powder من كلينيك، نوعها بودرة وجه مضغوطة.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | بودرة كلينيك المضغوطة الشفافة غير اللامعة&lt;/li&gt;&lt;li&gt;النوع | بودرة وجه مضغوطة&lt;/li&gt;&lt;li&gt;العلامة التجارية | كلينيك&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;بودرة وجه مضغوطة من كلينيك، يحدد اسمها أنها شفافة وغير لامعة. تأتي بصيغة مضغوطة وتندرج ضمن منتجات مكياج الوجه. لا يذكر الاسم درجة لونية أو حجماً محدداً، لذلك يفضل مراجعة بيانات العبوة أو المنتج للتعرف على أي تفاصيل إضافية قبل الاختيار.&lt;/p&gt;&lt;p&gt;تتيح طبيعتها المضغوطة حملها واستخدامها ضمن روتين المكياج، مع إمكانية توزيعها بأداة نظيفة مناسبة. وللحفاظ على مظهر متوازن، توضع بكمية قليلة وتزاد تدريجياً عند الحاجة، مع اتباع تعليمات الاستخدام التي يوردها المنتج.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;بودرة مخصصة لمكياج الوجه.&lt;/li&gt;&lt;li&gt;تركيبة مضغوطة وفق اسم المنتج.&lt;/li&gt;&lt;li&gt;موصوفة بأنها شفافة وغير لامعة.&lt;/li&gt;&lt;li&gt;من علامة كلينيك.&lt;/li&gt;&lt;li&gt;يمكن إدراجها ضمن خطوات وضع المكياج.&lt;/li&gt;&lt;li&gt;لا يحدد الاسم درجة لونية أو حجماً، لذا يمكن مراجعة معلومات العبوة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن بودرة وجه مضغوطة.&lt;/li&gt;&lt;li&gt;لمن يفضل وصفاً شفافاً وغير لامع في بودرة الوجه.&lt;/li&gt;&lt;li&gt;لمستخدمي مستحضرات المكياج من كلينيك.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;استخدمي أداة مكياج نظيفة، وخذي كمية مناسبة ثم وزعيها برفق على الوجه وفق حاجتك. ابدئي بطبقة خفيفة، ويمكن زيادة الكمية تدريجياً. راجعي تعليمات العبوة، وأغلقيها بعد الاستخدام لحماية المنتج من التلوث أو الانسكاب.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، تجنبي ملامسة العينين، وأبقي المنتج بعيداً عن متناول الأطفال. لا تستخدميه على بشرة متهيجة، وتوقفي عن الاستخدام إذا ظهر انزعاج.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;كلينيك علامة تجارية تقدم مستحضرات للمكياج والعناية بالبشرة. ويأتي هذا المنتج ضمن مستحضرات الوجه التي تحمل اسمها، مع ضرورة الرجوع إلى العبوة لمعرفة التفاصيل غير الواردة في اسم المنتج.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;س: ما نوع هذه البودرة؟&lt;/p&gt;&lt;p&gt;ج: بودرة وجه مضغوطة.&lt;/p&gt;&lt;p&gt;س: كيف يصف الاسم مظهرها؟&lt;/p&gt;&lt;p&gt;ج: يصفها بأنها شفافة وغير لامعة.&lt;/p&gt;&lt;p&gt;س: هل يذكر الاسم درجة أو حجماً؟&lt;/p&gt;&lt;p&gt;ج: لا يذكر الاسم المتاح درجة لونية أو حجماً.&lt;/p&gt;&lt;p&gt;س: ما طريقة وضعها؟&lt;/p&gt;&lt;p&gt;ج: توزع بأداة نظيفة وفق تعليمات العبوة، ويفضل البدء بكمية قليلة.&lt;/p&gt;</t>
+          <t>&lt;p&gt;كلينيك جل مرطب درامتكلي ديفرنت Clinique Dramatically Different Moisturizing Gel من كلينيك، نوعه جل مرطب للوجه، بحجم 125 مل.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | جل مرطب درامتكلي ديفرنت&lt;/li&gt;&lt;li&gt;النوع | جل مرطب للوجه&lt;/li&gt;&lt;li&gt;الحجم | 125 مل&lt;/li&gt;&lt;li&gt;العلامة التجارية | كلينيك&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;جل مرطب من كلينيك يحمل اسم درامتكلي ديفرنت، ويأتي بحجم 125 مل. يندرج ضمن مستحضرات ترطيب البشرة، وتمنحه صيغة الجل قواماً مختلفاً عن الكريمات التقليدية. يمكن إدخاله في روتين العناية بالوجه وفق الطريقة الموضحة على العبوة.&lt;/p&gt;&lt;p&gt;لا يحدد الاسم نوع البشرة أو أوقات الاستخدام، لذا اطلعي على بيانات المنتج قبل تطبيقه، خاصة إذا كنت تستخدمين منتجات أخرى ضمن الروتين نفسه. يوزع الجل على البشرة بالطريقة الملائمة حسب إرشادات العبوة، مع تجنب محيط العينين.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;جل مرطب للوجه من كلينيك.&lt;/li&gt;&lt;li&gt;يحمل اسم درامتكلي ديفرنت.&lt;/li&gt;&lt;li&gt;يأتي بحجم 125 مل.&lt;/li&gt;&lt;li&gt;صيغة جل ضمن منتجات ترطيب البشرة.&lt;/li&gt;&lt;li&gt;يمكن إدخاله ضمن روتين العناية بالوجه.&lt;/li&gt;&lt;li&gt;تعرض العبوة تعليمات الاستخدام والتفاصيل المتاحة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن مرطب للوجه بصيغة جل.&lt;/li&gt;&lt;li&gt;لمستخدمي منتجات كلينيك للعناية بالبشرة.&lt;/li&gt;&lt;li&gt;لمن يرغب في إضافة خطوة ترطيب إلى روتينه.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;ضعي الجل وفق تعليمات العبوة، ووزعيه برفق على بشرة الوجه مع تجنب العينين. ابدئي بالكمية التي توصي بها الشركة، واتركي المستحضر يمتص بحسب توجيهات المنتج قبل متابعة روتينك. راجعي العبوة لمعرفة التوقيت والتكرار المناسبين.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، تجنبي ملامسة العينين، واحفظي العبوة بعيداً عن متناول الأطفال. توقفي عن الاستخدام عند حدوث انزعاج، ولا تضعيه على بشرة متضررة.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;كلينيك علامة تجارية تشمل منتجات للعناية بالبشرة ومستحضرات المكياج. ويأتي جل درامتكلي ديفرنت ضمن مستحضرات الترطيب التي تحمل اسمها، وتوضح العبوة المعلومات الخاصة بطريقة الاستخدام.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;س: ما نوع المنتج؟&lt;/p&gt;&lt;p&gt;ج: هو جل مرطب للوجه.&lt;/p&gt;&lt;p&gt;س: ما حجمه؟&lt;/p&gt;&lt;p&gt;ج: الحجم المذكور على اسم المنتج هو 125 مل.&lt;/p&gt;&lt;p&gt;س: هل يحدد الاسم نوع البشرة؟&lt;/p&gt;&lt;p&gt;ج: لا يذكر الاسم المتاح نوعاً معيناً للبشرة.&lt;/p&gt;&lt;p&gt;س: متى يوضع الجل؟&lt;/p&gt;&lt;p&gt;ج: اتبعي توقيت الاستخدام وطريقته كما وردا على العبوة.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7166,7 +7176,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>MNT-R84</t>
+          <t>MNT-R87</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -7203,22 +7213,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>بخاخ مويستشر سيرج للوجه 125 مل - كلينيك</t>
+          <t>كلينيك صابون سائل للوجه للبشرة الدهنية 200مل</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>العناية والجمال &gt; العناية بالبشرة &gt; مرطبات</t>
+          <t>العناية والجمال &gt; العناية بالبشرة &gt; تنظيف الوجه</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/51Ib5MaxK9L.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41VlM2-R3mS.jpg</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>بخاخ مويستشر سيرج للوجه 125 مل - كلينيك</t>
+          <t>كلينيك صابون سائل للوجه للبشرة الدهنية 200مل</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -7228,12 +7238,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>&lt;p&gt;بخاخ مويستشر سيرج للوجه Moisture Surge Face Spray من كلينيك، نوعه رذاذ ترطيب الوجه، بحجم 125 مل.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | بخاخ مويستشر سيرج للوجه&lt;/li&gt;&lt;li&gt;النوع | رذاذ ترطيب الوجه&lt;/li&gt;&lt;li&gt;الحجم | 125 مل&lt;/li&gt;&lt;li&gt;العلامة التجارية | كلينيك&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;رذاذ للوجه من مجموعة مويستشر سيرج من كلينيك، ويأتي بحجم 125 مل. يندرج ضمن منتجات الترطيب والعناية بالبشرة، وتمنح صيغة البخاخ طريقة استخدام مختلفة عن الكريمات أو المستحضرات التي توزع باليد. يمكن إدخاله في روتين الوجه وفق الإرشادات المدونة على العبوة.&lt;/p&gt;&lt;p&gt;يحمل المنتج اسماً يوضح ارتباطه بترطيب الوجه، من دون أن يذكر الاسم نوع البشرة أو مكونات محددة. لذلك احرصي على مراجعة بيانات العبوة للتعرف على تفاصيل المنتج وطريقة تطبيقه، واستخدميه بحذر مع إبعاد الرذاذ عن العينين.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;بخاخ مخصص للوجه.&lt;/li&gt;&lt;li&gt;ينتمي إلى مجموعة مويستشر سيرج من كلينيك.&lt;/li&gt;&lt;li&gt;يأتي بحجم 125 مل.&lt;/li&gt;&lt;li&gt;مصنف ضمن منتجات ترطيب البشرة.&lt;/li&gt;&lt;li&gt;صيغة رذاذ سهلة الإدراج في روتين الوجه.&lt;/li&gt;&lt;li&gt;يمكن استخدامه وفق تعليمات العبوة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن رذاذ للوجه من كلينيك.&lt;/li&gt;&lt;li&gt;لمن يفضل مستحضرات الترطيب بصيغة البخاخ.&lt;/li&gt;&lt;li&gt;لمن يرغب في إضافة خطوة ترطيب إلى روتين البشرة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;راجعي الإرشادات على العبوة قبل الاستعمال. عند الاستخدام، أغمضي العينين واتبعي الطريقة المحددة للرش، مع تجنب توجيه الرذاذ مباشرة إلى العينين أو استنشاقه. لا تستبدلي تعليمات الشركة بطريقة غير موضحة، وأغلقي العبوة بعد الانتهاء.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، تجنبي ملامسة العينين، واحفظي العبوة بعيداً عن متناول الأطفال. أوقفي الاستخدام عند حدوث انزعاج، والتزمي بإرشادات العبوة.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;كلينيك علامة تجارية لمستحضرات التجميل والعناية بالبشرة، وتضم منتجات للوجه بصيغ متعددة. يحمل هذا الرذاذ اسم مويستشر سيرج، ويأتي ضمن أصناف العناية التي تحمل اسم العلامة.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;س: ما نوع المنتج؟&lt;/p&gt;&lt;p&gt;ج: هو بخاخ مخصص للوجه ضمن منتجات الترطيب.&lt;/p&gt;&lt;p&gt;س: ما حجمه؟&lt;/p&gt;&lt;p&gt;ج: الحجم المذكور هو 125 مل.&lt;/p&gt;&lt;p&gt;س: هل يحدد الاسم نوع البشرة؟&lt;/p&gt;&lt;p&gt;ج: لا يحدد الاسم المتاح نوعاً معيناً للبشرة.&lt;/p&gt;&lt;p&gt;س: أين أجد طريقة الاستخدام؟&lt;/p&gt;&lt;p&gt;ج: راجعي الإرشادات المطبوعة على العبوة قبل الاستعمال.&lt;/p&gt;</t>
+          <t>&lt;p&gt;كلينيك صابون سائل للوجه للبشرة الدهنية Clinique Liquid Facial Soap Oily Skin من كلينيك، نوعه غسول وجه سائل، بحجم 200 مل.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | صابون سائل للوجه للبشرة الدهنية&lt;/li&gt;&lt;li&gt;النوع | غسول وجه سائل&lt;/li&gt;&lt;li&gt;الحجم | 200 مل&lt;/li&gt;&lt;li&gt;العلامة التجارية | كلينيك&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;منظف سائل للوجه من كلينيك، يذكر اسمه أنه مخصص للبشرة الدهنية، ويأتي بحجم 200 مل. يندرج ضمن منتجات تنظيف الوجه، ويمكن إدراجه في خطوة غسل البشرة ضمن الروتين اليومي وفق تعليمات العبوة.&lt;/p&gt;&lt;p&gt;تساعد صيغة الصابون السائل على توزيع المنتج أثناء التنظيف، مع ضرورة الالتزام بطريقة الاستخدام الموصى بها وتجنب المبالغة في الغسل. إذا كانت لديك استفسارات حول ملاءمته لبشرتك أو توافقه مع مستحضرات أخرى، راجعي بيانات المنتج أو استشيري مختصاً.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;صابون سائل مخصص لتنظيف الوجه.&lt;/li&gt;&lt;li&gt;مذكور للبشرة الدهنية في الاسم.&lt;/li&gt;&lt;li&gt;من علامة كلينيك.&lt;/li&gt;&lt;li&gt;عبوة بحجم 200 مل.&lt;/li&gt;&lt;li&gt;صيغة سائلة مناسبة لخطوة غسل الوجه.&lt;/li&gt;&lt;li&gt;يستخدم وفق التعليمات الموضحة على العبوة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن منظف سائل للوجه.&lt;/li&gt;&lt;li&gt;لمن يختار منتجاً يذكر البشرة الدهنية في اسمه.&lt;/li&gt;&lt;li&gt;لمستخدمي مستحضرات العناية بالبشرة من كلينيك.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;اتبعي تعليمات العبوة، وبللي الوجه إذا كانت طريقة الاستخدام تنص على ذلك، ثم وزعي كمية مناسبة من المنظف بلطف واشطفيه جيداً عند الانتهاء. تجنبي ملامسة العينين، ولا تستخدميه على بشرة متضررة. أغلقي العبوة بعد الاستعمال.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، تجنبي ملامسة العينين، وأبقي المنتج بعيداً عن متناول الأطفال. أوقفي الاستخدام إذا ظهر انزعاج، والتزمي بتوجيهات العبوة.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;كلينيك علامة تجارية تقدم أصنافاً للمكياج والعناية بالبشرة. يندرج هذا الصابون السائل ضمن منتجات تنظيف الوجه التي تحمل اسمها، وتوضح العبوة تفاصيل الاستعمال الموصى بها.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;س: ما نوع المنتج؟&lt;/p&gt;&lt;p&gt;ج: صابون سائل لتنظيف الوجه.&lt;/p&gt;&lt;p&gt;س: لأي نوع بشرة يذكر المنتج؟&lt;/p&gt;&lt;p&gt;ج: يذكر الاسم أنه للبشرة الدهنية.&lt;/p&gt;&lt;p&gt;س: ما حجم العبوة؟&lt;/p&gt;&lt;p&gt;ج: تأتي العبوة بحجم 200 مل.&lt;/p&gt;&lt;p&gt;س: هل يستخدم حول العينين؟&lt;/p&gt;&lt;p&gt;ج: ينبغي تجنب ملامسة العينين واتباع تعليمات العبوة.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -7243,7 +7253,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>MNT-R85</t>
+          <t>MNT-R88</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -7280,22 +7290,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>كلينيك بلسم تنظيف تيك ذا داي اوف للجنسين125مل</t>
+          <t>زيت فيتامين E من دي لا كروز، 65 مل</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>العناية والجمال &gt; العناية بالبشرة &gt; تنظيف الوجه</t>
+          <t>العناية والجمال &gt; العناية بالبشرة &gt; زيوت وزبدات</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/61M-LA9OsgL.jpg</t>
+          <t>https://ecombe.nahdionline.com/media/catalog/product/1/0/102925696_65f774f377ff032f9_32226.png?width=1050&amp;height=1050&amp;canvas=1050,1050&amp;optimize=high&amp;bg-color=255,255,255&amp;fit=bounds</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>كلينيك بلسم تنظيف تيك ذا داي اوف للجنسين125مل</t>
+          <t>زيت فيتامين E من دي لا كروز، 65 مل</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -7305,12 +7315,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>&lt;p&gt;كلينيك بلسم تنظيف تيك ذا داي أوف Clinique Take The Day Off Cleansing Balm من كلينيك، نوعه بلسم تنظيف الوجه، بحجم 125 مل، ومذكور أنه للجنسين.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | بلسم تنظيف تيك ذا داي أوف&lt;/li&gt;&lt;li&gt;النوع | بلسم تنظيف الوجه&lt;/li&gt;&lt;li&gt;الحجم | 125 مل&lt;/li&gt;&lt;li&gt;العلامة التجارية | كلينيك&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;بلسم تنظيف للوجه من كلينيك يحمل اسم تيك ذا داي أوف، ويأتي بحجم 125 مل. ويشير الاسم الإنجليزي إلى بلسم للتنظيف، بينما يرد في بيانات المنتج أنه للجنسين. يمكن إدراجه في خطوات تنظيف الوجه، مع الرجوع إلى تعليمات العبوة لمعرفة كيفية تطبيقه وإزالته.&lt;/p&gt;&lt;p&gt;يقدم البلسم بديلاً بصيغة مختلفة عن الغسول السائل، ويتيح اختيار طريقة التنظيف وفق ما يلائم روتينك. لا يذكر الاسم نوع البشرة أو تفاصيل التركيبة؛ لذا من الأفضل مراجعة بيانات المنتج كاملة قبل الاستخدام، واتباع الخطوات الموضحة من العلامة.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;بلسم مخصص لتنظيف الوجه.&lt;/li&gt;&lt;li&gt;يحمل اسم تيك ذا داي أوف.&lt;/li&gt;&lt;li&gt;من علامة كلينيك.&lt;/li&gt;&lt;li&gt;حجم العبوة 125 مل.&lt;/li&gt;&lt;li&gt;مذكور أنه مناسب للجنسين.&lt;/li&gt;&lt;li&gt;صيغة بلسم ضمن خيارات تنظيف الوجه.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن بلسم لتنظيف الوجه.&lt;/li&gt;&lt;li&gt;للجنسين وفق بيانات المنتج المقدمة.&lt;/li&gt;&lt;li&gt;لمن يفضل إضافة منتج بصيغة البلسم إلى روتين التنظيف.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;اتبعي التعليمات المطبوعة على العبوة لمعرفة طريقة توزيع البلسم وإزالته. استخدميه على الوجه بالطريقة المحددة، ثم أكملي روتين التنظيف وفق احتياجك. تجنبي وضعه على محيط العينين ما لم توضح العبوة خلاف ذلك، واغسلي اليدين بعد الاستخدام.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، تجنبي ملامسة العينين، وأبقيه بعيداً عن متناول الأطفال. أوقفي الاستخدام عند حدوث انزعاج، وراجعي التعليمات قبل الاستعمال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;كلينيك علامة تجارية تقدم مستحضرات للمكياج والعناية بالبشرة. يشمل اسمها منتجات مخصصة لخطوات العناية بالوجه، وهذا البلسم أحد منتجات التنظيف التي تحمل اسمها.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;س: ما نوع منتج تيك ذا داي أوف؟&lt;/p&gt;&lt;p&gt;ج: هو بلسم تنظيف للوجه.&lt;/p&gt;&lt;p&gt;س: ما حجم العبوة؟&lt;/p&gt;&lt;p&gt;ج: العبوة بحجم 125 مل.&lt;/p&gt;&lt;p&gt;س: لمن يوجه المنتج؟&lt;/p&gt;&lt;p&gt;ج: يرد في بيانات المنتج أنه للجنسين.&lt;/p&gt;&lt;p&gt;س: كيف تتم إزالة البلسم؟&lt;/p&gt;&lt;p&gt;ج: اتبعي الطريقة الموضحة على العبوة للتطبيق والإزالة.&lt;/p&gt;</t>
+          <t>زيت فيتامين هـ من دي لا كروز، 65 مل — De La Cruz Vitamin E Oil, 65 ml؛ زيت للعناية بالبشرة من علامة دي لا كروز، بالحجم المذكور في الاسم. تأتي صيغته الزيتية لتكون خياراً واضحاً لمن يفضّلون إدراج الزيوت ضمن خطوات عنايتهم اليومية، مع الحفاظ على بساطة الاختيار بحسب طبيعة الروتين الشخصي.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | زيت فيتامين هـ من دي لا كروز&lt;/li&gt;&lt;li&gt;النوع | زيت فيتامين هـ&lt;/li&gt;&lt;li&gt;الحجم | 65 مل&lt;/li&gt;&lt;li&gt;العلامة التجارية | دي لا كروز&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;يجمع هذا المنتج بين شكل الزيت واسم فيتامين هـ في عبوة محددة الحجم، ليمنحك خياراً عملياً عند ترتيب منتجات العناية بالبشرة. ويمكن التعامل معه كخطوة مستقلة أو إدراجه ضمن الروتين المعتاد وفق تعليمات العبوة، مع اختيار موضع الاستخدام والكمية بما يلائم تفضيلاتك.&lt;/p&gt;&lt;p&gt;لا يذكر الاسم درجة لونية أو رائحة أو مواصفات إضافية؛ لذلك يظل التركيز هنا على هويته كزيت فيتامين هـ من دي لا كروز وحجمه البالغ 65 مل. اختاريه بناءً على رغبتك في استخدام مستحضر ذي قوام زيتي، وتحققي من إرشادات العبوة قبل إدخاله في روتينك.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مستحضر زيتي يحمل اسم فيتامين هـ.&lt;/li&gt;&lt;li&gt;حجم العبوة 65 مل كما ورد في اسم المنتج.&lt;/li&gt;&lt;li&gt;من علامة دي لا كروز.&lt;/li&gt;&lt;li&gt;يمكن إدراجه ضمن خطوات العناية بالبشرة بحسب تفضيلاتك.&lt;/li&gt;&lt;li&gt;اسم المنتج واضح ويسهل تمييزه عند تنظيم المستحضرات.&lt;/li&gt;&lt;li&gt;لا يتضمن الاسم درجة لونية محددة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحثون عن زيت فيتامين هـ للعناية بالبشرة.&lt;/li&gt;&lt;li&gt;لمن يفضّلون المستحضرات ذات القوام الزيتي.&lt;/li&gt;&lt;li&gt;لمن يرغبون في عبوة بحجم 65 مل.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;راجعي تعليمات العبوة أولاً، ثم ضعي كمية مناسبة على بشرة نظيفة في الموضع المرغوب. ابدئي بكمية قليلة، ووزّعيها بلطف، ولا تستخدميه بطريقة تخالف الإرشادات المدونة على المنتج.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. يُحفظ بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;دي لا كروز هي العلامة التجارية المذكورة على هذا المنتج. يظهر اسمها هنا على زيت فيتامين هـ بحجم 65 مل، وتُعرَف هوية المنتج من الاسم والعلامة المدونين عليه.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع هذا المنتج؟&lt;/p&gt;&lt;p&gt;هو زيت فيتامين هـ من دي لا كروز.&lt;/p&gt;&lt;p&gt;ما حجم العبوة؟&lt;/p&gt;&lt;p&gt;الحجم المذكور في الاسم هو 65 مل.&lt;/p&gt;&lt;p&gt;هل يذكر الاسم درجة لونية؟&lt;/p&gt;&lt;p&gt;لا، لا تظهر درجة لونية في اسم المنتج.&lt;/p&gt;&lt;p&gt;كيف أستخدمه؟&lt;/p&gt;&lt;p&gt;اتبعي تعليمات العبوة وضعي كمية مناسبة على البشرة مع تجنب ملامسة العينين.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -7320,7 +7330,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>MNT-R86</t>
+          <t>MNT-R91</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -7335,7 +7345,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>Clinique</t>
+          <t>De La Cruz</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -7357,7 +7367,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>كلينيك جل مرطب درامتكلي ديفرنت - 125 مل</t>
+          <t>كريم فيتامين هـ من دي لا كروز - 12جم</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -7367,12 +7377,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/61rjIWgNJoL.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0790/6462/9503/files/A2014VitminECreamTrialSize2025_1-PDP.png?v=1771025932</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>كلينيك جل مرطب درامتكلي ديفرنت - 125 مل</t>
+          <t>كريم فيتامين هـ من دي لا كروز - 12جم</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -7382,12 +7392,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>&lt;p&gt;كلينيك جل مرطب درامتكلي ديفرنت Clinique Dramatically Different Moisturizing Gel من كلينيك، نوعه جل مرطب للوجه، بحجم 125 مل.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | جل مرطب درامتكلي ديفرنت&lt;/li&gt;&lt;li&gt;النوع | جل مرطب للوجه&lt;/li&gt;&lt;li&gt;الحجم | 125 مل&lt;/li&gt;&lt;li&gt;العلامة التجارية | كلينيك&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;جل مرطب من كلينيك يحمل اسم درامتكلي ديفرنت، ويأتي بحجم 125 مل. يندرج ضمن مستحضرات ترطيب البشرة، وتمنحه صيغة الجل قواماً مختلفاً عن الكريمات التقليدية. يمكن إدخاله في روتين العناية بالوجه وفق الطريقة الموضحة على العبوة.&lt;/p&gt;&lt;p&gt;لا يحدد الاسم نوع البشرة أو أوقات الاستخدام، لذا اطلعي على بيانات المنتج قبل تطبيقه، خاصة إذا كنت تستخدمين منتجات أخرى ضمن الروتين نفسه. يوزع الجل على البشرة بالطريقة الملائمة حسب إرشادات العبوة، مع تجنب محيط العينين.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;جل مرطب للوجه من كلينيك.&lt;/li&gt;&lt;li&gt;يحمل اسم درامتكلي ديفرنت.&lt;/li&gt;&lt;li&gt;يأتي بحجم 125 مل.&lt;/li&gt;&lt;li&gt;صيغة جل ضمن منتجات ترطيب البشرة.&lt;/li&gt;&lt;li&gt;يمكن إدخاله ضمن روتين العناية بالوجه.&lt;/li&gt;&lt;li&gt;تعرض العبوة تعليمات الاستخدام والتفاصيل المتاحة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن مرطب للوجه بصيغة جل.&lt;/li&gt;&lt;li&gt;لمستخدمي منتجات كلينيك للعناية بالبشرة.&lt;/li&gt;&lt;li&gt;لمن يرغب في إضافة خطوة ترطيب إلى روتينه.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;ضعي الجل وفق تعليمات العبوة، ووزعيه برفق على بشرة الوجه مع تجنب العينين. ابدئي بالكمية التي توصي بها الشركة، واتركي المستحضر يمتص بحسب توجيهات المنتج قبل متابعة روتينك. راجعي العبوة لمعرفة التوقيت والتكرار المناسبين.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، تجنبي ملامسة العينين، واحفظي العبوة بعيداً عن متناول الأطفال. توقفي عن الاستخدام عند حدوث انزعاج، ولا تضعيه على بشرة متضررة.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;كلينيك علامة تجارية تشمل منتجات للعناية بالبشرة ومستحضرات المكياج. ويأتي جل درامتكلي ديفرنت ضمن مستحضرات الترطيب التي تحمل اسمها، وتوضح العبوة المعلومات الخاصة بطريقة الاستخدام.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;س: ما نوع المنتج؟&lt;/p&gt;&lt;p&gt;ج: هو جل مرطب للوجه.&lt;/p&gt;&lt;p&gt;س: ما حجمه؟&lt;/p&gt;&lt;p&gt;ج: الحجم المذكور على اسم المنتج هو 125 مل.&lt;/p&gt;&lt;p&gt;س: هل يحدد الاسم نوع البشرة؟&lt;/p&gt;&lt;p&gt;ج: لا يذكر الاسم المتاح نوعاً معيناً للبشرة.&lt;/p&gt;&lt;p&gt;س: متى يوضع الجل؟&lt;/p&gt;&lt;p&gt;ج: اتبعي توقيت الاستخدام وطريقته كما وردا على العبوة.&lt;/p&gt;</t>
+          <t>كريم فيتامين هـ من دي لا كروز، 12 جم — De La Cruz Vitamin E Cream, 12 g؛ كريم للعناية بالبشرة من علامة دي لا كروز، بحجم 12 جم. يأتي في صورة كريم سهلة التمييز عن المستحضرات الزيتية، ويقدّم خياراً محدد الاسم والحجم لمن يرغب في تنظيم مستحضراته واختيارها وفق شكل المنتج الذي يفضّله.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | كريم فيتامين هـ من دي لا كروز&lt;/li&gt;&lt;li&gt;النوع | كريم فيتامين هـ&lt;/li&gt;&lt;li&gt;الحجم | 12 جم&lt;/li&gt;&lt;li&gt;العلامة التجارية | دي لا كروز&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;يحمل الكريم اسم فيتامين هـ، وتأتي العبوة بحجم 12 جم، ما يجعل تفاصيله الأساسية واضحة عند المقارنة أو ترتيب منتجات العناية. ينسجم شكله الكريمي مع الروتين الذي يفضّل فيه المستخدم مستحضراً بهذا القوام، ويمكن استعماله وفق الإرشادات المكتوبة على العبوة.&lt;/p&gt;&lt;p&gt;لا يتضمن الاسم درجة أو رائحة أو معلومات أخرى عن خصائص المنتج؛ لذا يقتصر التعريف به على كونه كريم فيتامين هـ من دي لا كروز وحجمه المحدد. اختاري موضع الاستعمال وطريقته بالرجوع إلى تعليمات العبوة، وادمجيه في روتينك بما يتوافق مع تفضيلاتك.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;قوام كريم وفق نوع المنتج الوارد في الاسم.&lt;/li&gt;&lt;li&gt;يحمل اسم فيتامين هـ.&lt;/li&gt;&lt;li&gt;حجم العبوة 12 جم.&lt;/li&gt;&lt;li&gt;من علامة دي لا كروز.&lt;/li&gt;&lt;li&gt;تفاصيل النوع والحجم ظاهرة بوضوح في تعريف المنتج.&lt;/li&gt;&lt;li&gt;يمكن إدراجه ضمن روتين العناية وفق تعليمات العبوة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يفضلون الكريمات ضمن مستحضرات العناية بالبشرة.&lt;/li&gt;&lt;li&gt;لمن يبحثون عن كريم يحمل اسم فيتامين هـ.&lt;/li&gt;&lt;li&gt;لمن يريدون عبوة بحجم 12 جم.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;استخدميه وفق التعليمات المدونة على العبوة. ضعي كمية مناسبة على المنطقة المرغوبة من البشرة، ووزعيها بلطف، مع الحرص على عدم تجاوز طريقة الاستخدام المحددة من الشركة.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. أبقي العبوة بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;دي لا كروز هي العلامة التجارية المدونة على هذا الكريم. ويظهر المنتج ضمن اسمها بصيغة كريم فيتامين هـ وحجم 12 جم، وهما التفصيلان الأساسيان الواردان في تعريفه.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما شكل المنتج؟&lt;/p&gt;&lt;p&gt;هو كريم للعناية بالبشرة يحمل اسم فيتامين هـ.&lt;/p&gt;&lt;p&gt;كم يبلغ حجمه؟&lt;/p&gt;&lt;p&gt;حجم العبوة المذكور هو 12 جم.&lt;/p&gt;&lt;p&gt;ما العلامة التجارية؟&lt;/p&gt;&lt;p&gt;العلامة التجارية هي دي لا كروز.&lt;/p&gt;&lt;p&gt;هل وردت درجة لونية في الاسم؟&lt;/p&gt;&lt;p&gt;لا، لا يذكر الاسم درجة لونية لهذا المنتج.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -7397,7 +7407,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>MNT-R87</t>
+          <t>MNT-R92</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -7412,7 +7422,7 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>Clinique</t>
+          <t>De La Cruz</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
@@ -7434,22 +7444,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>كلينيك صابون سائل للوجه للبشرة الدهنية 200مل</t>
+          <t>كريم أساس 1 دبليو1 دبل وير من استي لودر</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>العناية والجمال &gt; العناية بالبشرة &gt; تنظيف الوجه</t>
+          <t>العناية والجمال &gt; الوجه &gt; أساس وبرايمر</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41VlM2-R3mS.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41xbYsVsvFL.jpg</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>كلينيك صابون سائل للوجه للبشرة الدهنية 200مل</t>
+          <t>كريم أساس 1 دبليو1 دبل وير من استي لودر</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -7459,12 +7469,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>156</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>&lt;p&gt;كلينيك صابون سائل للوجه للبشرة الدهنية Clinique Liquid Facial Soap Oily Skin من كلينيك، نوعه غسول وجه سائل، بحجم 200 مل.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | صابون سائل للوجه للبشرة الدهنية&lt;/li&gt;&lt;li&gt;النوع | غسول وجه سائل&lt;/li&gt;&lt;li&gt;الحجم | 200 مل&lt;/li&gt;&lt;li&gt;العلامة التجارية | كلينيك&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;منظف سائل للوجه من كلينيك، يذكر اسمه أنه مخصص للبشرة الدهنية، ويأتي بحجم 200 مل. يندرج ضمن منتجات تنظيف الوجه، ويمكن إدراجه في خطوة غسل البشرة ضمن الروتين اليومي وفق تعليمات العبوة.&lt;/p&gt;&lt;p&gt;تساعد صيغة الصابون السائل على توزيع المنتج أثناء التنظيف، مع ضرورة الالتزام بطريقة الاستخدام الموصى بها وتجنب المبالغة في الغسل. إذا كانت لديك استفسارات حول ملاءمته لبشرتك أو توافقه مع مستحضرات أخرى، راجعي بيانات المنتج أو استشيري مختصاً.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;صابون سائل مخصص لتنظيف الوجه.&lt;/li&gt;&lt;li&gt;مذكور للبشرة الدهنية في الاسم.&lt;/li&gt;&lt;li&gt;من علامة كلينيك.&lt;/li&gt;&lt;li&gt;عبوة بحجم 200 مل.&lt;/li&gt;&lt;li&gt;صيغة سائلة مناسبة لخطوة غسل الوجه.&lt;/li&gt;&lt;li&gt;يستخدم وفق التعليمات الموضحة على العبوة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحث عن منظف سائل للوجه.&lt;/li&gt;&lt;li&gt;لمن يختار منتجاً يذكر البشرة الدهنية في اسمه.&lt;/li&gt;&lt;li&gt;لمستخدمي مستحضرات العناية بالبشرة من كلينيك.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;اتبعي تعليمات العبوة، وبللي الوجه إذا كانت طريقة الاستخدام تنص على ذلك، ثم وزعي كمية مناسبة من المنظف بلطف واشطفيه جيداً عند الانتهاء. تجنبي ملامسة العينين، ولا تستخدميه على بشرة متضررة. أغلقي العبوة بعد الاستعمال.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، تجنبي ملامسة العينين، وأبقي المنتج بعيداً عن متناول الأطفال. أوقفي الاستخدام إذا ظهر انزعاج، والتزمي بتوجيهات العبوة.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;كلينيك علامة تجارية تقدم أصنافاً للمكياج والعناية بالبشرة. يندرج هذا الصابون السائل ضمن منتجات تنظيف الوجه التي تحمل اسمها، وتوضح العبوة تفاصيل الاستعمال الموصى بها.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;س: ما نوع المنتج؟&lt;/p&gt;&lt;p&gt;ج: صابون سائل لتنظيف الوجه.&lt;/p&gt;&lt;p&gt;س: لأي نوع بشرة يذكر المنتج؟&lt;/p&gt;&lt;p&gt;ج: يذكر الاسم أنه للبشرة الدهنية.&lt;/p&gt;&lt;p&gt;س: ما حجم العبوة؟&lt;/p&gt;&lt;p&gt;ج: تأتي العبوة بحجم 200 مل.&lt;/p&gt;&lt;p&gt;س: هل يستخدم حول العينين؟&lt;/p&gt;&lt;p&gt;ج: ينبغي تجنب ملامسة العينين واتباع تعليمات العبوة.&lt;/p&gt;</t>
+          <t>كريم أساس دبل وير بدرجة 1W1 من استي لودر — Estée Lauder Double Wear Foundation 1W1؛ كريم أساس للوجه من العلامة التجارية استي لودر، والدرجة المذكورة في الاسم هي 1W1. يقدم تعريف المنتج اسمه ودرجته بوضوح لتسهيل تمييزه عند اختيار كريم الأساس ومقارنته بالدرجات الأخرى من المجموعة.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | كريم أساس دبل وير من استي لودر&lt;/li&gt;&lt;li&gt;النوع | كريم أساس&lt;/li&gt;&lt;li&gt;الدرجة | 1W1&lt;/li&gt;&lt;li&gt;العلامة التجارية | استي لودر&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;يحمل هذا المنتج اسم دبل وير ودرجة 1W1، وهما التفصيلان الظاهران في تسمية كريم الأساس. يتيح لك تحديد الدرجة وفق ما تبحثين عنه عند تنسيق مكياج الوجه، مع الرجوع إلى ما يناسبك من خيارات الدرجات المتاحة لديك؛ فالاسم وحده لا يحدد وصفاً لونياً إضافياً للدرجة.&lt;/p&gt;&lt;p&gt;يمكن توزيع كريم الأساس على الوجه بالطريقة التي تفضلينها ضمن خطوات المكياج، مع مراعاة تجهيز البشرة بما يلائم روتينك. لا يذكر الاسم حجماً أو تفاصيل عن مستوى التغطية أو اللمسة النهائية، لذلك يقتصر الوصف على العلامة التجارية ونوع المنتج واسمه ودرجة 1W1.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;كريم أساس للوجه من استي لودر.&lt;/li&gt;&lt;li&gt;يحمل اسم دبل وير كما ورد في تعريف المنتج.&lt;/li&gt;&lt;li&gt;الدرجة المحددة في الاسم هي 1W1.&lt;/li&gt;&lt;li&gt;يُعرّف بوضوح كمنتج أساس ضمن المكياج.&lt;/li&gt;&lt;li&gt;يمكن توزيعه ضمن خطوات إعداد مكياج الوجه.&lt;/li&gt;&lt;li&gt;لا يذكر الاسم حجماً محدداً للعبوة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحثن عن كريم أساس من استي لودر.&lt;/li&gt;&lt;li&gt;لمن يختَرن درجة 1W1 بحسب تفضيلاتهن.&lt;/li&gt;&lt;li&gt;لمن يرغبن في إدراج كريم أساس ضمن خطوات المكياج.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;ضعي كمية مناسبة على بشرة الوجه بعد تجهيزها بالطريقة المعتادة، ثم وزعي المنتج بأداة المكياج التي تفضلينها حتى يصبح المظهر متناسقاً. ابدئي بكمية قليلة، وأضيفي المزيد عند الحاجة، مع الالتزام بإرشادات العبوة.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. يُحفظ بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;استي لودر هي العلامة التجارية المذكورة على هذا المنتج. يظهر كريم الأساس باسم دبل وير وبدرجة 1W1، وتتيح هذه البيانات التعرف إلى المنتج عند اختيار مستحضرات الوجه.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع المنتج؟&lt;/p&gt;&lt;p&gt;هو كريم أساس للوجه من استي لودر.&lt;/p&gt;&lt;p&gt;ما الدرجة المذكورة؟&lt;/p&gt;&lt;p&gt;الدرجة الواردة في الاسم هي 1W1.&lt;/p&gt;&lt;p&gt;هل يحدد الاسم حجم العبوة؟&lt;/p&gt;&lt;p&gt;لا، لا يظهر حجم في اسم المنتج.&lt;/p&gt;&lt;p&gt;كيف يوزع على الوجه؟&lt;/p&gt;&lt;p&gt;يوزع بكمية مناسبة وبالأداة المفضلة بعد تجهيز البشرة.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -7474,7 +7484,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>MNT-R88</t>
+          <t>MNT-R93</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -7489,7 +7499,7 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>Clinique</t>
+          <t>Estée Lauder</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
@@ -7511,22 +7521,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>زيت فيتامين E من دي لا كروز، 65 مل</t>
+          <t>كريم أساس دبل وير 1w2 من استي لودر</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>العناية والجمال &gt; العناية بالبشرة &gt; زيوت وزبدات</t>
+          <t>العناية والجمال &gt; الوجه &gt; أساس وبرايمر</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://ecombe.nahdionline.com/media/catalog/product/1/0/102925696_65f774f377ff032f9_32226.png?width=1050&amp;height=1050&amp;canvas=1050,1050&amp;optimize=high&amp;bg-color=255,255,255&amp;fit=bounds</t>
+          <t>https://m.media-amazon.com/images/I/51WxgrBQnPL.jpg</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>زيت فيتامين E من دي لا كروز، 65 مل</t>
+          <t>كريم أساس دبل وير 1w2 من استي لودر</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -7536,12 +7546,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>155</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>زيت فيتامين هـ من دي لا كروز، 65 مل — De La Cruz Vitamin E Oil, 65 ml؛ زيت للعناية بالبشرة من علامة دي لا كروز، بالحجم المذكور في الاسم. تأتي صيغته الزيتية لتكون خياراً واضحاً لمن يفضّلون إدراج الزيوت ضمن خطوات عنايتهم اليومية، مع الحفاظ على بساطة الاختيار بحسب طبيعة الروتين الشخصي.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | زيت فيتامين هـ من دي لا كروز&lt;/li&gt;&lt;li&gt;النوع | زيت فيتامين هـ&lt;/li&gt;&lt;li&gt;الحجم | 65 مل&lt;/li&gt;&lt;li&gt;العلامة التجارية | دي لا كروز&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;يجمع هذا المنتج بين شكل الزيت واسم فيتامين هـ في عبوة محددة الحجم، ليمنحك خياراً عملياً عند ترتيب منتجات العناية بالبشرة. ويمكن التعامل معه كخطوة مستقلة أو إدراجه ضمن الروتين المعتاد وفق تعليمات العبوة، مع اختيار موضع الاستخدام والكمية بما يلائم تفضيلاتك.&lt;/p&gt;&lt;p&gt;لا يذكر الاسم درجة لونية أو رائحة أو مواصفات إضافية؛ لذلك يظل التركيز هنا على هويته كزيت فيتامين هـ من دي لا كروز وحجمه البالغ 65 مل. اختاريه بناءً على رغبتك في استخدام مستحضر ذي قوام زيتي، وتحققي من إرشادات العبوة قبل إدخاله في روتينك.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مستحضر زيتي يحمل اسم فيتامين هـ.&lt;/li&gt;&lt;li&gt;حجم العبوة 65 مل كما ورد في اسم المنتج.&lt;/li&gt;&lt;li&gt;من علامة دي لا كروز.&lt;/li&gt;&lt;li&gt;يمكن إدراجه ضمن خطوات العناية بالبشرة بحسب تفضيلاتك.&lt;/li&gt;&lt;li&gt;اسم المنتج واضح ويسهل تمييزه عند تنظيم المستحضرات.&lt;/li&gt;&lt;li&gt;لا يتضمن الاسم درجة لونية محددة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحثون عن زيت فيتامين هـ للعناية بالبشرة.&lt;/li&gt;&lt;li&gt;لمن يفضّلون المستحضرات ذات القوام الزيتي.&lt;/li&gt;&lt;li&gt;لمن يرغبون في عبوة بحجم 65 مل.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;راجعي تعليمات العبوة أولاً، ثم ضعي كمية مناسبة على بشرة نظيفة في الموضع المرغوب. ابدئي بكمية قليلة، ووزّعيها بلطف، ولا تستخدميه بطريقة تخالف الإرشادات المدونة على المنتج.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. يُحفظ بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;دي لا كروز هي العلامة التجارية المذكورة على هذا المنتج. يظهر اسمها هنا على زيت فيتامين هـ بحجم 65 مل، وتُعرَف هوية المنتج من الاسم والعلامة المدونين عليه.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع هذا المنتج؟&lt;/p&gt;&lt;p&gt;هو زيت فيتامين هـ من دي لا كروز.&lt;/p&gt;&lt;p&gt;ما حجم العبوة؟&lt;/p&gt;&lt;p&gt;الحجم المذكور في الاسم هو 65 مل.&lt;/p&gt;&lt;p&gt;هل يذكر الاسم درجة لونية؟&lt;/p&gt;&lt;p&gt;لا، لا تظهر درجة لونية في اسم المنتج.&lt;/p&gt;&lt;p&gt;كيف أستخدمه؟&lt;/p&gt;&lt;p&gt;اتبعي تعليمات العبوة وضعي كمية مناسبة على البشرة مع تجنب ملامسة العينين.&lt;/p&gt;</t>
+          <t>كريم أساس دبل وير بدرجة 1W2 من استي لودر — Estée Lauder Double Wear Foundation 1W2؛ مستحضر أساس للوجه من علامة استي لودر، بدرجة 1W2 كما وردت في الاسم. يجمع تعريفه بين اسم دبل وير ورقم الدرجة، لتتمكني من تمييز هذا الخيار عن الدرجات الأخرى عند ترتيب مستحضرات المكياج أو اختيارها.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | كريم أساس دبل وير من استي لودر&lt;/li&gt;&lt;li&gt;النوع | كريم أساس&lt;/li&gt;&lt;li&gt;الدرجة | 1W2&lt;/li&gt;&lt;li&gt;العلامة التجارية | استي لودر&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;هذا كريم أساس يحمل اسم دبل وير، وتحدد التسمية درجته برقم 1W2. يساعد وضوح الاسم والدرجة على التعرف إلى النسخة المطلوبة عند المقارنة بين خيارات المكياج، مع اختيار الدرجة وفق تفضيلك الشخصي وما تعتمدينه عادةً لمظهر الوجه.&lt;/p&gt;&lt;p&gt;يُستخدم ضمن خطوات المكياج ويمكن توزيعه على الوجه بأداة مناسبة. لا يتضمن الاسم حجم العبوة أو وصفاً إضافياً للدرجة أو للنتيجة على البشرة؛ لذا لا تُفترض خصائص أخرى غير المعلومات الواردة. راجعي بيانات العبوة عند الحاجة إلى تفاصيل إضافية عن المنتج وطريقة استخدامه.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;كريم أساس من استي لودر.&lt;/li&gt;&lt;li&gt;يحمل تسمية دبل وير.&lt;/li&gt;&lt;li&gt;الدرجة الظاهرة في الاسم هي 1W2.&lt;/li&gt;&lt;li&gt;ينتمي إلى مستحضرات مكياج الوجه.&lt;/li&gt;&lt;li&gt;يمكن توزيعه بأداة المكياج التي تفضلينها.&lt;/li&gt;&lt;li&gt;يُعرّف بالعلامة التجارية والدرجة بوضوح.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يفضلن كريم الأساس ضمن روتين المكياج.&lt;/li&gt;&lt;li&gt;لمن يبحثن عن درجة 1W2 من استي لودر.&lt;/li&gt;&lt;li&gt;لمن يرغبن في اختيار منتج محدد الدرجة بالاسم.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;بعد تجهيز البشرة، وزعي كمية مناسبة من كريم الأساس على الوجه باستخدام الأصابع أو أداة المكياج المفضلة. ابدئي بطبقة خفيفة، ثم أكملي التوزيع بحسب رغبتك، مع اتباع الإرشادات المرفقة بالعبوة.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. أبقيه بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;استي لودر هي العلامة التجارية المدونة على المنتج. ويظهر هذا الخيار باسم دبل وير مع درجة 1W2، بما يحدد فئته ونسخته المذكورة في الاسم.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما درجة كريم الأساس؟&lt;/p&gt;&lt;p&gt;الدرجة المذكورة في اسم المنتج هي 1W2.&lt;/p&gt;&lt;p&gt;ما العلامة التجارية؟&lt;/p&gt;&lt;p&gt;العلامة التجارية هي استي لودر.&lt;/p&gt;&lt;p&gt;هل يتضمن الاسم حجم العبوة؟&lt;/p&gt;&lt;p&gt;لا، لا يورد الاسم حجماً محدداً.&lt;/p&gt;&lt;p&gt;كيف يمكن توزيعه؟&lt;/p&gt;&lt;p&gt;يوزع على الوجه بأداة المكياج المفضلة وفق طريقة الاستخدام المعتادة.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -7551,7 +7561,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>MNT-R91</t>
+          <t>MNT-R94</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -7566,7 +7576,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>De La Cruz</t>
+          <t>Estée Lauder</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -7588,22 +7598,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>كريم فيتامين هـ من دي لا كروز - 12جم</t>
+          <t>Estée Lauder كريم أساس مزدوج الثبات من ايستية لودر 2دابليو</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>العناية والجمال &gt; العناية بالبشرة &gt; مرطبات</t>
+          <t>العناية والجمال &gt; الوجه &gt; أساس وبرايمر</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0790/6462/9503/files/A2014VitminECreamTrialSize2025_1-PDP.png?v=1771025932</t>
+          <t>https://m.media-amazon.com/images/I/612XaNC86pL.jpg</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>كريم فيتامين هـ من دي لا كروز - 12جم</t>
+          <t>Estée Lauder كريم أساس مزدوج الثبات من ايستية لودر 2دابليو</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -7613,12 +7623,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>156</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>كريم فيتامين هـ من دي لا كروز، 12 جم — De La Cruz Vitamin E Cream, 12 g؛ كريم للعناية بالبشرة من علامة دي لا كروز، بحجم 12 جم. يأتي في صورة كريم سهلة التمييز عن المستحضرات الزيتية، ويقدّم خياراً محدد الاسم والحجم لمن يرغب في تنظيم مستحضراته واختيارها وفق شكل المنتج الذي يفضّله.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | كريم فيتامين هـ من دي لا كروز&lt;/li&gt;&lt;li&gt;النوع | كريم فيتامين هـ&lt;/li&gt;&lt;li&gt;الحجم | 12 جم&lt;/li&gt;&lt;li&gt;العلامة التجارية | دي لا كروز&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;يحمل الكريم اسم فيتامين هـ، وتأتي العبوة بحجم 12 جم، ما يجعل تفاصيله الأساسية واضحة عند المقارنة أو ترتيب منتجات العناية. ينسجم شكله الكريمي مع الروتين الذي يفضّل فيه المستخدم مستحضراً بهذا القوام، ويمكن استعماله وفق الإرشادات المكتوبة على العبوة.&lt;/p&gt;&lt;p&gt;لا يتضمن الاسم درجة أو رائحة أو معلومات أخرى عن خصائص المنتج؛ لذا يقتصر التعريف به على كونه كريم فيتامين هـ من دي لا كروز وحجمه المحدد. اختاري موضع الاستعمال وطريقته بالرجوع إلى تعليمات العبوة، وادمجيه في روتينك بما يتوافق مع تفضيلاتك.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;قوام كريم وفق نوع المنتج الوارد في الاسم.&lt;/li&gt;&lt;li&gt;يحمل اسم فيتامين هـ.&lt;/li&gt;&lt;li&gt;حجم العبوة 12 جم.&lt;/li&gt;&lt;li&gt;من علامة دي لا كروز.&lt;/li&gt;&lt;li&gt;تفاصيل النوع والحجم ظاهرة بوضوح في تعريف المنتج.&lt;/li&gt;&lt;li&gt;يمكن إدراجه ضمن روتين العناية وفق تعليمات العبوة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يفضلون الكريمات ضمن مستحضرات العناية بالبشرة.&lt;/li&gt;&lt;li&gt;لمن يبحثون عن كريم يحمل اسم فيتامين هـ.&lt;/li&gt;&lt;li&gt;لمن يريدون عبوة بحجم 12 جم.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;استخدميه وفق التعليمات المدونة على العبوة. ضعي كمية مناسبة على المنطقة المرغوبة من البشرة، ووزعيها بلطف، مع الحرص على عدم تجاوز طريقة الاستخدام المحددة من الشركة.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. أبقي العبوة بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;دي لا كروز هي العلامة التجارية المدونة على هذا الكريم. ويظهر المنتج ضمن اسمها بصيغة كريم فيتامين هـ وحجم 12 جم، وهما التفصيلان الأساسيان الواردان في تعريفه.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما شكل المنتج؟&lt;/p&gt;&lt;p&gt;هو كريم للعناية بالبشرة يحمل اسم فيتامين هـ.&lt;/p&gt;&lt;p&gt;كم يبلغ حجمه؟&lt;/p&gt;&lt;p&gt;حجم العبوة المذكور هو 12 جم.&lt;/p&gt;&lt;p&gt;ما العلامة التجارية؟&lt;/p&gt;&lt;p&gt;العلامة التجارية هي دي لا كروز.&lt;/p&gt;&lt;p&gt;هل وردت درجة لونية في الاسم؟&lt;/p&gt;&lt;p&gt;لا، لا يذكر الاسم درجة لونية لهذا المنتج.&lt;/p&gt;</t>
+          <t>كريم أساس مزدوج الثبات من استي لودر بدرجة 2W — Estée Lauder Double Wear Foundation 2W؛ مستحضر أساس للوجه من العلامة التجارية استي لودر، والدرجة المذكورة في الاسم هي 2W. يوضح اسم المنتج فئته ونسخته لتسهيل التعرف إليه عند اختيار كريم الأساس أو تنظيم مستحضرات المكياج.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | كريم أساس مزدوج الثبات من استي لودر&lt;/li&gt;&lt;li&gt;النوع | كريم أساس&lt;/li&gt;&lt;li&gt;الدرجة | 2W&lt;/li&gt;&lt;li&gt;العلامة التجارية | استي لودر&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;يأتي هذا المنتج تحت اسم كريم أساس مزدوج الثبات، مع الإشارة إلى الدرجة 2W في التسمية. يتيح ذلك تحديد الخيار المقصود بالاسم والدرجة عند المقارنة مع مستحضرات أخرى، من دون الحاجة إلى افتراض وصف لوني أو خصائص غير واردة في بيانات المنتج.&lt;/p&gt;&lt;p&gt;يمكن إدراجه ضمن مكياج الوجه وتوزيعه بالطريقة التي تفضلينها بعد تهيئة البشرة. لا يذكر الاسم حجماً للعبوة، كما لا يورد تفاصيل عن مستوى التغطية أو اللمسة النهائية؛ لذا يظل التعريف مقتصراً على كونه كريم أساس من استي لودر بدرجة 2W.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مستحضر كريم أساس للوجه.&lt;/li&gt;&lt;li&gt;من علامة استي لودر.&lt;/li&gt;&lt;li&gt;يحمل وصف مزدوج الثبات في الاسم.&lt;/li&gt;&lt;li&gt;الدرجة المذكورة هي 2W.&lt;/li&gt;&lt;li&gt;يمكن استخدامه ضمن خطوات المكياج المعتادة.&lt;/li&gt;&lt;li&gt;تظهر معلومات العلامة والدرجة في تسمية المنتج.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحثن عن كريم أساس من استي لودر.&lt;/li&gt;&lt;li&gt;لمن يختَرن الدرجة 2W وفق تفضيلاتهن.&lt;/li&gt;&lt;li&gt;لمن يرغبن في مستحضر أساس لمكياج الوجه.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;ضعي كمية مناسبة على الوجه بعد تجهيز البشرة، ثم وزعيها بالتساوي باستخدام أصابعك أو أداة مكياج مناسبة. يمكن إضافة كمية أخرى عند الحاجة، مع مراعاة تعليمات الاستخدام المكتوبة على العبوة.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. احفظيه بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;استي لودر هي العلامة التجارية المحددة لهذا المنتج. ويُعرَف هذا الخيار من كريم الأساس باسمه ودرجة 2W المذكورة في التسمية.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما درجة كريم الأساس؟&lt;/p&gt;&lt;p&gt;الدرجة الواردة في اسم المنتج هي 2W.&lt;/p&gt;&lt;p&gt;ما نوع المستحضر؟&lt;/p&gt;&lt;p&gt;هو كريم أساس للوجه من استي لودر.&lt;/p&gt;&lt;p&gt;هل يذكر الاسم حجم العبوة؟&lt;/p&gt;&lt;p&gt;لا، لا يرد حجم العبوة ضمن الاسم.&lt;/p&gt;&lt;p&gt;هل يوضح الاسم وصف الدرجة؟&lt;/p&gt;&lt;p&gt;يورد الاسم رمز 2W فقط، ولا يقدم وصفاً لونياً إضافياً.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -7628,7 +7638,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>MNT-R92</t>
+          <t>MNT-R95</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -7643,7 +7653,7 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>De La Cruz</t>
+          <t>Estée Lauder</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
@@ -7665,22 +7675,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>كريم أساس 1 دبليو1 دبل وير من استي لودر</t>
+          <t>ارم اند هامر اسنشيالز مزيل عرق النظافه 71 جم</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>العناية والجمال &gt; الوجه &gt; أساس وبرايمر</t>
+          <t>العناية والجمال &gt; العناية الشخصية</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41xbYsVsvFL.jpg</t>
+          <t>https://m.media-amazon.com/images/I/61O6HPC++jL.jpg</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>كريم أساس 1 دبليو1 دبل وير من استي لودر</t>
+          <t>ارم اند هامر اسنشيالز مزيل عرق النظافه 71 جم</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -7690,12 +7700,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>كريم أساس دبل وير بدرجة 1W1 من استي لودر — Estée Lauder Double Wear Foundation 1W1؛ كريم أساس للوجه من العلامة التجارية استي لودر، والدرجة المذكورة في الاسم هي 1W1. يقدم تعريف المنتج اسمه ودرجته بوضوح لتسهيل تمييزه عند اختيار كريم الأساس ومقارنته بالدرجات الأخرى من المجموعة.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | كريم أساس دبل وير من استي لودر&lt;/li&gt;&lt;li&gt;النوع | كريم أساس&lt;/li&gt;&lt;li&gt;الدرجة | 1W1&lt;/li&gt;&lt;li&gt;العلامة التجارية | استي لودر&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;يحمل هذا المنتج اسم دبل وير ودرجة 1W1، وهما التفصيلان الظاهران في تسمية كريم الأساس. يتيح لك تحديد الدرجة وفق ما تبحثين عنه عند تنسيق مكياج الوجه، مع الرجوع إلى ما يناسبك من خيارات الدرجات المتاحة لديك؛ فالاسم وحده لا يحدد وصفاً لونياً إضافياً للدرجة.&lt;/p&gt;&lt;p&gt;يمكن توزيع كريم الأساس على الوجه بالطريقة التي تفضلينها ضمن خطوات المكياج، مع مراعاة تجهيز البشرة بما يلائم روتينك. لا يذكر الاسم حجماً أو تفاصيل عن مستوى التغطية أو اللمسة النهائية، لذلك يقتصر الوصف على العلامة التجارية ونوع المنتج واسمه ودرجة 1W1.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;كريم أساس للوجه من استي لودر.&lt;/li&gt;&lt;li&gt;يحمل اسم دبل وير كما ورد في تعريف المنتج.&lt;/li&gt;&lt;li&gt;الدرجة المحددة في الاسم هي 1W1.&lt;/li&gt;&lt;li&gt;يُعرّف بوضوح كمنتج أساس ضمن المكياج.&lt;/li&gt;&lt;li&gt;يمكن توزيعه ضمن خطوات إعداد مكياج الوجه.&lt;/li&gt;&lt;li&gt;لا يذكر الاسم حجماً محدداً للعبوة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحثن عن كريم أساس من استي لودر.&lt;/li&gt;&lt;li&gt;لمن يختَرن درجة 1W1 بحسب تفضيلاتهن.&lt;/li&gt;&lt;li&gt;لمن يرغبن في إدراج كريم أساس ضمن خطوات المكياج.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;ضعي كمية مناسبة على بشرة الوجه بعد تجهيزها بالطريقة المعتادة، ثم وزعي المنتج بأداة المكياج التي تفضلينها حتى يصبح المظهر متناسقاً. ابدئي بكمية قليلة، وأضيفي المزيد عند الحاجة، مع الالتزام بإرشادات العبوة.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. يُحفظ بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;استي لودر هي العلامة التجارية المذكورة على هذا المنتج. يظهر كريم الأساس باسم دبل وير وبدرجة 1W1، وتتيح هذه البيانات التعرف إلى المنتج عند اختيار مستحضرات الوجه.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع المنتج؟&lt;/p&gt;&lt;p&gt;هو كريم أساس للوجه من استي لودر.&lt;/p&gt;&lt;p&gt;ما الدرجة المذكورة؟&lt;/p&gt;&lt;p&gt;الدرجة الواردة في الاسم هي 1W1.&lt;/p&gt;&lt;p&gt;هل يحدد الاسم حجم العبوة؟&lt;/p&gt;&lt;p&gt;لا، لا يظهر حجم في اسم المنتج.&lt;/p&gt;&lt;p&gt;كيف يوزع على الوجه؟&lt;/p&gt;&lt;p&gt;يوزع بكمية مناسبة وبالأداة المفضلة بعد تجهيز البشرة.&lt;/p&gt;</t>
+          <t>مزيل عرق إسنشيالز برائحة النظافة من ارم اند هامر، 71 جم — Arm &amp; Hammer Essentials Deodorant Clean, 71 g؛ مزيل عرق من علامة ارم اند هامر، بحجم 71 جم، ويشير الاسم إلى رائحة النظافة. يقدّم المنتج تعريفاً مباشراً بنوعه ورائحته وحجم العبوة، ليسهل تمييزه ضمن مستحضرات العناية الشخصية.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | مزيل عرق إسنشيالز برائحة النظافة من ارم اند هامر&lt;/li&gt;&lt;li&gt;النوع | مزيل عرق&lt;/li&gt;&lt;li&gt;الحجم | 71 جم&lt;/li&gt;&lt;li&gt;العلامة التجارية | ارم اند هامر&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;ينتمي هذا المنتج إلى فئة مزيلات العرق، ويحمل اسم إسنشيالز مع وصف رائحة النظافة كما ورد في التسمية. تأتي العبوة بحجم 71 جم، وهو تفصيل عملي عند التعرف إلى المنتج أو تمييزه عن أحجام أخرى. لا يذكر الاسم نوعاً آخر من الحماية أو خصائص إضافية، لذلك يقتصر وصفه على هويته ورائحته وحجمه.&lt;/p&gt;&lt;p&gt;يمكن إدراجه ضمن روتين العناية الشخصية اليومي وفق الطريقة الموضحة على العبوة. اختيار المنتج يعتمد على تفضيلك لرائحة النظافة وعلى شكل المستحضر المناسب لك؛ ويُرجى الرجوع إلى بيانات العبوة لمعرفة تعليمات الاستخدام الخاصة به.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مزيل عرق من علامة ارم اند هامر.&lt;/li&gt;&lt;li&gt;يحمل اسم إسنشيالز.&lt;/li&gt;&lt;li&gt;يرد وصف رائحة النظافة ضمن اسم المنتج.&lt;/li&gt;&lt;li&gt;حجم العبوة 71 جم.&lt;/li&gt;&lt;li&gt;ينتمي إلى مستحضرات العناية الشخصية.&lt;/li&gt;&lt;li&gt;تظهر تفاصيل النوع والحجم في تسمية المنتج.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحثون عن مزيل عرق للاستخدام ضمن العناية الشخصية.&lt;/li&gt;&lt;li&gt;لمن يفضلون المنتج الموصوف برائحة النظافة.&lt;/li&gt;&lt;li&gt;لمن يرغبون في عبوة بحجم 71 جم.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;استخدميه وفق التعليمات المكتوبة على العبوة وعلى بشرة نظيفة وجافة إذا كانت الإرشادات تسمح بذلك. مرريه أو ضعيه بالطريقة المحددة للمنتج، وأغلقي العبوة بعد الاستعمال.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. يُحفظ بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;ارم اند هامر هي العلامة التجارية المذكورة على هذا المنتج. ويظهر مزيل العرق هنا ضمن مجموعة إسنشيالز بالوصف والحجم الواردين في الاسم.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع هذا المنتج؟&lt;/p&gt;&lt;p&gt;هو مزيل عرق من ارم اند هامر.&lt;/p&gt;&lt;p&gt;ما حجمه؟&lt;/p&gt;&lt;p&gt;حجم العبوة المذكور هو 71 جم.&lt;/p&gt;&lt;p&gt;ما وصف الرائحة الوارد؟&lt;/p&gt;&lt;p&gt;يذكر الاسم رائحة النظافة.&lt;/p&gt;&lt;p&gt;ما المجموعة المذكورة في الاسم؟&lt;/p&gt;&lt;p&gt;المجموعة الواردة هي إسنشيالز.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -7705,7 +7715,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>MNT-R93</t>
+          <t>MNT-R96</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -7720,7 +7730,7 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>Estée Lauder</t>
+          <t>Arm &amp; Hammer</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
@@ -7742,22 +7752,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>كريم أساس دبل وير 1w2 من استي لودر</t>
+          <t>Arm &amp; Hammer مزيل العرق برائحة الروزماري واللافندر 71 جم</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>العناية والجمال &gt; الوجه &gt; أساس وبرايمر</t>
+          <t>العناية والجمال &gt; العناية الشخصية</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/51WxgrBQnPL.jpg</t>
+          <t>https://m.media-amazon.com/images/I/71Ua50uoKcL.jpg</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>كريم أساس دبل وير 1w2 من استي لودر</t>
+          <t>Arm &amp; Hammer مزيل العرق برائحة الروزماري واللافندر 71 جم</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -7767,12 +7777,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>كريم أساس دبل وير بدرجة 1W2 من استي لودر — Estée Lauder Double Wear Foundation 1W2؛ مستحضر أساس للوجه من علامة استي لودر، بدرجة 1W2 كما وردت في الاسم. يجمع تعريفه بين اسم دبل وير ورقم الدرجة، لتتمكني من تمييز هذا الخيار عن الدرجات الأخرى عند ترتيب مستحضرات المكياج أو اختيارها.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | كريم أساس دبل وير من استي لودر&lt;/li&gt;&lt;li&gt;النوع | كريم أساس&lt;/li&gt;&lt;li&gt;الدرجة | 1W2&lt;/li&gt;&lt;li&gt;العلامة التجارية | استي لودر&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;هذا كريم أساس يحمل اسم دبل وير، وتحدد التسمية درجته برقم 1W2. يساعد وضوح الاسم والدرجة على التعرف إلى النسخة المطلوبة عند المقارنة بين خيارات المكياج، مع اختيار الدرجة وفق تفضيلك الشخصي وما تعتمدينه عادةً لمظهر الوجه.&lt;/p&gt;&lt;p&gt;يُستخدم ضمن خطوات المكياج ويمكن توزيعه على الوجه بأداة مناسبة. لا يتضمن الاسم حجم العبوة أو وصفاً إضافياً للدرجة أو للنتيجة على البشرة؛ لذا لا تُفترض خصائص أخرى غير المعلومات الواردة. راجعي بيانات العبوة عند الحاجة إلى تفاصيل إضافية عن المنتج وطريقة استخدامه.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;كريم أساس من استي لودر.&lt;/li&gt;&lt;li&gt;يحمل تسمية دبل وير.&lt;/li&gt;&lt;li&gt;الدرجة الظاهرة في الاسم هي 1W2.&lt;/li&gt;&lt;li&gt;ينتمي إلى مستحضرات مكياج الوجه.&lt;/li&gt;&lt;li&gt;يمكن توزيعه بأداة المكياج التي تفضلينها.&lt;/li&gt;&lt;li&gt;يُعرّف بالعلامة التجارية والدرجة بوضوح.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يفضلن كريم الأساس ضمن روتين المكياج.&lt;/li&gt;&lt;li&gt;لمن يبحثن عن درجة 1W2 من استي لودر.&lt;/li&gt;&lt;li&gt;لمن يرغبن في اختيار منتج محدد الدرجة بالاسم.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;بعد تجهيز البشرة، وزعي كمية مناسبة من كريم الأساس على الوجه باستخدام الأصابع أو أداة المكياج المفضلة. ابدئي بطبقة خفيفة، ثم أكملي التوزيع بحسب رغبتك، مع اتباع الإرشادات المرفقة بالعبوة.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. أبقيه بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;استي لودر هي العلامة التجارية المدونة على المنتج. ويظهر هذا الخيار باسم دبل وير مع درجة 1W2، بما يحدد فئته ونسخته المذكورة في الاسم.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما درجة كريم الأساس؟&lt;/p&gt;&lt;p&gt;الدرجة المذكورة في اسم المنتج هي 1W2.&lt;/p&gt;&lt;p&gt;ما العلامة التجارية؟&lt;/p&gt;&lt;p&gt;العلامة التجارية هي استي لودر.&lt;/p&gt;&lt;p&gt;هل يتضمن الاسم حجم العبوة؟&lt;/p&gt;&lt;p&gt;لا، لا يورد الاسم حجماً محدداً.&lt;/p&gt;&lt;p&gt;كيف يمكن توزيعه؟&lt;/p&gt;&lt;p&gt;يوزع على الوجه بأداة المكياج المفضلة وفق طريقة الاستخدام المعتادة.&lt;/p&gt;</t>
+          <t>مزيل العرق من ارم اند هامر برائحة الروزماري واللافندر، 71 جم — Arm &amp; Hammer Rosemary Lavender Deodorant, 71 g؛ مزيل عرق للعناية الشخصية من علامة ارم اند هامر، بحجم 71 جم، ويذكر الاسم رائحتي الروزماري واللافندر. يجمع تعريفه بين العلامة التجارية ونوع المستحضر والرائحة والحجم في صياغة واضحة.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | مزيل العرق برائحة الروزماري واللافندر من ارم اند هامر&lt;/li&gt;&lt;li&gt;النوع | مزيل عرق&lt;/li&gt;&lt;li&gt;الحجم | 71 جم&lt;/li&gt;&lt;li&gt;العلامة التجارية | ارم اند هامر&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;يُعرَف هذا المنتج بوصفه مزيل عرق يحمل رائحة الروزماري واللافندر، وفق ما ورد في اسمه، وتبلغ كمية العبوة 71 جم. تمنحك هذه التفاصيل طريقة مباشرة للتمييز بينه وبين المنتجات ذات الروائح أو الأحجام الأخرى، من غير إضافة وصف لمكونات أو خصائص لم ترد في التسمية.&lt;/p&gt;&lt;p&gt;يناسب إدراجه ضمن خطوات العناية الشخصية بالطريقة الموضحة على العبوة. اختاريه إذا كان وصف الرائحة المذكور قريباً من تفضيلك، وراجعي بيانات المنتج لمعرفة إرشادات الاستخدام الدقيقة. لا يذكر الاسم أنه مانع للتعرق، لذا يُعرّف هنا بمزيل عرق فقط.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مزيل عرق من ارم اند هامر.&lt;/li&gt;&lt;li&gt;يذكر الاسم رائحة الروزماري واللافندر.&lt;/li&gt;&lt;li&gt;حجم العبوة 71 جم.&lt;/li&gt;&lt;li&gt;مخصص للاستخدام ضمن العناية الشخصية.&lt;/li&gt;&lt;li&gt;يوفر تعريفاً واضحاً بالرائحة والحجم.&lt;/li&gt;&lt;li&gt;لا يرد في الاسم وصف بأنه مانع للتعرق.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحثون عن مزيل عرق ضمن العناية الشخصية.&lt;/li&gt;&lt;li&gt;لمن يختارون المنتجات بحسب وصف رائحتها.&lt;/li&gt;&lt;li&gt;لمن يفضلون عبوة بحجم 71 جم.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;اتبعي طريقة الاستخدام المدونة على العبوة. ضعي المنتج بالطريقة المحددة على المنطقة المطلوبة، مع مراعاة أن تكون البشرة مناسبة للاستخدام وفق إرشادات المنتج، ثم أعيدي إغلاق العبوة.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. أبقيه بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;ارم اند هامر هي العلامة التجارية الظاهرة على مزيل العرق. ويرتبط هذا الخيار بوصف الروزماري واللافندر وبحجم 71 جم كما وردا في اسم المنتج.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما الرائحة المذكورة في الاسم؟&lt;/p&gt;&lt;p&gt;الروزماري واللافندر.&lt;/p&gt;&lt;p&gt;كم يبلغ حجم العبوة؟&lt;/p&gt;&lt;p&gt;حجمها المذكور هو 71 جم.&lt;/p&gt;&lt;p&gt;هل المنتج مانع للتعرق؟&lt;/p&gt;&lt;p&gt;لا يذكر الاسم ذلك؛ فهو مصنف كمزيل عرق.&lt;/p&gt;&lt;p&gt;ما العلامة التجارية؟&lt;/p&gt;&lt;p&gt;العلامة التجارية هي ارم اند هامر.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -7782,7 +7792,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>MNT-R94</t>
+          <t>MNT-R97</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -7797,7 +7807,7 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>Estée Lauder</t>
+          <t>Arm &amp; Hammer</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -7819,22 +7829,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Estée Lauder كريم أساس مزدوج الثبات من ايستية لودر 2دابليو</t>
+          <t>Arm &amp; Hammer مزيل مانع للتعرق الترا ماكس من ارم اندهامر28غ</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>العناية والجمال &gt; الوجه &gt; أساس وبرايمر</t>
+          <t>العناية والجمال &gt; العناية الشخصية</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/612XaNC86pL.jpg</t>
+          <t>https://m.media-amazon.com/images/I/61Tx3mgRaWL.jpg</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Estée Lauder كريم أساس مزدوج الثبات من ايستية لودر 2دابليو</t>
+          <t>Arm &amp; Hammer مزيل مانع للتعرق الترا ماكس من ارم اندهامر28غ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -7844,12 +7854,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>كريم أساس مزدوج الثبات من استي لودر بدرجة 2W — Estée Lauder Double Wear Foundation 2W؛ مستحضر أساس للوجه من العلامة التجارية استي لودر، والدرجة المذكورة في الاسم هي 2W. يوضح اسم المنتج فئته ونسخته لتسهيل التعرف إليه عند اختيار كريم الأساس أو تنظيم مستحضرات المكياج.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | كريم أساس مزدوج الثبات من استي لودر&lt;/li&gt;&lt;li&gt;النوع | كريم أساس&lt;/li&gt;&lt;li&gt;الدرجة | 2W&lt;/li&gt;&lt;li&gt;العلامة التجارية | استي لودر&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;يأتي هذا المنتج تحت اسم كريم أساس مزدوج الثبات، مع الإشارة إلى الدرجة 2W في التسمية. يتيح ذلك تحديد الخيار المقصود بالاسم والدرجة عند المقارنة مع مستحضرات أخرى، من دون الحاجة إلى افتراض وصف لوني أو خصائص غير واردة في بيانات المنتج.&lt;/p&gt;&lt;p&gt;يمكن إدراجه ضمن مكياج الوجه وتوزيعه بالطريقة التي تفضلينها بعد تهيئة البشرة. لا يذكر الاسم حجماً للعبوة، كما لا يورد تفاصيل عن مستوى التغطية أو اللمسة النهائية؛ لذا يظل التعريف مقتصراً على كونه كريم أساس من استي لودر بدرجة 2W.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مستحضر كريم أساس للوجه.&lt;/li&gt;&lt;li&gt;من علامة استي لودر.&lt;/li&gt;&lt;li&gt;يحمل وصف مزدوج الثبات في الاسم.&lt;/li&gt;&lt;li&gt;الدرجة المذكورة هي 2W.&lt;/li&gt;&lt;li&gt;يمكن استخدامه ضمن خطوات المكياج المعتادة.&lt;/li&gt;&lt;li&gt;تظهر معلومات العلامة والدرجة في تسمية المنتج.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحثن عن كريم أساس من استي لودر.&lt;/li&gt;&lt;li&gt;لمن يختَرن الدرجة 2W وفق تفضيلاتهن.&lt;/li&gt;&lt;li&gt;لمن يرغبن في مستحضر أساس لمكياج الوجه.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;ضعي كمية مناسبة على الوجه بعد تجهيز البشرة، ثم وزعيها بالتساوي باستخدام أصابعك أو أداة مكياج مناسبة. يمكن إضافة كمية أخرى عند الحاجة، مع مراعاة تعليمات الاستخدام المكتوبة على العبوة.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. احفظيه بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;استي لودر هي العلامة التجارية المحددة لهذا المنتج. ويُعرَف هذا الخيار من كريم الأساس باسمه ودرجة 2W المذكورة في التسمية.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما درجة كريم الأساس؟&lt;/p&gt;&lt;p&gt;الدرجة الواردة في اسم المنتج هي 2W.&lt;/p&gt;&lt;p&gt;ما نوع المستحضر؟&lt;/p&gt;&lt;p&gt;هو كريم أساس للوجه من استي لودر.&lt;/p&gt;&lt;p&gt;هل يذكر الاسم حجم العبوة؟&lt;/p&gt;&lt;p&gt;لا، لا يرد حجم العبوة ضمن الاسم.&lt;/p&gt;&lt;p&gt;هل يوضح الاسم وصف الدرجة؟&lt;/p&gt;&lt;p&gt;يورد الاسم رمز 2W فقط، ولا يقدم وصفاً لونياً إضافياً.&lt;/p&gt;</t>
+          <t>مزيل مانع للتعرق ألترا ماكس من ارم اند هامر، 28 جم — Arm &amp; Hammer Ultra Max Antiperspirant, 28 g؛ مستحضر للعناية الشخصية من علامة ارم اند هامر، بحجم 28 جم، ويحمل اسم ألترا ماكس. يعرّف الاسم المنتج بصفته مانعاً للتعرق، ويميزه عن مزيلات العرق التي لا يرد فيها هذا الوصف.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | مزيل مانع للتعرق ألترا ماكس من ارم اند هامر&lt;/li&gt;&lt;li&gt;النوع | مانع تعرّق&lt;/li&gt;&lt;li&gt;الحجم | 28 جم&lt;/li&gt;&lt;li&gt;العلامة التجارية | ارم اند هامر&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;يجمع المنتج بين وصف مانع التعرق واسم ألترا ماكس، ويأتي في عبوة محددة بحجم 28 جم. تبرز هذه المعلومات الأساسية لمن يرغب في تحديد نوع المستحضر وحجمه قبل إدراجه ضمن مستلزمات العناية الشخصية. لا يورد الاسم رائحة أو صيغة تطبيق محددة، لذلك لا تُضاف تفاصيل غير واردة في التسمية.&lt;/p&gt;&lt;p&gt;يمكن استخدامه وفق الإرشادات المدونة على العبوة، مع الانتباه إلى طريقة التطبيق المناسبة للمنتج. يظل اختيار هذا المستحضر مرتبطاً بتفضيلك لفئة موانع التعرق واسم ألترا ماكس، بينما يوضح الحجم مقدار العبوة المذكور للمنتج.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مانع تعرّق من علامة ارم اند هامر.&lt;/li&gt;&lt;li&gt;يحمل اسم ألترا ماكس.&lt;/li&gt;&lt;li&gt;حجم العبوة المذكور 28 جم.&lt;/li&gt;&lt;li&gt;يندرج ضمن مستحضرات العناية الشخصية.&lt;/li&gt;&lt;li&gt;يحدد الاسم فئة المنتج بوضوح.&lt;/li&gt;&lt;li&gt;لا يذكر الاسم رائحة أو صيغة تطبيق محددة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحثون عن مستحضر موصوف بأنه مانع للتعرق.&lt;/li&gt;&lt;li&gt;لمن يفضلون منتجات ألترا ماكس من ارم اند هامر.&lt;/li&gt;&lt;li&gt;لمن يرغبون في عبوة بحجم 28 جم.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;راجعي تعليمات العبوة قبل الاستخدام، ثم طبقي المنتج على المنطقة المحددة بالطريقة والوقت الواردين فيها. لا تستخدميه على نحو يخالف الإرشادات، وأعيدي إغلاق العبوة بعد الانتهاء.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. يُحفظ بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;ارم اند هامر هي العلامة التجارية المذكورة على المنتج. ويظهر هذا المستحضر ضمن اسم ألترا ماكس بوصفه مانعاً للتعرق وبحجم 28 جم.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع المنتج؟&lt;/p&gt;&lt;p&gt;هو مانع تعرّق من ارم اند هامر.&lt;/p&gt;&lt;p&gt;ما اسم المجموعة؟&lt;/p&gt;&lt;p&gt;الاسم الوارد للمنتج هو ألترا ماكس.&lt;/p&gt;&lt;p&gt;ما حجم العبوة؟&lt;/p&gt;&lt;p&gt;حجمها المذكور 28 جم.&lt;/p&gt;&lt;p&gt;هل يذكر الاسم رائحة؟&lt;/p&gt;&lt;p&gt;لا، لا يحدد الاسم رائحة معينة.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -7859,7 +7869,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>MNT-R95</t>
+          <t>MNT-R98</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -7874,7 +7884,7 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>Estée Lauder</t>
+          <t>Arm &amp; Hammer</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
@@ -7896,7 +7906,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ارم اند هامر اسنشيالز مزيل عرق النظافه 71 جم</t>
+          <t>Arm &amp; Hammer مزيل مانع للتعرق الترا ماكس للنساء 28غ</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -7906,12 +7916,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/61O6HPC++jL.jpg</t>
+          <t>https://m.media-amazon.com/images/I/71MkO0H7iSL.jpg</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>ارم اند هامر اسنشيالز مزيل عرق النظافه 71 جم</t>
+          <t>Arm &amp; Hammer مزيل مانع للتعرق الترا ماكس للنساء 28غ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -7926,7 +7936,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>مزيل عرق إسنشيالز برائحة النظافة من ارم اند هامر، 71 جم — Arm &amp; Hammer Essentials Deodorant Clean, 71 g؛ مزيل عرق من علامة ارم اند هامر، بحجم 71 جم، ويشير الاسم إلى رائحة النظافة. يقدّم المنتج تعريفاً مباشراً بنوعه ورائحته وحجم العبوة، ليسهل تمييزه ضمن مستحضرات العناية الشخصية.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | مزيل عرق إسنشيالز برائحة النظافة من ارم اند هامر&lt;/li&gt;&lt;li&gt;النوع | مزيل عرق&lt;/li&gt;&lt;li&gt;الحجم | 71 جم&lt;/li&gt;&lt;li&gt;العلامة التجارية | ارم اند هامر&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;ينتمي هذا المنتج إلى فئة مزيلات العرق، ويحمل اسم إسنشيالز مع وصف رائحة النظافة كما ورد في التسمية. تأتي العبوة بحجم 71 جم، وهو تفصيل عملي عند التعرف إلى المنتج أو تمييزه عن أحجام أخرى. لا يذكر الاسم نوعاً آخر من الحماية أو خصائص إضافية، لذلك يقتصر وصفه على هويته ورائحته وحجمه.&lt;/p&gt;&lt;p&gt;يمكن إدراجه ضمن روتين العناية الشخصية اليومي وفق الطريقة الموضحة على العبوة. اختيار المنتج يعتمد على تفضيلك لرائحة النظافة وعلى شكل المستحضر المناسب لك؛ ويُرجى الرجوع إلى بيانات العبوة لمعرفة تعليمات الاستخدام الخاصة به.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مزيل عرق من علامة ارم اند هامر.&lt;/li&gt;&lt;li&gt;يحمل اسم إسنشيالز.&lt;/li&gt;&lt;li&gt;يرد وصف رائحة النظافة ضمن اسم المنتج.&lt;/li&gt;&lt;li&gt;حجم العبوة 71 جم.&lt;/li&gt;&lt;li&gt;ينتمي إلى مستحضرات العناية الشخصية.&lt;/li&gt;&lt;li&gt;تظهر تفاصيل النوع والحجم في تسمية المنتج.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحثون عن مزيل عرق للاستخدام ضمن العناية الشخصية.&lt;/li&gt;&lt;li&gt;لمن يفضلون المنتج الموصوف برائحة النظافة.&lt;/li&gt;&lt;li&gt;لمن يرغبون في عبوة بحجم 71 جم.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;استخدميه وفق التعليمات المكتوبة على العبوة وعلى بشرة نظيفة وجافة إذا كانت الإرشادات تسمح بذلك. مرريه أو ضعيه بالطريقة المحددة للمنتج، وأغلقي العبوة بعد الاستعمال.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. يُحفظ بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;ارم اند هامر هي العلامة التجارية المذكورة على هذا المنتج. ويظهر مزيل العرق هنا ضمن مجموعة إسنشيالز بالوصف والحجم الواردين في الاسم.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع هذا المنتج؟&lt;/p&gt;&lt;p&gt;هو مزيل عرق من ارم اند هامر.&lt;/p&gt;&lt;p&gt;ما حجمه؟&lt;/p&gt;&lt;p&gt;حجم العبوة المذكور هو 71 جم.&lt;/p&gt;&lt;p&gt;ما وصف الرائحة الوارد؟&lt;/p&gt;&lt;p&gt;يذكر الاسم رائحة النظافة.&lt;/p&gt;&lt;p&gt;ما المجموعة المذكورة في الاسم؟&lt;/p&gt;&lt;p&gt;المجموعة الواردة هي إسنشيالز.&lt;/p&gt;</t>
+          <t>مزيل مانع للتعرق ألترا ماكس للنساء من ارم اند هامر، 28 جم — Arm &amp; Hammer Ultra Max Antiperspirant for Women, 28 g؛ مستحضر عناية شخصية موصوف للنساء، من علامة ارم اند هامر، بحجم 28 جم. يجمع الاسم بين فئة المنتج واسم ألترا ماكس والفئة المذكورة والحجم، لتكون معلوماته الأساسية واضحة عند الاختيار.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | مزيل مانع للتعرق ألترا ماكس للنساء من ارم اند هامر&lt;/li&gt;&lt;li&gt;النوع | مانع تعرّق&lt;/li&gt;&lt;li&gt;الحجم | 28 جم&lt;/li&gt;&lt;li&gt;العلامة التجارية | ارم اند هامر&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;هذا المنتج من فئة موانع التعرق، ويحمل اسم ألترا ماكس ويُذكر في تسميته أنه مخصص للنساء. حجم العبوة هو 28 جم، ما يتيح تمييزه من حيث الكمية إلى جانب اسم العلامة التجارية والفئة. ولا يذكر الاسم رائحة أو تفاصيل تركيب أو صيغة استخدام بعينها.&lt;/p&gt;&lt;p&gt;يمكن إدراجه ضمن روتين العناية الشخصية بحسب التعليمات المدونة على العبوة. عند اختيار المنتج، راجعي طريقة استعماله والبيانات المرفقة به، واستخدميه وفق ما توضحه الشركة. يقتصر هذا التعريف على تفاصيل الاسم والنوع والحجم دون إضافة ادعاءات أو مواصفات غير متاحة.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مانع تعرّق من ارم اند هامر.&lt;/li&gt;&lt;li&gt;يحمل اسم ألترا ماكس.&lt;/li&gt;&lt;li&gt;موصوف في الاسم بأنه للنساء.&lt;/li&gt;&lt;li&gt;حجم العبوة 28 جم.&lt;/li&gt;&lt;li&gt;مصنف ضمن مستحضرات العناية الشخصية.&lt;/li&gt;&lt;li&gt;لا يحدد الاسم رائحة معينة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;للنساء الباحثات عن مستحضر من فئة موانع التعرق.&lt;/li&gt;&lt;li&gt;لمن يفضلن اسم ألترا ماكس من ارم اند هامر.&lt;/li&gt;&lt;li&gt;لمن يرغبن في عبوة بحجم 28 جم.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;اتبعي الإرشادات الموضحة على العبوة، وطبقي المنتج بالطريقة المحددة فيها. تحققي من ملاءمة موضع الاستخدام المذكور، ولا تستخدميه على نحو مختلف عن التعليمات المرفقة.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. أبقي المنتج بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;ارم اند هامر هي العلامة التجارية المدونة على هذا المنتج. ويظهر خيار ألترا ماكس للنساء باسم مانع للتعرق وبحجم 28 جم، وفق المعلومات الواردة في التسمية.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;لمن وُصف هذا المنتج؟&lt;/p&gt;&lt;p&gt;يذكر الاسم أنه مخصص للنساء.&lt;/p&gt;&lt;p&gt;ما فئة المستحضر؟&lt;/p&gt;&lt;p&gt;هو مانع تعرّق من ارم اند هامر.&lt;/p&gt;&lt;p&gt;ما الحجم المذكور؟&lt;/p&gt;&lt;p&gt;حجم العبوة هو 28 جم.&lt;/p&gt;&lt;p&gt;هل يذكر الاسم رائحة محددة؟&lt;/p&gt;&lt;p&gt;لا، لا تظهر رائحة معينة ضمن الاسم.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -7936,7 +7946,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>MNT-R96</t>
+          <t>MNT-R99</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -7973,7 +7983,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Arm &amp; Hammer مزيل العرق برائحة الروزماري واللافندر 71 جم</t>
+          <t>ارم اند هامر الترا ماكس مزيل عرق ستيك غير معط</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -7983,12 +7993,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71Ua50uoKcL.jpg</t>
+          <t>https://m.media-amazon.com/images/I/71EE7M3-uvL.jpg</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Arm &amp; Hammer مزيل العرق برائحة الروزماري واللافندر 71 جم</t>
+          <t>ارم اند هامر الترا ماكس مزيل عرق ستيك غير معط</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -7998,12 +8008,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>مزيل العرق من ارم اند هامر برائحة الروزماري واللافندر، 71 جم — Arm &amp; Hammer Rosemary Lavender Deodorant, 71 g؛ مزيل عرق للعناية الشخصية من علامة ارم اند هامر، بحجم 71 جم، ويذكر الاسم رائحتي الروزماري واللافندر. يجمع تعريفه بين العلامة التجارية ونوع المستحضر والرائحة والحجم في صياغة واضحة.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | مزيل العرق برائحة الروزماري واللافندر من ارم اند هامر&lt;/li&gt;&lt;li&gt;النوع | مزيل عرق&lt;/li&gt;&lt;li&gt;الحجم | 71 جم&lt;/li&gt;&lt;li&gt;العلامة التجارية | ارم اند هامر&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;يُعرَف هذا المنتج بوصفه مزيل عرق يحمل رائحة الروزماري واللافندر، وفق ما ورد في اسمه، وتبلغ كمية العبوة 71 جم. تمنحك هذه التفاصيل طريقة مباشرة للتمييز بينه وبين المنتجات ذات الروائح أو الأحجام الأخرى، من غير إضافة وصف لمكونات أو خصائص لم ترد في التسمية.&lt;/p&gt;&lt;p&gt;يناسب إدراجه ضمن خطوات العناية الشخصية بالطريقة الموضحة على العبوة. اختاريه إذا كان وصف الرائحة المذكور قريباً من تفضيلك، وراجعي بيانات المنتج لمعرفة إرشادات الاستخدام الدقيقة. لا يذكر الاسم أنه مانع للتعرق، لذا يُعرّف هنا بمزيل عرق فقط.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مزيل عرق من ارم اند هامر.&lt;/li&gt;&lt;li&gt;يذكر الاسم رائحة الروزماري واللافندر.&lt;/li&gt;&lt;li&gt;حجم العبوة 71 جم.&lt;/li&gt;&lt;li&gt;مخصص للاستخدام ضمن العناية الشخصية.&lt;/li&gt;&lt;li&gt;يوفر تعريفاً واضحاً بالرائحة والحجم.&lt;/li&gt;&lt;li&gt;لا يرد في الاسم وصف بأنه مانع للتعرق.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحثون عن مزيل عرق ضمن العناية الشخصية.&lt;/li&gt;&lt;li&gt;لمن يختارون المنتجات بحسب وصف رائحتها.&lt;/li&gt;&lt;li&gt;لمن يفضلون عبوة بحجم 71 جم.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;اتبعي طريقة الاستخدام المدونة على العبوة. ضعي المنتج بالطريقة المحددة على المنطقة المطلوبة، مع مراعاة أن تكون البشرة مناسبة للاستخدام وفق إرشادات المنتج، ثم أعيدي إغلاق العبوة.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. أبقيه بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;ارم اند هامر هي العلامة التجارية الظاهرة على مزيل العرق. ويرتبط هذا الخيار بوصف الروزماري واللافندر وبحجم 71 جم كما وردا في اسم المنتج.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما الرائحة المذكورة في الاسم؟&lt;/p&gt;&lt;p&gt;الروزماري واللافندر.&lt;/p&gt;&lt;p&gt;كم يبلغ حجم العبوة؟&lt;/p&gt;&lt;p&gt;حجمها المذكور هو 71 جم.&lt;/p&gt;&lt;p&gt;هل المنتج مانع للتعرق؟&lt;/p&gt;&lt;p&gt;لا يذكر الاسم ذلك؛ فهو مصنف كمزيل عرق.&lt;/p&gt;&lt;p&gt;ما العلامة التجارية؟&lt;/p&gt;&lt;p&gt;العلامة التجارية هي ارم اند هامر.&lt;/p&gt;</t>
+          <t>مزيل عرق ستيك ألترا ماكس غير معطر من ارم اند هامر — Arm &amp; Hammer Ultra Max Unscented Deodorant Stick؛ مستحضر للعناية الشخصية بصيغة ستيك، وتوضح التسمية أنه غير معطر. يحمل المنتج اسم ألترا ماكس من علامة ارم اند هامر، ولا يرد حجم للعبوة في الاسم المتاح.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | مزيل عرق ستيك ألترا ماكس غير معطر من ارم اند هامر&lt;/li&gt;&lt;li&gt;النوع | مزيل عرق ستيك&lt;/li&gt;&lt;li&gt;العلامة التجارية | ارم اند هامر&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;يأتي هذا الخيار بصيغة ستيك، ويُعرَف بأنه مزيل عرق غير معطر وفق الوصف الوارد في الاسم. وتظهر علامة ارم اند هامر واسم ألترا ماكس ضمن هويته، ما يساعد على تحديد المنتج عند مقارنته بمزيلات العرق الأخرى. لا يتضمن الاسم حجم العبوة، لذلك لا تُضاف كمية غير مذكورة.&lt;/p&gt;&lt;p&gt;يمكن إدراجه ضمن روتين العناية الشخصية بالطريقة الموضحة على العبوة. ويمنح وصف غير معطر معلومة مباشرة عن الرائحة كما وردت في التسمية، من دون افتراض وجود رائحة أخرى. تحققي من الإرشادات المرفقة لتحديد كيفية التطبيق والموضع المناسب للاستخدام.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مزيل عرق بصيغة ستيك.&lt;/li&gt;&lt;li&gt;يحمل اسم ألترا ماكس من ارم اند هامر.&lt;/li&gt;&lt;li&gt;موصوف بأنه غير معطر.&lt;/li&gt;&lt;li&gt;ينتمي إلى مستحضرات العناية الشخصية.&lt;/li&gt;&lt;li&gt;لا يذكر الاسم حجماً محدداً للعبوة.&lt;/li&gt;&lt;li&gt;تظهر صيغة المنتج ووصف الرائحة في التسمية.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يفضلون مزيل العرق بصيغة ستيك.&lt;/li&gt;&lt;li&gt;لمن يبحثون عن منتج موصوف بأنه غير معطر.&lt;/li&gt;&lt;li&gt;لمن يختارون مستحضرات ألترا ماكس من ارم اند هامر.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;راجعي تعليمات العبوة قبل التطبيق، ثم مرري ستيك مزيل العرق على المنطقة المحددة بالطريقة الواردة فيها. استخدميه وفق الإرشادات وأغلقي الغطاء بعد الانتهاء. لا يرد حجم العبوة في الاسم المتاح.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. يُحفظ بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;ارم اند هامر هي العلامة التجارية المذكورة على هذا المنتج. ويظهر مزيل العرق ضمن اسم ألترا ماكس بصيغة ستيك وبوصف غير معطر، وفق التسمية المتاحة.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما صيغة المنتج؟&lt;/p&gt;&lt;p&gt;هو مزيل عرق بصيغة ستيك.&lt;/p&gt;&lt;p&gt;هل يذكر الاسم رائحة؟&lt;/p&gt;&lt;p&gt;نعم، يصفه بأنه غير معطر.&lt;/p&gt;&lt;p&gt;ما العلامة التجارية؟&lt;/p&gt;&lt;p&gt;العلامة التجارية هي ارم اند هامر.&lt;/p&gt;&lt;p&gt;هل يتوفر حجم محدد في الاسم؟&lt;/p&gt;&lt;p&gt;لا، لا يرد حجم للعبوة في الاسم المتاح.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -8013,7 +8023,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>MNT-R97</t>
+          <t>MNT-R100</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -8037,237 +8047,6 @@
         </is>
       </c>
       <c r="AA92" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>منتج</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Arm &amp; Hammer مزيل مانع للتعرق الترا ماكس من ارم اندهامر28غ</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>العناية والجمال &gt; العناية الشخصية</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61Tx3mgRaWL.jpg</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Arm &amp; Hammer مزيل مانع للتعرق الترا ماكس من ارم اندهامر28غ</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>منتج جاهز</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>مزيل مانع للتعرق ألترا ماكس من ارم اند هامر، 28 جم — Arm &amp; Hammer Ultra Max Antiperspirant, 28 g؛ مستحضر للعناية الشخصية من علامة ارم اند هامر، بحجم 28 جم، ويحمل اسم ألترا ماكس. يعرّف الاسم المنتج بصفته مانعاً للتعرق، ويميزه عن مزيلات العرق التي لا يرد فيها هذا الوصف.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | مزيل مانع للتعرق ألترا ماكس من ارم اند هامر&lt;/li&gt;&lt;li&gt;النوع | مانع تعرّق&lt;/li&gt;&lt;li&gt;الحجم | 28 جم&lt;/li&gt;&lt;li&gt;العلامة التجارية | ارم اند هامر&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;يجمع المنتج بين وصف مانع التعرق واسم ألترا ماكس، ويأتي في عبوة محددة بحجم 28 جم. تبرز هذه المعلومات الأساسية لمن يرغب في تحديد نوع المستحضر وحجمه قبل إدراجه ضمن مستلزمات العناية الشخصية. لا يورد الاسم رائحة أو صيغة تطبيق محددة، لذلك لا تُضاف تفاصيل غير واردة في التسمية.&lt;/p&gt;&lt;p&gt;يمكن استخدامه وفق الإرشادات المدونة على العبوة، مع الانتباه إلى طريقة التطبيق المناسبة للمنتج. يظل اختيار هذا المستحضر مرتبطاً بتفضيلك لفئة موانع التعرق واسم ألترا ماكس، بينما يوضح الحجم مقدار العبوة المذكور للمنتج.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مانع تعرّق من علامة ارم اند هامر.&lt;/li&gt;&lt;li&gt;يحمل اسم ألترا ماكس.&lt;/li&gt;&lt;li&gt;حجم العبوة المذكور 28 جم.&lt;/li&gt;&lt;li&gt;يندرج ضمن مستحضرات العناية الشخصية.&lt;/li&gt;&lt;li&gt;يحدد الاسم فئة المنتج بوضوح.&lt;/li&gt;&lt;li&gt;لا يذكر الاسم رائحة أو صيغة تطبيق محددة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يبحثون عن مستحضر موصوف بأنه مانع للتعرق.&lt;/li&gt;&lt;li&gt;لمن يفضلون منتجات ألترا ماكس من ارم اند هامر.&lt;/li&gt;&lt;li&gt;لمن يرغبون في عبوة بحجم 28 جم.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;راجعي تعليمات العبوة قبل الاستخدام، ثم طبقي المنتج على المنطقة المحددة بالطريقة والوقت الواردين فيها. لا تستخدميه على نحو يخالف الإرشادات، وأعيدي إغلاق العبوة بعد الانتهاء.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. يُحفظ بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;ارم اند هامر هي العلامة التجارية المذكورة على المنتج. ويظهر هذا المستحضر ضمن اسم ألترا ماكس بوصفه مانعاً للتعرق وبحجم 28 جم.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما نوع المنتج؟&lt;/p&gt;&lt;p&gt;هو مانع تعرّق من ارم اند هامر.&lt;/p&gt;&lt;p&gt;ما اسم المجموعة؟&lt;/p&gt;&lt;p&gt;الاسم الوارد للمنتج هو ألترا ماكس.&lt;/p&gt;&lt;p&gt;ما حجم العبوة؟&lt;/p&gt;&lt;p&gt;حجمها المذكور 28 جم.&lt;/p&gt;&lt;p&gt;هل يذكر الاسم رائحة؟&lt;/p&gt;&lt;p&gt;لا، لا يحدد الاسم رائحة معينة.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>MNT-R98</t>
-        </is>
-      </c>
-      <c r="R93" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="T93" t="inlineStr">
-        <is>
-          <t>Arm &amp; Hammer</t>
-        </is>
-      </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="AA93" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>منتج</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Arm &amp; Hammer مزيل مانع للتعرق الترا ماكس للنساء 28غ</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>العناية والجمال &gt; العناية الشخصية</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71MkO0H7iSL.jpg</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Arm &amp; Hammer مزيل مانع للتعرق الترا ماكس للنساء 28غ</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>منتج جاهز</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>مزيل مانع للتعرق ألترا ماكس للنساء من ارم اند هامر، 28 جم — Arm &amp; Hammer Ultra Max Antiperspirant for Women, 28 g؛ مستحضر عناية شخصية موصوف للنساء، من علامة ارم اند هامر، بحجم 28 جم. يجمع الاسم بين فئة المنتج واسم ألترا ماكس والفئة المذكورة والحجم، لتكون معلوماته الأساسية واضحة عند الاختيار.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | مزيل مانع للتعرق ألترا ماكس للنساء من ارم اند هامر&lt;/li&gt;&lt;li&gt;النوع | مانع تعرّق&lt;/li&gt;&lt;li&gt;الحجم | 28 جم&lt;/li&gt;&lt;li&gt;العلامة التجارية | ارم اند هامر&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;هذا المنتج من فئة موانع التعرق، ويحمل اسم ألترا ماكس ويُذكر في تسميته أنه مخصص للنساء. حجم العبوة هو 28 جم، ما يتيح تمييزه من حيث الكمية إلى جانب اسم العلامة التجارية والفئة. ولا يذكر الاسم رائحة أو تفاصيل تركيب أو صيغة استخدام بعينها.&lt;/p&gt;&lt;p&gt;يمكن إدراجه ضمن روتين العناية الشخصية بحسب التعليمات المدونة على العبوة. عند اختيار المنتج، راجعي طريقة استعماله والبيانات المرفقة به، واستخدميه وفق ما توضحه الشركة. يقتصر هذا التعريف على تفاصيل الاسم والنوع والحجم دون إضافة ادعاءات أو مواصفات غير متاحة.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مانع تعرّق من ارم اند هامر.&lt;/li&gt;&lt;li&gt;يحمل اسم ألترا ماكس.&lt;/li&gt;&lt;li&gt;موصوف في الاسم بأنه للنساء.&lt;/li&gt;&lt;li&gt;حجم العبوة 28 جم.&lt;/li&gt;&lt;li&gt;مصنف ضمن مستحضرات العناية الشخصية.&lt;/li&gt;&lt;li&gt;لا يحدد الاسم رائحة معينة.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;للنساء الباحثات عن مستحضر من فئة موانع التعرق.&lt;/li&gt;&lt;li&gt;لمن يفضلن اسم ألترا ماكس من ارم اند هامر.&lt;/li&gt;&lt;li&gt;لمن يرغبن في عبوة بحجم 28 جم.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;اتبعي الإرشادات الموضحة على العبوة، وطبقي المنتج بالطريقة المحددة فيها. تحققي من ملاءمة موضع الاستخدام المذكور، ولا تستخدميه على نحو مختلف عن التعليمات المرفقة.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. أبقي المنتج بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;ارم اند هامر هي العلامة التجارية المدونة على هذا المنتج. ويظهر خيار ألترا ماكس للنساء باسم مانع للتعرق وبحجم 28 جم، وفق المعلومات الواردة في التسمية.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;لمن وُصف هذا المنتج؟&lt;/p&gt;&lt;p&gt;يذكر الاسم أنه مخصص للنساء.&lt;/p&gt;&lt;p&gt;ما فئة المستحضر؟&lt;/p&gt;&lt;p&gt;هو مانع تعرّق من ارم اند هامر.&lt;/p&gt;&lt;p&gt;ما الحجم المذكور؟&lt;/p&gt;&lt;p&gt;حجم العبوة هو 28 جم.&lt;/p&gt;&lt;p&gt;هل يذكر الاسم رائحة محددة؟&lt;/p&gt;&lt;p&gt;لا، لا تظهر رائحة معينة ضمن الاسم.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>MNT-R99</t>
-        </is>
-      </c>
-      <c r="R94" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>Arm &amp; Hammer</t>
-        </is>
-      </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>منتج</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>ارم اند هامر الترا ماكس مزيل عرق ستيك غير معط</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>العناية والجمال &gt; العناية الشخصية</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71EE7M3-uvL.jpg</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>ارم اند هامر الترا ماكس مزيل عرق ستيك غير معط</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>منتج جاهز</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>مزيل عرق ستيك ألترا ماكس غير معطر من ارم اند هامر — Arm &amp; Hammer Ultra Max Unscented Deodorant Stick؛ مستحضر للعناية الشخصية بصيغة ستيك، وتوضح التسمية أنه غير معطر. يحمل المنتج اسم ألترا ماكس من علامة ارم اند هامر، ولا يرد حجم للعبوة في الاسم المتاح.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;معلومات المنتج:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;الأسم | مزيل عرق ستيك ألترا ماكس غير معطر من ارم اند هامر&lt;/li&gt;&lt;li&gt;النوع | مزيل عرق ستيك&lt;/li&gt;&lt;li&gt;العلامة التجارية | ارم اند هامر&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;وصف المنتج:&lt;/p&gt;&lt;p&gt;يأتي هذا الخيار بصيغة ستيك، ويُعرَف بأنه مزيل عرق غير معطر وفق الوصف الوارد في الاسم. وتظهر علامة ارم اند هامر واسم ألترا ماكس ضمن هويته، ما يساعد على تحديد المنتج عند مقارنته بمزيلات العرق الأخرى. لا يتضمن الاسم حجم العبوة، لذلك لا تُضاف كمية غير مذكورة.&lt;/p&gt;&lt;p&gt;يمكن إدراجه ضمن روتين العناية الشخصية بالطريقة الموضحة على العبوة. ويمنح وصف غير معطر معلومة مباشرة عن الرائحة كما وردت في التسمية، من دون افتراض وجود رائحة أخرى. تحققي من الإرشادات المرفقة لتحديد كيفية التطبيق والموضع المناسب للاستخدام.&lt;/p&gt;&lt;p&gt;المميزات:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;مزيل عرق بصيغة ستيك.&lt;/li&gt;&lt;li&gt;يحمل اسم ألترا ماكس من ارم اند هامر.&lt;/li&gt;&lt;li&gt;موصوف بأنه غير معطر.&lt;/li&gt;&lt;li&gt;ينتمي إلى مستحضرات العناية الشخصية.&lt;/li&gt;&lt;li&gt;لا يذكر الاسم حجماً محدداً للعبوة.&lt;/li&gt;&lt;li&gt;تظهر صيغة المنتج ووصف الرائحة في التسمية.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;لمن يناسب؟:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;لمن يفضلون مزيل العرق بصيغة ستيك.&lt;/li&gt;&lt;li&gt;لمن يبحثون عن منتج موصوف بأنه غير معطر.&lt;/li&gt;&lt;li&gt;لمن يختارون مستحضرات ألترا ماكس من ارم اند هامر.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;طريقة الاستخدام:&lt;/p&gt;&lt;p&gt;راجعي تعليمات العبوة قبل التطبيق، ثم مرري ستيك مزيل العرق على المنطقة المحددة بالطريقة الواردة فيها. استخدميه وفق الإرشادات وأغلقي الغطاء بعد الانتهاء. لا يرد حجم العبوة في الاسم المتاح.&lt;/p&gt;&lt;p&gt;تنبيهات:&lt;/p&gt;&lt;p&gt;للاستخدام الخارجي فقط، وتجنبي ملامسة العينين. يُحفظ بعيداً عن متناول الأطفال.&lt;/p&gt;&lt;p&gt;نبذة عن العلامة التجارية:&lt;/p&gt;&lt;p&gt;ارم اند هامر هي العلامة التجارية المذكورة على هذا المنتج. ويظهر مزيل العرق ضمن اسم ألترا ماكس بصيغة ستيك وبوصف غير معطر، وفق التسمية المتاحة.&lt;/p&gt;&lt;p&gt;الأسئلة الشائعة:&lt;/p&gt;&lt;p&gt;ما صيغة المنتج؟&lt;/p&gt;&lt;p&gt;هو مزيل عرق بصيغة ستيك.&lt;/p&gt;&lt;p&gt;هل يذكر الاسم رائحة؟&lt;/p&gt;&lt;p&gt;نعم، يصفه بأنه غير معطر.&lt;/p&gt;&lt;p&gt;ما العلامة التجارية؟&lt;/p&gt;&lt;p&gt;العلامة التجارية هي ارم اند هامر.&lt;/p&gt;&lt;p&gt;هل يتوفر حجم محدد في الاسم؟&lt;/p&gt;&lt;p&gt;لا، لا يرد حجم للعبوة في الاسم المتاح.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>MNT-R100</t>
-        </is>
-      </c>
-      <c r="R95" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>Arm &amp; Hammer</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="AA95" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>

--- a/المنتجات/batch1-products-complete.xlsx
+++ b/المنتجات/batch1-products-complete.xlsx
@@ -839,7 +839,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.maybelline-me.com/-/media/project/loreal/brand-sites/mny/apac/mena/products/eye-makeup/mascara/great-lash-lots-of-lashes-washable/maybelline-mascara-great-lash-lol-blackest-black-041554239423-o.jpg?rev=9bb75d148bc34da8ad910b950ab8e2c2&amp;cx=0&amp;cy=0&amp;cw=760&amp;ch=1130&amp;hash=87A884B660F5CC4E09ABD4D2729E559D</t>
+          <t>https://medino-product.imgix.net/maybelline-the-colossal-waterproof-mascara-glam-black-2cfc820.png?w=1200&amp;h=1200&amp;fit=fill&amp;bg=FFF&amp;auto=format,compress&amp;q=90</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.maybelline-me.com/-/media/project/loreal/brand-sites/mny/apac/mena/products/eye-makeup/mascara/great-lash-lots-of-lashes-washable/maybelline-mascara-great-lash-lol-blackest-black-041554239423-o.jpg?rev=9bb75d148bc34da8ad910b950ab8e2c2&amp;cx=0&amp;cy=0&amp;cw=760&amp;ch=1130&amp;hash=87A884B660F5CC4E09ABD4D2729E559D</t>
+          <t>https://www.watsons.sa/cdn/shop/files/ASW200002611_101.jpg?v=1711442935&amp;width=1946</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">

--- a/المنتجات/batch1-products-complete.xlsx
+++ b/المنتجات/batch1-products-complete.xlsx
@@ -7839,7 +7839,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/61Tx3mgRaWL.jpg</t>
+          <t>https://m.media-amazon.com/images/I/71MkO0H7iSL.jpg</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71MkO0H7iSL.jpg</t>
+          <t>https://m.media-amazon.com/images/I/61Tx3mgRaWL.jpg</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
